--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="收支与赞助鸣谢" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="113">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -156,70 +156,70 @@
     <t>匿名玩家</t>
   </si>
   <si>
+    <t>srdownb</t>
+  </si>
+  <si>
+    <t>↑11</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>火药、遗物</t>
+  </si>
+  <si>
     <t>Xs1st_</t>
   </si>
   <si>
-    <t>火药、遗物</t>
+    <t>Alhion_WWW</t>
   </si>
   <si>
     <t>chunfeng</t>
   </si>
   <si>
-    <t>Alhion_WWW</t>
+    <t>darkmoon114514</t>
   </si>
   <si>
     <t>KAMI</t>
   </si>
   <si>
-    <t>darkmoon114514</t>
+    <t>3组烟花</t>
   </si>
   <si>
     <t>91kk</t>
   </si>
   <si>
-    <t>3组烟花</t>
-  </si>
-  <si>
     <t>faxi</t>
   </si>
   <si>
-    <t>↑25</t>
+    <t>捐樱花映射VIP</t>
   </si>
   <si>
     <t>wybhh51811</t>
   </si>
   <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>捐樱花映射VIP</t>
+    <t>樱花映射VIP</t>
   </si>
   <si>
     <t>Goocheu_fox</t>
   </si>
   <si>
-    <t>樱花映射VIP</t>
+    <t>5下界合金锭</t>
   </si>
   <si>
     <t>Cr_Dragon</t>
   </si>
   <si>
-    <t>5下界合金锭</t>
-  </si>
-  <si>
     <t>XL12</t>
   </si>
   <si>
     <t>拍卖账号</t>
   </si>
   <si>
+    <t>鞘翅、TP、电费、羊毛、村民、TNT</t>
+  </si>
+  <si>
     <t>Onion520</t>
-  </si>
-  <si>
-    <t>鞘翅、TP、电费、羊毛、村民、TNT</t>
-  </si>
-  <si>
-    <t>kim</t>
   </si>
   <si>
     <t>电费、经验</t>
@@ -1213,7 +1213,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1328,6 +1328,9 @@
     <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1336,6 +1339,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1673,7 +1682,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K147"/>
+  <dimension ref="A1:K149"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -1687,6 +1696,7 @@
     <col min="10" max="10" width="15.625" style="3" customWidth="1"/>
     <col min="11" max="11" width="5.125" customWidth="1"/>
     <col min="13" max="13" width="15.625"/>
+    <col min="14" max="14" width="13.375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -2202,14 +2212,18 @@
       <c r="G19" s="15">
         <v>17</v>
       </c>
-      <c r="H19" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" s="16">
-        <v>10</v>
+      <c r="H19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="2">
+        <f>SUM(C135,C139,C146)</f>
+        <v>10.5</v>
       </c>
       <c r="J19" s="3">
-        <v>44953</v>
+        <v>46145</v>
+      </c>
+      <c r="K19" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2231,13 +2245,16 @@
         <v>18</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I20" s="16">
         <v>10</v>
       </c>
       <c r="J20" s="3">
-        <v>45234</v>
+        <v>44953</v>
+      </c>
+      <c r="K20" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2256,19 +2273,22 @@
         <v>-428.73</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G21" s="15">
         <v>19</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I21" s="16">
         <v>10</v>
       </c>
       <c r="J21" s="3">
-        <v>45325</v>
+        <v>45234</v>
+      </c>
+      <c r="K21" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2276,7 +2296,7 @@
         <v>45140</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C22" s="13">
         <v>0.11</v>
@@ -2290,13 +2310,16 @@
         <v>20</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I22" s="16">
         <v>10</v>
       </c>
       <c r="J22" s="3">
-        <v>45649</v>
+        <v>45325</v>
+      </c>
+      <c r="K22" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2304,7 +2327,7 @@
         <v>45141</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C23" s="13">
         <v>1.01</v>
@@ -2317,14 +2340,17 @@
       <c r="G23" s="15">
         <v>21</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I23" s="2">
+      <c r="H23" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I23" s="16">
         <v>10</v>
       </c>
       <c r="J23" s="3">
-        <v>46069</v>
+        <v>45649</v>
+      </c>
+      <c r="K23" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2337,22 +2363,22 @@
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G24" s="15">
         <v>22</v>
       </c>
-      <c r="H24" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I24" s="16">
+      <c r="H24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24" s="2">
         <v>10</v>
       </c>
       <c r="J24" s="3">
-        <v>46145</v>
+        <v>46069</v>
       </c>
       <c r="K24" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2374,16 +2400,16 @@
         <v>23</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="I25" s="2">
-        <v>8</v>
+        <v>53</v>
+      </c>
+      <c r="I25" s="16">
+        <v>10</v>
       </c>
       <c r="J25" s="3">
-        <v>45860</v>
+        <v>46145</v>
       </c>
       <c r="K25" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2391,7 +2417,7 @@
         <v>45234</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C26" s="13">
         <v>10</v>
@@ -2406,17 +2432,17 @@
       <c r="G26">
         <v>24</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" s="10" t="s">
         <v>55</v>
       </c>
       <c r="I26" s="2">
-        <v>7.33</v>
+        <v>8</v>
       </c>
       <c r="J26" s="3">
-        <v>45907</v>
+        <v>45860</v>
       </c>
       <c r="K26" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2432,18 +2458,17 @@
       <c r="G27">
         <v>25</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I27" s="16">
-        <f>SUM(C82,C84,C94)</f>
-        <v>6.98</v>
+      <c r="I27" s="2">
+        <v>7.33</v>
       </c>
       <c r="J27" s="3">
-        <v>45861</v>
+        <v>45907</v>
       </c>
       <c r="K27" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2469,14 +2494,15 @@
       <c r="H28" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="I28" s="2">
-        <v>6</v>
+      <c r="I28" s="16">
+        <f>SUM(C82,C84,C94)</f>
+        <v>6.98</v>
       </c>
       <c r="J28" s="3">
-        <v>45868</v>
+        <v>45861</v>
       </c>
       <c r="K28" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2498,16 +2524,16 @@
         <v>27</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="I29" s="16">
-        <v>5.02</v>
+        <v>60</v>
+      </c>
+      <c r="I29" s="2">
+        <v>6</v>
       </c>
       <c r="J29" s="3">
-        <v>44787</v>
+        <v>45868</v>
       </c>
       <c r="K29" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2515,7 +2541,7 @@
         <v>45325</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C30" s="13">
         <v>10</v>
@@ -2525,22 +2551,22 @@
         <v>-340.11</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G30">
         <v>28</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="I30" s="16">
-        <v>5</v>
+        <v>5.02</v>
       </c>
       <c r="J30" s="3">
-        <v>45634</v>
+        <v>44787</v>
       </c>
       <c r="K30" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2563,18 +2589,17 @@
       <c r="G31">
         <v>29</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="I31" s="2">
-        <f>SUM(C135,C139)</f>
-        <v>4.5</v>
+      <c r="I31" s="16">
+        <v>5</v>
       </c>
       <c r="J31" s="3">
-        <v>46130</v>
+        <v>45634</v>
       </c>
       <c r="K31" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2606,11 +2631,8 @@
       <c r="J32" s="3">
         <v>45707</v>
       </c>
-      <c r="K32" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="17">
         <v>45387</v>
       </c>
@@ -2639,11 +2661,8 @@
       <c r="J33" s="3">
         <v>45885</v>
       </c>
-      <c r="K33" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="17">
         <v>45394</v>
       </c>
@@ -2673,11 +2692,8 @@
       <c r="J34" s="3">
         <v>45934</v>
       </c>
-      <c r="K34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="17">
         <v>45396</v>
       </c>
@@ -2706,11 +2722,8 @@
       <c r="J35" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K35" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="17">
         <v>45403</v>
       </c>
@@ -2737,11 +2750,8 @@
       <c r="J36" s="3">
         <v>45500</v>
       </c>
-      <c r="K36" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="17">
         <v>45403</v>
       </c>
@@ -2770,11 +2780,8 @@
       <c r="J37" s="3">
         <v>45976</v>
       </c>
-      <c r="K37" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="17">
         <v>45412</v>
       </c>
@@ -2804,11 +2811,8 @@
       <c r="J38" s="3">
         <v>45396</v>
       </c>
-      <c r="K38" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="17">
         <v>45417</v>
       </c>
@@ -2837,11 +2841,8 @@
       <c r="J39" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K39" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="17">
         <v>45421</v>
       </c>
@@ -2870,11 +2871,8 @@
       <c r="J40" s="3">
         <v>45907</v>
       </c>
-      <c r="K40" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="17">
         <v>45478</v>
       </c>
@@ -2902,11 +2900,8 @@
       <c r="J41" s="3">
         <v>44958</v>
       </c>
-      <c r="K41" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="17">
         <v>45494</v>
       </c>
@@ -2935,11 +2930,8 @@
       <c r="J42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K42" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="17"/>
       <c r="B43" s="8" t="s">
         <v>13</v>
@@ -2955,7 +2947,7 @@
         <v>41</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I43" s="16">
         <v>1.01</v>
@@ -2963,11 +2955,8 @@
       <c r="J43" s="3">
         <v>45141</v>
       </c>
-      <c r="K43" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="25">
         <v>45495</v>
       </c>
@@ -2996,11 +2985,8 @@
       <c r="J44" s="3">
         <v>45794</v>
       </c>
-      <c r="K44" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="25">
         <v>45496</v>
       </c>
@@ -3027,11 +3013,8 @@
       <c r="J45" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K45" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" s="29"/>
       <c r="B46" s="26" t="s">
         <v>30</v>
@@ -3055,11 +3038,8 @@
       <c r="J46" s="3">
         <v>45697</v>
       </c>
-      <c r="K46" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" s="17">
         <v>45497</v>
       </c>
@@ -3088,11 +3068,8 @@
       <c r="J47" s="3">
         <v>45885</v>
       </c>
-      <c r="K47" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" s="25">
         <v>45500</v>
       </c>
@@ -3111,7 +3088,7 @@
         <v>46</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I48" s="16">
         <v>0.11</v>
@@ -3119,11 +3096,8 @@
       <c r="J48" s="3">
         <v>45140</v>
       </c>
-      <c r="K48" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="31"/>
       <c r="B49" s="26" t="s">
         <v>15</v>
@@ -3147,11 +3121,8 @@
       <c r="J49" s="3">
         <v>44213</v>
       </c>
-      <c r="K49" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="25">
         <v>45505</v>
       </c>
@@ -3169,7 +3140,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:10">
       <c r="A51" s="25">
         <v>45507</v>
       </c>
@@ -3187,7 +3158,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:10">
       <c r="A52" s="31"/>
       <c r="B52" s="26" t="s">
         <v>25</v>
@@ -3200,7 +3171,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:10">
       <c r="A53" s="25">
         <v>45508</v>
       </c>
@@ -3218,7 +3189,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:10">
       <c r="A54" s="31"/>
       <c r="B54" s="26" t="s">
         <v>17</v>
@@ -3229,7 +3200,7 @@
       <c r="D54" s="30"/>
       <c r="E54" s="28"/>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:10">
       <c r="A55" s="25">
         <v>45509</v>
       </c>
@@ -3245,7 +3216,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:10">
       <c r="A56" s="31"/>
       <c r="B56" s="26" t="s">
         <v>30</v>
@@ -3256,7 +3227,7 @@
       <c r="D56" s="30"/>
       <c r="E56" s="28"/>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:10">
       <c r="A57" s="25">
         <v>45510</v>
       </c>
@@ -3274,7 +3245,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:10">
       <c r="A58" s="25">
         <v>45525</v>
       </c>
@@ -3293,7 +3264,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:10">
       <c r="A59" s="25">
         <v>45525</v>
       </c>
@@ -3311,7 +3282,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:10">
       <c r="A60" s="25">
         <v>45549</v>
       </c>
@@ -3329,7 +3300,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:10">
       <c r="A61" s="29"/>
       <c r="B61" s="33" t="s">
         <v>17</v>
@@ -3342,7 +3313,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:10">
       <c r="A62" s="31">
         <v>45551</v>
       </c>
@@ -3358,7 +3329,7 @@
       </c>
       <c r="E62" s="28"/>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:10">
       <c r="A63" s="25">
         <v>45552</v>
       </c>
@@ -3374,7 +3345,7 @@
       </c>
       <c r="E63" s="28"/>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:10">
       <c r="A64" s="25">
         <v>45555</v>
       </c>
@@ -3530,7 +3501,7 @@
         <v>45634</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C73" s="27">
         <v>5</v>
@@ -3561,7 +3532,7 @@
         <v>45649</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C75" s="27">
         <v>10</v>
@@ -3677,7 +3648,7 @@
         <v>45844</v>
       </c>
       <c r="B82" s="33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C82" s="27">
         <v>2.48</v>
@@ -3693,7 +3664,7 @@
         <v>45860</v>
       </c>
       <c r="B83" s="33" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C83" s="27">
         <v>8</v>
@@ -3709,7 +3680,7 @@
         <v>45861</v>
       </c>
       <c r="B84" s="33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C84" s="27">
         <v>0.5</v>
@@ -3757,7 +3728,7 @@
         <v>45868</v>
       </c>
       <c r="B87" s="33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C87" s="27">
         <v>6</v>
@@ -3870,7 +3841,7 @@
     <row r="94" spans="1:5">
       <c r="A94" s="17"/>
       <c r="B94" s="33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C94" s="27">
         <v>4</v>
@@ -3917,7 +3888,7 @@
         <v>45905</v>
       </c>
       <c r="B97" s="33" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C97" s="27">
         <v>7.33</v>
@@ -4475,7 +4446,7 @@
     <row r="132" spans="1:5">
       <c r="A132" s="31"/>
       <c r="B132" s="33" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C132" s="27">
         <v>10</v>
@@ -4521,7 +4492,7 @@
         <v>46074</v>
       </c>
       <c r="B135" s="33" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C135" s="27">
         <v>1.5</v>
@@ -4589,7 +4560,7 @@
         <v>46130</v>
       </c>
       <c r="B139" s="33" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C139" s="27">
         <v>3</v>
@@ -4684,41 +4655,62 @@
       <c r="A145" s="37">
         <v>46145</v>
       </c>
-      <c r="B145" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="C145" s="39">
+      <c r="B145" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C145" s="27">
         <v>10</v>
       </c>
       <c r="D145" s="21">
         <f>SUM(C3:C145)</f>
         <v>-3105.15</v>
       </c>
-      <c r="E145" s="40" t="s">
+      <c r="E145" s="34" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="146" ht="14.25" spans="1:5">
-      <c r="A146" s="41"/>
-      <c r="B146" s="42"/>
-      <c r="C146" s="43"/>
-      <c r="D146" s="43"/>
-      <c r="E146" s="44"/>
+    <row r="146" spans="1:5">
+      <c r="A146" s="38"/>
+      <c r="B146" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="C146" s="40">
+        <v>6</v>
+      </c>
+      <c r="D146" s="21">
+        <f>SUM(C3:C146)</f>
+        <v>-3099.15</v>
+      </c>
+      <c r="E146" s="41"/>
     </row>
     <row r="147" spans="1:5">
-      <c r="A147" s="45" t="s">
+      <c r="A147" s="42"/>
+      <c r="B147" s="39"/>
+      <c r="C147" s="40"/>
+      <c r="D147" s="43"/>
+      <c r="E147" s="41"/>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="44"/>
+      <c r="B148" s="45"/>
+      <c r="C148" s="46"/>
+      <c r="D148" s="46"/>
+      <c r="E148" s="47"/>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="B147" s="45"/>
-      <c r="C147" s="45"/>
-      <c r="D147" s="45"/>
-      <c r="E147" s="45"/>
+      <c r="B149" s="48"/>
+      <c r="C149" s="48"/>
+      <c r="D149" s="48"/>
+      <c r="E149" s="48"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="40">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A147:E147"/>
+    <mergeCell ref="A149:E149"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A23:A24"/>
@@ -4740,6 +4732,7 @@
     <mergeCell ref="A130:A132"/>
     <mergeCell ref="A133:A134"/>
     <mergeCell ref="A142:A143"/>
+    <mergeCell ref="A145:A146"/>
     <mergeCell ref="D3:D7"/>
     <mergeCell ref="D18:D19"/>
     <mergeCell ref="D23:D24"/>
@@ -4756,7 +4749,7 @@
     <mergeCell ref="D92:D94"/>
     <mergeCell ref="D98:D102"/>
   </mergeCells>
-  <conditionalFormatting sqref="I24">
+  <conditionalFormatting sqref="I25">
     <cfRule type="dataBar" priority="18">
       <dataBar>
         <cfvo type="min"/>
@@ -4765,199 +4758,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{389561d2-172a-4190-9afc-6707f3545bd0}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="17">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{087d165e-4bd0-4a94-8100-a0acd96b2f2b}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="16">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b89ede23-dff7-42e5-a980-bb0bb5b489f0}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="15">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{65b9b3f5-ebb4-420f-8f25-ea946c5dde1f}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="14">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aab00c2f-b1e6-4482-8dda-01a44d974ac7}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="13">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c46f833c-1e2b-4103-81f2-6e4bc88efb5f}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="12">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6dba48f8-171a-401a-b441-8d4a4b95bfae}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="11">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8d3ec5b5-d8a0-47a9-aeff-d96b3a660a5b}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="10">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d6580730-f074-4be4-94b1-4c1592119700}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="9">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{54337740-0684-4fdf-a725-814a4990810b}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="8">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c7f7dc79-24c8-4504-a9a1-19221ca54a1e}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="7">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{98ff1e53-8170-4212-9371-91bbc1c4dd16}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="6">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8cc558ee-c087-4e18-9ce4-25e9004b77b1}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="5">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9524bba1-1a5e-4714-aa7e-cdcf0350a21a}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="4">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ca85366f-c0c2-46a4-ac86-eb746b219b15}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2e7f437e-2d40-463f-9e92-c41b7bb6981b}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="2">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2ab5ba3d-c1b4-4936-89b7-b461e3dc3c58}</x14:id>
+          <x14:id>{a3a89a44-494d-4a73-aafb-c1e96abdd0c0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4971,12 +4772,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1f33692c-bbe5-4707-bc73-165c16f9692b}</x14:id>
+          <x14:id>{76b7f713-8792-45e8-85e1-c292eaae9a39}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D146 D148:D1048576">
+  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D148 D150:D1048576">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="min"/>
@@ -4997,12 +4798,54 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dbe0f120-fb1c-4cba-976c-e7566c5d720c}</x14:id>
+          <x14:id>{5b9a4018-093f-4a1b-8acd-a47fdc2f81ff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I23 I25:I1048576">
+  <conditionalFormatting sqref="I1:I18 I26:I1048576 I20:I24">
+    <cfRule type="dataBar" priority="21">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{d0c3e341-e30e-45b1-9053-30a0847da470}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I14 I26:I1048576 I16:I18 I20:I24">
+    <cfRule type="dataBar" priority="22">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2f5ad379-8006-4912-a4c8-bfb3bc270001}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I14 I26:I1048576 I16:I18 I20:I23">
+    <cfRule type="dataBar" priority="23">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9d1ba638-a1a3-46fe-a2c0-2c4dd90c935d}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I24 I26:I1048576">
     <cfRule type="dataBar" priority="19">
       <dataBar>
         <cfvo type="min"/>
@@ -5011,49 +4854,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{73f274d4-fddd-431e-9500-d521a25521f7}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I14 I32:I1048576 I16:I23 I25:I30">
-    <cfRule type="dataBar" priority="22">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{040e3fb2-1e79-4bce-acaf-01ec323631f5}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I23 I32:I1048576 I25:I30">
-    <cfRule type="dataBar" priority="21">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{32c4fe8f-19ec-4664-956f-577048c50798}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I14 I32:I1048576 I16:I22 I25:I30">
-    <cfRule type="dataBar" priority="23">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bfd63136-94f8-44cc-801f-161117580e5c}</x14:id>
+          <x14:id>{e09b7592-7dd7-4687-919f-2162438a37b7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5067,12 +4868,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5131f3c6-d93f-4fa8-bd1d-d1ff890c0789}</x14:id>
+          <x14:id>{47693bc7-c3df-43e7-ae50-4c255c1dd0d7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6 I9:I14 I38:I1048576 I16:I22 I32:I36 I25:I30">
+  <conditionalFormatting sqref="I2:I6 I9:I14 I38:I1048576 I16:I18 I26:I36 I20:I23">
     <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
@@ -5081,12 +4882,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{628fb4eb-145a-4fba-a741-7b90f4c4ab44}</x14:id>
+          <x14:id>{b4210962-ead4-49f1-a279-8954a3a63554}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6 I9:I14 I38:I1048576 I16 I18:I22 I32:I36 I25:I30">
+  <conditionalFormatting sqref="I2:I6 I9:I14 I38:I1048576 I18 I26:I36 I16 I20:I23">
     <cfRule type="dataBar" priority="30">
       <dataBar>
         <cfvo type="min"/>
@@ -5095,7 +4896,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8cbb24d6-e4d9-468c-9fd1-f7739e49d892}</x14:id>
+          <x14:id>{2db4a1fa-9e3b-4f33-ae4a-0bffb45cad40}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5132,7 +4933,147 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I23 I25:I49">
+  <conditionalFormatting sqref="I3:I6 I9 I11:I13 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I26 I28">
+    <cfRule type="dataBar" priority="36">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{642b3ba4-d08d-42c6-9850-b34d428e251c}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I6 I9 I11:I13 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I28">
+    <cfRule type="dataBar" priority="37">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{12d604db-7ad9-4a5c-becc-3436f8237bd8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I6 I9 I11:I13 I18 I35:I36 I16 I38:I39 I30:I32 I48:I49 I41:I46 I20:I23 I26 I28">
+    <cfRule type="dataBar" priority="34">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{c3b453bb-5798-43d5-a180-81c708b3fc3a}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I6 I9:I13 I18 I28:I33 I16 I35:I36 I41:I49 I38:I39 I20:I23 I26">
+    <cfRule type="dataBar" priority="32">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{921189c0-7804-4782-8983-6353c7389125}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I6 I9:I13 I18 I35:I36 I16 I38:I39 I28:I32 I48:I49 I41:I46 I20:I23 I26">
+    <cfRule type="dataBar" priority="33">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{aa9064ff-ed1c-477f-8fa6-ec2ff2673d28}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I6 I9:I14 I18 I26:I36 I16 I38:I49 I20:I23">
+    <cfRule type="dataBar" priority="28">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{7fb8792a-0cd7-4f1a-9270-c418a0d2123d}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I6 I9:I14 I18 I38:I49 I16 I28:I36 I20:I23 I26">
+    <cfRule type="dataBar" priority="31">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{387e8b30-4b60-4c2e-b233-d7b853e3d071}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I6 I9:I14 I16:I18 I38:I49 I26:I36 I20:I23">
+    <cfRule type="dataBar" priority="27">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{ce42ac36-320e-4221-a5ee-769c6ac140d3}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I7 I9:I14 I16:I18 I26:I49 I20:I23">
+    <cfRule type="dataBar" priority="24">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{dac606d2-c189-4909-abc3-177e7b03c7a9}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I7 I9:I14 I16:I18 I26:I36 I38:I49 I20:I23">
+    <cfRule type="dataBar" priority="25">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{dc19a4fc-2a60-4090-81e7-0b20ec958218}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I24 I26:I49">
     <cfRule type="dataBar" priority="20">
       <dataBar>
         <cfvo type="min"/>
@@ -5141,147 +5082,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{758531ab-253c-46aa-b399-2ab96a21589e}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9 I11:I13 I18:I22 I41:I46 I32 I29:I30 I27 I25 I48:I49 I35:I36 I38:I39">
-    <cfRule type="dataBar" priority="36">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{01bdcd54-7144-4b45-ac81-db0a7d861409}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9 I11:I13 I18:I22 I41:I46 I32 I29:I30 I27 I48:I49 I35:I36 I38:I39">
-    <cfRule type="dataBar" priority="37">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8088a726-43ea-41fd-b0a1-ab84a11074c4}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9 I11:I13 I18:I22 I16 I38:I39 I29:I30 I27 I25 I41:I46 I48:I49 I32 I35:I36">
-    <cfRule type="dataBar" priority="34">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ccd380ea-40a9-43cb-985b-2c7d40eea050}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I13 I18:I22 I16 I35:I36 I27:I30 I25 I38:I39 I41:I49 I32:I33">
-    <cfRule type="dataBar" priority="32">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ae3f2f0-a75a-455f-aa40-92291fb7c08a}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I13 I18:I22 I16 I38:I39 I32 I27:I30 I25 I41:I46 I48:I49 I35:I36">
-    <cfRule type="dataBar" priority="33">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d031f12b-42e7-4596-a5f1-339438d22e0b}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I14 I18:I22 I16 I38:I49 I25:I30 I32:I36">
-    <cfRule type="dataBar" priority="28">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{619a7a01-7190-4aa6-8211-7f04097f4e1a}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I14 I18:I22 I16 I27:I30 I25 I32:I36 I38:I49">
-    <cfRule type="dataBar" priority="31">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{03e4cdcf-e3a5-4eb8-987a-c19a33819916}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I14 I16:I22 I32:I36 I25:I30 I38:I49">
-    <cfRule type="dataBar" priority="27">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38183e64-1efe-4eca-8efe-41216fda781f}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I7 I9:I14 I16:I22 I25:I30 I32:I49">
-    <cfRule type="dataBar" priority="24">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4663b001-7f01-4319-9469-4eee158e9b28}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I7 I9:I14 I16:I22 I25:I30 I38:I49 I32:I36">
-    <cfRule type="dataBar" priority="25">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{80d42469-69ff-4d50-a011-19ef5def386a}</x14:id>
+          <x14:id>{cfeaebc1-5b44-4c0e-9a83-65efeeb4df1d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5289,13 +5090,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
+    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{389561d2-172a-4190-9afc-6707f3545bd0}">
+          <x14:cfRule type="dataBar" id="{a3a89a44-494d-4a73-aafb-c1e96abdd0c0}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5303,138 +5104,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{087d165e-4bd0-4a94-8100-a0acd96b2f2b}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b89ede23-dff7-42e5-a980-bb0bb5b489f0}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{65b9b3f5-ebb4-420f-8f25-ea946c5dde1f}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{aab00c2f-b1e6-4482-8dda-01a44d974ac7}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c46f833c-1e2b-4103-81f2-6e4bc88efb5f}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6dba48f8-171a-401a-b441-8d4a4b95bfae}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8d3ec5b5-d8a0-47a9-aeff-d96b3a660a5b}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d6580730-f074-4be4-94b1-4c1592119700}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{54337740-0684-4fdf-a725-814a4990810b}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c7f7dc79-24c8-4504-a9a1-19221ca54a1e}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{98ff1e53-8170-4212-9371-91bbc1c4dd16}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8cc558ee-c087-4e18-9ce4-25e9004b77b1}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9524bba1-1a5e-4714-aa7e-cdcf0350a21a}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ca85366f-c0c2-46a4-ac86-eb746b219b15}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2e7f437e-2d40-463f-9e92-c41b7bb6981b}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2ab5ba3d-c1b4-4936-89b7-b461e3dc3c58}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>I24</xm:sqref>
+          <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1f33692c-bbe5-4707-bc73-165c16f9692b}">
+          <x14:cfRule type="dataBar" id="{76b7f713-8792-45e8-85e1-c292eaae9a39}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5445,7 +5118,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dbe0f120-fb1c-4cba-976c-e7566c5d720c}">
+          <x14:cfRule type="dataBar" id="{5b9a4018-093f-4a1b-8acd-a47fdc2f81ff}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5458,7 +5131,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{73f274d4-fddd-431e-9500-d521a25521f7}">
+          <x14:cfRule type="dataBar" id="{d0c3e341-e30e-45b1-9053-30a0847da470}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5466,10 +5139,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I23 I25:I1048576</xm:sqref>
+          <xm:sqref>I1:I18 I26:I1048576 I20:I24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{040e3fb2-1e79-4bce-acaf-01ec323631f5}">
+          <x14:cfRule type="dataBar" id="{2f5ad379-8006-4912-a4c8-bfb3bc270001}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5477,10 +5150,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I14 I32:I1048576 I16:I23 I25:I30</xm:sqref>
+          <xm:sqref>I1:I14 I26:I1048576 I16:I18 I20:I24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{32c4fe8f-19ec-4664-956f-577048c50798}">
+          <x14:cfRule type="dataBar" id="{9d1ba638-a1a3-46fe-a2c0-2c4dd90c935d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5488,10 +5161,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I23 I32:I1048576 I25:I30</xm:sqref>
+          <xm:sqref>I1:I14 I26:I1048576 I16:I18 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bfd63136-94f8-44cc-801f-161117580e5c}">
+          <x14:cfRule type="dataBar" id="{e09b7592-7dd7-4687-919f-2162438a37b7}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5499,10 +5172,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I14 I32:I1048576 I16:I22 I25:I30</xm:sqref>
+          <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5131f3c6-d93f-4fa8-bd1d-d1ff890c0789}">
+          <x14:cfRule type="dataBar" id="{47693bc7-c3df-43e7-ae50-4c255c1dd0d7}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5513,7 +5186,7 @@
           <xm:sqref>I2 I50:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{628fb4eb-145a-4fba-a741-7b90f4c4ab44}">
+          <x14:cfRule type="dataBar" id="{b4210962-ead4-49f1-a279-8954a3a63554}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5521,10 +5194,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I6 I9:I14 I38:I1048576 I16:I22 I32:I36 I25:I30</xm:sqref>
+          <xm:sqref>I2:I6 I9:I14 I38:I1048576 I16:I18 I26:I36 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8cbb24d6-e4d9-468c-9fd1-f7739e49d892}">
+          <x14:cfRule type="dataBar" id="{2db4a1fa-9e3b-4f33-ae4a-0bffb45cad40}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5532,10 +5205,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I6 I9:I14 I38:I1048576 I16 I18:I22 I32:I36 I25:I30</xm:sqref>
+          <xm:sqref>I2:I6 I9:I14 I38:I1048576 I18 I26:I36 I16 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{758531ab-253c-46aa-b399-2ab96a21589e}">
+          <x14:cfRule type="dataBar" id="{642b3ba4-d08d-42c6-9850-b34d428e251c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5543,10 +5216,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I23 I25:I49</xm:sqref>
+          <xm:sqref>I3:I6 I9 I11:I13 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I26 I28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{01bdcd54-7144-4b45-ac81-db0a7d861409}">
+          <x14:cfRule type="dataBar" id="{12d604db-7ad9-4a5c-becc-3436f8237bd8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5554,10 +5227,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9 I11:I13 I18:I22 I41:I46 I32 I29:I30 I27 I25 I48:I49 I35:I36 I38:I39</xm:sqref>
+          <xm:sqref>I3:I6 I9 I11:I13 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8088a726-43ea-41fd-b0a1-ab84a11074c4}">
+          <x14:cfRule type="dataBar" id="{c3b453bb-5798-43d5-a180-81c708b3fc3a}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5565,10 +5238,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9 I11:I13 I18:I22 I41:I46 I32 I29:I30 I27 I48:I49 I35:I36 I38:I39</xm:sqref>
+          <xm:sqref>I3:I6 I9 I11:I13 I18 I35:I36 I16 I38:I39 I30:I32 I48:I49 I41:I46 I20:I23 I26 I28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ccd380ea-40a9-43cb-985b-2c7d40eea050}">
+          <x14:cfRule type="dataBar" id="{921189c0-7804-4782-8983-6353c7389125}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5576,10 +5249,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9 I11:I13 I18:I22 I16 I38:I39 I29:I30 I27 I25 I41:I46 I48:I49 I32 I35:I36</xm:sqref>
+          <xm:sqref>I3:I6 I9:I13 I18 I28:I33 I16 I35:I36 I41:I49 I38:I39 I20:I23 I26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6ae3f2f0-a75a-455f-aa40-92291fb7c08a}">
+          <x14:cfRule type="dataBar" id="{aa9064ff-ed1c-477f-8fa6-ec2ff2673d28}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5587,10 +5260,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I13 I18:I22 I16 I35:I36 I27:I30 I25 I38:I39 I41:I49 I32:I33</xm:sqref>
+          <xm:sqref>I3:I6 I9:I13 I18 I35:I36 I16 I38:I39 I28:I32 I48:I49 I41:I46 I20:I23 I26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d031f12b-42e7-4596-a5f1-339438d22e0b}">
+          <x14:cfRule type="dataBar" id="{7fb8792a-0cd7-4f1a-9270-c418a0d2123d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5598,10 +5271,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I13 I18:I22 I16 I38:I39 I32 I27:I30 I25 I41:I46 I48:I49 I35:I36</xm:sqref>
+          <xm:sqref>I3:I6 I9:I14 I18 I26:I36 I16 I38:I49 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{619a7a01-7190-4aa6-8211-7f04097f4e1a}">
+          <x14:cfRule type="dataBar" id="{387e8b30-4b60-4c2e-b233-d7b853e3d071}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5609,10 +5282,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I14 I18:I22 I16 I38:I49 I25:I30 I32:I36</xm:sqref>
+          <xm:sqref>I3:I6 I9:I14 I18 I38:I49 I16 I28:I36 I20:I23 I26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{03e4cdcf-e3a5-4eb8-987a-c19a33819916}">
+          <x14:cfRule type="dataBar" id="{ce42ac36-320e-4221-a5ee-769c6ac140d3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5620,10 +5293,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I14 I18:I22 I16 I27:I30 I25 I32:I36 I38:I49</xm:sqref>
+          <xm:sqref>I3:I6 I9:I14 I16:I18 I38:I49 I26:I36 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{38183e64-1efe-4eca-8efe-41216fda781f}">
+          <x14:cfRule type="dataBar" id="{dac606d2-c189-4909-abc3-177e7b03c7a9}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5631,10 +5304,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I14 I16:I22 I32:I36 I25:I30 I38:I49</xm:sqref>
+          <xm:sqref>I3:I7 I9:I14 I16:I18 I26:I49 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4663b001-7f01-4319-9469-4eee158e9b28}">
+          <x14:cfRule type="dataBar" id="{dc19a4fc-2a60-4090-81e7-0b20ec958218}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5642,10 +5315,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I7 I9:I14 I16:I22 I25:I30 I32:I49</xm:sqref>
+          <xm:sqref>I3:I7 I9:I14 I16:I18 I26:I36 I38:I49 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{80d42469-69ff-4d50-a011-19ef5def386a}">
+          <x14:cfRule type="dataBar" id="{cfeaebc1-5b44-4c0e-9a83-65efeeb4df1d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5653,7 +5326,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I7 I9:I14 I16:I22 I25:I30 I38:I49 I32:I36</xm:sqref>
+          <xm:sqref>I3:I24 I26:I49</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="收支与赞助鸣谢" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="113">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -120,21 +120,27 @@
     <t>xiaoshenjin233</t>
   </si>
   <si>
+    <t>moqi</t>
+  </si>
+  <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>主板、硬盘、机箱</t>
+  </si>
+  <si>
     <t>rocksuger</t>
   </si>
   <si>
-    <t>主板、硬盘、机箱</t>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>物品、电费</t>
   </si>
   <si>
     <t>SNHGY</t>
   </si>
   <si>
-    <t>物品、电费</t>
-  </si>
-  <si>
-    <t>moqi</t>
-  </si>
-  <si>
     <t>Sz05</t>
   </si>
   <si>
@@ -157,12 +163,6 @@
   </si>
   <si>
     <t>srdownb</t>
-  </si>
-  <si>
-    <t>↑11</t>
-  </si>
-  <si>
-    <t>↓1</t>
   </si>
   <si>
     <t>火药、遗物</t>
@@ -1213,7 +1213,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1324,27 +1324,6 @@
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2037,15 +2016,18 @@
       <c r="G13" s="15">
         <v>11</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="16">
-        <f>SUM(C56,C46,C74)</f>
-        <v>23</v>
+      <c r="I13" s="2">
+        <f>SUM(C133,C143,C147)</f>
+        <v>38.32</v>
       </c>
       <c r="J13" s="3">
-        <v>45634</v>
+        <v>46146</v>
+      </c>
+      <c r="K13" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2061,20 +2043,23 @@
         <v>-780.05</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G14" s="15">
         <v>12</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="2">
-        <f>SUM(C99,C109,C130,C137,C144)</f>
-        <v>18.45</v>
+        <v>33</v>
+      </c>
+      <c r="I14" s="16">
+        <f>SUM(C56,C46,C74)</f>
+        <v>23</v>
       </c>
       <c r="J14" s="3">
-        <v>46144</v>
+        <v>45634</v>
+      </c>
+      <c r="K14" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2092,20 +2077,23 @@
         <v>-660.05</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G15" s="15">
         <v>13</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="2">
+        <f>SUM(C99,C109,C130,C137,C144)</f>
+        <v>18.45</v>
+      </c>
+      <c r="J15" s="3">
+        <v>46144</v>
+      </c>
+      <c r="K15" t="s">
         <v>34</v>
-      </c>
-      <c r="I15" s="2">
-        <f>SUM(C133,C143)</f>
-        <v>18.32</v>
-      </c>
-      <c r="J15" s="3">
-        <v>46141</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2127,7 +2115,7 @@
         <v>14</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I16" s="2">
         <f>SUM(C85:C85,C89,C96:C98,C117,C120,C122)</f>
@@ -2137,12 +2125,12 @@
         <v>46039</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:10">
       <c r="A17" s="17">
         <v>44953</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C17" s="13">
         <v>10</v>
@@ -2152,13 +2140,13 @@
         <v>-637.05</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G17" s="15">
         <v>15</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I17" s="2">
         <v>15</v>
@@ -2167,7 +2155,7 @@
         <v>45930</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:10">
       <c r="A18" s="17">
         <v>44958</v>
       </c>
@@ -2183,13 +2171,13 @@
         <v>-550.73</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G18" s="15">
         <v>16</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I18" s="16">
         <f>SUM(C40,C64)</f>
@@ -2199,10 +2187,10 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:10">
       <c r="A19" s="17"/>
       <c r="B19" s="22" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C19" s="13">
         <v>1.32</v>
@@ -2213,7 +2201,7 @@
         <v>17</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I19" s="2">
         <f>SUM(C135,C139,C146)</f>
@@ -2222,11 +2210,8 @@
       <c r="J19" s="3">
         <v>46145</v>
       </c>
-      <c r="K19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="17">
         <v>44961</v>
       </c>
@@ -2245,7 +2230,7 @@
         <v>18</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I20" s="16">
         <v>10</v>
@@ -2253,11 +2238,8 @@
       <c r="J20" s="3">
         <v>44953</v>
       </c>
-      <c r="K20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="17">
         <v>45138</v>
       </c>
@@ -2287,11 +2269,8 @@
       <c r="J21" s="3">
         <v>45234</v>
       </c>
-      <c r="K21" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="17">
         <v>45140</v>
       </c>
@@ -2318,11 +2297,8 @@
       <c r="J22" s="3">
         <v>45325</v>
       </c>
-      <c r="K22" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="17">
         <v>45141</v>
       </c>
@@ -2349,11 +2325,8 @@
       <c r="J23" s="3">
         <v>45649</v>
       </c>
-      <c r="K23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="17"/>
       <c r="B24" s="8" t="s">
         <v>13</v>
@@ -2377,11 +2350,8 @@
       <c r="J24" s="3">
         <v>46069</v>
       </c>
-      <c r="K24" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="17">
         <v>45160</v>
       </c>
@@ -2408,11 +2378,8 @@
       <c r="J25" s="3">
         <v>46145</v>
       </c>
-      <c r="K25" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="17">
         <v>45234</v>
       </c>
@@ -2441,11 +2408,8 @@
       <c r="J26" s="3">
         <v>45860</v>
       </c>
-      <c r="K26" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="17"/>
       <c r="B27" s="8"/>
       <c r="C27" s="18">
@@ -2467,11 +2431,8 @@
       <c r="J27" s="3">
         <v>45907</v>
       </c>
-      <c r="K27" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="17">
         <v>45249</v>
       </c>
@@ -2501,11 +2462,8 @@
       <c r="J28" s="3">
         <v>45861</v>
       </c>
-      <c r="K28" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="17">
         <v>45305</v>
       </c>
@@ -2532,11 +2490,8 @@
       <c r="J29" s="3">
         <v>45868</v>
       </c>
-      <c r="K29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="17">
         <v>45325</v>
       </c>
@@ -2565,11 +2520,8 @@
       <c r="J30" s="3">
         <v>44787</v>
       </c>
-      <c r="K30" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="17">
         <v>45341</v>
       </c>
@@ -2598,11 +2550,8 @@
       <c r="J31" s="3">
         <v>45634</v>
       </c>
-      <c r="K31" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="17">
         <v>45368</v>
       </c>
@@ -2847,7 +2796,7 @@
         <v>45421</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C40" s="13">
         <v>5</v>
@@ -2892,7 +2841,7 @@
         <v>39</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I41" s="16">
         <v>1.32</v>
@@ -3017,7 +2966,7 @@
     <row r="46" spans="1:10">
       <c r="A46" s="29"/>
       <c r="B46" s="26" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C46" s="27">
         <v>3</v>
@@ -3219,7 +3168,7 @@
     <row r="56" spans="1:10">
       <c r="A56" s="31"/>
       <c r="B56" s="26" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C56" s="27">
         <v>10</v>
@@ -3350,7 +3299,7 @@
         <v>45555</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C64" s="27">
         <v>6</v>
@@ -3517,7 +3466,7 @@
     <row r="74" spans="1:5">
       <c r="A74" s="17"/>
       <c r="B74" s="33" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C74" s="27">
         <v>10</v>
@@ -3696,7 +3645,7 @@
         <v>45865</v>
       </c>
       <c r="B85" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C85" s="27">
         <v>3</v>
@@ -3764,7 +3713,7 @@
         <v>45878</v>
       </c>
       <c r="B89" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C89" s="27">
         <v>0.01</v>
@@ -3872,7 +3821,7 @@
         <v>45894</v>
       </c>
       <c r="B96" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C96" s="27">
         <v>1</v>
@@ -3904,7 +3853,7 @@
         <v>45907</v>
       </c>
       <c r="B98" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C98" s="27">
         <v>2</v>
@@ -3918,7 +3867,7 @@
     <row r="99" spans="1:5">
       <c r="A99" s="31"/>
       <c r="B99" s="33" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C99" s="27">
         <v>2</v>
@@ -4014,7 +3963,7 @@
         <v>45930</v>
       </c>
       <c r="B106" s="33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C106" s="27">
         <v>15</v>
@@ -4058,7 +4007,7 @@
     <row r="109" spans="1:5">
       <c r="A109" s="31"/>
       <c r="B109" s="33" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C109" s="27">
         <v>0.45</v>
@@ -4194,7 +4143,7 @@
         <v>45990</v>
       </c>
       <c r="B117" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C117" s="27">
         <v>1</v>
@@ -4246,7 +4195,7 @@
         <v>46031</v>
       </c>
       <c r="B120" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C120" s="27">
         <v>2</v>
@@ -4280,7 +4229,7 @@
         <v>46039</v>
       </c>
       <c r="B122" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C122" s="27">
         <v>1</v>
@@ -4416,7 +4365,7 @@
         <v>46069</v>
       </c>
       <c r="B130" s="33" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C130" s="27">
         <v>5</v>
@@ -4462,7 +4411,7 @@
         <v>46070</v>
       </c>
       <c r="B133" s="33" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C133" s="27">
         <v>8.32</v>
@@ -4492,7 +4441,7 @@
         <v>46074</v>
       </c>
       <c r="B135" s="33" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C135" s="27">
         <v>1.5</v>
@@ -4526,7 +4475,7 @@
         <v>46085</v>
       </c>
       <c r="B137" s="33" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C137" s="27">
         <v>10</v>
@@ -4560,7 +4509,7 @@
         <v>46130</v>
       </c>
       <c r="B139" s="33" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C139" s="27">
         <v>3</v>
@@ -4624,7 +4573,7 @@
     <row r="143" spans="1:5">
       <c r="A143" s="31"/>
       <c r="B143" s="33" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C143" s="27">
         <v>10</v>
@@ -4640,7 +4589,7 @@
         <v>46144</v>
       </c>
       <c r="B144" s="33" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C144" s="27">
         <v>1</v>
@@ -4652,7 +4601,7 @@
       <c r="E144" s="34"/>
     </row>
     <row r="145" spans="1:5">
-      <c r="A145" s="37">
+      <c r="A145" s="25">
         <v>46145</v>
       </c>
       <c r="B145" s="33" t="s">
@@ -4670,41 +4619,50 @@
       </c>
     </row>
     <row r="146" spans="1:5">
-      <c r="A146" s="38"/>
-      <c r="B146" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="C146" s="40">
+      <c r="A146" s="31"/>
+      <c r="B146" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C146" s="27">
         <v>6</v>
       </c>
       <c r="D146" s="21">
         <f>SUM(C3:C146)</f>
         <v>-3099.15</v>
       </c>
-      <c r="E146" s="41"/>
+      <c r="E146" s="34"/>
     </row>
     <row r="147" spans="1:5">
-      <c r="A147" s="42"/>
-      <c r="B147" s="39"/>
-      <c r="C147" s="40"/>
-      <c r="D147" s="43"/>
-      <c r="E147" s="41"/>
-    </row>
-    <row r="148" spans="1:5">
-      <c r="A148" s="44"/>
-      <c r="B148" s="45"/>
-      <c r="C148" s="46"/>
-      <c r="D148" s="46"/>
-      <c r="E148" s="47"/>
+      <c r="A147" s="25">
+        <v>46146</v>
+      </c>
+      <c r="B147" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C147" s="27">
+        <v>20</v>
+      </c>
+      <c r="D147" s="21">
+        <f>SUM(C3:C147)</f>
+        <v>-3079.15</v>
+      </c>
+      <c r="E147" s="34"/>
+    </row>
+    <row r="148" ht="14.25" spans="1:5">
+      <c r="A148" s="37"/>
+      <c r="B148" s="38"/>
+      <c r="C148" s="39"/>
+      <c r="D148" s="39"/>
+      <c r="E148" s="40"/>
     </row>
     <row r="149" spans="1:5">
-      <c r="A149" s="48" t="s">
+      <c r="A149" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="B149" s="48"/>
-      <c r="C149" s="48"/>
-      <c r="D149" s="48"/>
-      <c r="E149" s="48"/>
+      <c r="B149" s="41"/>
+      <c r="C149" s="41"/>
+      <c r="D149" s="41"/>
+      <c r="E149" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="40">
@@ -4758,7 +4716,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a3a89a44-494d-4a73-aafb-c1e96abdd0c0}</x14:id>
+          <x14:id>{e2ab790d-33f9-48ea-85a8-01caa9a6b713}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4772,7 +4730,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{76b7f713-8792-45e8-85e1-c292eaae9a39}</x14:id>
+          <x14:id>{9b1946bd-04a7-4453-82a2-54f7bbd67618}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4798,7 +4756,35 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5b9a4018-093f-4a1b-8acd-a47fdc2f81ff}</x14:id>
+          <x14:id>{ab125945-82b1-4d78-954c-646b0a084aa3}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I12 I20:I24 I26:I1048576 I14:I18">
+    <cfRule type="dataBar" priority="22">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2078db2c-cecc-48e1-829f-61186f805d4e}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I12 I20:I23 I26:I1048576 I14:I18">
+    <cfRule type="dataBar" priority="23">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{66210601-d661-43a1-a7c1-4fbf87af2e47}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4812,35 +4798,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d0c3e341-e30e-45b1-9053-30a0847da470}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I14 I26:I1048576 I16:I18 I20:I24">
-    <cfRule type="dataBar" priority="22">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2f5ad379-8006-4912-a4c8-bfb3bc270001}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I14 I26:I1048576 I16:I18 I20:I23">
-    <cfRule type="dataBar" priority="23">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9d1ba638-a1a3-46fe-a2c0-2c4dd90c935d}</x14:id>
+          <x14:id>{28559485-5980-47e0-9f6c-daac2554fdf4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4854,7 +4812,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e09b7592-7dd7-4687-919f-2162438a37b7}</x14:id>
+          <x14:id>{82d23e15-2fde-4b6e-b16e-bbc2be0aaff8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4868,12 +4826,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{47693bc7-c3df-43e7-ae50-4c255c1dd0d7}</x14:id>
+          <x14:id>{a9a6d7d4-9d2c-4543-919f-3da34aa4abe9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6 I9:I14 I38:I1048576 I16:I18 I26:I36 I20:I23">
+  <conditionalFormatting sqref="I2:I6 I9:I12 I20:I23 I38:I1048576 I14:I18 I26:I36">
     <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
@@ -4882,12 +4840,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b4210962-ead4-49f1-a279-8954a3a63554}</x14:id>
+          <x14:id>{6478a7a8-75de-4eb2-84cc-47a6d127c814}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6 I9:I14 I38:I1048576 I18 I26:I36 I16 I20:I23">
+  <conditionalFormatting sqref="I2:I6 I9:I12 I20:I23 I38:I1048576 I18 I26:I36 I14:I16">
     <cfRule type="dataBar" priority="30">
       <dataBar>
         <cfvo type="min"/>
@@ -4896,7 +4854,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2db4a1fa-9e3b-4f33-ae4a-0bffb45cad40}</x14:id>
+          <x14:id>{bc70300b-ea36-44a5-8949-8ea95d106fc4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4933,7 +4891,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9 I11:I13 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I26 I28">
+  <conditionalFormatting sqref="I3:I6 I9 I11:I12 I28 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I26 I14">
     <cfRule type="dataBar" priority="36">
       <dataBar>
         <cfvo type="min"/>
@@ -4942,12 +4900,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{642b3ba4-d08d-42c6-9850-b34d428e251c}</x14:id>
+          <x14:id>{e3eedc17-0557-4346-852d-3d614a565146}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9 I11:I13 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I28">
+  <conditionalFormatting sqref="I3:I6 I9 I11:I12 I28 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I14">
     <cfRule type="dataBar" priority="37">
       <dataBar>
         <cfvo type="min"/>
@@ -4956,12 +4914,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{12d604db-7ad9-4a5c-becc-3436f8237bd8}</x14:id>
+          <x14:id>{7e02d5ec-c006-49e8-8cee-fb2fc76cf772}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9 I11:I13 I18 I35:I36 I16 I38:I39 I30:I32 I48:I49 I41:I46 I20:I23 I26 I28">
+  <conditionalFormatting sqref="I3:I6 I9 I11:I12 I28 I18 I35:I36 I16 I38:I39 I30:I32 I48:I49 I41:I46 I20:I23 I26 I14">
     <cfRule type="dataBar" priority="34">
       <dataBar>
         <cfvo type="min"/>
@@ -4970,12 +4928,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c3b453bb-5798-43d5-a180-81c708b3fc3a}</x14:id>
+          <x14:id>{d45fd17b-95e3-4699-8b83-cb2afeef5ef8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I13 I18 I28:I33 I16 I35:I36 I41:I49 I38:I39 I20:I23 I26">
+  <conditionalFormatting sqref="I3:I6 I9:I12 I26 I18 I28:I33 I16 I35:I36 I41:I49 I38:I39 I20:I23 I14">
     <cfRule type="dataBar" priority="32">
       <dataBar>
         <cfvo type="min"/>
@@ -4984,12 +4942,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{921189c0-7804-4782-8983-6353c7389125}</x14:id>
+          <x14:id>{52fcc040-0974-4598-8fa2-039ac65f51f8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I13 I18 I35:I36 I16 I38:I39 I28:I32 I48:I49 I41:I46 I20:I23 I26">
+  <conditionalFormatting sqref="I3:I6 I9:I12 I26 I18 I35:I36 I16 I38:I39 I28:I32 I48:I49 I41:I46 I20:I23 I14">
     <cfRule type="dataBar" priority="33">
       <dataBar>
         <cfvo type="min"/>
@@ -4998,12 +4956,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aa9064ff-ed1c-477f-8fa6-ec2ff2673d28}</x14:id>
+          <x14:id>{be6f9de4-a6ed-4d6d-ad0a-b20138ee5636}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I14 I18 I26:I36 I16 I38:I49 I20:I23">
+  <conditionalFormatting sqref="I3:I6 I9:I12 I20:I23 I18 I26:I36 I14:I16 I38:I49">
     <cfRule type="dataBar" priority="28">
       <dataBar>
         <cfvo type="min"/>
@@ -5012,12 +4970,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7fb8792a-0cd7-4f1a-9270-c418a0d2123d}</x14:id>
+          <x14:id>{35eb46ab-5868-40a6-9abe-85654d2ee47e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I14 I18 I38:I49 I16 I28:I36 I20:I23 I26">
+  <conditionalFormatting sqref="I3:I6 I9:I12 I26 I18 I38:I49 I14:I16 I28:I36 I20:I23">
     <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
@@ -5026,12 +4984,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{387e8b30-4b60-4c2e-b233-d7b853e3d071}</x14:id>
+          <x14:id>{433be48e-3cb8-4e63-88c8-3ebbdc18a869}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I14 I16:I18 I38:I49 I26:I36 I20:I23">
+  <conditionalFormatting sqref="I3:I6 I9:I12 I20:I23 I14:I18 I38:I49 I26:I36">
     <cfRule type="dataBar" priority="27">
       <dataBar>
         <cfvo type="min"/>
@@ -5040,12 +4998,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ce42ac36-320e-4221-a5ee-769c6ac140d3}</x14:id>
+          <x14:id>{a9cef11f-f284-4dbc-a7bb-95a9a164d0d8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I7 I9:I14 I16:I18 I26:I49 I20:I23">
+  <conditionalFormatting sqref="I3:I7 I9:I12 I20:I23 I14:I18 I26:I49">
     <cfRule type="dataBar" priority="24">
       <dataBar>
         <cfvo type="min"/>
@@ -5054,12 +5012,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dac606d2-c189-4909-abc3-177e7b03c7a9}</x14:id>
+          <x14:id>{7ebfde5b-1d44-4a5c-9d04-7ed20fc88af6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I7 I9:I14 I16:I18 I26:I36 I38:I49 I20:I23">
+  <conditionalFormatting sqref="I3:I7 I9:I12 I20:I23 I14:I18 I26:I36 I38:I49">
     <cfRule type="dataBar" priority="25">
       <dataBar>
         <cfvo type="min"/>
@@ -5068,7 +5026,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc19a4fc-2a60-4090-81e7-0b20ec958218}</x14:id>
+          <x14:id>{dfef82c0-ed34-4091-a0ae-0ede5b2c5cf3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5082,7 +5040,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cfeaebc1-5b44-4c0e-9a83-65efeeb4df1d}</x14:id>
+          <x14:id>{fc81d9b0-f6d8-4b92-b1ae-e00ae5cd5249}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5090,13 +5048,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
+    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a3a89a44-494d-4a73-aafb-c1e96abdd0c0}">
+          <x14:cfRule type="dataBar" id="{e2ab790d-33f9-48ea-85a8-01caa9a6b713}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5107,7 +5065,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{76b7f713-8792-45e8-85e1-c292eaae9a39}">
+          <x14:cfRule type="dataBar" id="{9b1946bd-04a7-4453-82a2-54f7bbd67618}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5118,7 +5076,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5b9a4018-093f-4a1b-8acd-a47fdc2f81ff}">
+          <x14:cfRule type="dataBar" id="{ab125945-82b1-4d78-954c-646b0a084aa3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5131,7 +5089,29 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d0c3e341-e30e-45b1-9053-30a0847da470}">
+          <x14:cfRule type="dataBar" id="{2078db2c-cecc-48e1-829f-61186f805d4e}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I1:I12 I20:I24 I26:I1048576 I14:I18</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{66210601-d661-43a1-a7c1-4fbf87af2e47}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I1:I12 I20:I23 I26:I1048576 I14:I18</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{28559485-5980-47e0-9f6c-daac2554fdf4}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5142,29 +5122,7 @@
           <xm:sqref>I1:I18 I26:I1048576 I20:I24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2f5ad379-8006-4912-a4c8-bfb3bc270001}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>I1:I14 I26:I1048576 I16:I18 I20:I24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9d1ba638-a1a3-46fe-a2c0-2c4dd90c935d}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>I1:I14 I26:I1048576 I16:I18 I20:I23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e09b7592-7dd7-4687-919f-2162438a37b7}">
+          <x14:cfRule type="dataBar" id="{82d23e15-2fde-4b6e-b16e-bbc2be0aaff8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5175,7 +5133,7 @@
           <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{47693bc7-c3df-43e7-ae50-4c255c1dd0d7}">
+          <x14:cfRule type="dataBar" id="{a9a6d7d4-9d2c-4543-919f-3da34aa4abe9}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5186,7 +5144,7 @@
           <xm:sqref>I2 I50:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b4210962-ead4-49f1-a279-8954a3a63554}">
+          <x14:cfRule type="dataBar" id="{6478a7a8-75de-4eb2-84cc-47a6d127c814}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5194,10 +5152,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I6 I9:I14 I38:I1048576 I16:I18 I26:I36 I20:I23</xm:sqref>
+          <xm:sqref>I2:I6 I9:I12 I20:I23 I38:I1048576 I14:I18 I26:I36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2db4a1fa-9e3b-4f33-ae4a-0bffb45cad40}">
+          <x14:cfRule type="dataBar" id="{bc70300b-ea36-44a5-8949-8ea95d106fc4}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5205,10 +5163,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I6 I9:I14 I38:I1048576 I18 I26:I36 I16 I20:I23</xm:sqref>
+          <xm:sqref>I2:I6 I9:I12 I20:I23 I38:I1048576 I18 I26:I36 I14:I16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{642b3ba4-d08d-42c6-9850-b34d428e251c}">
+          <x14:cfRule type="dataBar" id="{e3eedc17-0557-4346-852d-3d614a565146}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5216,10 +5174,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9 I11:I13 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I26 I28</xm:sqref>
+          <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I26 I14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{12d604db-7ad9-4a5c-becc-3436f8237bd8}">
+          <x14:cfRule type="dataBar" id="{7e02d5ec-c006-49e8-8cee-fb2fc76cf772}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5227,10 +5185,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9 I11:I13 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I28</xm:sqref>
+          <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c3b453bb-5798-43d5-a180-81c708b3fc3a}">
+          <x14:cfRule type="dataBar" id="{d45fd17b-95e3-4699-8b83-cb2afeef5ef8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5238,10 +5196,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9 I11:I13 I18 I35:I36 I16 I38:I39 I30:I32 I48:I49 I41:I46 I20:I23 I26 I28</xm:sqref>
+          <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I35:I36 I16 I38:I39 I30:I32 I48:I49 I41:I46 I20:I23 I26 I14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{921189c0-7804-4782-8983-6353c7389125}">
+          <x14:cfRule type="dataBar" id="{52fcc040-0974-4598-8fa2-039ac65f51f8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5249,10 +5207,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I13 I18 I28:I33 I16 I35:I36 I41:I49 I38:I39 I20:I23 I26</xm:sqref>
+          <xm:sqref>I3:I6 I9:I12 I26 I18 I28:I33 I16 I35:I36 I41:I49 I38:I39 I20:I23 I14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{aa9064ff-ed1c-477f-8fa6-ec2ff2673d28}">
+          <x14:cfRule type="dataBar" id="{be6f9de4-a6ed-4d6d-ad0a-b20138ee5636}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5260,10 +5218,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I13 I18 I35:I36 I16 I38:I39 I28:I32 I48:I49 I41:I46 I20:I23 I26</xm:sqref>
+          <xm:sqref>I3:I6 I9:I12 I26 I18 I35:I36 I16 I38:I39 I28:I32 I48:I49 I41:I46 I20:I23 I14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7fb8792a-0cd7-4f1a-9270-c418a0d2123d}">
+          <x14:cfRule type="dataBar" id="{35eb46ab-5868-40a6-9abe-85654d2ee47e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5271,10 +5229,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I14 I18 I26:I36 I16 I38:I49 I20:I23</xm:sqref>
+          <xm:sqref>I3:I6 I9:I12 I20:I23 I18 I26:I36 I14:I16 I38:I49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{387e8b30-4b60-4c2e-b233-d7b853e3d071}">
+          <x14:cfRule type="dataBar" id="{433be48e-3cb8-4e63-88c8-3ebbdc18a869}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5282,10 +5240,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I14 I18 I38:I49 I16 I28:I36 I20:I23 I26</xm:sqref>
+          <xm:sqref>I3:I6 I9:I12 I26 I18 I38:I49 I14:I16 I28:I36 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ce42ac36-320e-4221-a5ee-769c6ac140d3}">
+          <x14:cfRule type="dataBar" id="{a9cef11f-f284-4dbc-a7bb-95a9a164d0d8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5293,10 +5251,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I14 I16:I18 I38:I49 I26:I36 I20:I23</xm:sqref>
+          <xm:sqref>I3:I6 I9:I12 I20:I23 I14:I18 I38:I49 I26:I36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dac606d2-c189-4909-abc3-177e7b03c7a9}">
+          <x14:cfRule type="dataBar" id="{7ebfde5b-1d44-4a5c-9d04-7ed20fc88af6}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5304,10 +5262,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I7 I9:I14 I16:I18 I26:I49 I20:I23</xm:sqref>
+          <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dc19a4fc-2a60-4090-81e7-0b20ec958218}">
+          <x14:cfRule type="dataBar" id="{dfef82c0-ed34-4091-a0ae-0ede5b2c5cf3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5315,10 +5273,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I7 I9:I14 I16:I18 I26:I36 I38:I49 I20:I23</xm:sqref>
+          <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I36 I38:I49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cfeaebc1-5b44-4c0e-9a83-65efeeb4df1d}">
+          <x14:cfRule type="dataBar" id="{fc81d9b0-f6d8-4b92-b1ae-e00ae5cd5249}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="113">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -1661,7 +1661,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K149"/>
+  <dimension ref="A1:K151"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -1772,11 +1772,11 @@
         <v>15</v>
       </c>
       <c r="I4" s="16">
-        <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141)</f>
-        <v>427</v>
+        <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148)</f>
+        <v>437</v>
       </c>
       <c r="J4" s="3">
-        <v>46137</v>
+        <v>46146</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -4648,27 +4648,50 @@
       </c>
       <c r="E147" s="34"/>
     </row>
-    <row r="148" ht="14.25" spans="1:5">
-      <c r="A148" s="37"/>
-      <c r="B148" s="38"/>
-      <c r="C148" s="39"/>
-      <c r="D148" s="39"/>
-      <c r="E148" s="40"/>
+    <row r="148" spans="1:5">
+      <c r="A148" s="31"/>
+      <c r="B148" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C148" s="27">
+        <v>10</v>
+      </c>
+      <c r="D148" s="21">
+        <f>SUM(C3:C148)</f>
+        <v>-3069.15</v>
+      </c>
+      <c r="E148" s="34" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="149" spans="1:5">
-      <c r="A149" s="41" t="s">
+      <c r="A149" s="25"/>
+      <c r="B149" s="33"/>
+      <c r="C149" s="27"/>
+      <c r="D149" s="21"/>
+      <c r="E149" s="34"/>
+    </row>
+    <row r="150" ht="14.25" spans="1:5">
+      <c r="A150" s="37"/>
+      <c r="B150" s="38"/>
+      <c r="C150" s="39"/>
+      <c r="D150" s="39"/>
+      <c r="E150" s="40"/>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="B149" s="41"/>
-      <c r="C149" s="41"/>
-      <c r="D149" s="41"/>
-      <c r="E149" s="41"/>
+      <c r="B151" s="41"/>
+      <c r="C151" s="41"/>
+      <c r="D151" s="41"/>
+      <c r="E151" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="41">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A149:E149"/>
+    <mergeCell ref="A151:E151"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A23:A24"/>
@@ -4691,6 +4714,7 @@
     <mergeCell ref="A133:A134"/>
     <mergeCell ref="A142:A143"/>
     <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A147:A148"/>
     <mergeCell ref="D3:D7"/>
     <mergeCell ref="D18:D19"/>
     <mergeCell ref="D23:D24"/>
@@ -4716,7 +4740,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e2ab790d-33f9-48ea-85a8-01caa9a6b713}</x14:id>
+          <x14:id>{9ff1a31f-2fb0-430d-aaad-6b70c6b70156}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4730,12 +4754,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9b1946bd-04a7-4453-82a2-54f7bbd67618}</x14:id>
+          <x14:id>{41cca850-ed86-43e2-b46b-2388aee97e54}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D148 D150:D1048576">
+  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D150 D152:D1048576">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="min"/>
@@ -4756,7 +4780,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ab125945-82b1-4d78-954c-646b0a084aa3}</x14:id>
+          <x14:id>{b3c9d57e-a14f-4e84-a549-d39ad05a2160}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4770,7 +4794,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2078db2c-cecc-48e1-829f-61186f805d4e}</x14:id>
+          <x14:id>{89230102-36ce-42cf-b24d-1f93ccdec507}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4784,7 +4808,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{66210601-d661-43a1-a7c1-4fbf87af2e47}</x14:id>
+          <x14:id>{9d2f38b4-5a7f-437c-ab0b-ef4c6099f109}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4798,7 +4822,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{28559485-5980-47e0-9f6c-daac2554fdf4}</x14:id>
+          <x14:id>{d6fd2163-85f3-4668-8c82-ad21b23badb6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4812,7 +4836,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{82d23e15-2fde-4b6e-b16e-bbc2be0aaff8}</x14:id>
+          <x14:id>{75a6a0bc-e9cb-4c9d-9377-6fe22cd88d72}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4826,7 +4850,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a9a6d7d4-9d2c-4543-919f-3da34aa4abe9}</x14:id>
+          <x14:id>{6317facf-61ab-47f3-8e4a-47334f96abb7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4840,7 +4864,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6478a7a8-75de-4eb2-84cc-47a6d127c814}</x14:id>
+          <x14:id>{861259e2-c2b9-4276-867c-556f89cc1d92}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4854,7 +4878,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bc70300b-ea36-44a5-8949-8ea95d106fc4}</x14:id>
+          <x14:id>{0190ca56-9582-4144-8a7e-5311535f93bc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4900,7 +4924,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e3eedc17-0557-4346-852d-3d614a565146}</x14:id>
+          <x14:id>{a0f2058a-4957-42f6-b88b-560e4a83d32f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4914,7 +4938,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7e02d5ec-c006-49e8-8cee-fb2fc76cf772}</x14:id>
+          <x14:id>{9272cd51-95d9-4384-bcf7-72c2587bba15}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4928,7 +4952,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d45fd17b-95e3-4699-8b83-cb2afeef5ef8}</x14:id>
+          <x14:id>{346fd514-81b1-4c5d-8cf4-b662b2f22947}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4942,7 +4966,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{52fcc040-0974-4598-8fa2-039ac65f51f8}</x14:id>
+          <x14:id>{c3a4d738-1b55-4688-b063-1c951bce5ea6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4956,7 +4980,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{be6f9de4-a6ed-4d6d-ad0a-b20138ee5636}</x14:id>
+          <x14:id>{4e03c9d6-0be3-4b05-b59a-aa947a351cb1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4970,7 +4994,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{35eb46ab-5868-40a6-9abe-85654d2ee47e}</x14:id>
+          <x14:id>{5e1ad14b-9e97-461c-af97-e4fe11dec4fa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4984,7 +5008,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{433be48e-3cb8-4e63-88c8-3ebbdc18a869}</x14:id>
+          <x14:id>{d50af652-6eb1-4db8-b32c-6d8f96822659}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4998,7 +5022,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a9cef11f-f284-4dbc-a7bb-95a9a164d0d8}</x14:id>
+          <x14:id>{2ebb1f94-8aef-4b27-b0bb-f05524f4c813}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5012,7 +5036,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7ebfde5b-1d44-4a5c-9d04-7ed20fc88af6}</x14:id>
+          <x14:id>{2eeec38e-c114-4de4-92ae-ba659346d99a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5026,7 +5050,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dfef82c0-ed34-4091-a0ae-0ede5b2c5cf3}</x14:id>
+          <x14:id>{fab690a4-4f66-4f82-b945-ebe7dc6333ac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5040,7 +5064,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fc81d9b0-f6d8-4b92-b1ae-e00ae5cd5249}</x14:id>
+          <x14:id>{f2a55db1-ff6c-4750-bc9a-09f51b79be73}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5054,7 +5078,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e2ab790d-33f9-48ea-85a8-01caa9a6b713}">
+          <x14:cfRule type="dataBar" id="{9ff1a31f-2fb0-430d-aaad-6b70c6b70156}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5065,7 +5089,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9b1946bd-04a7-4453-82a2-54f7bbd67618}">
+          <x14:cfRule type="dataBar" id="{41cca850-ed86-43e2-b46b-2388aee97e54}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5076,7 +5100,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ab125945-82b1-4d78-954c-646b0a084aa3}">
+          <x14:cfRule type="dataBar" id="{b3c9d57e-a14f-4e84-a549-d39ad05a2160}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5089,7 +5113,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2078db2c-cecc-48e1-829f-61186f805d4e}">
+          <x14:cfRule type="dataBar" id="{89230102-36ce-42cf-b24d-1f93ccdec507}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5100,7 +5124,7 @@
           <xm:sqref>I1:I12 I20:I24 I26:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{66210601-d661-43a1-a7c1-4fbf87af2e47}">
+          <x14:cfRule type="dataBar" id="{9d2f38b4-5a7f-437c-ab0b-ef4c6099f109}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5111,7 +5135,7 @@
           <xm:sqref>I1:I12 I20:I23 I26:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{28559485-5980-47e0-9f6c-daac2554fdf4}">
+          <x14:cfRule type="dataBar" id="{d6fd2163-85f3-4668-8c82-ad21b23badb6}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5122,7 +5146,7 @@
           <xm:sqref>I1:I18 I26:I1048576 I20:I24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{82d23e15-2fde-4b6e-b16e-bbc2be0aaff8}">
+          <x14:cfRule type="dataBar" id="{75a6a0bc-e9cb-4c9d-9377-6fe22cd88d72}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5133,7 +5157,7 @@
           <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a9a6d7d4-9d2c-4543-919f-3da34aa4abe9}">
+          <x14:cfRule type="dataBar" id="{6317facf-61ab-47f3-8e4a-47334f96abb7}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5144,7 +5168,7 @@
           <xm:sqref>I2 I50:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6478a7a8-75de-4eb2-84cc-47a6d127c814}">
+          <x14:cfRule type="dataBar" id="{861259e2-c2b9-4276-867c-556f89cc1d92}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5155,7 +5179,7 @@
           <xm:sqref>I2:I6 I9:I12 I20:I23 I38:I1048576 I14:I18 I26:I36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bc70300b-ea36-44a5-8949-8ea95d106fc4}">
+          <x14:cfRule type="dataBar" id="{0190ca56-9582-4144-8a7e-5311535f93bc}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5166,7 +5190,7 @@
           <xm:sqref>I2:I6 I9:I12 I20:I23 I38:I1048576 I18 I26:I36 I14:I16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e3eedc17-0557-4346-852d-3d614a565146}">
+          <x14:cfRule type="dataBar" id="{a0f2058a-4957-42f6-b88b-560e4a83d32f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5177,7 +5201,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I26 I14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7e02d5ec-c006-49e8-8cee-fb2fc76cf772}">
+          <x14:cfRule type="dataBar" id="{9272cd51-95d9-4384-bcf7-72c2587bba15}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5188,7 +5212,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d45fd17b-95e3-4699-8b83-cb2afeef5ef8}">
+          <x14:cfRule type="dataBar" id="{346fd514-81b1-4c5d-8cf4-b662b2f22947}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5199,7 +5223,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I35:I36 I16 I38:I39 I30:I32 I48:I49 I41:I46 I20:I23 I26 I14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{52fcc040-0974-4598-8fa2-039ac65f51f8}">
+          <x14:cfRule type="dataBar" id="{c3a4d738-1b55-4688-b063-1c951bce5ea6}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5210,7 +5234,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I28:I33 I16 I35:I36 I41:I49 I38:I39 I20:I23 I14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{be6f9de4-a6ed-4d6d-ad0a-b20138ee5636}">
+          <x14:cfRule type="dataBar" id="{4e03c9d6-0be3-4b05-b59a-aa947a351cb1}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5221,7 +5245,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I35:I36 I16 I38:I39 I28:I32 I48:I49 I41:I46 I20:I23 I14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{35eb46ab-5868-40a6-9abe-85654d2ee47e}">
+          <x14:cfRule type="dataBar" id="{5e1ad14b-9e97-461c-af97-e4fe11dec4fa}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5232,7 +5256,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I18 I26:I36 I14:I16 I38:I49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{433be48e-3cb8-4e63-88c8-3ebbdc18a869}">
+          <x14:cfRule type="dataBar" id="{d50af652-6eb1-4db8-b32c-6d8f96822659}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5243,7 +5267,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I38:I49 I14:I16 I28:I36 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a9cef11f-f284-4dbc-a7bb-95a9a164d0d8}">
+          <x14:cfRule type="dataBar" id="{2ebb1f94-8aef-4b27-b0bb-f05524f4c813}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5254,7 +5278,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I14:I18 I38:I49 I26:I36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7ebfde5b-1d44-4a5c-9d04-7ed20fc88af6}">
+          <x14:cfRule type="dataBar" id="{2eeec38e-c114-4de4-92ae-ba659346d99a}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5265,7 +5289,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dfef82c0-ed34-4091-a0ae-0ede5b2c5cf3}">
+          <x14:cfRule type="dataBar" id="{fab690a4-4f66-4f82-b945-ebe7dc6333ac}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5276,7 +5300,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I36 I38:I49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fc81d9b0-f6d8-4b92-b1ae-e00ae5cd5249}">
+          <x14:cfRule type="dataBar" id="{f2a55db1-ff6c-4750-bc9a-09f51b79be73}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -1773,10 +1773,10 @@
       </c>
       <c r="I4" s="16">
         <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148)</f>
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="J4" s="3">
-        <v>46146</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -4649,16 +4649,18 @@
       <c r="E147" s="34"/>
     </row>
     <row r="148" spans="1:5">
-      <c r="A148" s="31"/>
+      <c r="A148" s="31">
+        <v>46158</v>
+      </c>
       <c r="B148" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C148" s="27">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D148" s="21">
         <f>SUM(C3:C148)</f>
-        <v>-3069.15</v>
+        <v>-3059.15</v>
       </c>
       <c r="E148" s="34" t="s">
         <v>69</v>
@@ -4688,7 +4690,7 @@
       <c r="E151" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="40">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
     <mergeCell ref="A151:E151"/>
@@ -4714,7 +4716,6 @@
     <mergeCell ref="A133:A134"/>
     <mergeCell ref="A142:A143"/>
     <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A147:A148"/>
     <mergeCell ref="D3:D7"/>
     <mergeCell ref="D18:D19"/>
     <mergeCell ref="D23:D24"/>
@@ -4740,7 +4741,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9ff1a31f-2fb0-430d-aaad-6b70c6b70156}</x14:id>
+          <x14:id>{ca3f7337-8b20-4f8b-bf3d-0fc89392532e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4754,7 +4755,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{41cca850-ed86-43e2-b46b-2388aee97e54}</x14:id>
+          <x14:id>{cb529123-2615-4185-ae8a-1300ac46286c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4780,7 +4781,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b3c9d57e-a14f-4e84-a549-d39ad05a2160}</x14:id>
+          <x14:id>{fee40219-2945-41ef-a154-33749d15d7fd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4794,7 +4795,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{89230102-36ce-42cf-b24d-1f93ccdec507}</x14:id>
+          <x14:id>{7be60097-537f-4649-a969-153ebdf0b9e2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4808,7 +4809,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9d2f38b4-5a7f-437c-ab0b-ef4c6099f109}</x14:id>
+          <x14:id>{f43dddfa-b840-452c-9d20-0389af1d8f5d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4822,7 +4823,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d6fd2163-85f3-4668-8c82-ad21b23badb6}</x14:id>
+          <x14:id>{28413033-465a-4a00-bd43-3b8ae8fb9880}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4836,7 +4837,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{75a6a0bc-e9cb-4c9d-9377-6fe22cd88d72}</x14:id>
+          <x14:id>{fba0073a-1fd9-42a9-8504-037dc0d785aa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4850,7 +4851,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6317facf-61ab-47f3-8e4a-47334f96abb7}</x14:id>
+          <x14:id>{264687bd-ea52-4aed-b9b2-1a5c67f0c458}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4864,7 +4865,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{861259e2-c2b9-4276-867c-556f89cc1d92}</x14:id>
+          <x14:id>{373045db-0ba9-4016-b108-1115e5c86dda}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4878,7 +4879,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0190ca56-9582-4144-8a7e-5311535f93bc}</x14:id>
+          <x14:id>{0a20a6c5-2f6e-4bfa-b35f-66c1ffcf528e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4924,7 +4925,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a0f2058a-4957-42f6-b88b-560e4a83d32f}</x14:id>
+          <x14:id>{7ea99793-e682-4dfd-8532-3f0493029785}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4938,7 +4939,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9272cd51-95d9-4384-bcf7-72c2587bba15}</x14:id>
+          <x14:id>{f06d1e4f-e5e9-443b-a1e2-25a42889a3a2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4952,7 +4953,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{346fd514-81b1-4c5d-8cf4-b662b2f22947}</x14:id>
+          <x14:id>{f420fe5d-6ed5-49d2-be1f-ae00f500f2ae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4966,7 +4967,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c3a4d738-1b55-4688-b063-1c951bce5ea6}</x14:id>
+          <x14:id>{3aa6ec18-7073-428a-bc66-13c49b9cd056}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4980,7 +4981,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4e03c9d6-0be3-4b05-b59a-aa947a351cb1}</x14:id>
+          <x14:id>{cea24bfa-581a-4653-9be6-ae579dea1f0d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4994,7 +4995,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5e1ad14b-9e97-461c-af97-e4fe11dec4fa}</x14:id>
+          <x14:id>{37c1793a-2b9f-415c-800f-e2c7c30400fd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5008,7 +5009,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d50af652-6eb1-4db8-b32c-6d8f96822659}</x14:id>
+          <x14:id>{becb1def-d715-46d0-9ae8-7b7ac6a579ea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5022,7 +5023,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2ebb1f94-8aef-4b27-b0bb-f05524f4c813}</x14:id>
+          <x14:id>{127974dd-771d-4b3e-b4de-2e37cdc82447}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5036,7 +5037,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2eeec38e-c114-4de4-92ae-ba659346d99a}</x14:id>
+          <x14:id>{44fdc5ab-a5a3-445e-a957-985446d1498f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5050,7 +5051,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fab690a4-4f66-4f82-b945-ebe7dc6333ac}</x14:id>
+          <x14:id>{50053df3-a665-43f8-8dcd-4e11722aeac5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5064,7 +5065,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f2a55db1-ff6c-4750-bc9a-09f51b79be73}</x14:id>
+          <x14:id>{6039b81c-9e45-4583-88dd-4ecbbdcbfb2c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5072,13 +5073,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
+    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9ff1a31f-2fb0-430d-aaad-6b70c6b70156}">
+          <x14:cfRule type="dataBar" id="{ca3f7337-8b20-4f8b-bf3d-0fc89392532e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5089,7 +5090,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{41cca850-ed86-43e2-b46b-2388aee97e54}">
+          <x14:cfRule type="dataBar" id="{cb529123-2615-4185-ae8a-1300ac46286c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5100,7 +5101,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b3c9d57e-a14f-4e84-a549-d39ad05a2160}">
+          <x14:cfRule type="dataBar" id="{fee40219-2945-41ef-a154-33749d15d7fd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5113,7 +5114,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{89230102-36ce-42cf-b24d-1f93ccdec507}">
+          <x14:cfRule type="dataBar" id="{7be60097-537f-4649-a969-153ebdf0b9e2}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5124,7 +5125,7 @@
           <xm:sqref>I1:I12 I20:I24 I26:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9d2f38b4-5a7f-437c-ab0b-ef4c6099f109}">
+          <x14:cfRule type="dataBar" id="{f43dddfa-b840-452c-9d20-0389af1d8f5d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5135,7 +5136,7 @@
           <xm:sqref>I1:I12 I20:I23 I26:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d6fd2163-85f3-4668-8c82-ad21b23badb6}">
+          <x14:cfRule type="dataBar" id="{28413033-465a-4a00-bd43-3b8ae8fb9880}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5146,7 +5147,7 @@
           <xm:sqref>I1:I18 I26:I1048576 I20:I24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{75a6a0bc-e9cb-4c9d-9377-6fe22cd88d72}">
+          <x14:cfRule type="dataBar" id="{fba0073a-1fd9-42a9-8504-037dc0d785aa}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5157,7 +5158,7 @@
           <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6317facf-61ab-47f3-8e4a-47334f96abb7}">
+          <x14:cfRule type="dataBar" id="{264687bd-ea52-4aed-b9b2-1a5c67f0c458}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5168,7 +5169,7 @@
           <xm:sqref>I2 I50:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{861259e2-c2b9-4276-867c-556f89cc1d92}">
+          <x14:cfRule type="dataBar" id="{373045db-0ba9-4016-b108-1115e5c86dda}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5179,7 +5180,7 @@
           <xm:sqref>I2:I6 I9:I12 I20:I23 I38:I1048576 I14:I18 I26:I36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0190ca56-9582-4144-8a7e-5311535f93bc}">
+          <x14:cfRule type="dataBar" id="{0a20a6c5-2f6e-4bfa-b35f-66c1ffcf528e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5190,7 +5191,7 @@
           <xm:sqref>I2:I6 I9:I12 I20:I23 I38:I1048576 I18 I26:I36 I14:I16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a0f2058a-4957-42f6-b88b-560e4a83d32f}">
+          <x14:cfRule type="dataBar" id="{7ea99793-e682-4dfd-8532-3f0493029785}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5201,7 +5202,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I26 I14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9272cd51-95d9-4384-bcf7-72c2587bba15}">
+          <x14:cfRule type="dataBar" id="{f06d1e4f-e5e9-443b-a1e2-25a42889a3a2}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5212,7 +5213,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{346fd514-81b1-4c5d-8cf4-b662b2f22947}">
+          <x14:cfRule type="dataBar" id="{f420fe5d-6ed5-49d2-be1f-ae00f500f2ae}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5223,7 +5224,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I35:I36 I16 I38:I39 I30:I32 I48:I49 I41:I46 I20:I23 I26 I14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c3a4d738-1b55-4688-b063-1c951bce5ea6}">
+          <x14:cfRule type="dataBar" id="{3aa6ec18-7073-428a-bc66-13c49b9cd056}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5234,7 +5235,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I28:I33 I16 I35:I36 I41:I49 I38:I39 I20:I23 I14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4e03c9d6-0be3-4b05-b59a-aa947a351cb1}">
+          <x14:cfRule type="dataBar" id="{cea24bfa-581a-4653-9be6-ae579dea1f0d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5245,7 +5246,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I35:I36 I16 I38:I39 I28:I32 I48:I49 I41:I46 I20:I23 I14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5e1ad14b-9e97-461c-af97-e4fe11dec4fa}">
+          <x14:cfRule type="dataBar" id="{37c1793a-2b9f-415c-800f-e2c7c30400fd}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5256,7 +5257,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I18 I26:I36 I14:I16 I38:I49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d50af652-6eb1-4db8-b32c-6d8f96822659}">
+          <x14:cfRule type="dataBar" id="{becb1def-d715-46d0-9ae8-7b7ac6a579ea}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5267,7 +5268,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I38:I49 I14:I16 I28:I36 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2ebb1f94-8aef-4b27-b0bb-f05524f4c813}">
+          <x14:cfRule type="dataBar" id="{127974dd-771d-4b3e-b4de-2e37cdc82447}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5278,7 +5279,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I14:I18 I38:I49 I26:I36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2eeec38e-c114-4de4-92ae-ba659346d99a}">
+          <x14:cfRule type="dataBar" id="{44fdc5ab-a5a3-445e-a957-985446d1498f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5289,7 +5290,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fab690a4-4f66-4f82-b945-ebe7dc6333ac}">
+          <x14:cfRule type="dataBar" id="{50053df3-a665-43f8-8dcd-4e11722aeac5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5300,7 +5301,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I36 I38:I49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f2a55db1-ff6c-4750-bc9a-09f51b79be73}">
+          <x14:cfRule type="dataBar" id="{6039b81c-9e45-4583-88dd-4ecbbdcbfb2c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="114">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -123,147 +123,150 @@
     <t>moqi</t>
   </si>
   <si>
-    <t>↑2</t>
-  </si>
-  <si>
     <t>主板、硬盘、机箱</t>
   </si>
   <si>
     <t>rocksuger</t>
   </si>
   <si>
+    <t>物品、电费</t>
+  </si>
+  <si>
+    <t>SNHGY</t>
+  </si>
+  <si>
+    <t>Sz05</t>
+  </si>
+  <si>
+    <t>woshixiaoliu_ovo</t>
+  </si>
+  <si>
+    <t>10天群管理员</t>
+  </si>
+  <si>
+    <t>Y37MzZ_TrusT</t>
+  </si>
+  <si>
+    <t>潜影盒、鞘翅、凋灵骷髅头颅</t>
+  </si>
+  <si>
+    <t>cgh</t>
+  </si>
+  <si>
+    <t>匿名玩家</t>
+  </si>
+  <si>
+    <t>srdownb</t>
+  </si>
+  <si>
+    <t>火药、遗物</t>
+  </si>
+  <si>
+    <t>Xs1st_</t>
+  </si>
+  <si>
+    <t>Alhion_WWW</t>
+  </si>
+  <si>
+    <t>chunfeng</t>
+  </si>
+  <si>
+    <t>darkmoon114514</t>
+  </si>
+  <si>
+    <t>KAMI</t>
+  </si>
+  <si>
+    <t>3组烟花</t>
+  </si>
+  <si>
+    <t>91kk</t>
+  </si>
+  <si>
+    <t>faxi</t>
+  </si>
+  <si>
+    <t>捐樱花映射VIP</t>
+  </si>
+  <si>
+    <t>wybhh51811</t>
+  </si>
+  <si>
+    <t>樱花映射VIP</t>
+  </si>
+  <si>
+    <t>Goocheu_fox</t>
+  </si>
+  <si>
+    <t>5下界合金锭</t>
+  </si>
+  <si>
+    <t>Cr_Dragon</t>
+  </si>
+  <si>
+    <t>XL12</t>
+  </si>
+  <si>
+    <t>拍卖账号</t>
+  </si>
+  <si>
+    <t>Xiaoyingawa</t>
+  </si>
+  <si>
+    <t>↑20</t>
+  </si>
+  <si>
+    <t>鞘翅、TP、电费、羊毛、村民、TNT</t>
+  </si>
+  <si>
     <t>↓1</t>
   </si>
   <si>
-    <t>物品、电费</t>
-  </si>
-  <si>
-    <t>SNHGY</t>
-  </si>
-  <si>
-    <t>Sz05</t>
-  </si>
-  <si>
-    <t>woshixiaoliu_ovo</t>
-  </si>
-  <si>
-    <t>10天群管理员</t>
-  </si>
-  <si>
-    <t>Y37MzZ_TrusT</t>
-  </si>
-  <si>
-    <t>潜影盒、鞘翅、凋灵骷髅头颅</t>
-  </si>
-  <si>
-    <t>cgh</t>
-  </si>
-  <si>
-    <t>匿名玩家</t>
-  </si>
-  <si>
-    <t>srdownb</t>
-  </si>
-  <si>
-    <t>火药、遗物</t>
-  </si>
-  <si>
-    <t>Xs1st_</t>
-  </si>
-  <si>
-    <t>Alhion_WWW</t>
-  </si>
-  <si>
-    <t>chunfeng</t>
-  </si>
-  <si>
-    <t>darkmoon114514</t>
-  </si>
-  <si>
-    <t>KAMI</t>
-  </si>
-  <si>
-    <t>3组烟花</t>
-  </si>
-  <si>
-    <t>91kk</t>
-  </si>
-  <si>
-    <t>faxi</t>
-  </si>
-  <si>
-    <t>捐樱花映射VIP</t>
-  </si>
-  <si>
-    <t>wybhh51811</t>
-  </si>
-  <si>
-    <t>樱花映射VIP</t>
-  </si>
-  <si>
-    <t>Goocheu_fox</t>
-  </si>
-  <si>
-    <t>5下界合金锭</t>
-  </si>
-  <si>
-    <t>Cr_Dragon</t>
-  </si>
-  <si>
-    <t>XL12</t>
-  </si>
-  <si>
-    <t>拍卖账号</t>
-  </si>
-  <si>
-    <t>鞘翅、TP、电费、羊毛、村民、TNT</t>
+    <t>电费、经验</t>
   </si>
   <si>
     <t>Onion520</t>
   </si>
   <si>
-    <t>电费、经验</t>
+    <t>hanfengzunzhe</t>
+  </si>
+  <si>
+    <t>书架、紫珀块</t>
   </si>
   <si>
     <t>lhl</t>
   </si>
   <si>
-    <t>hanfengzunzhe</t>
-  </si>
-  <si>
-    <t>书架、紫珀块</t>
+    <t>电费</t>
   </si>
   <si>
     <t>xhf</t>
   </si>
   <si>
-    <t>电费</t>
+    <t>10书架</t>
   </si>
   <si>
     <t>YuSaMa1145</t>
   </si>
   <si>
-    <t>10书架</t>
-  </si>
-  <si>
     <t>Mo_Xuan_Yu</t>
   </si>
   <si>
+    <t>拍卖账号等</t>
+  </si>
+  <si>
     <t>xiaomin</t>
   </si>
   <si>
-    <t>拍卖账号等</t>
-  </si>
-  <si>
     <t>前哨战坐标等</t>
   </si>
   <si>
+    <t>主板、CPU、电源、机械硬盘</t>
+  </si>
+  <si>
     <t>A1TanJZ</t>
   </si>
   <si>
-    <t>主板、CPU、电源、机械硬盘</t>
-  </si>
-  <si>
     <t>海绵、电费、鞘翅、遗物</t>
   </si>
   <si>
@@ -279,10 +282,10 @@
     <t>2村民蛋</t>
   </si>
   <si>
+    <t>鞘翅、神镐</t>
+  </si>
+  <si>
     <t>QSWY_MC</t>
-  </si>
-  <si>
-    <t>鞘翅、神镐</t>
   </si>
   <si>
     <t>CHYunyou</t>
@@ -2026,9 +2029,6 @@
       <c r="J13" s="3">
         <v>46146</v>
       </c>
-      <c r="K13" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="17">
@@ -2043,13 +2043,13 @@
         <v>-780.05</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G14" s="15">
         <v>12</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I14" s="16">
         <f>SUM(C56,C46,C74)</f>
@@ -2058,9 +2058,6 @@
       <c r="J14" s="3">
         <v>45634</v>
       </c>
-      <c r="K14" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="17">
@@ -2077,13 +2074,13 @@
         <v>-660.05</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G15" s="15">
         <v>13</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I15" s="2">
         <f>SUM(C99,C109,C130,C137,C144)</f>
@@ -2092,9 +2089,6 @@
       <c r="J15" s="3">
         <v>46144</v>
       </c>
-      <c r="K15" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="17">
@@ -2115,7 +2109,7 @@
         <v>14</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I16" s="2">
         <f>SUM(C85:C85,C89,C96:C98,C117,C120,C122)</f>
@@ -2125,12 +2119,12 @@
         <v>46039</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:11">
       <c r="A17" s="17">
         <v>44953</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C17" s="13">
         <v>10</v>
@@ -2140,13 +2134,13 @@
         <v>-637.05</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G17" s="15">
         <v>15</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I17" s="2">
         <v>15</v>
@@ -2155,7 +2149,7 @@
         <v>45930</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:11">
       <c r="A18" s="17">
         <v>44958</v>
       </c>
@@ -2171,13 +2165,13 @@
         <v>-550.73</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G18" s="15">
         <v>16</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I18" s="16">
         <f>SUM(C40,C64)</f>
@@ -2187,10 +2181,10 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:11">
       <c r="A19" s="17"/>
       <c r="B19" s="22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C19" s="13">
         <v>1.32</v>
@@ -2201,7 +2195,7 @@
         <v>17</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I19" s="2">
         <f>SUM(C135,C139,C146)</f>
@@ -2211,7 +2205,7 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:11">
       <c r="A20" s="17">
         <v>44961</v>
       </c>
@@ -2230,7 +2224,7 @@
         <v>18</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I20" s="16">
         <v>10</v>
@@ -2239,7 +2233,7 @@
         <v>44953</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:11">
       <c r="A21" s="17">
         <v>45138</v>
       </c>
@@ -2255,13 +2249,13 @@
         <v>-428.73</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G21" s="15">
         <v>19</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I21" s="16">
         <v>10</v>
@@ -2270,12 +2264,12 @@
         <v>45234</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:11">
       <c r="A22" s="17">
         <v>45140</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C22" s="13">
         <v>0.11</v>
@@ -2289,7 +2283,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I22" s="16">
         <v>10</v>
@@ -2298,12 +2292,12 @@
         <v>45325</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:11">
       <c r="A23" s="17">
         <v>45141</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C23" s="13">
         <v>1.01</v>
@@ -2317,7 +2311,7 @@
         <v>21</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I23" s="16">
         <v>10</v>
@@ -2326,7 +2320,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:11">
       <c r="A24" s="17"/>
       <c r="B24" s="8" t="s">
         <v>13</v>
@@ -2336,13 +2330,13 @@
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G24" s="15">
         <v>22</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I24" s="2">
         <v>10</v>
@@ -2351,7 +2345,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:11">
       <c r="A25" s="17">
         <v>45160</v>
       </c>
@@ -2370,7 +2364,7 @@
         <v>23</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I25" s="16">
         <v>10</v>
@@ -2379,12 +2373,12 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:11">
       <c r="A26" s="17">
         <v>45234</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C26" s="13">
         <v>10</v>
@@ -2394,13 +2388,13 @@
         <v>-415.61</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G26">
         <v>24</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I26" s="2">
         <v>8</v>
@@ -2409,7 +2403,7 @@
         <v>45860</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:11">
       <c r="A27" s="17"/>
       <c r="B27" s="8"/>
       <c r="C27" s="18">
@@ -2417,13 +2411,13 @@
       </c>
       <c r="D27" s="23"/>
       <c r="E27" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G27">
         <v>25</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I27" s="2">
         <v>7.33</v>
@@ -2432,7 +2426,7 @@
         <v>45907</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:11">
       <c r="A28" s="17">
         <v>45249</v>
       </c>
@@ -2447,13 +2441,13 @@
         <v>-400.11</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G28">
         <v>26</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I28" s="16">
         <f>SUM(C82,C84,C94)</f>
@@ -2463,7 +2457,7 @@
         <v>45861</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:11">
       <c r="A29" s="17">
         <v>45305</v>
       </c>
@@ -2482,7 +2476,7 @@
         <v>27</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I29" s="2">
         <v>6</v>
@@ -2491,12 +2485,12 @@
         <v>45868</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:11">
       <c r="A30" s="17">
         <v>45325</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C30" s="13">
         <v>10</v>
@@ -2506,22 +2500,25 @@
         <v>-340.11</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G30">
         <v>28</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="I30" s="16">
-        <v>5.02</v>
+        <v>60</v>
+      </c>
+      <c r="I30" s="2">
+        <v>5.04</v>
       </c>
       <c r="J30" s="3">
-        <v>44787</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>46160</v>
+      </c>
+      <c r="K30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="17">
         <v>45341</v>
       </c>
@@ -2542,16 +2539,19 @@
         <v>29</v>
       </c>
       <c r="H31" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I31" s="16">
+        <v>5.02</v>
+      </c>
+      <c r="J31" s="3">
+        <v>44787</v>
+      </c>
+      <c r="K31" t="s">
         <v>63</v>
       </c>
-      <c r="I31" s="16">
-        <v>5</v>
-      </c>
-      <c r="J31" s="3">
-        <v>45634</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="17">
         <v>45368</v>
       </c>
@@ -2575,13 +2575,16 @@
         <v>65</v>
       </c>
       <c r="I32" s="16">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="J32" s="3">
-        <v>45707</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>45634</v>
+      </c>
+      <c r="K32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="17">
         <v>45387</v>
       </c>
@@ -2604,14 +2607,17 @@
       <c r="H33" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="I33" s="2">
-        <v>4</v>
+      <c r="I33" s="16">
+        <v>4.15</v>
       </c>
       <c r="J33" s="3">
-        <v>45885</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+        <v>45707</v>
+      </c>
+      <c r="K33" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" s="17">
         <v>45394</v>
       </c>
@@ -2631,18 +2637,20 @@
       <c r="G34">
         <v>32</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" s="10" t="s">
         <v>70</v>
       </c>
       <c r="I34" s="2">
-        <f>SUM(C100,C108)</f>
         <v>4</v>
       </c>
       <c r="J34" s="3">
-        <v>45934</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>45885</v>
+      </c>
+      <c r="K34" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" s="17">
         <v>45396</v>
       </c>
@@ -2662,17 +2670,21 @@
       <c r="G35">
         <v>33</v>
       </c>
-      <c r="H35" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" s="16">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+      <c r="H35" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I35" s="2">
+        <f>SUM(C100,C108)</f>
+        <v>4</v>
+      </c>
+      <c r="J35" s="3">
+        <v>45934</v>
+      </c>
+      <c r="K35" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="17">
         <v>45403</v>
       </c>
@@ -2691,16 +2703,19 @@
         <v>34</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="I36" s="16">
         <v>3</v>
       </c>
-      <c r="J36" s="3">
-        <v>45500</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+      <c r="J36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K36" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" s="17">
         <v>45403</v>
       </c>
@@ -2723,14 +2738,17 @@
       <c r="H37" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I37" s="2">
-        <v>2.5</v>
+      <c r="I37" s="16">
+        <v>3</v>
       </c>
       <c r="J37" s="3">
-        <v>45976</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+        <v>45500</v>
+      </c>
+      <c r="K37" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" s="17">
         <v>45412</v>
       </c>
@@ -2751,17 +2769,19 @@
         <v>36</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="I38" s="16">
-        <f>SUM(C35,C33:C33)</f>
-        <v>2.18</v>
+        <v>75</v>
+      </c>
+      <c r="I38" s="2">
+        <v>2.5</v>
       </c>
       <c r="J38" s="3">
-        <v>45396</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>45976</v>
+      </c>
+      <c r="K38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" s="17">
         <v>45417</v>
       </c>
@@ -2776,27 +2796,31 @@
         <v>-194.72</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G39" s="15">
         <v>37</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="I39" s="16">
-        <v>2</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <f>SUM(C35,C33:C33)</f>
+        <v>2.18</v>
+      </c>
+      <c r="J39" s="3">
+        <v>45396</v>
+      </c>
+      <c r="K39" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" s="17">
         <v>45421</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C40" s="13">
         <v>5</v>
@@ -2811,17 +2835,20 @@
       <c r="G40" s="15">
         <v>38</v>
       </c>
-      <c r="H40" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I40" s="2">
+      <c r="H40" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" s="16">
         <v>2</v>
       </c>
-      <c r="J40" s="3">
-        <v>45907</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+      <c r="J40" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K40" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" s="17">
         <v>45478</v>
       </c>
@@ -2840,17 +2867,20 @@
       <c r="G41">
         <v>39</v>
       </c>
-      <c r="H41" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="I41" s="16">
-        <v>1.32</v>
+      <c r="H41" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I41" s="2">
+        <v>2</v>
       </c>
       <c r="J41" s="3">
-        <v>44958</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <v>45907</v>
+      </c>
+      <c r="K41" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" s="17">
         <v>45494</v>
       </c>
@@ -2865,22 +2895,25 @@
         <v>-1915.27</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G42" s="15">
         <v>40</v>
       </c>
-      <c r="H42" s="10" t="s">
-        <v>20</v>
+      <c r="H42" s="24" t="s">
+        <v>41</v>
       </c>
       <c r="I42" s="16">
-        <v>1.28</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>1.32</v>
+      </c>
+      <c r="J42" s="3">
+        <v>44958</v>
+      </c>
+      <c r="K42" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" s="17"/>
       <c r="B43" s="8" t="s">
         <v>13</v>
@@ -2890,22 +2923,25 @@
       </c>
       <c r="D43" s="23"/>
       <c r="E43" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G43">
         <v>41</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="I43" s="16">
-        <v>1.01</v>
-      </c>
-      <c r="J43" s="3">
-        <v>45141</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
+        <v>1.28</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K43" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" s="25">
         <v>45495</v>
       </c>
@@ -2920,22 +2956,25 @@
         <v>-1907.27</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G44">
         <v>42</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="I44" s="16">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="J44" s="3">
-        <v>45794</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>45141</v>
+      </c>
+      <c r="K44" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" s="25">
         <v>45496</v>
       </c>
@@ -2954,41 +2993,47 @@
         <v>43</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="I45" s="16">
-        <v>0.55</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
+        <v>1</v>
+      </c>
+      <c r="J45" s="3">
+        <v>45794</v>
+      </c>
+      <c r="K45" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" s="29"/>
       <c r="B46" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C46" s="27">
         <v>3</v>
       </c>
       <c r="D46" s="30"/>
       <c r="E46" s="28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G46">
         <v>44</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="I46" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="J46" s="3">
-        <v>45697</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
+        <v>0.55</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K46" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" s="17">
         <v>45497</v>
       </c>
@@ -3011,19 +3056,22 @@
       <c r="H47" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="I47" s="2">
+      <c r="I47" s="16">
         <v>0.5</v>
       </c>
       <c r="J47" s="3">
-        <v>45885</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
+        <v>45697</v>
+      </c>
+      <c r="K47" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" s="25">
         <v>45500</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C48" s="27">
         <v>3</v>
@@ -3037,16 +3085,19 @@
         <v>46</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="I48" s="16">
-        <v>0.11</v>
+        <v>86</v>
+      </c>
+      <c r="I48" s="2">
+        <v>0.5</v>
       </c>
       <c r="J48" s="3">
-        <v>45140</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+        <v>45885</v>
+      </c>
+      <c r="K48" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" s="31"/>
       <c r="B49" s="26" t="s">
         <v>15</v>
@@ -3062,16 +3113,19 @@
         <v>47</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="I49" s="16">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="J49" s="3">
-        <v>44213</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
+        <v>45140</v>
+      </c>
+      <c r="K49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" s="25">
         <v>45505</v>
       </c>
@@ -3086,10 +3140,25 @@
         <v>-1856.27</v>
       </c>
       <c r="E50" s="28" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+        <v>87</v>
+      </c>
+      <c r="G50">
+        <v>48</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="J50" s="3">
+        <v>44213</v>
+      </c>
+      <c r="K50" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" s="25">
         <v>45507</v>
       </c>
@@ -3107,7 +3176,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:11">
       <c r="A52" s="31"/>
       <c r="B52" s="26" t="s">
         <v>25</v>
@@ -3117,10 +3186,10 @@
       </c>
       <c r="D52" s="30"/>
       <c r="E52" s="28" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53" s="25">
         <v>45508</v>
       </c>
@@ -3138,7 +3207,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:11">
       <c r="A54" s="31"/>
       <c r="B54" s="26" t="s">
         <v>17</v>
@@ -3149,7 +3218,7 @@
       <c r="D54" s="30"/>
       <c r="E54" s="28"/>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:11">
       <c r="A55" s="25">
         <v>45509</v>
       </c>
@@ -3162,13 +3231,13 @@
         <v>-1737.27</v>
       </c>
       <c r="E55" s="28" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
       <c r="A56" s="31"/>
       <c r="B56" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C56" s="27">
         <v>10</v>
@@ -3176,7 +3245,7 @@
       <c r="D56" s="30"/>
       <c r="E56" s="28"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:11">
       <c r="A57" s="25">
         <v>45510</v>
       </c>
@@ -3191,10 +3260,10 @@
         <v>-1697.27</v>
       </c>
       <c r="E57" s="28" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" s="25">
         <v>45525</v>
       </c>
@@ -3210,10 +3279,10 @@
         <v>-1625.27</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
       <c r="A59" s="25">
         <v>45525</v>
       </c>
@@ -3228,10 +3297,10 @@
         <v>-1619.27</v>
       </c>
       <c r="E59" s="28" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60" s="25">
         <v>45549</v>
       </c>
@@ -3249,7 +3318,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:11">
       <c r="A61" s="29"/>
       <c r="B61" s="33" t="s">
         <v>17</v>
@@ -3259,10 +3328,10 @@
       </c>
       <c r="D61" s="30"/>
       <c r="E61" s="28" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62" s="31">
         <v>45551</v>
       </c>
@@ -3278,7 +3347,7 @@
       </c>
       <c r="E62" s="28"/>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:11">
       <c r="A63" s="25">
         <v>45552</v>
       </c>
@@ -3294,12 +3363,12 @@
       </c>
       <c r="E63" s="28"/>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:11">
       <c r="A64" s="25">
         <v>45555</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C64" s="27">
         <v>6</v>
@@ -3320,7 +3389,7 @@
       </c>
       <c r="D65" s="30"/>
       <c r="E65" s="28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3372,7 +3441,7 @@
         <v>-1389.27</v>
       </c>
       <c r="E68" s="28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3450,7 +3519,7 @@
         <v>45634</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C73" s="27">
         <v>5</v>
@@ -3466,14 +3535,14 @@
     <row r="74" spans="1:5">
       <c r="A74" s="17"/>
       <c r="B74" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C74" s="27">
         <v>10</v>
       </c>
       <c r="D74" s="30"/>
       <c r="E74" s="28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3481,7 +3550,7 @@
         <v>45649</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C75" s="27">
         <v>10</v>
@@ -3507,7 +3576,7 @@
         <v>-1304.27</v>
       </c>
       <c r="E76" s="28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3533,7 +3602,7 @@
         <v>45697</v>
       </c>
       <c r="B78" s="33" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C78" s="27">
         <v>0.5</v>
@@ -3549,7 +3618,7 @@
         <v>45707</v>
       </c>
       <c r="B79" s="33" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C79" s="27">
         <v>4.15</v>
@@ -3565,7 +3634,7 @@
         <v>45794</v>
       </c>
       <c r="B80" s="33" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C80" s="27">
         <v>1</v>
@@ -3597,7 +3666,7 @@
         <v>45844</v>
       </c>
       <c r="B82" s="33" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C82" s="27">
         <v>2.48</v>
@@ -3613,7 +3682,7 @@
         <v>45860</v>
       </c>
       <c r="B83" s="33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C83" s="27">
         <v>8</v>
@@ -3629,7 +3698,7 @@
         <v>45861</v>
       </c>
       <c r="B84" s="33" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C84" s="27">
         <v>0.5</v>
@@ -3645,7 +3714,7 @@
         <v>45865</v>
       </c>
       <c r="B85" s="33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C85" s="27">
         <v>3</v>
@@ -3677,7 +3746,7 @@
         <v>45868</v>
       </c>
       <c r="B87" s="33" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C87" s="27">
         <v>6</v>
@@ -3687,7 +3756,7 @@
         <v>-1237.97</v>
       </c>
       <c r="E87" s="28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -3713,7 +3782,7 @@
         <v>45878</v>
       </c>
       <c r="B89" s="33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C89" s="27">
         <v>0.01</v>
@@ -3739,7 +3808,7 @@
         <v>-1206.96</v>
       </c>
       <c r="E90" s="34" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -3765,7 +3834,7 @@
         <v>45885</v>
       </c>
       <c r="B92" s="33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C92" s="27">
         <v>0.5</v>
@@ -3779,7 +3848,7 @@
     <row r="93" spans="1:5">
       <c r="A93" s="17"/>
       <c r="B93" s="33" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C93" s="27">
         <v>6</v>
@@ -3790,7 +3859,7 @@
     <row r="94" spans="1:5">
       <c r="A94" s="17"/>
       <c r="B94" s="33" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C94" s="27">
         <v>4</v>
@@ -3821,7 +3890,7 @@
         <v>45894</v>
       </c>
       <c r="B96" s="33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C96" s="27">
         <v>1</v>
@@ -3837,7 +3906,7 @@
         <v>45905</v>
       </c>
       <c r="B97" s="33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C97" s="27">
         <v>7.33</v>
@@ -3853,7 +3922,7 @@
         <v>45907</v>
       </c>
       <c r="B98" s="33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C98" s="27">
         <v>2</v>
@@ -3867,7 +3936,7 @@
     <row r="99" spans="1:5">
       <c r="A99" s="31"/>
       <c r="B99" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C99" s="27">
         <v>2</v>
@@ -3878,7 +3947,7 @@
     <row r="100" spans="1:5">
       <c r="A100" s="31"/>
       <c r="B100" s="33" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C100" s="27">
         <v>2</v>
@@ -3900,7 +3969,7 @@
     <row r="102" spans="1:5">
       <c r="A102" s="31"/>
       <c r="B102" s="33" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C102" s="27">
         <v>2</v>
@@ -3921,7 +3990,7 @@
         <v>-1298.13</v>
       </c>
       <c r="E103" s="34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -3963,7 +4032,7 @@
         <v>45930</v>
       </c>
       <c r="B106" s="33" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C106" s="27">
         <v>15</v>
@@ -3993,7 +4062,7 @@
     <row r="108" spans="1:5">
       <c r="A108" s="31"/>
       <c r="B108" s="33" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C108" s="27">
         <v>2</v>
@@ -4007,7 +4076,7 @@
     <row r="109" spans="1:5">
       <c r="A109" s="31"/>
       <c r="B109" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C109" s="27">
         <v>0.45</v>
@@ -4033,7 +4102,7 @@
         <v>-1202.68</v>
       </c>
       <c r="E110" s="34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -4083,7 +4152,7 @@
         <v>-1131.68</v>
       </c>
       <c r="E113" s="34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -4101,7 +4170,7 @@
         <v>-1094.68</v>
       </c>
       <c r="E114" s="34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -4109,7 +4178,7 @@
         <v>45976</v>
       </c>
       <c r="B115" s="33" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C115" s="27">
         <v>2.5</v>
@@ -4135,7 +4204,7 @@
         <v>-1072.18</v>
       </c>
       <c r="E116" s="34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -4143,7 +4212,7 @@
         <v>45990</v>
       </c>
       <c r="B117" s="33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C117" s="27">
         <v>1</v>
@@ -4153,7 +4222,7 @@
         <v>-1071.18</v>
       </c>
       <c r="E117" s="34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -4187,7 +4256,7 @@
         <v>-1045.18</v>
       </c>
       <c r="E119" s="34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -4195,7 +4264,7 @@
         <v>46031</v>
       </c>
       <c r="B120" s="33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C120" s="27">
         <v>2</v>
@@ -4221,7 +4290,7 @@
         <v>-977.18</v>
       </c>
       <c r="E121" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -4229,7 +4298,7 @@
         <v>46039</v>
       </c>
       <c r="B122" s="33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C122" s="27">
         <v>1</v>
@@ -4255,7 +4324,7 @@
         <v>-969.18</v>
       </c>
       <c r="E123" s="34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -4305,7 +4374,7 @@
         <v>-917.18</v>
       </c>
       <c r="E126" s="34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -4341,7 +4410,7 @@
         <v>-834.18</v>
       </c>
       <c r="E128" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -4357,7 +4426,7 @@
         <v>-804.18</v>
       </c>
       <c r="E129" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -4365,7 +4434,7 @@
         <v>46069</v>
       </c>
       <c r="B130" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C130" s="27">
         <v>5</v>
@@ -4389,13 +4458,13 @@
         <v>-791.18</v>
       </c>
       <c r="E131" s="34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="31"/>
       <c r="B132" s="33" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C132" s="27">
         <v>10</v>
@@ -4441,7 +4510,7 @@
         <v>46074</v>
       </c>
       <c r="B135" s="33" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C135" s="27">
         <v>1.5</v>
@@ -4475,7 +4544,7 @@
         <v>46085</v>
       </c>
       <c r="B137" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C137" s="27">
         <v>10</v>
@@ -4501,7 +4570,7 @@
         <v>-656.36</v>
       </c>
       <c r="E138" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -4509,7 +4578,7 @@
         <v>46130</v>
       </c>
       <c r="B139" s="33" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C139" s="27">
         <v>3</v>
@@ -4533,7 +4602,7 @@
         <v>-3151.15</v>
       </c>
       <c r="E140" s="34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -4589,7 +4658,7 @@
         <v>46144</v>
       </c>
       <c r="B144" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C144" s="27">
         <v>1</v>
@@ -4605,7 +4674,7 @@
         <v>46145</v>
       </c>
       <c r="B145" s="33" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C145" s="27">
         <v>10</v>
@@ -4615,13 +4684,13 @@
         <v>-3105.15</v>
       </c>
       <c r="E145" s="34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="31"/>
       <c r="B146" s="33" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C146" s="27">
         <v>6</v>
@@ -4649,7 +4718,7 @@
       <c r="E147" s="34"/>
     </row>
     <row r="148" spans="1:5">
-      <c r="A148" s="31">
+      <c r="A148" s="25">
         <v>46158</v>
       </c>
       <c r="B148" s="33" t="s">
@@ -4667,10 +4736,19 @@
       </c>
     </row>
     <row r="149" spans="1:5">
-      <c r="A149" s="25"/>
-      <c r="B149" s="33"/>
-      <c r="C149" s="27"/>
-      <c r="D149" s="21"/>
+      <c r="A149" s="25">
+        <v>46160</v>
+      </c>
+      <c r="B149" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="C149" s="27">
+        <v>5.04</v>
+      </c>
+      <c r="D149" s="21">
+        <f>SUM(C3:C149)</f>
+        <v>-3054.11</v>
+      </c>
       <c r="E149" s="34"/>
     </row>
     <row r="150" ht="14.25" spans="1:5">
@@ -4682,7 +4760,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B151" s="41"/>
       <c r="C151" s="41"/>
@@ -4741,7 +4819,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ca3f7337-8b20-4f8b-bf3d-0fc89392532e}</x14:id>
+          <x14:id>{0b29485f-bd08-4cd6-bd45-dba2328b1f11}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4755,7 +4833,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cb529123-2615-4185-ae8a-1300ac46286c}</x14:id>
+          <x14:id>{690d3e6e-4505-43f4-a25c-823005d0a858}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4781,7 +4859,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fee40219-2945-41ef-a154-33749d15d7fd}</x14:id>
+          <x14:id>{2a41adf2-2db3-4cf6-aa7a-308ea3a2133d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4795,7 +4873,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7be60097-537f-4649-a969-153ebdf0b9e2}</x14:id>
+          <x14:id>{9767feb8-9cdd-42ed-855f-c0b1edc8600a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4809,7 +4887,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f43dddfa-b840-452c-9d20-0389af1d8f5d}</x14:id>
+          <x14:id>{d5ccb50b-c433-43d0-87e7-d471e645ede0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4823,7 +4901,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{28413033-465a-4a00-bd43-3b8ae8fb9880}</x14:id>
+          <x14:id>{37180e11-4451-4020-8b55-f787f2baf81e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4837,12 +4915,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fba0073a-1fd9-42a9-8504-037dc0d785aa}</x14:id>
+          <x14:id>{d511bdef-69e4-4d25-9c35-6568b6fcb24f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2 I50:I1048576">
+  <conditionalFormatting sqref="I2 I51:I1048576 I30">
     <cfRule type="dataBar" priority="49">
       <dataBar>
         <cfvo type="min"/>
@@ -4851,12 +4929,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{264687bd-ea52-4aed-b9b2-1a5c67f0c458}</x14:id>
+          <x14:id>{6e58f400-c314-4155-a9f5-c73f0b435b4f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6 I9:I12 I20:I23 I38:I1048576 I14:I18 I26:I36">
+  <conditionalFormatting sqref="I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I14:I18">
     <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
@@ -4865,12 +4943,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{373045db-0ba9-4016-b108-1115e5c86dda}</x14:id>
+          <x14:id>{9369830c-1952-48ef-9f69-03a4542470fd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6 I9:I12 I20:I23 I38:I1048576 I18 I26:I36 I14:I16">
+  <conditionalFormatting sqref="I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I14:I16 I18">
     <cfRule type="dataBar" priority="30">
       <dataBar>
         <cfvo type="min"/>
@@ -4879,7 +4957,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0a20a6c5-2f6e-4bfa-b35f-66c1ffcf528e}</x14:id>
+          <x14:id>{19a35f9b-7b53-456f-94e0-bdabd2ec3b48}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4916,7 +4994,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9 I11:I12 I28 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I26 I14">
+  <conditionalFormatting sqref="I3:I6 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40">
     <cfRule type="dataBar" priority="36">
       <dataBar>
         <cfvo type="min"/>
@@ -4925,12 +5003,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7ea99793-e682-4dfd-8532-3f0493029785}</x14:id>
+          <x14:id>{7066d8e0-0ce3-4220-98ec-23c3f947f511}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9 I11:I12 I28 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I14">
+  <conditionalFormatting sqref="I3:I6 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40">
     <cfRule type="dataBar" priority="37">
       <dataBar>
         <cfvo type="min"/>
@@ -4939,12 +5017,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f06d1e4f-e5e9-443b-a1e2-25a42889a3a2}</x14:id>
+          <x14:id>{f30f10af-0d6a-4467-b923-982a8206ac00}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9 I11:I12 I28 I18 I35:I36 I16 I38:I39 I30:I32 I48:I49 I41:I46 I20:I23 I26 I14">
+  <conditionalFormatting sqref="I3:I6 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37">
     <cfRule type="dataBar" priority="34">
       <dataBar>
         <cfvo type="min"/>
@@ -4953,12 +5031,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f420fe5d-6ed5-49d2-be1f-ae00f500f2ae}</x14:id>
+          <x14:id>{8c9476b5-146a-4427-ab22-b41fca1a4429}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I12 I26 I18 I28:I33 I16 I35:I36 I41:I49 I38:I39 I20:I23 I14">
+  <conditionalFormatting sqref="I3:I6 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50 I36:I37 I31:I34">
     <cfRule type="dataBar" priority="32">
       <dataBar>
         <cfvo type="min"/>
@@ -4967,12 +5045,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3aa6ec18-7073-428a-bc66-13c49b9cd056}</x14:id>
+          <x14:id>{75590e2c-7eb7-43c9-b824-07a5efd4ad5f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I12 I26 I18 I35:I36 I16 I38:I39 I28:I32 I48:I49 I41:I46 I20:I23 I14">
+  <conditionalFormatting sqref="I3:I6 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37">
     <cfRule type="dataBar" priority="33">
       <dataBar>
         <cfvo type="min"/>
@@ -4981,12 +5059,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cea24bfa-581a-4653-9be6-ae579dea1f0d}</x14:id>
+          <x14:id>{73a77893-f295-410c-a1c4-059fdc987fb2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I12 I20:I23 I18 I26:I36 I14:I16 I38:I49">
+  <conditionalFormatting sqref="I3:I6 I9:I12 I20:I23 I18 I26:I29 I14:I16 I39:I50 I31:I37">
     <cfRule type="dataBar" priority="28">
       <dataBar>
         <cfvo type="min"/>
@@ -4995,12 +5073,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{37c1793a-2b9f-415c-800f-e2c7c30400fd}</x14:id>
+          <x14:id>{e454e790-6218-4581-87b8-5874d0e3a72d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I12 I26 I18 I38:I49 I14:I16 I28:I36 I20:I23">
+  <conditionalFormatting sqref="I3:I6 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29 I39:I50 I31:I37">
     <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
@@ -5009,12 +5087,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{becb1def-d715-46d0-9ae8-7b7ac6a579ea}</x14:id>
+          <x14:id>{ec64f6cc-1d94-47d2-9206-0e0cf7f4fc30}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I12 I20:I23 I14:I18 I38:I49 I26:I36">
+  <conditionalFormatting sqref="I3:I6 I9:I12 I20:I23 I14:I18 I26:I29 I31:I37 I39:I50">
     <cfRule type="dataBar" priority="27">
       <dataBar>
         <cfvo type="min"/>
@@ -5023,12 +5101,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{127974dd-771d-4b3e-b4de-2e37cdc82447}</x14:id>
+          <x14:id>{e2274de6-035c-4ea0-9030-e5f686f4b934}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I7 I9:I12 I20:I23 I14:I18 I26:I49">
+  <conditionalFormatting sqref="I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I31:I50">
     <cfRule type="dataBar" priority="24">
       <dataBar>
         <cfvo type="min"/>
@@ -5037,12 +5115,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{44fdc5ab-a5a3-445e-a957-985446d1498f}</x14:id>
+          <x14:id>{a606e63d-2867-4f23-840d-fbb5dfdc91f9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I7 I9:I12 I20:I23 I14:I18 I26:I36 I38:I49">
+  <conditionalFormatting sqref="I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I39:I50 I31:I37">
     <cfRule type="dataBar" priority="25">
       <dataBar>
         <cfvo type="min"/>
@@ -5051,12 +5129,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{50053df3-a665-43f8-8dcd-4e11722aeac5}</x14:id>
+          <x14:id>{d4946e87-e0a5-4e65-9627-e0471e6d35b3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I24 I26:I49">
+  <conditionalFormatting sqref="I3:I24 I26:I29 I31:I50">
     <cfRule type="dataBar" priority="20">
       <dataBar>
         <cfvo type="min"/>
@@ -5065,7 +5143,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6039b81c-9e45-4583-88dd-4ecbbdcbfb2c}</x14:id>
+          <x14:id>{c5c00115-49c0-495b-a74d-52e207203cb6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5079,7 +5157,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ca3f7337-8b20-4f8b-bf3d-0fc89392532e}">
+          <x14:cfRule type="dataBar" id="{0b29485f-bd08-4cd6-bd45-dba2328b1f11}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5090,7 +5168,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cb529123-2615-4185-ae8a-1300ac46286c}">
+          <x14:cfRule type="dataBar" id="{690d3e6e-4505-43f4-a25c-823005d0a858}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5101,7 +5179,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fee40219-2945-41ef-a154-33749d15d7fd}">
+          <x14:cfRule type="dataBar" id="{2a41adf2-2db3-4cf6-aa7a-308ea3a2133d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5114,7 +5192,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7be60097-537f-4649-a969-153ebdf0b9e2}">
+          <x14:cfRule type="dataBar" id="{9767feb8-9cdd-42ed-855f-c0b1edc8600a}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5125,7 +5203,7 @@
           <xm:sqref>I1:I12 I20:I24 I26:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f43dddfa-b840-452c-9d20-0389af1d8f5d}">
+          <x14:cfRule type="dataBar" id="{d5ccb50b-c433-43d0-87e7-d471e645ede0}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5136,7 +5214,7 @@
           <xm:sqref>I1:I12 I20:I23 I26:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{28413033-465a-4a00-bd43-3b8ae8fb9880}">
+          <x14:cfRule type="dataBar" id="{37180e11-4451-4020-8b55-f787f2baf81e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5147,7 +5225,7 @@
           <xm:sqref>I1:I18 I26:I1048576 I20:I24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fba0073a-1fd9-42a9-8504-037dc0d785aa}">
+          <x14:cfRule type="dataBar" id="{d511bdef-69e4-4d25-9c35-6568b6fcb24f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5158,7 +5236,7 @@
           <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{264687bd-ea52-4aed-b9b2-1a5c67f0c458}">
+          <x14:cfRule type="dataBar" id="{6e58f400-c314-4155-a9f5-c73f0b435b4f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5166,10 +5244,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2 I50:I1048576</xm:sqref>
+          <xm:sqref>I2 I51:I1048576 I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{373045db-0ba9-4016-b108-1115e5c86dda}">
+          <x14:cfRule type="dataBar" id="{9369830c-1952-48ef-9f69-03a4542470fd}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5177,10 +5255,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I6 I9:I12 I20:I23 I38:I1048576 I14:I18 I26:I36</xm:sqref>
+          <xm:sqref>I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0a20a6c5-2f6e-4bfa-b35f-66c1ffcf528e}">
+          <x14:cfRule type="dataBar" id="{19a35f9b-7b53-456f-94e0-bdabd2ec3b48}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5188,10 +5266,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I6 I9:I12 I20:I23 I38:I1048576 I18 I26:I36 I14:I16</xm:sqref>
+          <xm:sqref>I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I14:I16 I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7ea99793-e682-4dfd-8532-3f0493029785}">
+          <x14:cfRule type="dataBar" id="{7066d8e0-0ce3-4220-98ec-23c3f947f511}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5199,10 +5277,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I26 I14</xm:sqref>
+          <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f06d1e4f-e5e9-443b-a1e2-25a42889a3a2}">
+          <x14:cfRule type="dataBar" id="{f30f10af-0d6a-4467-b923-982a8206ac00}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5210,10 +5288,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I38:I39 I41:I46 I30:I32 I35:I36 I48:I49 I20:I23 I14</xm:sqref>
+          <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f420fe5d-6ed5-49d2-be1f-ae00f500f2ae}">
+          <x14:cfRule type="dataBar" id="{8c9476b5-146a-4427-ab22-b41fca1a4429}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5221,10 +5299,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I35:I36 I16 I38:I39 I30:I32 I48:I49 I41:I46 I20:I23 I26 I14</xm:sqref>
+          <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3aa6ec18-7073-428a-bc66-13c49b9cd056}">
+          <x14:cfRule type="dataBar" id="{75590e2c-7eb7-43c9-b824-07a5efd4ad5f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5232,10 +5310,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I12 I26 I18 I28:I33 I16 I35:I36 I41:I49 I38:I39 I20:I23 I14</xm:sqref>
+          <xm:sqref>I3:I6 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50 I36:I37 I31:I34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cea24bfa-581a-4653-9be6-ae579dea1f0d}">
+          <x14:cfRule type="dataBar" id="{73a77893-f295-410c-a1c4-059fdc987fb2}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5243,10 +5321,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I12 I26 I18 I35:I36 I16 I38:I39 I28:I32 I48:I49 I41:I46 I20:I23 I14</xm:sqref>
+          <xm:sqref>I3:I6 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{37c1793a-2b9f-415c-800f-e2c7c30400fd}">
+          <x14:cfRule type="dataBar" id="{e454e790-6218-4581-87b8-5874d0e3a72d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5254,10 +5332,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I12 I20:I23 I18 I26:I36 I14:I16 I38:I49</xm:sqref>
+          <xm:sqref>I3:I6 I9:I12 I20:I23 I18 I26:I29 I14:I16 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{becb1def-d715-46d0-9ae8-7b7ac6a579ea}">
+          <x14:cfRule type="dataBar" id="{ec64f6cc-1d94-47d2-9206-0e0cf7f4fc30}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5265,10 +5343,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I12 I26 I18 I38:I49 I14:I16 I28:I36 I20:I23</xm:sqref>
+          <xm:sqref>I3:I6 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{127974dd-771d-4b3e-b4de-2e37cdc82447}">
+          <x14:cfRule type="dataBar" id="{e2274de6-035c-4ea0-9030-e5f686f4b934}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5276,10 +5354,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I12 I20:I23 I14:I18 I38:I49 I26:I36</xm:sqref>
+          <xm:sqref>I3:I6 I9:I12 I20:I23 I14:I18 I26:I29 I31:I37 I39:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{44fdc5ab-a5a3-445e-a957-985446d1498f}">
+          <x14:cfRule type="dataBar" id="{a606e63d-2867-4f23-840d-fbb5dfdc91f9}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5287,10 +5365,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I49</xm:sqref>
+          <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I31:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{50053df3-a665-43f8-8dcd-4e11722aeac5}">
+          <x14:cfRule type="dataBar" id="{d4946e87-e0a5-4e65-9627-e0471e6d35b3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5298,10 +5376,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I36 I38:I49</xm:sqref>
+          <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6039b81c-9e45-4583-88dd-4ecbbdcbfb2c}">
+          <x14:cfRule type="dataBar" id="{c5c00115-49c0-495b-a74d-52e207203cb6}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5309,7 +5387,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I24 I26:I49</xm:sqref>
+          <xm:sqref>I3:I24 I26:I29 I31:I50</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="114">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -1664,7 +1664,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K151"/>
+  <dimension ref="A1:K152"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -1775,11 +1775,11 @@
         <v>15</v>
       </c>
       <c r="I4" s="16">
-        <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148)</f>
-        <v>447</v>
+        <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150)</f>
+        <v>457</v>
       </c>
       <c r="J4" s="3">
-        <v>46158</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -4751,27 +4751,45 @@
       </c>
       <c r="E149" s="34"/>
     </row>
-    <row r="150" ht="14.25" spans="1:5">
-      <c r="A150" s="37"/>
-      <c r="B150" s="38"/>
-      <c r="C150" s="39"/>
-      <c r="D150" s="39"/>
-      <c r="E150" s="40"/>
-    </row>
-    <row r="151" spans="1:5">
-      <c r="A151" s="41" t="s">
+    <row r="150" spans="1:5">
+      <c r="A150" s="25">
+        <v>46164</v>
+      </c>
+      <c r="B150" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C150" s="27">
+        <v>10</v>
+      </c>
+      <c r="D150" s="21">
+        <f>SUM(C3:C150)</f>
+        <v>-3044.11</v>
+      </c>
+      <c r="E150" s="34" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="151" ht="14.25" spans="1:5">
+      <c r="A151" s="37"/>
+      <c r="B151" s="38"/>
+      <c r="C151" s="39"/>
+      <c r="D151" s="39"/>
+      <c r="E151" s="40"/>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="B151" s="41"/>
-      <c r="C151" s="41"/>
-      <c r="D151" s="41"/>
-      <c r="E151" s="41"/>
+      <c r="B152" s="41"/>
+      <c r="C152" s="41"/>
+      <c r="D152" s="41"/>
+      <c r="E152" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="40">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A151:E151"/>
+    <mergeCell ref="A152:E152"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A23:A24"/>
@@ -4819,7 +4837,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0b29485f-bd08-4cd6-bd45-dba2328b1f11}</x14:id>
+          <x14:id>{53843d58-6c7f-4490-8c2b-27f9149e5d53}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4833,12 +4851,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{690d3e6e-4505-43f4-a25c-823005d0a858}</x14:id>
+          <x14:id>{83d675d8-8006-4175-84d0-f85520d11f3b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D150 D152:D1048576">
+  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D151 D153:D1048576">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="min"/>
@@ -4859,7 +4877,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2a41adf2-2db3-4cf6-aa7a-308ea3a2133d}</x14:id>
+          <x14:id>{8fa0fc19-538d-4667-bdd2-402d6bcd61d1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4873,7 +4891,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9767feb8-9cdd-42ed-855f-c0b1edc8600a}</x14:id>
+          <x14:id>{fd3b6ede-4a80-4960-9a74-e4083121ad96}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4887,7 +4905,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d5ccb50b-c433-43d0-87e7-d471e645ede0}</x14:id>
+          <x14:id>{c5c8f9e4-50ac-4341-a287-df1bfde493a5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4901,7 +4919,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{37180e11-4451-4020-8b55-f787f2baf81e}</x14:id>
+          <x14:id>{d1596149-b951-4de8-b201-1b89835f4b96}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4915,7 +4933,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d511bdef-69e4-4d25-9c35-6568b6fcb24f}</x14:id>
+          <x14:id>{ca861ad9-b800-45a7-8ba7-afd253e8ab9b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4929,7 +4947,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6e58f400-c314-4155-a9f5-c73f0b435b4f}</x14:id>
+          <x14:id>{c0ac978f-faca-4191-bb7c-ded42332b06c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4943,12 +4961,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9369830c-1952-48ef-9f69-03a4542470fd}</x14:id>
+          <x14:id>{ff187304-2c3c-4dbb-a307-3b8d19cf5a06}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I14:I16 I18">
+  <conditionalFormatting sqref="I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I18 I14:I16">
     <cfRule type="dataBar" priority="30">
       <dataBar>
         <cfvo type="min"/>
@@ -4957,7 +4975,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{19a35f9b-7b53-456f-94e0-bdabd2ec3b48}</x14:id>
+          <x14:id>{5fe64bf4-0b16-4633-9237-5020dce9ae44}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5003,7 +5021,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7066d8e0-0ce3-4220-98ec-23c3f947f511}</x14:id>
+          <x14:id>{475691f5-1118-4652-9688-3933a47eb5bf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5017,7 +5035,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f30f10af-0d6a-4467-b923-982a8206ac00}</x14:id>
+          <x14:id>{064a0126-d955-4ea5-88ec-84d1f9f1e26f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5031,7 +5049,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8c9476b5-146a-4427-ab22-b41fca1a4429}</x14:id>
+          <x14:id>{46c37741-1621-4ef6-968d-48102a58fce3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5045,7 +5063,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{75590e2c-7eb7-43c9-b824-07a5efd4ad5f}</x14:id>
+          <x14:id>{9c1bb44b-4c1b-49be-8127-3bb900eef6c8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5059,7 +5077,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{73a77893-f295-410c-a1c4-059fdc987fb2}</x14:id>
+          <x14:id>{37c8993e-93af-400e-84ed-14ca14d10675}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5073,7 +5091,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e454e790-6218-4581-87b8-5874d0e3a72d}</x14:id>
+          <x14:id>{1af46bab-52bd-4e8c-85be-8208ccacd0af}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5087,7 +5105,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ec64f6cc-1d94-47d2-9206-0e0cf7f4fc30}</x14:id>
+          <x14:id>{88b2752b-1afd-42a0-8095-6cfbbed8a98e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5101,7 +5119,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e2274de6-035c-4ea0-9030-e5f686f4b934}</x14:id>
+          <x14:id>{493387fc-1612-407d-89a1-ef6bbf3690f5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5115,7 +5133,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a606e63d-2867-4f23-840d-fbb5dfdc91f9}</x14:id>
+          <x14:id>{d2cb2116-8a81-4c7d-892c-56cc83bbedd3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5129,7 +5147,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d4946e87-e0a5-4e65-9627-e0471e6d35b3}</x14:id>
+          <x14:id>{07f5fe19-d351-480b-a802-b4f4c78f566d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5143,7 +5161,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c5c00115-49c0-495b-a74d-52e207203cb6}</x14:id>
+          <x14:id>{b1ed2012-629e-4dce-bc70-4f157a8d2e5f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5157,7 +5175,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0b29485f-bd08-4cd6-bd45-dba2328b1f11}">
+          <x14:cfRule type="dataBar" id="{53843d58-6c7f-4490-8c2b-27f9149e5d53}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5168,7 +5186,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{690d3e6e-4505-43f4-a25c-823005d0a858}">
+          <x14:cfRule type="dataBar" id="{83d675d8-8006-4175-84d0-f85520d11f3b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5179,7 +5197,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2a41adf2-2db3-4cf6-aa7a-308ea3a2133d}">
+          <x14:cfRule type="dataBar" id="{8fa0fc19-538d-4667-bdd2-402d6bcd61d1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5192,7 +5210,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9767feb8-9cdd-42ed-855f-c0b1edc8600a}">
+          <x14:cfRule type="dataBar" id="{fd3b6ede-4a80-4960-9a74-e4083121ad96}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5203,7 +5221,7 @@
           <xm:sqref>I1:I12 I20:I24 I26:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d5ccb50b-c433-43d0-87e7-d471e645ede0}">
+          <x14:cfRule type="dataBar" id="{c5c8f9e4-50ac-4341-a287-df1bfde493a5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5214,7 +5232,7 @@
           <xm:sqref>I1:I12 I20:I23 I26:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{37180e11-4451-4020-8b55-f787f2baf81e}">
+          <x14:cfRule type="dataBar" id="{d1596149-b951-4de8-b201-1b89835f4b96}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5225,7 +5243,7 @@
           <xm:sqref>I1:I18 I26:I1048576 I20:I24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d511bdef-69e4-4d25-9c35-6568b6fcb24f}">
+          <x14:cfRule type="dataBar" id="{ca861ad9-b800-45a7-8ba7-afd253e8ab9b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5236,7 +5254,7 @@
           <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6e58f400-c314-4155-a9f5-c73f0b435b4f}">
+          <x14:cfRule type="dataBar" id="{c0ac978f-faca-4191-bb7c-ded42332b06c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5247,7 +5265,7 @@
           <xm:sqref>I2 I51:I1048576 I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9369830c-1952-48ef-9f69-03a4542470fd}">
+          <x14:cfRule type="dataBar" id="{ff187304-2c3c-4dbb-a307-3b8d19cf5a06}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5258,7 +5276,7 @@
           <xm:sqref>I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{19a35f9b-7b53-456f-94e0-bdabd2ec3b48}">
+          <x14:cfRule type="dataBar" id="{5fe64bf4-0b16-4633-9237-5020dce9ae44}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5266,10 +5284,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I14:I16 I18</xm:sqref>
+          <xm:sqref>I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I18 I14:I16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7066d8e0-0ce3-4220-98ec-23c3f947f511}">
+          <x14:cfRule type="dataBar" id="{475691f5-1118-4652-9688-3933a47eb5bf}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5280,7 +5298,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f30f10af-0d6a-4467-b923-982a8206ac00}">
+          <x14:cfRule type="dataBar" id="{064a0126-d955-4ea5-88ec-84d1f9f1e26f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5291,7 +5309,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8c9476b5-146a-4427-ab22-b41fca1a4429}">
+          <x14:cfRule type="dataBar" id="{46c37741-1621-4ef6-968d-48102a58fce3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5302,7 +5320,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{75590e2c-7eb7-43c9-b824-07a5efd4ad5f}">
+          <x14:cfRule type="dataBar" id="{9c1bb44b-4c1b-49be-8127-3bb900eef6c8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5313,7 +5331,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50 I36:I37 I31:I34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{73a77893-f295-410c-a1c4-059fdc987fb2}">
+          <x14:cfRule type="dataBar" id="{37c8993e-93af-400e-84ed-14ca14d10675}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5324,7 +5342,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e454e790-6218-4581-87b8-5874d0e3a72d}">
+          <x14:cfRule type="dataBar" id="{1af46bab-52bd-4e8c-85be-8208ccacd0af}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5335,7 +5353,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I18 I26:I29 I14:I16 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ec64f6cc-1d94-47d2-9206-0e0cf7f4fc30}">
+          <x14:cfRule type="dataBar" id="{88b2752b-1afd-42a0-8095-6cfbbed8a98e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5346,7 +5364,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e2274de6-035c-4ea0-9030-e5f686f4b934}">
+          <x14:cfRule type="dataBar" id="{493387fc-1612-407d-89a1-ef6bbf3690f5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5357,7 +5375,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I14:I18 I26:I29 I31:I37 I39:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a606e63d-2867-4f23-840d-fbb5dfdc91f9}">
+          <x14:cfRule type="dataBar" id="{d2cb2116-8a81-4c7d-892c-56cc83bbedd3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5368,7 +5386,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I31:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d4946e87-e0a5-4e65-9627-e0471e6d35b3}">
+          <x14:cfRule type="dataBar" id="{07f5fe19-d351-480b-a802-b4f4c78f566d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5379,7 +5397,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c5c00115-49c0-495b-a74d-52e207203cb6}">
+          <x14:cfRule type="dataBar" id="{b1ed2012-629e-4dce-bc70-4f157a8d2e5f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -1776,10 +1776,10 @@
       </c>
       <c r="I4" s="16">
         <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150)</f>
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="J4" s="3">
-        <v>46164</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -4753,23 +4753,23 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="25">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="B150" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C150" s="27">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D150" s="21">
         <f>SUM(C3:C150)</f>
-        <v>-3044.11</v>
+        <v>-3034.11</v>
       </c>
       <c r="E150" s="34" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="151" ht="14.25" spans="1:5">
+    <row r="151" spans="1:5">
       <c r="A151" s="37"/>
       <c r="B151" s="38"/>
       <c r="C151" s="39"/>
@@ -4837,7 +4837,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{53843d58-6c7f-4490-8c2b-27f9149e5d53}</x14:id>
+          <x14:id>{43c85be9-54f6-40c9-ae77-22fd367253e1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4851,7 +4851,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{83d675d8-8006-4175-84d0-f85520d11f3b}</x14:id>
+          <x14:id>{dc0761b5-a979-42cc-8415-0f47e2f3220f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4877,7 +4877,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8fa0fc19-538d-4667-bdd2-402d6bcd61d1}</x14:id>
+          <x14:id>{c1dbd120-c9fb-42d2-bcbf-74dfd27bf9b5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4891,7 +4891,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fd3b6ede-4a80-4960-9a74-e4083121ad96}</x14:id>
+          <x14:id>{765f9aee-4d77-4927-bccf-2469725987e1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4905,7 +4905,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c5c8f9e4-50ac-4341-a287-df1bfde493a5}</x14:id>
+          <x14:id>{ebbe8c5c-7008-463d-b8be-446da2b62818}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4919,7 +4919,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d1596149-b951-4de8-b201-1b89835f4b96}</x14:id>
+          <x14:id>{798c81e2-ab45-4535-9850-61005dbb6071}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4933,7 +4933,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ca861ad9-b800-45a7-8ba7-afd253e8ab9b}</x14:id>
+          <x14:id>{c4cec568-7678-42a1-b537-c2d7d5f1daed}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4947,7 +4947,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c0ac978f-faca-4191-bb7c-ded42332b06c}</x14:id>
+          <x14:id>{416a41bf-aa28-4940-a540-3f0e8ecdbee8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4961,7 +4961,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ff187304-2c3c-4dbb-a307-3b8d19cf5a06}</x14:id>
+          <x14:id>{370cab5f-92d9-4e60-a0ee-c929137c2584}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4975,7 +4975,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5fe64bf4-0b16-4633-9237-5020dce9ae44}</x14:id>
+          <x14:id>{dc241099-46f7-406d-8590-c235b5d6ca40}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5021,7 +5021,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{475691f5-1118-4652-9688-3933a47eb5bf}</x14:id>
+          <x14:id>{808a4bd6-7ca6-45a5-82a7-69648ea8ff68}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5035,7 +5035,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{064a0126-d955-4ea5-88ec-84d1f9f1e26f}</x14:id>
+          <x14:id>{29ea0459-d21e-4fab-bb91-694ea0653c5b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5049,7 +5049,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{46c37741-1621-4ef6-968d-48102a58fce3}</x14:id>
+          <x14:id>{efc66dbb-23ad-4112-a5b5-8a87fdc8fff2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5063,7 +5063,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9c1bb44b-4c1b-49be-8127-3bb900eef6c8}</x14:id>
+          <x14:id>{fcc7e5d4-4ada-45f1-bc0e-d97e54fc2571}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5077,7 +5077,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{37c8993e-93af-400e-84ed-14ca14d10675}</x14:id>
+          <x14:id>{a4aa093b-5005-481e-9aa1-0d1430b6d76e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5091,7 +5091,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1af46bab-52bd-4e8c-85be-8208ccacd0af}</x14:id>
+          <x14:id>{f248b541-ba81-4873-8c13-c4227fdf23c6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5105,7 +5105,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{88b2752b-1afd-42a0-8095-6cfbbed8a98e}</x14:id>
+          <x14:id>{6cce7c7f-df32-42b3-ad7b-2051cf165a04}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5119,7 +5119,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{493387fc-1612-407d-89a1-ef6bbf3690f5}</x14:id>
+          <x14:id>{b1da287d-1aa5-42a6-8ade-407998bf2971}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5133,7 +5133,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d2cb2116-8a81-4c7d-892c-56cc83bbedd3}</x14:id>
+          <x14:id>{e85f78b0-af4f-4518-ad58-bae150bd5b72}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5147,7 +5147,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{07f5fe19-d351-480b-a802-b4f4c78f566d}</x14:id>
+          <x14:id>{621a7c7b-7679-4350-adc6-d829048060c9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5161,7 +5161,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b1ed2012-629e-4dce-bc70-4f157a8d2e5f}</x14:id>
+          <x14:id>{8de6c89f-cc47-4545-bbfb-f5c5c945cf3e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5169,13 +5169,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
+    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{53843d58-6c7f-4490-8c2b-27f9149e5d53}">
+          <x14:cfRule type="dataBar" id="{43c85be9-54f6-40c9-ae77-22fd367253e1}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5186,7 +5186,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{83d675d8-8006-4175-84d0-f85520d11f3b}">
+          <x14:cfRule type="dataBar" id="{dc0761b5-a979-42cc-8415-0f47e2f3220f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5197,7 +5197,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8fa0fc19-538d-4667-bdd2-402d6bcd61d1}">
+          <x14:cfRule type="dataBar" id="{c1dbd120-c9fb-42d2-bcbf-74dfd27bf9b5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5210,7 +5210,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fd3b6ede-4a80-4960-9a74-e4083121ad96}">
+          <x14:cfRule type="dataBar" id="{765f9aee-4d77-4927-bccf-2469725987e1}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5221,7 +5221,7 @@
           <xm:sqref>I1:I12 I20:I24 I26:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c5c8f9e4-50ac-4341-a287-df1bfde493a5}">
+          <x14:cfRule type="dataBar" id="{ebbe8c5c-7008-463d-b8be-446da2b62818}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5232,7 +5232,7 @@
           <xm:sqref>I1:I12 I20:I23 I26:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d1596149-b951-4de8-b201-1b89835f4b96}">
+          <x14:cfRule type="dataBar" id="{798c81e2-ab45-4535-9850-61005dbb6071}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5243,7 +5243,7 @@
           <xm:sqref>I1:I18 I26:I1048576 I20:I24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ca861ad9-b800-45a7-8ba7-afd253e8ab9b}">
+          <x14:cfRule type="dataBar" id="{c4cec568-7678-42a1-b537-c2d7d5f1daed}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5254,7 +5254,7 @@
           <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c0ac978f-faca-4191-bb7c-ded42332b06c}">
+          <x14:cfRule type="dataBar" id="{416a41bf-aa28-4940-a540-3f0e8ecdbee8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5265,7 +5265,7 @@
           <xm:sqref>I2 I51:I1048576 I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ff187304-2c3c-4dbb-a307-3b8d19cf5a06}">
+          <x14:cfRule type="dataBar" id="{370cab5f-92d9-4e60-a0ee-c929137c2584}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5276,7 +5276,7 @@
           <xm:sqref>I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5fe64bf4-0b16-4633-9237-5020dce9ae44}">
+          <x14:cfRule type="dataBar" id="{dc241099-46f7-406d-8590-c235b5d6ca40}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5287,7 +5287,7 @@
           <xm:sqref>I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I18 I14:I16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{475691f5-1118-4652-9688-3933a47eb5bf}">
+          <x14:cfRule type="dataBar" id="{808a4bd6-7ca6-45a5-82a7-69648ea8ff68}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5298,7 +5298,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{064a0126-d955-4ea5-88ec-84d1f9f1e26f}">
+          <x14:cfRule type="dataBar" id="{29ea0459-d21e-4fab-bb91-694ea0653c5b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5309,7 +5309,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{46c37741-1621-4ef6-968d-48102a58fce3}">
+          <x14:cfRule type="dataBar" id="{efc66dbb-23ad-4112-a5b5-8a87fdc8fff2}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5320,7 +5320,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9c1bb44b-4c1b-49be-8127-3bb900eef6c8}">
+          <x14:cfRule type="dataBar" id="{fcc7e5d4-4ada-45f1-bc0e-d97e54fc2571}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5331,7 +5331,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50 I36:I37 I31:I34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{37c8993e-93af-400e-84ed-14ca14d10675}">
+          <x14:cfRule type="dataBar" id="{a4aa093b-5005-481e-9aa1-0d1430b6d76e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5342,7 +5342,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1af46bab-52bd-4e8c-85be-8208ccacd0af}">
+          <x14:cfRule type="dataBar" id="{f248b541-ba81-4873-8c13-c4227fdf23c6}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5353,7 +5353,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I18 I26:I29 I14:I16 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{88b2752b-1afd-42a0-8095-6cfbbed8a98e}">
+          <x14:cfRule type="dataBar" id="{6cce7c7f-df32-42b3-ad7b-2051cf165a04}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5364,7 +5364,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{493387fc-1612-407d-89a1-ef6bbf3690f5}">
+          <x14:cfRule type="dataBar" id="{b1da287d-1aa5-42a6-8ade-407998bf2971}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5375,7 +5375,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I14:I18 I26:I29 I31:I37 I39:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d2cb2116-8a81-4c7d-892c-56cc83bbedd3}">
+          <x14:cfRule type="dataBar" id="{e85f78b0-af4f-4518-ad58-bae150bd5b72}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5386,7 +5386,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I31:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{07f5fe19-d351-480b-a802-b4f4c78f566d}">
+          <x14:cfRule type="dataBar" id="{621a7c7b-7679-4350-adc6-d829048060c9}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5397,7 +5397,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b1ed2012-629e-4dce-bc70-4f157a8d2e5f}">
+          <x14:cfRule type="dataBar" id="{8de6c89f-cc47-4545-bbfb-f5c5c945cf3e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="25600" windowHeight="12200"/>
   </bookViews>
   <sheets>
     <sheet name="收支与赞助鸣谢" sheetId="1" r:id="rId1"/>
@@ -1665,20 +1665,20 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:K152"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15.625" customWidth="1"/>
-    <col min="2" max="2" width="18.2583333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="9.375" customWidth="1"/>
-    <col min="5" max="5" width="33.125" customWidth="1"/>
-    <col min="7" max="7" width="5.125" customWidth="1"/>
-    <col min="8" max="8" width="18.2583333333333" customWidth="1"/>
-    <col min="9" max="9" width="12.875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="5.125" customWidth="1"/>
-    <col min="13" max="13" width="15.625"/>
-    <col min="14" max="14" width="13.375"/>
+    <col min="1" max="1" width="15.6272727272727" customWidth="1"/>
+    <col min="2" max="2" width="18.2545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
+    <col min="4" max="4" width="9.37272727272727" customWidth="1"/>
+    <col min="5" max="5" width="33.1272727272727" customWidth="1"/>
+    <col min="7" max="7" width="5.12727272727273" customWidth="1"/>
+    <col min="8" max="8" width="18.2545454545455" customWidth="1"/>
+    <col min="9" max="9" width="12.8727272727273" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.6272727272727" style="3" customWidth="1"/>
+    <col min="11" max="11" width="5.12727272727273" customWidth="1"/>
+    <col min="13" max="13" width="15.6272727272727"/>
+    <col min="14" max="14" width="13.3727272727273"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1776,10 +1776,10 @@
       </c>
       <c r="I4" s="16">
         <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150)</f>
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="J4" s="3">
-        <v>46171</v>
+        <v>46172</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -4753,17 +4753,17 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="25">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B150" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C150" s="27">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D150" s="21">
         <f>SUM(C3:C150)</f>
-        <v>-3034.11</v>
+        <v>-3029.11</v>
       </c>
       <c r="E150" s="34" t="s">
         <v>69</v>
@@ -4837,7 +4837,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{43c85be9-54f6-40c9-ae77-22fd367253e1}</x14:id>
+          <x14:id>{933a67b1-b783-4472-a201-cc1adadbd18c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4851,7 +4851,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc0761b5-a979-42cc-8415-0f47e2f3220f}</x14:id>
+          <x14:id>{2765d310-c09b-46f4-ae8b-ece295989681}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4877,7 +4877,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c1dbd120-c9fb-42d2-bcbf-74dfd27bf9b5}</x14:id>
+          <x14:id>{6308037a-4baa-47de-8208-bef380ecb8de}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4891,7 +4891,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{765f9aee-4d77-4927-bccf-2469725987e1}</x14:id>
+          <x14:id>{5022821e-5e3c-4957-abfc-d9103766c321}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4905,7 +4905,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ebbe8c5c-7008-463d-b8be-446da2b62818}</x14:id>
+          <x14:id>{567bb189-816b-40cc-a940-daefca7effaf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4919,7 +4919,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{798c81e2-ab45-4535-9850-61005dbb6071}</x14:id>
+          <x14:id>{43d5de2d-cbfd-4e77-a7d2-b56e484403dd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4933,7 +4933,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c4cec568-7678-42a1-b537-c2d7d5f1daed}</x14:id>
+          <x14:id>{d714ee69-4a3f-4997-abca-0440933933a6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4947,7 +4947,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{416a41bf-aa28-4940-a540-3f0e8ecdbee8}</x14:id>
+          <x14:id>{9e78b118-b1cd-41a5-9956-db77f4cbb70f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4961,7 +4961,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{370cab5f-92d9-4e60-a0ee-c929137c2584}</x14:id>
+          <x14:id>{47dc8066-b89b-4eb0-a0ba-37f3c8c9c0df}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4975,7 +4975,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc241099-46f7-406d-8590-c235b5d6ca40}</x14:id>
+          <x14:id>{f50f5e17-8b7c-401b-9915-14801edfab77}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5021,7 +5021,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{808a4bd6-7ca6-45a5-82a7-69648ea8ff68}</x14:id>
+          <x14:id>{f769efde-be6f-4057-9d1d-0f1ebced81b5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5035,7 +5035,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{29ea0459-d21e-4fab-bb91-694ea0653c5b}</x14:id>
+          <x14:id>{58e7a7d0-0dd2-43bf-819d-8ccaf5f88c70}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5049,7 +5049,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{efc66dbb-23ad-4112-a5b5-8a87fdc8fff2}</x14:id>
+          <x14:id>{10d9494e-dc33-4cde-b058-e16e50a6f92b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5063,7 +5063,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fcc7e5d4-4ada-45f1-bc0e-d97e54fc2571}</x14:id>
+          <x14:id>{a87a8ad9-e4bd-4e7a-a479-2dcf3e08d1ed}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5077,7 +5077,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a4aa093b-5005-481e-9aa1-0d1430b6d76e}</x14:id>
+          <x14:id>{99475709-b4b7-4cbd-9143-e85138cc85d0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5091,7 +5091,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f248b541-ba81-4873-8c13-c4227fdf23c6}</x14:id>
+          <x14:id>{8f224365-8639-4dba-88de-10bd2fc78c4f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5105,7 +5105,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6cce7c7f-df32-42b3-ad7b-2051cf165a04}</x14:id>
+          <x14:id>{b03ec369-f31f-4b3f-96e0-2cf3a1056e20}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5119,7 +5119,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b1da287d-1aa5-42a6-8ade-407998bf2971}</x14:id>
+          <x14:id>{c6151f24-42bc-4784-9404-3d87987e74f2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5133,7 +5133,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e85f78b0-af4f-4518-ad58-bae150bd5b72}</x14:id>
+          <x14:id>{c1ad63b6-c4f5-4787-b3a2-beb2b05fc4da}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5147,7 +5147,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{621a7c7b-7679-4350-adc6-d829048060c9}</x14:id>
+          <x14:id>{261ec224-735b-4838-83ee-3889e12eafb2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5161,7 +5161,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8de6c89f-cc47-4545-bbfb-f5c5c945cf3e}</x14:id>
+          <x14:id>{4a5b4603-8ea2-41b7-bc8f-9decfb59c6fa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5169,13 +5169,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
+    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{43c85be9-54f6-40c9-ae77-22fd367253e1}">
+          <x14:cfRule type="dataBar" id="{933a67b1-b783-4472-a201-cc1adadbd18c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5186,7 +5186,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dc0761b5-a979-42cc-8415-0f47e2f3220f}">
+          <x14:cfRule type="dataBar" id="{2765d310-c09b-46f4-ae8b-ece295989681}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5197,7 +5197,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c1dbd120-c9fb-42d2-bcbf-74dfd27bf9b5}">
+          <x14:cfRule type="dataBar" id="{6308037a-4baa-47de-8208-bef380ecb8de}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5210,7 +5210,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{765f9aee-4d77-4927-bccf-2469725987e1}">
+          <x14:cfRule type="dataBar" id="{5022821e-5e3c-4957-abfc-d9103766c321}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5221,7 +5221,7 @@
           <xm:sqref>I1:I12 I20:I24 I26:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ebbe8c5c-7008-463d-b8be-446da2b62818}">
+          <x14:cfRule type="dataBar" id="{567bb189-816b-40cc-a940-daefca7effaf}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5232,7 +5232,7 @@
           <xm:sqref>I1:I12 I20:I23 I26:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{798c81e2-ab45-4535-9850-61005dbb6071}">
+          <x14:cfRule type="dataBar" id="{43d5de2d-cbfd-4e77-a7d2-b56e484403dd}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5243,7 +5243,7 @@
           <xm:sqref>I1:I18 I26:I1048576 I20:I24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c4cec568-7678-42a1-b537-c2d7d5f1daed}">
+          <x14:cfRule type="dataBar" id="{d714ee69-4a3f-4997-abca-0440933933a6}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5254,7 +5254,7 @@
           <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{416a41bf-aa28-4940-a540-3f0e8ecdbee8}">
+          <x14:cfRule type="dataBar" id="{9e78b118-b1cd-41a5-9956-db77f4cbb70f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5265,7 +5265,7 @@
           <xm:sqref>I2 I51:I1048576 I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{370cab5f-92d9-4e60-a0ee-c929137c2584}">
+          <x14:cfRule type="dataBar" id="{47dc8066-b89b-4eb0-a0ba-37f3c8c9c0df}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5276,7 +5276,7 @@
           <xm:sqref>I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dc241099-46f7-406d-8590-c235b5d6ca40}">
+          <x14:cfRule type="dataBar" id="{f50f5e17-8b7c-401b-9915-14801edfab77}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5287,7 +5287,7 @@
           <xm:sqref>I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I18 I14:I16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{808a4bd6-7ca6-45a5-82a7-69648ea8ff68}">
+          <x14:cfRule type="dataBar" id="{f769efde-be6f-4057-9d1d-0f1ebced81b5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5298,7 +5298,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{29ea0459-d21e-4fab-bb91-694ea0653c5b}">
+          <x14:cfRule type="dataBar" id="{58e7a7d0-0dd2-43bf-819d-8ccaf5f88c70}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5309,7 +5309,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{efc66dbb-23ad-4112-a5b5-8a87fdc8fff2}">
+          <x14:cfRule type="dataBar" id="{10d9494e-dc33-4cde-b058-e16e50a6f92b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5320,7 +5320,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fcc7e5d4-4ada-45f1-bc0e-d97e54fc2571}">
+          <x14:cfRule type="dataBar" id="{a87a8ad9-e4bd-4e7a-a479-2dcf3e08d1ed}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5331,7 +5331,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50 I36:I37 I31:I34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a4aa093b-5005-481e-9aa1-0d1430b6d76e}">
+          <x14:cfRule type="dataBar" id="{99475709-b4b7-4cbd-9143-e85138cc85d0}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5342,7 +5342,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f248b541-ba81-4873-8c13-c4227fdf23c6}">
+          <x14:cfRule type="dataBar" id="{8f224365-8639-4dba-88de-10bd2fc78c4f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5353,7 +5353,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I18 I26:I29 I14:I16 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6cce7c7f-df32-42b3-ad7b-2051cf165a04}">
+          <x14:cfRule type="dataBar" id="{b03ec369-f31f-4b3f-96e0-2cf3a1056e20}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5364,7 +5364,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b1da287d-1aa5-42a6-8ade-407998bf2971}">
+          <x14:cfRule type="dataBar" id="{c6151f24-42bc-4784-9404-3d87987e74f2}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5375,7 +5375,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I14:I18 I26:I29 I31:I37 I39:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e85f78b0-af4f-4518-ad58-bae150bd5b72}">
+          <x14:cfRule type="dataBar" id="{c1ad63b6-c4f5-4787-b3a2-beb2b05fc4da}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5386,7 +5386,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I31:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{621a7c7b-7679-4350-adc6-d829048060c9}">
+          <x14:cfRule type="dataBar" id="{261ec224-735b-4838-83ee-3889e12eafb2}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5397,7 +5397,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8de6c89f-cc47-4545-bbfb-f5c5c945cf3e}">
+          <x14:cfRule type="dataBar" id="{4a5b4603-8ea2-41b7-bc8f-9decfb59c6fa}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5417,11 +5417,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
-    <col min="2" max="2" width="8.125" customWidth="1"/>
-    <col min="3" max="3" width="8.875" customWidth="1"/>
+    <col min="2" max="2" width="8.12727272727273" customWidth="1"/>
+    <col min="3" max="3" width="8.87272727272727" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12200"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="收支与赞助鸣谢" sheetId="1" r:id="rId1"/>
@@ -1665,20 +1665,20 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:K152"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="15.6272727272727" customWidth="1"/>
-    <col min="2" max="2" width="18.2545454545455" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
-    <col min="4" max="4" width="9.37272727272727" customWidth="1"/>
-    <col min="5" max="5" width="33.1272727272727" customWidth="1"/>
-    <col min="7" max="7" width="5.12727272727273" customWidth="1"/>
-    <col min="8" max="8" width="18.2545454545455" customWidth="1"/>
-    <col min="9" max="9" width="12.8727272727273" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.6272727272727" style="3" customWidth="1"/>
-    <col min="11" max="11" width="5.12727272727273" customWidth="1"/>
-    <col min="13" max="13" width="15.6272727272727"/>
-    <col min="14" max="14" width="13.3727272727273"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="18.2583333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="9.375" customWidth="1"/>
+    <col min="5" max="5" width="33.125" customWidth="1"/>
+    <col min="7" max="7" width="5.125" customWidth="1"/>
+    <col min="8" max="8" width="18.2583333333333" customWidth="1"/>
+    <col min="9" max="9" width="12.875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="5.125" customWidth="1"/>
+    <col min="13" max="13" width="15.625"/>
+    <col min="14" max="14" width="13.375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1776,10 +1776,10 @@
       </c>
       <c r="I4" s="16">
         <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150)</f>
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="J4" s="3">
-        <v>46172</v>
+        <v>46179</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -4753,17 +4753,17 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="25">
-        <v>46172</v>
+        <v>46179</v>
       </c>
       <c r="B150" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C150" s="27">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D150" s="21">
         <f>SUM(C3:C150)</f>
-        <v>-3029.11</v>
+        <v>-3024.11</v>
       </c>
       <c r="E150" s="34" t="s">
         <v>69</v>
@@ -4837,7 +4837,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{933a67b1-b783-4472-a201-cc1adadbd18c}</x14:id>
+          <x14:id>{e0b941f0-f69c-4e44-adac-5a31980a7f70}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4851,7 +4851,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2765d310-c09b-46f4-ae8b-ece295989681}</x14:id>
+          <x14:id>{5cbc82b5-c41f-4e69-92ed-301fa718cc0f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4877,7 +4877,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6308037a-4baa-47de-8208-bef380ecb8de}</x14:id>
+          <x14:id>{b30ea240-0fe9-4e35-ad32-68965a6693b8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4891,7 +4891,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5022821e-5e3c-4957-abfc-d9103766c321}</x14:id>
+          <x14:id>{8e3f230d-0d13-4413-99d8-bb77f7a64cf3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4905,7 +4905,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{567bb189-816b-40cc-a940-daefca7effaf}</x14:id>
+          <x14:id>{34fd5b0f-ff0b-494d-861b-373c297c3dd0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4919,7 +4919,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{43d5de2d-cbfd-4e77-a7d2-b56e484403dd}</x14:id>
+          <x14:id>{79e7ae76-6e45-4607-9926-42dbc7e9a0a3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4933,7 +4933,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d714ee69-4a3f-4997-abca-0440933933a6}</x14:id>
+          <x14:id>{77685108-21bc-44a7-bcdb-f5fff6eff14e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4947,7 +4947,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9e78b118-b1cd-41a5-9956-db77f4cbb70f}</x14:id>
+          <x14:id>{34448550-a0dd-4d13-a5a8-5331a8a85945}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4961,7 +4961,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{47dc8066-b89b-4eb0-a0ba-37f3c8c9c0df}</x14:id>
+          <x14:id>{dfb5c182-fd1c-4291-91f0-6ee554dc0271}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4975,7 +4975,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f50f5e17-8b7c-401b-9915-14801edfab77}</x14:id>
+          <x14:id>{f5566deb-5ab2-4727-9006-4a8a4865e320}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5021,7 +5021,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f769efde-be6f-4057-9d1d-0f1ebced81b5}</x14:id>
+          <x14:id>{a98614a5-d042-4fae-a1a2-66c91a0dad9d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5035,7 +5035,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{58e7a7d0-0dd2-43bf-819d-8ccaf5f88c70}</x14:id>
+          <x14:id>{529094b4-9510-49aa-a889-b21b491d1746}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5049,7 +5049,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{10d9494e-dc33-4cde-b058-e16e50a6f92b}</x14:id>
+          <x14:id>{ef2d5ce2-a902-43c8-b7f2-c1b9d9a76299}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5063,7 +5063,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a87a8ad9-e4bd-4e7a-a479-2dcf3e08d1ed}</x14:id>
+          <x14:id>{86acde78-db38-4734-804b-76ae85af27bd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5077,7 +5077,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{99475709-b4b7-4cbd-9143-e85138cc85d0}</x14:id>
+          <x14:id>{3c2d9287-e5b1-42a7-95df-683be818227e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5091,7 +5091,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8f224365-8639-4dba-88de-10bd2fc78c4f}</x14:id>
+          <x14:id>{50997f2b-06b1-4f62-9803-d52024f7a9db}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5105,7 +5105,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b03ec369-f31f-4b3f-96e0-2cf3a1056e20}</x14:id>
+          <x14:id>{db175aee-ee08-4861-90ca-1b9b5f76c590}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5119,7 +5119,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c6151f24-42bc-4784-9404-3d87987e74f2}</x14:id>
+          <x14:id>{a76e740f-69e0-4f68-b5a4-70fff31ce869}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5133,7 +5133,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c1ad63b6-c4f5-4787-b3a2-beb2b05fc4da}</x14:id>
+          <x14:id>{511a86ce-bb26-4fbc-ad60-a5f50889e509}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5147,7 +5147,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{261ec224-735b-4838-83ee-3889e12eafb2}</x14:id>
+          <x14:id>{a3391b13-e71c-4ad6-bc36-9bc3d95a93bb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5161,7 +5161,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4a5b4603-8ea2-41b7-bc8f-9decfb59c6fa}</x14:id>
+          <x14:id>{529a1ef9-d6d4-48e0-ab2c-c1de389c9abf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5169,13 +5169,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
+    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{933a67b1-b783-4472-a201-cc1adadbd18c}">
+          <x14:cfRule type="dataBar" id="{e0b941f0-f69c-4e44-adac-5a31980a7f70}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5186,7 +5186,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2765d310-c09b-46f4-ae8b-ece295989681}">
+          <x14:cfRule type="dataBar" id="{5cbc82b5-c41f-4e69-92ed-301fa718cc0f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5197,7 +5197,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6308037a-4baa-47de-8208-bef380ecb8de}">
+          <x14:cfRule type="dataBar" id="{b30ea240-0fe9-4e35-ad32-68965a6693b8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5210,7 +5210,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5022821e-5e3c-4957-abfc-d9103766c321}">
+          <x14:cfRule type="dataBar" id="{8e3f230d-0d13-4413-99d8-bb77f7a64cf3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5221,7 +5221,7 @@
           <xm:sqref>I1:I12 I20:I24 I26:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{567bb189-816b-40cc-a940-daefca7effaf}">
+          <x14:cfRule type="dataBar" id="{34fd5b0f-ff0b-494d-861b-373c297c3dd0}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5232,7 +5232,7 @@
           <xm:sqref>I1:I12 I20:I23 I26:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{43d5de2d-cbfd-4e77-a7d2-b56e484403dd}">
+          <x14:cfRule type="dataBar" id="{79e7ae76-6e45-4607-9926-42dbc7e9a0a3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5243,7 +5243,7 @@
           <xm:sqref>I1:I18 I26:I1048576 I20:I24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d714ee69-4a3f-4997-abca-0440933933a6}">
+          <x14:cfRule type="dataBar" id="{77685108-21bc-44a7-bcdb-f5fff6eff14e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5254,7 +5254,7 @@
           <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9e78b118-b1cd-41a5-9956-db77f4cbb70f}">
+          <x14:cfRule type="dataBar" id="{34448550-a0dd-4d13-a5a8-5331a8a85945}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5265,7 +5265,7 @@
           <xm:sqref>I2 I51:I1048576 I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{47dc8066-b89b-4eb0-a0ba-37f3c8c9c0df}">
+          <x14:cfRule type="dataBar" id="{dfb5c182-fd1c-4291-91f0-6ee554dc0271}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5276,7 +5276,7 @@
           <xm:sqref>I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f50f5e17-8b7c-401b-9915-14801edfab77}">
+          <x14:cfRule type="dataBar" id="{f5566deb-5ab2-4727-9006-4a8a4865e320}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5287,7 +5287,7 @@
           <xm:sqref>I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I18 I14:I16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f769efde-be6f-4057-9d1d-0f1ebced81b5}">
+          <x14:cfRule type="dataBar" id="{a98614a5-d042-4fae-a1a2-66c91a0dad9d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5298,7 +5298,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{58e7a7d0-0dd2-43bf-819d-8ccaf5f88c70}">
+          <x14:cfRule type="dataBar" id="{529094b4-9510-49aa-a889-b21b491d1746}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5309,7 +5309,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{10d9494e-dc33-4cde-b058-e16e50a6f92b}">
+          <x14:cfRule type="dataBar" id="{ef2d5ce2-a902-43c8-b7f2-c1b9d9a76299}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5320,7 +5320,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a87a8ad9-e4bd-4e7a-a479-2dcf3e08d1ed}">
+          <x14:cfRule type="dataBar" id="{86acde78-db38-4734-804b-76ae85af27bd}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5331,7 +5331,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50 I36:I37 I31:I34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{99475709-b4b7-4cbd-9143-e85138cc85d0}">
+          <x14:cfRule type="dataBar" id="{3c2d9287-e5b1-42a7-95df-683be818227e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5342,7 +5342,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8f224365-8639-4dba-88de-10bd2fc78c4f}">
+          <x14:cfRule type="dataBar" id="{50997f2b-06b1-4f62-9803-d52024f7a9db}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5353,7 +5353,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I18 I26:I29 I14:I16 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b03ec369-f31f-4b3f-96e0-2cf3a1056e20}">
+          <x14:cfRule type="dataBar" id="{db175aee-ee08-4861-90ca-1b9b5f76c590}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5364,7 +5364,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c6151f24-42bc-4784-9404-3d87987e74f2}">
+          <x14:cfRule type="dataBar" id="{a76e740f-69e0-4f68-b5a4-70fff31ce869}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5375,7 +5375,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I14:I18 I26:I29 I31:I37 I39:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c1ad63b6-c4f5-4787-b3a2-beb2b05fc4da}">
+          <x14:cfRule type="dataBar" id="{511a86ce-bb26-4fbc-ad60-a5f50889e509}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5386,7 +5386,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I31:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{261ec224-735b-4838-83ee-3889e12eafb2}">
+          <x14:cfRule type="dataBar" id="{a3391b13-e71c-4ad6-bc36-9bc3d95a93bb}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5397,7 +5397,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4a5b4603-8ea2-41b7-bc8f-9decfb59c6fa}">
+          <x14:cfRule type="dataBar" id="{529a1ef9-d6d4-48e0-ab2c-c1de389c9abf}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5417,11 +5417,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
-    <col min="2" max="2" width="8.12727272727273" customWidth="1"/>
-    <col min="3" max="3" width="8.87272727272727" customWidth="1"/>
+    <col min="2" max="2" width="8.125" customWidth="1"/>
+    <col min="3" max="3" width="8.875" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="25600" windowHeight="12200"/>
   </bookViews>
   <sheets>
     <sheet name="收支与赞助鸣谢" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="114">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -1216,7 +1216,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1326,6 +1326,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -1664,21 +1676,21 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K152"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:K153"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15.625" customWidth="1"/>
-    <col min="2" max="2" width="18.2583333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="9.375" customWidth="1"/>
-    <col min="5" max="5" width="33.125" customWidth="1"/>
-    <col min="7" max="7" width="5.125" customWidth="1"/>
-    <col min="8" max="8" width="18.2583333333333" customWidth="1"/>
-    <col min="9" max="9" width="12.875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="5.125" customWidth="1"/>
-    <col min="13" max="13" width="15.625"/>
-    <col min="14" max="14" width="13.375"/>
+    <col min="1" max="1" width="15.6272727272727" customWidth="1"/>
+    <col min="2" max="2" width="18.2545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
+    <col min="4" max="4" width="9.37272727272727" customWidth="1"/>
+    <col min="5" max="5" width="33.1272727272727" customWidth="1"/>
+    <col min="7" max="7" width="5.12727272727273" customWidth="1"/>
+    <col min="8" max="8" width="18.2545454545455" customWidth="1"/>
+    <col min="9" max="9" width="12.8727272727273" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.6272727272727" style="3" customWidth="1"/>
+    <col min="11" max="11" width="5.12727272727273" customWidth="1"/>
+    <col min="13" max="13" width="15.6272727272727"/>
+    <col min="14" max="14" width="13.3727272727273"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1847,11 +1859,11 @@
         <v>21</v>
       </c>
       <c r="I7" s="2">
-        <f>SUM(C110:C110,C113,C116,C118,C129,C134,C142)</f>
-        <v>200</v>
+        <f>SUM(C110:C110,C113,C116,C118,C129,C134,C142,C151)</f>
+        <v>210</v>
       </c>
       <c r="J7" s="3">
-        <v>46141</v>
+        <v>46184</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -4770,26 +4782,42 @@
       </c>
     </row>
     <row r="151" spans="1:5">
-      <c r="A151" s="37"/>
-      <c r="B151" s="38"/>
-      <c r="C151" s="39"/>
-      <c r="D151" s="39"/>
+      <c r="A151" s="37">
+        <v>46184</v>
+      </c>
+      <c r="B151" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C151" s="39">
+        <v>10</v>
+      </c>
+      <c r="D151" s="21">
+        <f>SUM(C3:C151)</f>
+        <v>-3014.11</v>
+      </c>
       <c r="E151" s="40"/>
     </row>
-    <row r="152" spans="1:5">
-      <c r="A152" s="41" t="s">
+    <row r="152" ht="14.75" spans="1:5">
+      <c r="A152" s="41"/>
+      <c r="B152" s="42"/>
+      <c r="C152" s="43"/>
+      <c r="D152" s="43"/>
+      <c r="E152" s="44"/>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="B152" s="41"/>
-      <c r="C152" s="41"/>
-      <c r="D152" s="41"/>
-      <c r="E152" s="41"/>
+      <c r="B153" s="45"/>
+      <c r="C153" s="45"/>
+      <c r="D153" s="45"/>
+      <c r="E153" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="40">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A152:E152"/>
+    <mergeCell ref="A153:E153"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A23:A24"/>
@@ -4837,7 +4865,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e0b941f0-f69c-4e44-adac-5a31980a7f70}</x14:id>
+          <x14:id>{80ed6f52-0c11-4644-8cc6-c3cff34ca8eb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4851,12 +4879,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5cbc82b5-c41f-4e69-92ed-301fa718cc0f}</x14:id>
+          <x14:id>{67726c1f-744c-4267-8690-0e14372953c5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D151 D153:D1048576">
+  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D152 D154:D1048576">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="min"/>
@@ -4877,49 +4905,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b30ea240-0fe9-4e35-ad32-68965a6693b8}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I12 I20:I24 I26:I1048576 I14:I18">
-    <cfRule type="dataBar" priority="22">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e3f230d-0d13-4413-99d8-bb77f7a64cf3}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I12 I20:I23 I26:I1048576 I14:I18">
-    <cfRule type="dataBar" priority="23">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{34fd5b0f-ff0b-494d-861b-373c297c3dd0}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I18 I26:I1048576 I20:I24">
-    <cfRule type="dataBar" priority="21">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{79e7ae76-6e45-4607-9926-42dbc7e9a0a3}</x14:id>
+          <x14:id>{7b23d84e-3946-4898-8139-4a65a186e383}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4933,12 +4919,54 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{77685108-21bc-44a7-bcdb-f5fff6eff14e}</x14:id>
+          <x14:id>{f36992a5-477c-4674-9aa3-ab558df53c66}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2 I51:I1048576 I30">
+  <conditionalFormatting sqref="I1:I12 I14:I18 I20:I24 I26:I1048576">
+    <cfRule type="dataBar" priority="22">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0858f954-5fb0-4629-9d3e-9432f83bb3c4}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I12 I14:I18 I20:I23 I26:I1048576">
+    <cfRule type="dataBar" priority="23">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{e8da21ff-a7e5-4d46-b4cc-9a22fd219315}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I18 I20:I24 I26:I1048576">
+    <cfRule type="dataBar" priority="21">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{f404b8fd-0ec7-4247-b2ad-d96ade6a4ef6}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2 I30 I51:I1048576">
     <cfRule type="dataBar" priority="49">
       <dataBar>
         <cfvo type="min"/>
@@ -4947,12 +4975,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{34448550-a0dd-4d13-a5a8-5331a8a85945}</x14:id>
+          <x14:id>{72d75f31-a67e-4ee8-a064-64b4e7ac7548}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I14:I18">
+  <conditionalFormatting sqref="I2:I6 I9:I12 I14:I18 I20:I23 I26:I37 I39:I1048576">
     <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
@@ -4961,12 +4989,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dfb5c182-fd1c-4291-91f0-6ee554dc0271}</x14:id>
+          <x14:id>{424bbbef-58ff-4c5e-b5ed-8dad76d6b7cc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I18 I14:I16">
+  <conditionalFormatting sqref="I2:I6 I9:I12 I14:I16 I18 I20:I23 I26:I37 I39:I1048576">
     <cfRule type="dataBar" priority="30">
       <dataBar>
         <cfvo type="min"/>
@@ -4975,7 +5003,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f5566deb-5ab2-4727-9006-4a8a4865e320}</x14:id>
+          <x14:id>{93dc8ac5-2acf-4426-8312-11a4e75f3146}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5021,7 +5049,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a98614a5-d042-4fae-a1a2-66c91a0dad9d}</x14:id>
+          <x14:id>{41133774-ab9d-4509-88b1-13c7f5c4fd2b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5035,7 +5063,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{529094b4-9510-49aa-a889-b21b491d1746}</x14:id>
+          <x14:id>{3058704e-e275-4c38-b056-f6fc68cef297}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5049,7 +5077,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ef2d5ce2-a902-43c8-b7f2-c1b9d9a76299}</x14:id>
+          <x14:id>{f8e50102-63ac-47f4-8d07-3a994c5a4167}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5063,7 +5091,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{86acde78-db38-4734-804b-76ae85af27bd}</x14:id>
+          <x14:id>{8e896a14-5671-432b-8cc2-f20ff8dfbbdd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5077,7 +5105,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3c2d9287-e5b1-42a7-95df-683be818227e}</x14:id>
+          <x14:id>{f107cd0b-85b9-4443-8233-4fc5ba8bb13d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5091,7 +5119,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{50997f2b-06b1-4f62-9803-d52024f7a9db}</x14:id>
+          <x14:id>{9abe42cb-926e-452d-aa4f-a815d2f05f18}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5105,7 +5133,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{db175aee-ee08-4861-90ca-1b9b5f76c590}</x14:id>
+          <x14:id>{dc839076-db62-4981-8f76-804606ce146e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5119,7 +5147,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a76e740f-69e0-4f68-b5a4-70fff31ce869}</x14:id>
+          <x14:id>{48bc1b5d-414b-489c-8dae-acd65f07e0fa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5133,7 +5161,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{511a86ce-bb26-4fbc-ad60-a5f50889e509}</x14:id>
+          <x14:id>{b1bce020-d1ae-4f05-b014-60c7eb164594}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5147,7 +5175,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a3391b13-e71c-4ad6-bc36-9bc3d95a93bb}</x14:id>
+          <x14:id>{fb7496ec-cd5f-4807-a564-563cfd6c0dca}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5161,7 +5189,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{529a1ef9-d6d4-48e0-ab2c-c1de389c9abf}</x14:id>
+          <x14:id>{289d19fb-fabc-4de2-8fa5-f180558fbd28}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5169,13 +5197,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
+    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e0b941f0-f69c-4e44-adac-5a31980a7f70}">
+          <x14:cfRule type="dataBar" id="{80ed6f52-0c11-4644-8cc6-c3cff34ca8eb}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5186,7 +5214,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5cbc82b5-c41f-4e69-92ed-301fa718cc0f}">
+          <x14:cfRule type="dataBar" id="{67726c1f-744c-4267-8690-0e14372953c5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5197,7 +5225,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b30ea240-0fe9-4e35-ad32-68965a6693b8}">
+          <x14:cfRule type="dataBar" id="{7b23d84e-3946-4898-8139-4a65a186e383}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5210,40 +5238,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8e3f230d-0d13-4413-99d8-bb77f7a64cf3}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>I1:I12 I20:I24 I26:I1048576 I14:I18</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{34fd5b0f-ff0b-494d-861b-373c297c3dd0}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>I1:I12 I20:I23 I26:I1048576 I14:I18</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{79e7ae76-6e45-4607-9926-42dbc7e9a0a3}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>I1:I18 I26:I1048576 I20:I24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{77685108-21bc-44a7-bcdb-f5fff6eff14e}">
+          <x14:cfRule type="dataBar" id="{f36992a5-477c-4674-9aa3-ab558df53c66}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5254,7 +5249,7 @@
           <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{34448550-a0dd-4d13-a5a8-5331a8a85945}">
+          <x14:cfRule type="dataBar" id="{0858f954-5fb0-4629-9d3e-9432f83bb3c4}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5262,10 +5257,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2 I51:I1048576 I30</xm:sqref>
+          <xm:sqref>I1:I12 I14:I18 I20:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dfb5c182-fd1c-4291-91f0-6ee554dc0271}">
+          <x14:cfRule type="dataBar" id="{e8da21ff-a7e5-4d46-b4cc-9a22fd219315}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5273,10 +5268,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I14:I18</xm:sqref>
+          <xm:sqref>I1:I12 I14:I18 I20:I23 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f5566deb-5ab2-4727-9006-4a8a4865e320}">
+          <x14:cfRule type="dataBar" id="{f404b8fd-0ec7-4247-b2ad-d96ade6a4ef6}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5284,10 +5279,43 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I6 I9:I12 I20:I23 I26:I37 I39:I1048576 I18 I14:I16</xm:sqref>
+          <xm:sqref>I1:I18 I20:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a98614a5-d042-4fae-a1a2-66c91a0dad9d}">
+          <x14:cfRule type="dataBar" id="{72d75f31-a67e-4ee8-a064-64b4e7ac7548}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I2 I30 I51:I1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{424bbbef-58ff-4c5e-b5ed-8dad76d6b7cc}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I2:I6 I9:I12 I14:I18 I20:I23 I26:I37 I39:I1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{93dc8ac5-2acf-4426-8312-11a4e75f3146}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I2:I6 I9:I12 I14:I16 I18 I20:I23 I26:I37 I39:I1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{41133774-ab9d-4509-88b1-13c7f5c4fd2b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5298,7 +5326,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{529094b4-9510-49aa-a889-b21b491d1746}">
+          <x14:cfRule type="dataBar" id="{3058704e-e275-4c38-b056-f6fc68cef297}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5309,7 +5337,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ef2d5ce2-a902-43c8-b7f2-c1b9d9a76299}">
+          <x14:cfRule type="dataBar" id="{f8e50102-63ac-47f4-8d07-3a994c5a4167}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5320,7 +5348,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{86acde78-db38-4734-804b-76ae85af27bd}">
+          <x14:cfRule type="dataBar" id="{8e896a14-5671-432b-8cc2-f20ff8dfbbdd}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5331,7 +5359,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50 I36:I37 I31:I34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3c2d9287-e5b1-42a7-95df-683be818227e}">
+          <x14:cfRule type="dataBar" id="{f107cd0b-85b9-4443-8233-4fc5ba8bb13d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5342,7 +5370,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{50997f2b-06b1-4f62-9803-d52024f7a9db}">
+          <x14:cfRule type="dataBar" id="{9abe42cb-926e-452d-aa4f-a815d2f05f18}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5353,7 +5381,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I18 I26:I29 I14:I16 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{db175aee-ee08-4861-90ca-1b9b5f76c590}">
+          <x14:cfRule type="dataBar" id="{dc839076-db62-4981-8f76-804606ce146e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5364,7 +5392,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a76e740f-69e0-4f68-b5a4-70fff31ce869}">
+          <x14:cfRule type="dataBar" id="{48bc1b5d-414b-489c-8dae-acd65f07e0fa}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5375,7 +5403,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I14:I18 I26:I29 I31:I37 I39:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{511a86ce-bb26-4fbc-ad60-a5f50889e509}">
+          <x14:cfRule type="dataBar" id="{b1bce020-d1ae-4f05-b014-60c7eb164594}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5386,7 +5414,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I31:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a3391b13-e71c-4ad6-bc36-9bc3d95a93bb}">
+          <x14:cfRule type="dataBar" id="{fb7496ec-cd5f-4807-a564-563cfd6c0dca}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5397,7 +5425,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{529a1ef9-d6d4-48e0-ab2c-c1de389c9abf}">
+          <x14:cfRule type="dataBar" id="{289d19fb-fabc-4de2-8fa5-f180558fbd28}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5417,11 +5445,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
-    <col min="2" max="2" width="8.125" customWidth="1"/>
-    <col min="3" max="3" width="8.875" customWidth="1"/>
+    <col min="2" max="2" width="8.12727272727273" customWidth="1"/>
+    <col min="3" max="3" width="8.87272727272727" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12200"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="收支与赞助鸣谢" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="114">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -1676,21 +1676,21 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K153"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:K154"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="15.6272727272727" customWidth="1"/>
-    <col min="2" max="2" width="18.2545454545455" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
-    <col min="4" max="4" width="9.37272727272727" customWidth="1"/>
-    <col min="5" max="5" width="33.1272727272727" customWidth="1"/>
-    <col min="7" max="7" width="5.12727272727273" customWidth="1"/>
-    <col min="8" max="8" width="18.2545454545455" customWidth="1"/>
-    <col min="9" max="9" width="12.8727272727273" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.6272727272727" style="3" customWidth="1"/>
-    <col min="11" max="11" width="5.12727272727273" customWidth="1"/>
-    <col min="13" max="13" width="15.6272727272727"/>
-    <col min="14" max="14" width="13.3727272727273"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="18.2583333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="9.375" customWidth="1"/>
+    <col min="5" max="5" width="33.125" customWidth="1"/>
+    <col min="7" max="7" width="5.125" customWidth="1"/>
+    <col min="8" max="8" width="18.2583333333333" customWidth="1"/>
+    <col min="9" max="9" width="12.875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="5.125" customWidth="1"/>
+    <col min="13" max="13" width="15.625"/>
+    <col min="14" max="14" width="13.375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1787,11 +1787,11 @@
         <v>15</v>
       </c>
       <c r="I4" s="16">
-        <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150)</f>
-        <v>477</v>
+        <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150,C152)</f>
+        <v>487</v>
       </c>
       <c r="J4" s="3">
-        <v>46179</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -4782,42 +4782,60 @@
       </c>
     </row>
     <row r="151" spans="1:5">
-      <c r="A151" s="37">
+      <c r="A151" s="25">
         <v>46184</v>
       </c>
-      <c r="B151" s="38" t="s">
+      <c r="B151" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C151" s="39">
+      <c r="C151" s="27">
         <v>10</v>
       </c>
       <c r="D151" s="21">
         <f>SUM(C3:C151)</f>
         <v>-3014.11</v>
       </c>
-      <c r="E151" s="40"/>
-    </row>
-    <row r="152" ht="14.75" spans="1:5">
-      <c r="A152" s="41"/>
-      <c r="B152" s="42"/>
-      <c r="C152" s="43"/>
-      <c r="D152" s="43"/>
-      <c r="E152" s="44"/>
-    </row>
-    <row r="153" spans="1:5">
-      <c r="A153" s="45" t="s">
+      <c r="E151" s="34"/>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="37">
+        <v>46185</v>
+      </c>
+      <c r="B152" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C152" s="39">
+        <v>10</v>
+      </c>
+      <c r="D152" s="21">
+        <f>SUM(C3:C152)</f>
+        <v>-3004.11</v>
+      </c>
+      <c r="E152" s="40" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="153" ht="14.25" spans="1:5">
+      <c r="A153" s="41"/>
+      <c r="B153" s="42"/>
+      <c r="C153" s="43"/>
+      <c r="D153" s="43"/>
+      <c r="E153" s="44"/>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="B153" s="45"/>
-      <c r="C153" s="45"/>
-      <c r="D153" s="45"/>
-      <c r="E153" s="45"/>
+      <c r="B154" s="45"/>
+      <c r="C154" s="45"/>
+      <c r="D154" s="45"/>
+      <c r="E154" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="40">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A153:E153"/>
+    <mergeCell ref="A154:E154"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A23:A24"/>
@@ -4865,7 +4883,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{80ed6f52-0c11-4644-8cc6-c3cff34ca8eb}</x14:id>
+          <x14:id>{11c20624-cca7-4969-a160-f8f1a06d3edf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4879,12 +4897,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{67726c1f-744c-4267-8690-0e14372953c5}</x14:id>
+          <x14:id>{96e1a1c2-b5cf-4c37-a236-134006fcc150}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D152 D154:D1048576">
+  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D153 D155:D1048576">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="min"/>
@@ -4905,7 +4923,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7b23d84e-3946-4898-8139-4a65a186e383}</x14:id>
+          <x14:id>{4cb89c65-df4e-435f-8b3c-7553c7db7a17}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4919,7 +4937,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f36992a5-477c-4674-9aa3-ab558df53c66}</x14:id>
+          <x14:id>{7baab82c-08a7-415b-a339-b936b892aaa2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4933,7 +4951,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0858f954-5fb0-4629-9d3e-9432f83bb3c4}</x14:id>
+          <x14:id>{5060c949-2182-47a4-bafb-0c35df2037f5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4947,7 +4965,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e8da21ff-a7e5-4d46-b4cc-9a22fd219315}</x14:id>
+          <x14:id>{6cfeaa87-d1ee-4961-af91-3dc7caccd8d7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4961,7 +4979,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f404b8fd-0ec7-4247-b2ad-d96ade6a4ef6}</x14:id>
+          <x14:id>{fe996b9a-44f7-4cd7-abad-a89463bd3d1d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4975,7 +4993,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{72d75f31-a67e-4ee8-a064-64b4e7ac7548}</x14:id>
+          <x14:id>{394470d6-f0ec-4f58-a7bd-7b178afa8359}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4989,7 +5007,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{424bbbef-58ff-4c5e-b5ed-8dad76d6b7cc}</x14:id>
+          <x14:id>{472fa193-5ed5-4ca9-9d87-79540424bf90}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5003,7 +5021,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{93dc8ac5-2acf-4426-8312-11a4e75f3146}</x14:id>
+          <x14:id>{4197c474-0cfc-4eda-bd58-f96265d8b99d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5049,7 +5067,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{41133774-ab9d-4509-88b1-13c7f5c4fd2b}</x14:id>
+          <x14:id>{27848d45-9659-48c1-b151-e88113bf64ce}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5063,7 +5081,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3058704e-e275-4c38-b056-f6fc68cef297}</x14:id>
+          <x14:id>{8a80f8e3-635f-412c-8381-826863f6e9d7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5077,7 +5095,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f8e50102-63ac-47f4-8d07-3a994c5a4167}</x14:id>
+          <x14:id>{8a3cb4c5-545e-4b31-978c-60e2b0a74d79}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5091,7 +5109,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e896a14-5671-432b-8cc2-f20ff8dfbbdd}</x14:id>
+          <x14:id>{5255e83d-0ee6-4766-bf5f-222e6ce6a51b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5105,7 +5123,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f107cd0b-85b9-4443-8233-4fc5ba8bb13d}</x14:id>
+          <x14:id>{53a8b7cb-c3ab-4cd6-b7e8-8a9ee31a30d6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5119,7 +5137,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9abe42cb-926e-452d-aa4f-a815d2f05f18}</x14:id>
+          <x14:id>{683cadd7-8897-4cd7-b85e-68bbfe489d1d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5133,7 +5151,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc839076-db62-4981-8f76-804606ce146e}</x14:id>
+          <x14:id>{21482ca7-5971-4f6c-89f7-3b74fff1e52c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5147,7 +5165,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{48bc1b5d-414b-489c-8dae-acd65f07e0fa}</x14:id>
+          <x14:id>{2ad523de-54f5-48b9-9a29-7696c126fe64}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5161,7 +5179,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b1bce020-d1ae-4f05-b014-60c7eb164594}</x14:id>
+          <x14:id>{5eb06887-4750-47b3-9a38-3fcc9f0a0fbd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5175,7 +5193,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fb7496ec-cd5f-4807-a564-563cfd6c0dca}</x14:id>
+          <x14:id>{52e18953-f226-4e4c-8f95-edb4ce8fa8c3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5189,7 +5207,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{289d19fb-fabc-4de2-8fa5-f180558fbd28}</x14:id>
+          <x14:id>{477ba8de-ff5f-4aa8-89e9-f2828ef23b26}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5197,13 +5215,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
+    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{80ed6f52-0c11-4644-8cc6-c3cff34ca8eb}">
+          <x14:cfRule type="dataBar" id="{11c20624-cca7-4969-a160-f8f1a06d3edf}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5214,7 +5232,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{67726c1f-744c-4267-8690-0e14372953c5}">
+          <x14:cfRule type="dataBar" id="{96e1a1c2-b5cf-4c37-a236-134006fcc150}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5225,7 +5243,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7b23d84e-3946-4898-8139-4a65a186e383}">
+          <x14:cfRule type="dataBar" id="{4cb89c65-df4e-435f-8b3c-7553c7db7a17}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5238,7 +5256,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f36992a5-477c-4674-9aa3-ab558df53c66}">
+          <x14:cfRule type="dataBar" id="{7baab82c-08a7-415b-a339-b936b892aaa2}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5249,7 +5267,7 @@
           <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0858f954-5fb0-4629-9d3e-9432f83bb3c4}">
+          <x14:cfRule type="dataBar" id="{5060c949-2182-47a4-bafb-0c35df2037f5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5260,7 +5278,7 @@
           <xm:sqref>I1:I12 I14:I18 I20:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e8da21ff-a7e5-4d46-b4cc-9a22fd219315}">
+          <x14:cfRule type="dataBar" id="{6cfeaa87-d1ee-4961-af91-3dc7caccd8d7}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5271,7 +5289,7 @@
           <xm:sqref>I1:I12 I14:I18 I20:I23 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f404b8fd-0ec7-4247-b2ad-d96ade6a4ef6}">
+          <x14:cfRule type="dataBar" id="{fe996b9a-44f7-4cd7-abad-a89463bd3d1d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5282,7 +5300,7 @@
           <xm:sqref>I1:I18 I20:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{72d75f31-a67e-4ee8-a064-64b4e7ac7548}">
+          <x14:cfRule type="dataBar" id="{394470d6-f0ec-4f58-a7bd-7b178afa8359}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5293,7 +5311,7 @@
           <xm:sqref>I2 I30 I51:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{424bbbef-58ff-4c5e-b5ed-8dad76d6b7cc}">
+          <x14:cfRule type="dataBar" id="{472fa193-5ed5-4ca9-9d87-79540424bf90}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5304,7 +5322,7 @@
           <xm:sqref>I2:I6 I9:I12 I14:I18 I20:I23 I26:I37 I39:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{93dc8ac5-2acf-4426-8312-11a4e75f3146}">
+          <x14:cfRule type="dataBar" id="{4197c474-0cfc-4eda-bd58-f96265d8b99d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5315,7 +5333,7 @@
           <xm:sqref>I2:I6 I9:I12 I14:I16 I18 I20:I23 I26:I37 I39:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{41133774-ab9d-4509-88b1-13c7f5c4fd2b}">
+          <x14:cfRule type="dataBar" id="{27848d45-9659-48c1-b151-e88113bf64ce}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5326,7 +5344,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3058704e-e275-4c38-b056-f6fc68cef297}">
+          <x14:cfRule type="dataBar" id="{8a80f8e3-635f-412c-8381-826863f6e9d7}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5337,7 +5355,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f8e50102-63ac-47f4-8d07-3a994c5a4167}">
+          <x14:cfRule type="dataBar" id="{8a3cb4c5-545e-4b31-978c-60e2b0a74d79}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5348,7 +5366,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8e896a14-5671-432b-8cc2-f20ff8dfbbdd}">
+          <x14:cfRule type="dataBar" id="{5255e83d-0ee6-4766-bf5f-222e6ce6a51b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5359,7 +5377,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50 I36:I37 I31:I34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f107cd0b-85b9-4443-8233-4fc5ba8bb13d}">
+          <x14:cfRule type="dataBar" id="{53a8b7cb-c3ab-4cd6-b7e8-8a9ee31a30d6}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5370,7 +5388,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9abe42cb-926e-452d-aa4f-a815d2f05f18}">
+          <x14:cfRule type="dataBar" id="{683cadd7-8897-4cd7-b85e-68bbfe489d1d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5381,7 +5399,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I18 I26:I29 I14:I16 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dc839076-db62-4981-8f76-804606ce146e}">
+          <x14:cfRule type="dataBar" id="{21482ca7-5971-4f6c-89f7-3b74fff1e52c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5392,7 +5410,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{48bc1b5d-414b-489c-8dae-acd65f07e0fa}">
+          <x14:cfRule type="dataBar" id="{2ad523de-54f5-48b9-9a29-7696c126fe64}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5403,7 +5421,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I14:I18 I26:I29 I31:I37 I39:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b1bce020-d1ae-4f05-b014-60c7eb164594}">
+          <x14:cfRule type="dataBar" id="{5eb06887-4750-47b3-9a38-3fcc9f0a0fbd}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5414,7 +5432,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I31:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fb7496ec-cd5f-4807-a564-563cfd6c0dca}">
+          <x14:cfRule type="dataBar" id="{52e18953-f226-4e4c-8f95-edb4ce8fa8c3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5425,7 +5443,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{289d19fb-fabc-4de2-8fa5-f180558fbd28}">
+          <x14:cfRule type="dataBar" id="{477ba8de-ff5f-4aa8-89e9-f2828ef23b26}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5445,11 +5463,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
-    <col min="2" max="2" width="8.12727272727273" customWidth="1"/>
-    <col min="3" max="3" width="8.87272727272727" customWidth="1"/>
+    <col min="2" max="2" width="8.125" customWidth="1"/>
+    <col min="3" max="3" width="8.875" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -1216,7 +1216,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1326,18 +1326,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -1788,10 +1776,10 @@
       </c>
       <c r="I4" s="16">
         <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150,C152)</f>
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="J4" s="3">
-        <v>46185</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -4798,38 +4786,38 @@
       <c r="E151" s="34"/>
     </row>
     <row r="152" spans="1:5">
-      <c r="A152" s="37">
-        <v>46185</v>
-      </c>
-      <c r="B152" s="38" t="s">
+      <c r="A152" s="25">
+        <v>46192</v>
+      </c>
+      <c r="B152" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C152" s="39">
-        <v>10</v>
+      <c r="C152" s="27">
+        <v>20</v>
       </c>
       <c r="D152" s="21">
         <f>SUM(C3:C152)</f>
-        <v>-3004.11</v>
-      </c>
-      <c r="E152" s="40" t="s">
+        <v>-2994.11</v>
+      </c>
+      <c r="E152" s="34" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="153" ht="14.25" spans="1:5">
-      <c r="A153" s="41"/>
-      <c r="B153" s="42"/>
-      <c r="C153" s="43"/>
-      <c r="D153" s="43"/>
-      <c r="E153" s="44"/>
+    <row r="153" spans="1:5">
+      <c r="A153" s="37"/>
+      <c r="B153" s="38"/>
+      <c r="C153" s="39"/>
+      <c r="D153" s="39"/>
+      <c r="E153" s="40"/>
     </row>
     <row r="154" spans="1:5">
-      <c r="A154" s="45" t="s">
+      <c r="A154" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="B154" s="45"/>
-      <c r="C154" s="45"/>
-      <c r="D154" s="45"/>
-      <c r="E154" s="45"/>
+      <c r="B154" s="41"/>
+      <c r="C154" s="41"/>
+      <c r="D154" s="41"/>
+      <c r="E154" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="40">
@@ -4883,7 +4871,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{11c20624-cca7-4969-a160-f8f1a06d3edf}</x14:id>
+          <x14:id>{d874043d-01f5-4f74-9dd7-685054b41c05}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4897,7 +4885,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{96e1a1c2-b5cf-4c37-a236-134006fcc150}</x14:id>
+          <x14:id>{f5a791b0-d87a-4c25-a890-176a0b0da86e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4923,7 +4911,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4cb89c65-df4e-435f-8b3c-7553c7db7a17}</x14:id>
+          <x14:id>{67c4f6a7-4045-43ef-8dca-a112ca968af6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4937,7 +4925,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7baab82c-08a7-415b-a339-b936b892aaa2}</x14:id>
+          <x14:id>{af12ab7f-055f-41f1-a3fa-3d37ae336ddc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4951,7 +4939,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5060c949-2182-47a4-bafb-0c35df2037f5}</x14:id>
+          <x14:id>{9fe27cb5-6e00-4061-a4f8-db742fdb69e5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4965,7 +4953,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6cfeaa87-d1ee-4961-af91-3dc7caccd8d7}</x14:id>
+          <x14:id>{e4c70073-8daf-44d1-b044-949063a060fa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4979,7 +4967,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fe996b9a-44f7-4cd7-abad-a89463bd3d1d}</x14:id>
+          <x14:id>{f7b009f3-b4be-4526-b21f-3b1b30d72131}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4993,7 +4981,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{394470d6-f0ec-4f58-a7bd-7b178afa8359}</x14:id>
+          <x14:id>{16f48cc6-30e1-41de-8108-d466092ea8e7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5007,7 +4995,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{472fa193-5ed5-4ca9-9d87-79540424bf90}</x14:id>
+          <x14:id>{7504c11d-1cac-4be5-9426-f64b600ed25d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5021,7 +5009,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4197c474-0cfc-4eda-bd58-f96265d8b99d}</x14:id>
+          <x14:id>{be3970ca-ef8f-47fe-a732-143679a56917}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5067,7 +5055,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{27848d45-9659-48c1-b151-e88113bf64ce}</x14:id>
+          <x14:id>{6991815c-3116-4a25-a95e-4f7ca7fa6e85}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5081,7 +5069,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8a80f8e3-635f-412c-8381-826863f6e9d7}</x14:id>
+          <x14:id>{a621f7b0-9298-406e-867e-a0571996f1b5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5095,7 +5083,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8a3cb4c5-545e-4b31-978c-60e2b0a74d79}</x14:id>
+          <x14:id>{fe5c2988-b27f-4e8e-8e30-bc12ddc9eb0c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5109,7 +5097,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5255e83d-0ee6-4766-bf5f-222e6ce6a51b}</x14:id>
+          <x14:id>{62b559a9-5a1f-48bd-b9a8-c5f3d39353ad}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5123,7 +5111,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{53a8b7cb-c3ab-4cd6-b7e8-8a9ee31a30d6}</x14:id>
+          <x14:id>{3d77954c-164a-45ae-a728-dd5c5a50bf95}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5137,7 +5125,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{683cadd7-8897-4cd7-b85e-68bbfe489d1d}</x14:id>
+          <x14:id>{91bb7c13-ae47-44ef-8617-869a0172883b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5151,7 +5139,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{21482ca7-5971-4f6c-89f7-3b74fff1e52c}</x14:id>
+          <x14:id>{73b2ceda-b8ee-4b73-92d8-f4873aa3098e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5165,7 +5153,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2ad523de-54f5-48b9-9a29-7696c126fe64}</x14:id>
+          <x14:id>{1ebf6f1e-aef9-46bb-8b26-d54908b9e4c0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5179,7 +5167,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5eb06887-4750-47b3-9a38-3fcc9f0a0fbd}</x14:id>
+          <x14:id>{7cde5f1d-66f5-4f2f-9d9a-c2e3e7527720}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5193,7 +5181,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{52e18953-f226-4e4c-8f95-edb4ce8fa8c3}</x14:id>
+          <x14:id>{edee130d-c17d-4af6-b5fe-c07c2afee020}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5207,7 +5195,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{477ba8de-ff5f-4aa8-89e9-f2828ef23b26}</x14:id>
+          <x14:id>{0088ad77-f334-4873-8cd7-1e22ad12206b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5215,13 +5203,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
+    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{11c20624-cca7-4969-a160-f8f1a06d3edf}">
+          <x14:cfRule type="dataBar" id="{d874043d-01f5-4f74-9dd7-685054b41c05}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5232,7 +5220,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{96e1a1c2-b5cf-4c37-a236-134006fcc150}">
+          <x14:cfRule type="dataBar" id="{f5a791b0-d87a-4c25-a890-176a0b0da86e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5243,7 +5231,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4cb89c65-df4e-435f-8b3c-7553c7db7a17}">
+          <x14:cfRule type="dataBar" id="{67c4f6a7-4045-43ef-8dca-a112ca968af6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5256,7 +5244,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7baab82c-08a7-415b-a339-b936b892aaa2}">
+          <x14:cfRule type="dataBar" id="{af12ab7f-055f-41f1-a3fa-3d37ae336ddc}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5267,7 +5255,7 @@
           <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5060c949-2182-47a4-bafb-0c35df2037f5}">
+          <x14:cfRule type="dataBar" id="{9fe27cb5-6e00-4061-a4f8-db742fdb69e5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5278,7 +5266,7 @@
           <xm:sqref>I1:I12 I14:I18 I20:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6cfeaa87-d1ee-4961-af91-3dc7caccd8d7}">
+          <x14:cfRule type="dataBar" id="{e4c70073-8daf-44d1-b044-949063a060fa}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5289,7 +5277,7 @@
           <xm:sqref>I1:I12 I14:I18 I20:I23 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fe996b9a-44f7-4cd7-abad-a89463bd3d1d}">
+          <x14:cfRule type="dataBar" id="{f7b009f3-b4be-4526-b21f-3b1b30d72131}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5300,7 +5288,7 @@
           <xm:sqref>I1:I18 I20:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{394470d6-f0ec-4f58-a7bd-7b178afa8359}">
+          <x14:cfRule type="dataBar" id="{16f48cc6-30e1-41de-8108-d466092ea8e7}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5311,7 +5299,7 @@
           <xm:sqref>I2 I30 I51:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{472fa193-5ed5-4ca9-9d87-79540424bf90}">
+          <x14:cfRule type="dataBar" id="{7504c11d-1cac-4be5-9426-f64b600ed25d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5322,7 +5310,7 @@
           <xm:sqref>I2:I6 I9:I12 I14:I18 I20:I23 I26:I37 I39:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4197c474-0cfc-4eda-bd58-f96265d8b99d}">
+          <x14:cfRule type="dataBar" id="{be3970ca-ef8f-47fe-a732-143679a56917}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5333,7 +5321,7 @@
           <xm:sqref>I2:I6 I9:I12 I14:I16 I18 I20:I23 I26:I37 I39:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{27848d45-9659-48c1-b151-e88113bf64ce}">
+          <x14:cfRule type="dataBar" id="{6991815c-3116-4a25-a95e-4f7ca7fa6e85}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5344,7 +5332,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8a80f8e3-635f-412c-8381-826863f6e9d7}">
+          <x14:cfRule type="dataBar" id="{a621f7b0-9298-406e-867e-a0571996f1b5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5355,7 +5343,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8a3cb4c5-545e-4b31-978c-60e2b0a74d79}">
+          <x14:cfRule type="dataBar" id="{fe5c2988-b27f-4e8e-8e30-bc12ddc9eb0c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5366,7 +5354,7 @@
           <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5255e83d-0ee6-4766-bf5f-222e6ce6a51b}">
+          <x14:cfRule type="dataBar" id="{62b559a9-5a1f-48bd-b9a8-c5f3d39353ad}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5377,7 +5365,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50 I36:I37 I31:I34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{53a8b7cb-c3ab-4cd6-b7e8-8a9ee31a30d6}">
+          <x14:cfRule type="dataBar" id="{3d77954c-164a-45ae-a728-dd5c5a50bf95}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5388,7 +5376,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{683cadd7-8897-4cd7-b85e-68bbfe489d1d}">
+          <x14:cfRule type="dataBar" id="{91bb7c13-ae47-44ef-8617-869a0172883b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5399,7 +5387,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I18 I26:I29 I14:I16 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{21482ca7-5971-4f6c-89f7-3b74fff1e52c}">
+          <x14:cfRule type="dataBar" id="{73b2ceda-b8ee-4b73-92d8-f4873aa3098e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5410,7 +5398,7 @@
           <xm:sqref>I3:I6 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2ad523de-54f5-48b9-9a29-7696c126fe64}">
+          <x14:cfRule type="dataBar" id="{1ebf6f1e-aef9-46bb-8b26-d54908b9e4c0}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5421,7 +5409,7 @@
           <xm:sqref>I3:I6 I9:I12 I20:I23 I14:I18 I26:I29 I31:I37 I39:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5eb06887-4750-47b3-9a38-3fcc9f0a0fbd}">
+          <x14:cfRule type="dataBar" id="{7cde5f1d-66f5-4f2f-9d9a-c2e3e7527720}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5432,7 +5420,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I31:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{52e18953-f226-4e4c-8f95-edb4ce8fa8c3}">
+          <x14:cfRule type="dataBar" id="{edee130d-c17d-4af6-b5fe-c07c2afee020}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5443,7 +5431,7 @@
           <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I39:I50 I31:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{477ba8de-ff5f-4aa8-89e9-f2828ef23b26}">
+          <x14:cfRule type="dataBar" id="{0088ad77-f334-4873-8cd7-1e22ad12206b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="114">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -87,13 +87,19 @@
     <t>Mtve</t>
   </si>
   <si>
+    <t>KIRINIT</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>zkiftie</t>
+  </si>
+  <si>
     <t>Disha_UUU2</t>
   </si>
   <si>
-    <t>zkiftie</t>
-  </si>
-  <si>
-    <t>KIRINIT</t>
+    <t>↓1</t>
   </si>
   <si>
     <t>_LoveSelf_</t>
@@ -213,13 +219,7 @@
     <t>Xiaoyingawa</t>
   </si>
   <si>
-    <t>↑20</t>
-  </si>
-  <si>
     <t>鞘翅、TP、电费、羊毛、村民、TNT</t>
-  </si>
-  <si>
-    <t>↓1</t>
   </si>
   <si>
     <t>电费、经验</t>
@@ -1216,7 +1216,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1326,6 +1326,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -1664,7 +1676,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K154"/>
+  <dimension ref="A1:K155"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -1819,21 +1831,24 @@
       <c r="G6" s="15">
         <v>4</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="16">
-        <f>SUM(C11,C16,C29,C25,C62,C81:C81)</f>
-        <v>239.66</v>
+      <c r="I6" s="2">
+        <f>SUM(C110:C110,C113,C116,C118,C129,C134,C142,C151,C153)</f>
+        <v>260</v>
       </c>
       <c r="J6" s="3">
-        <v>45829</v>
+        <v>46193</v>
+      </c>
+      <c r="K6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="12"/>
       <c r="B7" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="13">
         <v>1.28</v>
@@ -1843,15 +1858,18 @@
       <c r="G7" s="15">
         <v>5</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="2">
-        <f>SUM(C110:C110,C113,C116,C118,C129,C134,C142,C151)</f>
-        <v>210</v>
+      <c r="H7" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="16">
+        <f>SUM(C11,C16,C29,C25,C62,C81:C81)</f>
+        <v>239.66</v>
       </c>
       <c r="J7" s="3">
-        <v>46184</v>
+        <v>45829</v>
+      </c>
+      <c r="K7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1859,7 +1877,7 @@
         <v>44164</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="13">
         <v>9</v>
@@ -1873,7 +1891,7 @@
         <v>6</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I8" s="2">
         <f>SUM(C121,C123,C126,C128,C131)</f>
@@ -1888,7 +1906,7 @@
         <v>44213</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="13">
         <v>0.1</v>
@@ -1902,7 +1920,7 @@
         <v>7</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I9" s="16">
         <f>SUM(C52,C65)</f>
@@ -1931,7 +1949,7 @@
         <v>8</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I10" s="2">
         <f>SUM(C86,C101,C105,C107,C112,C119,C124)</f>
@@ -1946,7 +1964,7 @@
         <v>44781</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C11" s="13">
         <v>130</v>
@@ -1956,13 +1974,13 @@
         <v>193.93</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G11" s="15">
         <v>9</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I11" s="16">
         <f>SUM(C8:C8,C47,C45,C50:C50)</f>
@@ -1985,7 +2003,7 @@
         <v>-5.06999999999999</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G12" s="15">
         <v>10</v>
@@ -2006,7 +2024,7 @@
         <v>44787</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C13" s="13">
         <v>5.02</v>
@@ -2020,7 +2038,7 @@
         <v>11</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I13" s="2">
         <f>SUM(C133,C143,C147)</f>
@@ -2043,13 +2061,13 @@
         <v>-780.05</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G14" s="15">
         <v>12</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I14" s="16">
         <f>SUM(C56,C46,C74)</f>
@@ -2074,13 +2092,13 @@
         <v>-660.05</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G15" s="15">
         <v>13</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I15" s="2">
         <f>SUM(C99,C109,C130,C137,C144)</f>
@@ -2095,7 +2113,7 @@
         <v>44946</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C16" s="13">
         <v>13</v>
@@ -2109,7 +2127,7 @@
         <v>14</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I16" s="2">
         <f>SUM(C85:C85,C89,C96:C98,C117,C120,C122)</f>
@@ -2119,12 +2137,12 @@
         <v>46039</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:10">
       <c r="A17" s="17">
         <v>44953</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C17" s="13">
         <v>10</v>
@@ -2134,13 +2152,13 @@
         <v>-637.05</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G17" s="15">
         <v>15</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I17" s="2">
         <v>15</v>
@@ -2149,7 +2167,7 @@
         <v>45930</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:10">
       <c r="A18" s="17">
         <v>44958</v>
       </c>
@@ -2165,13 +2183,13 @@
         <v>-550.73</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G18" s="15">
         <v>16</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I18" s="16">
         <f>SUM(C40,C64)</f>
@@ -2181,10 +2199,10 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:10">
       <c r="A19" s="17"/>
       <c r="B19" s="22" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C19" s="13">
         <v>1.32</v>
@@ -2195,7 +2213,7 @@
         <v>17</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I19" s="2">
         <f>SUM(C135,C139,C146)</f>
@@ -2205,7 +2223,7 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:10">
       <c r="A20" s="17">
         <v>44961</v>
       </c>
@@ -2224,7 +2242,7 @@
         <v>18</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I20" s="16">
         <v>10</v>
@@ -2233,7 +2251,7 @@
         <v>44953</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:10">
       <c r="A21" s="17">
         <v>45138</v>
       </c>
@@ -2249,13 +2267,13 @@
         <v>-428.73</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G21" s="15">
         <v>19</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I21" s="16">
         <v>10</v>
@@ -2264,12 +2282,12 @@
         <v>45234</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:10">
       <c r="A22" s="17">
         <v>45140</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C22" s="13">
         <v>0.11</v>
@@ -2283,7 +2301,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I22" s="16">
         <v>10</v>
@@ -2292,12 +2310,12 @@
         <v>45325</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:10">
       <c r="A23" s="17">
         <v>45141</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C23" s="13">
         <v>1.01</v>
@@ -2311,7 +2329,7 @@
         <v>21</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I23" s="16">
         <v>10</v>
@@ -2320,7 +2338,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:10">
       <c r="A24" s="17"/>
       <c r="B24" s="8" t="s">
         <v>13</v>
@@ -2330,13 +2348,13 @@
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G24" s="15">
         <v>22</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I24" s="2">
         <v>10</v>
@@ -2345,12 +2363,12 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:10">
       <c r="A25" s="17">
         <v>45160</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C25" s="13">
         <v>3</v>
@@ -2364,7 +2382,7 @@
         <v>23</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I25" s="16">
         <v>10</v>
@@ -2373,12 +2391,12 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:10">
       <c r="A26" s="17">
         <v>45234</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C26" s="13">
         <v>10</v>
@@ -2388,13 +2406,13 @@
         <v>-415.61</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G26">
         <v>24</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I26" s="2">
         <v>8</v>
@@ -2403,7 +2421,7 @@
         <v>45860</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:10">
       <c r="A27" s="17"/>
       <c r="B27" s="8"/>
       <c r="C27" s="18">
@@ -2411,13 +2429,13 @@
       </c>
       <c r="D27" s="23"/>
       <c r="E27" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G27">
         <v>25</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I27" s="2">
         <v>7.33</v>
@@ -2426,7 +2444,7 @@
         <v>45907</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:10">
       <c r="A28" s="17">
         <v>45249</v>
       </c>
@@ -2441,13 +2459,13 @@
         <v>-400.11</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G28">
         <v>26</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I28" s="16">
         <f>SUM(C82,C84,C94)</f>
@@ -2457,12 +2475,12 @@
         <v>45861</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:10">
       <c r="A29" s="17">
         <v>45305</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C29" s="13">
         <v>50</v>
@@ -2476,7 +2494,7 @@
         <v>27</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I29" s="2">
         <v>6</v>
@@ -2485,12 +2503,12 @@
         <v>45868</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:10">
       <c r="A30" s="17">
         <v>45325</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C30" s="13">
         <v>10</v>
@@ -2500,13 +2518,13 @@
         <v>-340.11</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G30">
         <v>28</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I30" s="2">
         <v>5.04</v>
@@ -2514,11 +2532,8 @@
       <c r="J30" s="3">
         <v>46160</v>
       </c>
-      <c r="K30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="17">
         <v>45341</v>
       </c>
@@ -2533,13 +2548,13 @@
         <v>-272.11</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G31">
         <v>29</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I31" s="16">
         <v>5.02</v>
@@ -2547,11 +2562,8 @@
       <c r="J31" s="3">
         <v>44787</v>
       </c>
-      <c r="K31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="17">
         <v>45368</v>
       </c>
@@ -2580,11 +2592,8 @@
       <c r="J32" s="3">
         <v>45634</v>
       </c>
-      <c r="K32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="17">
         <v>45387</v>
       </c>
@@ -2613,11 +2622,8 @@
       <c r="J33" s="3">
         <v>45707</v>
       </c>
-      <c r="K33" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="17">
         <v>45394</v>
       </c>
@@ -2646,11 +2652,8 @@
       <c r="J34" s="3">
         <v>45885</v>
       </c>
-      <c r="K34" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="17">
         <v>45396</v>
       </c>
@@ -2680,11 +2683,8 @@
       <c r="J35" s="3">
         <v>45934</v>
       </c>
-      <c r="K35" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="17">
         <v>45403</v>
       </c>
@@ -2711,11 +2711,8 @@
       <c r="J36" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K36" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="17">
         <v>45403</v>
       </c>
@@ -2744,11 +2741,8 @@
       <c r="J37" s="3">
         <v>45500</v>
       </c>
-      <c r="K37" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="17">
         <v>45412</v>
       </c>
@@ -2777,11 +2771,8 @@
       <c r="J38" s="3">
         <v>45976</v>
       </c>
-      <c r="K38" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="17">
         <v>45417</v>
       </c>
@@ -2811,16 +2802,13 @@
       <c r="J39" s="3">
         <v>45396</v>
       </c>
-      <c r="K39" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="17">
         <v>45421</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C40" s="13">
         <v>5</v>
@@ -2844,11 +2832,8 @@
       <c r="J40" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K40" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="17">
         <v>45478</v>
       </c>
@@ -2876,11 +2861,8 @@
       <c r="J41" s="3">
         <v>45907</v>
       </c>
-      <c r="K41" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="17">
         <v>45494</v>
       </c>
@@ -2901,7 +2883,7 @@
         <v>40</v>
       </c>
       <c r="H42" s="24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I42" s="16">
         <v>1.32</v>
@@ -2909,11 +2891,8 @@
       <c r="J42" s="3">
         <v>44958</v>
       </c>
-      <c r="K42" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="17"/>
       <c r="B43" s="8" t="s">
         <v>13</v>
@@ -2929,7 +2908,7 @@
         <v>41</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I43" s="16">
         <v>1.28</v>
@@ -2937,11 +2916,8 @@
       <c r="J43" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K43" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="25">
         <v>45495</v>
       </c>
@@ -2962,7 +2938,7 @@
         <v>42</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I44" s="16">
         <v>1.01</v>
@@ -2970,16 +2946,13 @@
       <c r="J44" s="3">
         <v>45141</v>
       </c>
-      <c r="K44" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="25">
         <v>45496</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C45" s="27">
         <v>5</v>
@@ -3001,14 +2974,11 @@
       <c r="J45" s="3">
         <v>45794</v>
       </c>
-      <c r="K45" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" s="29"/>
       <c r="B46" s="26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C46" s="27">
         <v>3</v>
@@ -3029,16 +2999,13 @@
       <c r="J46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K46" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" s="17">
         <v>45497</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C47" s="27">
         <v>25</v>
@@ -3062,11 +3029,8 @@
       <c r="J47" s="3">
         <v>45697</v>
       </c>
-      <c r="K47" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" s="25">
         <v>45500</v>
       </c>
@@ -3093,11 +3057,8 @@
       <c r="J48" s="3">
         <v>45885</v>
       </c>
-      <c r="K48" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="31"/>
       <c r="B49" s="26" t="s">
         <v>15</v>
@@ -3113,7 +3074,7 @@
         <v>47</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I49" s="16">
         <v>0.11</v>
@@ -3121,16 +3082,13 @@
       <c r="J49" s="3">
         <v>45140</v>
       </c>
-      <c r="K49" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="25">
         <v>45505</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C50" s="27">
         <v>10</v>
@@ -3146,7 +3104,7 @@
         <v>48</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I50" s="16">
         <v>0.1</v>
@@ -3154,11 +3112,8 @@
       <c r="J50" s="3">
         <v>44213</v>
       </c>
-      <c r="K50" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" s="25">
         <v>45507</v>
       </c>
@@ -3176,10 +3131,10 @@
         <v>69</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:10">
       <c r="A52" s="31"/>
       <c r="B52" s="26" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C52" s="27">
         <v>86</v>
@@ -3189,7 +3144,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:10">
       <c r="A53" s="25">
         <v>45508</v>
       </c>
@@ -3207,7 +3162,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:10">
       <c r="A54" s="31"/>
       <c r="B54" s="26" t="s">
         <v>17</v>
@@ -3218,7 +3173,7 @@
       <c r="D54" s="30"/>
       <c r="E54" s="28"/>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:10">
       <c r="A55" s="25">
         <v>45509</v>
       </c>
@@ -3234,10 +3189,10 @@
         <v>89</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:10">
       <c r="A56" s="31"/>
       <c r="B56" s="26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C56" s="27">
         <v>10</v>
@@ -3245,7 +3200,7 @@
       <c r="D56" s="30"/>
       <c r="E56" s="28"/>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:10">
       <c r="A57" s="25">
         <v>45510</v>
       </c>
@@ -3263,7 +3218,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:10">
       <c r="A58" s="25">
         <v>45525</v>
       </c>
@@ -3282,7 +3237,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:10">
       <c r="A59" s="25">
         <v>45525</v>
       </c>
@@ -3300,7 +3255,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:10">
       <c r="A60" s="25">
         <v>45549</v>
       </c>
@@ -3318,7 +3273,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:10">
       <c r="A61" s="29"/>
       <c r="B61" s="33" t="s">
         <v>17</v>
@@ -3331,12 +3286,12 @@
         <v>88</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:10">
       <c r="A62" s="31">
         <v>45551</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C62" s="27">
         <v>17</v>
@@ -3347,7 +3302,7 @@
       </c>
       <c r="E62" s="28"/>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:10">
       <c r="A63" s="25">
         <v>45552</v>
       </c>
@@ -3363,12 +3318,12 @@
       </c>
       <c r="E63" s="28"/>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:10">
       <c r="A64" s="25">
         <v>45555</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C64" s="27">
         <v>6</v>
@@ -3382,7 +3337,7 @@
     <row r="65" spans="1:5">
       <c r="A65" s="31"/>
       <c r="B65" s="33" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C65" s="27">
         <v>20</v>
@@ -3535,7 +3490,7 @@
     <row r="74" spans="1:5">
       <c r="A74" s="17"/>
       <c r="B74" s="33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C74" s="27">
         <v>10</v>
@@ -3550,7 +3505,7 @@
         <v>45649</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C75" s="27">
         <v>10</v>
@@ -3650,7 +3605,7 @@
         <v>45829</v>
       </c>
       <c r="B81" s="33" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C81" s="27">
         <v>26.66</v>
@@ -3666,7 +3621,7 @@
         <v>45844</v>
       </c>
       <c r="B82" s="33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C82" s="27">
         <v>2.48</v>
@@ -3682,7 +3637,7 @@
         <v>45860</v>
       </c>
       <c r="B83" s="33" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C83" s="27">
         <v>8</v>
@@ -3698,7 +3653,7 @@
         <v>45861</v>
       </c>
       <c r="B84" s="33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C84" s="27">
         <v>0.5</v>
@@ -3714,7 +3669,7 @@
         <v>45865</v>
       </c>
       <c r="B85" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C85" s="27">
         <v>3</v>
@@ -3730,7 +3685,7 @@
         <v>45868</v>
       </c>
       <c r="B86" s="33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C86" s="27">
         <v>5.01</v>
@@ -3746,7 +3701,7 @@
         <v>45868</v>
       </c>
       <c r="B87" s="33" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C87" s="27">
         <v>6</v>
@@ -3782,7 +3737,7 @@
         <v>45878</v>
       </c>
       <c r="B89" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C89" s="27">
         <v>0.01</v>
@@ -3859,7 +3814,7 @@
     <row r="94" spans="1:5">
       <c r="A94" s="17"/>
       <c r="B94" s="33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C94" s="27">
         <v>4</v>
@@ -3890,7 +3845,7 @@
         <v>45894</v>
       </c>
       <c r="B96" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C96" s="27">
         <v>1</v>
@@ -3906,7 +3861,7 @@
         <v>45905</v>
       </c>
       <c r="B97" s="33" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C97" s="27">
         <v>7.33</v>
@@ -3922,7 +3877,7 @@
         <v>45907</v>
       </c>
       <c r="B98" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C98" s="27">
         <v>2</v>
@@ -3936,7 +3891,7 @@
     <row r="99" spans="1:5">
       <c r="A99" s="31"/>
       <c r="B99" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C99" s="27">
         <v>2</v>
@@ -3958,7 +3913,7 @@
     <row r="101" spans="1:5">
       <c r="A101" s="31"/>
       <c r="B101" s="33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C101" s="27">
         <v>2</v>
@@ -4016,7 +3971,7 @@
         <v>45925</v>
       </c>
       <c r="B105" s="33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C105" s="27">
         <v>10</v>
@@ -4032,7 +3987,7 @@
         <v>45930</v>
       </c>
       <c r="B106" s="33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C106" s="27">
         <v>15</v>
@@ -4048,7 +4003,7 @@
         <v>45934</v>
       </c>
       <c r="B107" s="33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C107" s="27">
         <v>2</v>
@@ -4076,7 +4031,7 @@
     <row r="109" spans="1:5">
       <c r="A109" s="31"/>
       <c r="B109" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C109" s="27">
         <v>0.45</v>
@@ -4092,7 +4047,7 @@
         <v>45965</v>
       </c>
       <c r="B110" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C110" s="27">
         <v>60</v>
@@ -4126,7 +4081,7 @@
         <v>45969</v>
       </c>
       <c r="B112" s="33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C112" s="27">
         <v>6</v>
@@ -4142,7 +4097,7 @@
         <v>45972</v>
       </c>
       <c r="B113" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C113" s="27">
         <v>60</v>
@@ -4194,7 +4149,7 @@
         <v>45980</v>
       </c>
       <c r="B116" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C116" s="27">
         <v>20</v>
@@ -4212,7 +4167,7 @@
         <v>45990</v>
       </c>
       <c r="B117" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C117" s="27">
         <v>1</v>
@@ -4230,7 +4185,7 @@
         <v>46012</v>
       </c>
       <c r="B118" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C118" s="27">
         <v>10</v>
@@ -4246,7 +4201,7 @@
         <v>46029</v>
       </c>
       <c r="B119" s="33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C119" s="27">
         <v>16</v>
@@ -4264,7 +4219,7 @@
         <v>46031</v>
       </c>
       <c r="B120" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C120" s="27">
         <v>2</v>
@@ -4280,7 +4235,7 @@
         <v>46038</v>
       </c>
       <c r="B121" s="33" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C121" s="27">
         <v>66</v>
@@ -4298,7 +4253,7 @@
         <v>46039</v>
       </c>
       <c r="B122" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C122" s="27">
         <v>1</v>
@@ -4314,7 +4269,7 @@
         <v>46047</v>
       </c>
       <c r="B123" s="33" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C123" s="27">
         <v>7</v>
@@ -4330,7 +4285,7 @@
     <row r="124" spans="1:5">
       <c r="A124" s="31"/>
       <c r="B124" s="33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C124" s="27">
         <v>11</v>
@@ -4364,7 +4319,7 @@
         <v>46055</v>
       </c>
       <c r="B126" s="33" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C126" s="27">
         <v>36</v>
@@ -4400,7 +4355,7 @@
         <v>46068</v>
       </c>
       <c r="B128" s="33" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C128" s="27">
         <v>78</v>
@@ -4416,7 +4371,7 @@
     <row r="129" spans="1:5">
       <c r="A129" s="36"/>
       <c r="B129" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C129" s="27">
         <v>30</v>
@@ -4434,7 +4389,7 @@
         <v>46069</v>
       </c>
       <c r="B130" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C130" s="27">
         <v>5</v>
@@ -4448,7 +4403,7 @@
     <row r="131" spans="1:5">
       <c r="A131" s="31"/>
       <c r="B131" s="33" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C131" s="27">
         <v>8</v>
@@ -4464,7 +4419,7 @@
     <row r="132" spans="1:5">
       <c r="A132" s="31"/>
       <c r="B132" s="33" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C132" s="27">
         <v>10</v>
@@ -4480,7 +4435,7 @@
         <v>46070</v>
       </c>
       <c r="B133" s="33" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C133" s="27">
         <v>8.32</v>
@@ -4494,7 +4449,7 @@
     <row r="134" spans="1:5">
       <c r="A134" s="31"/>
       <c r="B134" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C134" s="27">
         <v>10</v>
@@ -4510,7 +4465,7 @@
         <v>46074</v>
       </c>
       <c r="B135" s="33" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C135" s="27">
         <v>1.5</v>
@@ -4544,7 +4499,7 @@
         <v>46085</v>
       </c>
       <c r="B137" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C137" s="27">
         <v>10</v>
@@ -4578,7 +4533,7 @@
         <v>46130</v>
       </c>
       <c r="B139" s="33" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C139" s="27">
         <v>3</v>
@@ -4628,7 +4583,7 @@
         <v>46141</v>
       </c>
       <c r="B142" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C142" s="27">
         <v>10</v>
@@ -4642,7 +4597,7 @@
     <row r="143" spans="1:5">
       <c r="A143" s="31"/>
       <c r="B143" s="33" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C143" s="27">
         <v>10</v>
@@ -4658,7 +4613,7 @@
         <v>46144</v>
       </c>
       <c r="B144" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C144" s="27">
         <v>1</v>
@@ -4674,7 +4629,7 @@
         <v>46145</v>
       </c>
       <c r="B145" s="33" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C145" s="27">
         <v>10</v>
@@ -4690,7 +4645,7 @@
     <row r="146" spans="1:5">
       <c r="A146" s="31"/>
       <c r="B146" s="33" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C146" s="27">
         <v>6</v>
@@ -4706,7 +4661,7 @@
         <v>46146</v>
       </c>
       <c r="B147" s="33" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C147" s="27">
         <v>20</v>
@@ -4740,7 +4695,7 @@
         <v>46160</v>
       </c>
       <c r="B149" s="33" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C149" s="27">
         <v>5.04</v>
@@ -4774,7 +4729,7 @@
         <v>46184</v>
       </c>
       <c r="B151" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C151" s="27">
         <v>10</v>
@@ -4804,26 +4759,42 @@
       </c>
     </row>
     <row r="153" spans="1:5">
-      <c r="A153" s="37"/>
-      <c r="B153" s="38"/>
-      <c r="C153" s="39"/>
-      <c r="D153" s="39"/>
+      <c r="A153" s="37">
+        <v>46193</v>
+      </c>
+      <c r="B153" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C153" s="39">
+        <v>50</v>
+      </c>
+      <c r="D153" s="21">
+        <f>SUM(C3:C153)</f>
+        <v>-2944.11</v>
+      </c>
       <c r="E153" s="40"/>
     </row>
-    <row r="154" spans="1:5">
-      <c r="A154" s="41" t="s">
+    <row r="154" ht="14.25" spans="1:5">
+      <c r="A154" s="41"/>
+      <c r="B154" s="42"/>
+      <c r="C154" s="43"/>
+      <c r="D154" s="43"/>
+      <c r="E154" s="44"/>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="B154" s="41"/>
-      <c r="C154" s="41"/>
-      <c r="D154" s="41"/>
-      <c r="E154" s="41"/>
+      <c r="B155" s="45"/>
+      <c r="C155" s="45"/>
+      <c r="D155" s="45"/>
+      <c r="E155" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="40">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A154:E154"/>
+    <mergeCell ref="A155:E155"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A23:A24"/>
@@ -4871,7 +4842,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d874043d-01f5-4f74-9dd7-685054b41c05}</x14:id>
+          <x14:id>{98a94f9c-e0c3-4870-adac-f2367bfd30b1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4885,12 +4856,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f5a791b0-d87a-4c25-a890-176a0b0da86e}</x14:id>
+          <x14:id>{ff01631d-39c9-4c9f-bfc5-bba5bec48ea1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D153 D155:D1048576">
+  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D154 D156:D1048576">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="min"/>
@@ -4911,7 +4882,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{67c4f6a7-4045-43ef-8dca-a112ca968af6}</x14:id>
+          <x14:id>{86a41523-3f0d-4c7b-948f-419a27183af5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4925,12 +4896,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{af12ab7f-055f-41f1-a3fa-3d37ae336ddc}</x14:id>
+          <x14:id>{bd849766-44d4-4525-b1e4-5a48fdccd65e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I12 I14:I18 I20:I24 I26:I1048576">
+  <conditionalFormatting sqref="I1:I12 I20:I24 I26:I1048576 I14:I18">
     <cfRule type="dataBar" priority="22">
       <dataBar>
         <cfvo type="min"/>
@@ -4939,12 +4910,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9fe27cb5-6e00-4061-a4f8-db742fdb69e5}</x14:id>
+          <x14:id>{7f6ce5aa-7bdc-418d-a6a1-e7c6818c589c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I12 I14:I18 I20:I23 I26:I1048576">
+  <conditionalFormatting sqref="I1:I12 I20:I23 I26:I1048576 I14:I18">
     <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="min"/>
@@ -4953,7 +4924,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e4c70073-8daf-44d1-b044-949063a060fa}</x14:id>
+          <x14:id>{8e898cec-500c-4080-9cbe-38899be16c06}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4967,7 +4938,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f7b009f3-b4be-4526-b21f-3b1b30d72131}</x14:id>
+          <x14:id>{0e2c7e0f-8bb5-42f0-a174-dbfbe7ae683b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4981,12 +4952,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{16f48cc6-30e1-41de-8108-d466092ea8e7}</x14:id>
+          <x14:id>{c93b6b46-28f5-4cd2-aa8d-b6c797d31cf1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6 I9:I12 I14:I18 I20:I23 I26:I37 I39:I1048576">
+  <conditionalFormatting sqref="I2:I5 I39:I1048576 I9:I12 I14:I18 I20:I23 I26:I37 I7">
     <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
@@ -4995,12 +4966,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7504c11d-1cac-4be5-9426-f64b600ed25d}</x14:id>
+          <x14:id>{c715dd4e-a1a8-4450-84a1-294245efb383}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6 I9:I12 I14:I16 I18 I20:I23 I26:I37 I39:I1048576">
+  <conditionalFormatting sqref="I2:I5 I39:I1048576 I9:I12 I14:I16 I18 I20:I23 I26:I37 I7">
     <cfRule type="dataBar" priority="30">
       <dataBar>
         <cfvo type="min"/>
@@ -5009,7 +4980,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{be3970ca-ef8f-47fe-a732-143679a56917}</x14:id>
+          <x14:id>{58db08af-b63e-44a7-a054-279b5ee1b5db}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5046,7 +5017,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40">
+  <conditionalFormatting sqref="I3:I5 I39:I40 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I7">
     <cfRule type="dataBar" priority="36">
       <dataBar>
         <cfvo type="min"/>
@@ -5055,12 +5026,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6991815c-3116-4a25-a95e-4f7ca7fa6e85}</x14:id>
+          <x14:id>{8d32aa55-f044-437d-b59b-54f9c7916967}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40">
+  <conditionalFormatting sqref="I3:I5 I39:I40 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I7">
     <cfRule type="dataBar" priority="37">
       <dataBar>
         <cfvo type="min"/>
@@ -5069,12 +5040,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a621f7b0-9298-406e-867e-a0571996f1b5}</x14:id>
+          <x14:id>{f327f583-e5b7-4900-988b-c80741b2f08d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37">
+  <conditionalFormatting sqref="I3:I5 I36:I37 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33 I39:I40 I7">
     <cfRule type="dataBar" priority="34">
       <dataBar>
         <cfvo type="min"/>
@@ -5083,12 +5054,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fe5c2988-b27f-4e8e-8e30-bc12ddc9eb0c}</x14:id>
+          <x14:id>{9b086bb2-6dd0-427d-b3d3-7fcb7bf1cfa5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50 I36:I37 I31:I34">
+  <conditionalFormatting sqref="I3:I5 I31:I34 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50 I36:I37 I7">
     <cfRule type="dataBar" priority="32">
       <dataBar>
         <cfvo type="min"/>
@@ -5097,12 +5068,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{62b559a9-5a1f-48bd-b9a8-c5f3d39353ad}</x14:id>
+          <x14:id>{60ec178e-31ef-4f64-ab1d-0eebd9a6bf6b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37">
+  <conditionalFormatting sqref="I3:I5 I36:I37 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33 I39:I40 I7">
     <cfRule type="dataBar" priority="33">
       <dataBar>
         <cfvo type="min"/>
@@ -5111,12 +5082,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3d77954c-164a-45ae-a728-dd5c5a50bf95}</x14:id>
+          <x14:id>{1291ca00-67bd-412a-89b5-54c1a6af1fb2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I12 I20:I23 I18 I26:I29 I14:I16 I39:I50 I31:I37">
+  <conditionalFormatting sqref="I3:I5 I31:I37 I9:I12 I20:I23 I18 I26:I29 I14:I16 I39:I50 I7">
     <cfRule type="dataBar" priority="28">
       <dataBar>
         <cfvo type="min"/>
@@ -5125,12 +5096,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{91bb7c13-ae47-44ef-8617-869a0172883b}</x14:id>
+          <x14:id>{af1e29ee-bc5d-4681-a745-b361abd42c49}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29 I39:I50 I31:I37">
+  <conditionalFormatting sqref="I3:I5 I31:I37 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29 I39:I50 I7">
     <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
@@ -5139,12 +5110,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{73b2ceda-b8ee-4b73-92d8-f4873aa3098e}</x14:id>
+          <x14:id>{cf4fe5e7-b1b8-44be-b8fc-6e3f21bd54da}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I6 I9:I12 I20:I23 I14:I18 I26:I29 I31:I37 I39:I50">
+  <conditionalFormatting sqref="I3:I5 I39:I50 I9:I12 I20:I23 I14:I18 I26:I29 I31:I37 I7">
     <cfRule type="dataBar" priority="27">
       <dataBar>
         <cfvo type="min"/>
@@ -5153,12 +5124,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1ebf6f1e-aef9-46bb-8b26-d54908b9e4c0}</x14:id>
+          <x14:id>{2e577af9-f0b7-4600-a7fd-a88c0ecf8126}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I31:I50">
+  <conditionalFormatting sqref="I3:I7 I31:I50 I9:I12 I20:I23 I14:I18 I26:I29">
     <cfRule type="dataBar" priority="24">
       <dataBar>
         <cfvo type="min"/>
@@ -5167,12 +5138,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7cde5f1d-66f5-4f2f-9d9a-c2e3e7527720}</x14:id>
+          <x14:id>{8525fa08-37b2-48c0-a29f-38a9fdf3ef8b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I39:I50 I31:I37">
+  <conditionalFormatting sqref="I3:I7 I31:I37 I9:I12 I20:I23 I14:I18 I26:I29 I39:I50">
     <cfRule type="dataBar" priority="25">
       <dataBar>
         <cfvo type="min"/>
@@ -5181,7 +5152,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{edee130d-c17d-4af6-b5fe-c07c2afee020}</x14:id>
+          <x14:id>{a386a4b5-2781-420c-baa8-7a2d6f97403f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5195,7 +5166,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0088ad77-f334-4873-8cd7-1e22ad12206b}</x14:id>
+          <x14:id>{861a1f09-eddf-4662-b10c-6fa755587ec5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5203,13 +5174,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
+    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d874043d-01f5-4f74-9dd7-685054b41c05}">
+          <x14:cfRule type="dataBar" id="{98a94f9c-e0c3-4870-adac-f2367bfd30b1}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5220,7 +5191,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f5a791b0-d87a-4c25-a890-176a0b0da86e}">
+          <x14:cfRule type="dataBar" id="{ff01631d-39c9-4c9f-bfc5-bba5bec48ea1}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5231,7 +5202,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{67c4f6a7-4045-43ef-8dca-a112ca968af6}">
+          <x14:cfRule type="dataBar" id="{86a41523-3f0d-4c7b-948f-419a27183af5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5244,7 +5215,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{af12ab7f-055f-41f1-a3fa-3d37ae336ddc}">
+          <x14:cfRule type="dataBar" id="{bd849766-44d4-4525-b1e4-5a48fdccd65e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5255,7 +5226,7 @@
           <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9fe27cb5-6e00-4061-a4f8-db742fdb69e5}">
+          <x14:cfRule type="dataBar" id="{7f6ce5aa-7bdc-418d-a6a1-e7c6818c589c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5263,10 +5234,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I12 I14:I18 I20:I24 I26:I1048576</xm:sqref>
+          <xm:sqref>I1:I12 I20:I24 I26:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e4c70073-8daf-44d1-b044-949063a060fa}">
+          <x14:cfRule type="dataBar" id="{8e898cec-500c-4080-9cbe-38899be16c06}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5274,10 +5245,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I12 I14:I18 I20:I23 I26:I1048576</xm:sqref>
+          <xm:sqref>I1:I12 I20:I23 I26:I1048576 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f7b009f3-b4be-4526-b21f-3b1b30d72131}">
+          <x14:cfRule type="dataBar" id="{0e2c7e0f-8bb5-42f0-a174-dbfbe7ae683b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5288,7 +5259,7 @@
           <xm:sqref>I1:I18 I20:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{16f48cc6-30e1-41de-8108-d466092ea8e7}">
+          <x14:cfRule type="dataBar" id="{c93b6b46-28f5-4cd2-aa8d-b6c797d31cf1}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5299,7 +5270,7 @@
           <xm:sqref>I2 I30 I51:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7504c11d-1cac-4be5-9426-f64b600ed25d}">
+          <x14:cfRule type="dataBar" id="{c715dd4e-a1a8-4450-84a1-294245efb383}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5307,10 +5278,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I6 I9:I12 I14:I18 I20:I23 I26:I37 I39:I1048576</xm:sqref>
+          <xm:sqref>I2:I5 I39:I1048576 I9:I12 I14:I18 I20:I23 I26:I37 I7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{be3970ca-ef8f-47fe-a732-143679a56917}">
+          <x14:cfRule type="dataBar" id="{58db08af-b63e-44a7-a054-279b5ee1b5db}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5318,10 +5289,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I6 I9:I12 I14:I16 I18 I20:I23 I26:I37 I39:I1048576</xm:sqref>
+          <xm:sqref>I2:I5 I39:I1048576 I9:I12 I14:I16 I18 I20:I23 I26:I37 I7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6991815c-3116-4a25-a95e-4f7ca7fa6e85}">
+          <x14:cfRule type="dataBar" id="{8d32aa55-f044-437d-b59b-54f9c7916967}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5329,10 +5300,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
+          <xm:sqref>I3:I5 I39:I40 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a621f7b0-9298-406e-867e-a0571996f1b5}">
+          <x14:cfRule type="dataBar" id="{f327f583-e5b7-4900-988b-c80741b2f08d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5340,10 +5311,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I39:I40</xm:sqref>
+          <xm:sqref>I3:I5 I39:I40 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fe5c2988-b27f-4e8e-8e30-bc12ddc9eb0c}">
+          <x14:cfRule type="dataBar" id="{9b086bb2-6dd0-427d-b3d3-7fcb7bf1cfa5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5351,10 +5322,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
+          <xm:sqref>I3:I5 I36:I37 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33 I39:I40 I7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{62b559a9-5a1f-48bd-b9a8-c5f3d39353ad}">
+          <x14:cfRule type="dataBar" id="{60ec178e-31ef-4f64-ab1d-0eebd9a6bf6b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5362,10 +5333,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50 I36:I37 I31:I34</xm:sqref>
+          <xm:sqref>I3:I5 I31:I34 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50 I36:I37 I7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3d77954c-164a-45ae-a728-dd5c5a50bf95}">
+          <x14:cfRule type="dataBar" id="{1291ca00-67bd-412a-89b5-54c1a6af1fb2}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5373,10 +5344,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33 I39:I40 I36:I37</xm:sqref>
+          <xm:sqref>I3:I5 I36:I37 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33 I39:I40 I7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{91bb7c13-ae47-44ef-8617-869a0172883b}">
+          <x14:cfRule type="dataBar" id="{af1e29ee-bc5d-4681-a745-b361abd42c49}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5384,10 +5355,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I12 I20:I23 I18 I26:I29 I14:I16 I39:I50 I31:I37</xm:sqref>
+          <xm:sqref>I3:I5 I31:I37 I9:I12 I20:I23 I18 I26:I29 I14:I16 I39:I50 I7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{73b2ceda-b8ee-4b73-92d8-f4873aa3098e}">
+          <x14:cfRule type="dataBar" id="{cf4fe5e7-b1b8-44be-b8fc-6e3f21bd54da}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5395,10 +5366,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29 I39:I50 I31:I37</xm:sqref>
+          <xm:sqref>I3:I5 I31:I37 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29 I39:I50 I7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1ebf6f1e-aef9-46bb-8b26-d54908b9e4c0}">
+          <x14:cfRule type="dataBar" id="{2e577af9-f0b7-4600-a7fd-a88c0ecf8126}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5406,10 +5377,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I6 I9:I12 I20:I23 I14:I18 I26:I29 I31:I37 I39:I50</xm:sqref>
+          <xm:sqref>I3:I5 I39:I50 I9:I12 I20:I23 I14:I18 I26:I29 I31:I37 I7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7cde5f1d-66f5-4f2f-9d9a-c2e3e7527720}">
+          <x14:cfRule type="dataBar" id="{8525fa08-37b2-48c0-a29f-38a9fdf3ef8b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5417,10 +5388,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I31:I50</xm:sqref>
+          <xm:sqref>I3:I7 I31:I50 I9:I12 I20:I23 I14:I18 I26:I29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{edee130d-c17d-4af6-b5fe-c07c2afee020}">
+          <x14:cfRule type="dataBar" id="{a386a4b5-2781-420c-baa8-7a2d6f97403f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5428,10 +5399,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I7 I9:I12 I20:I23 I14:I18 I26:I29 I39:I50 I31:I37</xm:sqref>
+          <xm:sqref>I3:I7 I31:I37 I9:I12 I20:I23 I14:I18 I26:I29 I39:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0088ad77-f334-4873-8cd7-1e22ad12206b}">
+          <x14:cfRule type="dataBar" id="{861a1f09-eddf-4662-b10c-6fa755587ec5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="114">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -69,13 +69,19 @@
     <t>Moquan0_0</t>
   </si>
   <si>
+    <t>AL_1S_2</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>MoFangYa_</t>
+  </si>
+  <si>
     <t>Celi2357</t>
   </si>
   <si>
-    <t>MoFangYa_</t>
-  </si>
-  <si>
-    <t>AL_1S_2</t>
+    <t>↓1</t>
   </si>
   <si>
     <t>BYyihan</t>
@@ -90,16 +96,10 @@
     <t>KIRINIT</t>
   </si>
   <si>
-    <t>↑1</t>
-  </si>
-  <si>
     <t>zkiftie</t>
   </si>
   <si>
     <t>Disha_UUU2</t>
-  </si>
-  <si>
-    <t>↓1</t>
   </si>
   <si>
     <t>_LoveSelf_</t>
@@ -1216,7 +1216,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1331,6 +1331,9 @@
     <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1339,6 +1342,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1676,7 +1685,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K155"/>
+  <dimension ref="A1:K157"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -1763,17 +1772,20 @@
         <v>13</v>
       </c>
       <c r="I3" s="16">
-        <f>SUM(C10,C15,C18:C18,C21:C21,C24,C31:C31,C36,C43,C88,C90,C114)</f>
-        <v>504.2</v>
+        <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150,C152,C154)</f>
+        <v>507</v>
       </c>
       <c r="J3" s="3">
-        <v>45975</v>
+        <v>46193</v>
+      </c>
+      <c r="K3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="12"/>
       <c r="B4" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="13">
         <v>0.55</v>
@@ -1784,20 +1796,23 @@
         <v>2</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="16">
-        <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150,C152)</f>
-        <v>497</v>
+        <f>SUM(C10,C15,C18:C18,C21:C21,C24,C31:C31,C36,C43,C88,C90,C114)</f>
+        <v>504.2</v>
       </c>
       <c r="J4" s="3">
-        <v>46192</v>
+        <v>45975</v>
+      </c>
+      <c r="K4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="12"/>
       <c r="B5" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" s="13">
         <v>2</v>
@@ -1808,7 +1823,7 @@
         <v>3</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I5" s="16">
         <f>SUM(C28:C28,C32:C32,C34:C34,C37,C39,C42:C42,C54,C57,C59,C61,C67,C69,C71,C76)</f>
@@ -1821,7 +1836,7 @@
     <row r="6" spans="1:11">
       <c r="A6" s="12"/>
       <c r="B6" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="13">
         <v>3</v>
@@ -1832,7 +1847,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I6" s="2">
         <f>SUM(C110:C110,C113,C116,C118,C129,C134,C142,C151,C153)</f>
@@ -1841,14 +1856,11 @@
       <c r="J6" s="3">
         <v>46193</v>
       </c>
-      <c r="K6" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="12"/>
       <c r="B7" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="13">
         <v>1.28</v>
@@ -1859,7 +1871,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I7" s="16">
         <f>SUM(C11,C16,C29,C25,C62,C81:C81)</f>
@@ -1868,9 +1880,6 @@
       <c r="J7" s="3">
         <v>45829</v>
       </c>
-      <c r="K7" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="17">
@@ -1935,7 +1944,7 @@
         <v>44774</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C10" s="13">
         <v>39</v>
@@ -1964,7 +1973,7 @@
         <v>44781</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" s="13">
         <v>130</v>
@@ -2082,7 +2091,7 @@
         <v>44926</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C15" s="13">
         <v>120</v>
@@ -2113,7 +2122,7 @@
         <v>44946</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="13">
         <v>13</v>
@@ -2172,7 +2181,7 @@
         <v>44958</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C18" s="13">
         <f>11+45+29</f>
@@ -2256,7 +2265,7 @@
         <v>45138</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C21" s="13">
         <f>6+84+10+10</f>
@@ -2341,7 +2350,7 @@
     <row r="24" spans="1:10">
       <c r="A24" s="17"/>
       <c r="B24" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C24" s="13">
         <v>9</v>
@@ -2368,7 +2377,7 @@
         <v>45160</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C25" s="13">
         <v>3</v>
@@ -2449,7 +2458,7 @@
         <v>45249</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C28" s="13">
         <v>15.5</v>
@@ -2480,7 +2489,7 @@
         <v>45305</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C29" s="13">
         <v>50</v>
@@ -2538,7 +2547,7 @@
         <v>45341</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C31" s="13">
         <v>68</v>
@@ -2568,7 +2577,7 @@
         <v>45368</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C32" s="13">
         <v>33.01</v>
@@ -2628,7 +2637,7 @@
         <v>45394</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C34" s="13">
         <v>16</v>
@@ -2689,7 +2698,7 @@
         <v>45403</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C36" s="13">
         <v>3.2</v>
@@ -2703,7 +2712,7 @@
         <v>34</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I36" s="16">
         <v>3</v>
@@ -2717,7 +2726,7 @@
         <v>45403</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C37" s="13">
         <v>5</v>
@@ -2777,7 +2786,7 @@
         <v>45417</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C39" s="13">
         <v>11</v>
@@ -2824,7 +2833,7 @@
         <v>38</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I40" s="16">
         <v>2</v>
@@ -2867,7 +2876,7 @@
         <v>45494</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C42" s="13">
         <v>82.45</v>
@@ -2895,7 +2904,7 @@
     <row r="43" spans="1:10">
       <c r="A43" s="17"/>
       <c r="B43" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C43" s="13">
         <v>2</v>
@@ -2908,7 +2917,7 @@
         <v>41</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I43" s="16">
         <v>1.28</v>
@@ -2922,7 +2931,7 @@
         <v>45495</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C44" s="27">
         <v>8</v>
@@ -2991,7 +3000,7 @@
         <v>44</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I46" s="16">
         <v>0.55</v>
@@ -3061,7 +3070,7 @@
     <row r="49" spans="1:10">
       <c r="A49" s="31"/>
       <c r="B49" s="26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C49" s="27">
         <v>5</v>
@@ -3118,7 +3127,7 @@
         <v>45507</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C51" s="27">
         <v>14</v>
@@ -3149,7 +3158,7 @@
         <v>45508</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C53" s="27">
         <v>9</v>
@@ -3165,7 +3174,7 @@
     <row r="54" spans="1:10">
       <c r="A54" s="31"/>
       <c r="B54" s="26" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C54" s="27">
         <v>10</v>
@@ -3205,7 +3214,7 @@
         <v>45510</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C57" s="27">
         <v>40</v>
@@ -3223,7 +3232,7 @@
         <v>45525</v>
       </c>
       <c r="B58" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C58" s="27">
         <f>6+5+5+5+6+5+5+5+30</f>
@@ -3242,7 +3251,7 @@
         <v>45525</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C59" s="27">
         <v>6</v>
@@ -3260,7 +3269,7 @@
         <v>45549</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C60" s="27">
         <v>30</v>
@@ -3276,7 +3285,7 @@
     <row r="61" spans="1:10">
       <c r="A61" s="29"/>
       <c r="B61" s="33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C61" s="27">
         <v>20</v>
@@ -3291,7 +3300,7 @@
         <v>45551</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C62" s="27">
         <v>17</v>
@@ -3307,7 +3316,7 @@
         <v>45552</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C63" s="27">
         <v>40</v>
@@ -3352,7 +3361,7 @@
         <v>45584</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C66" s="27">
         <v>30</v>
@@ -3370,7 +3379,7 @@
         <v>45584</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C67" s="27">
         <v>7</v>
@@ -3386,7 +3395,7 @@
         <v>45592</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C68" s="27">
         <v>60</v>
@@ -3404,7 +3413,7 @@
         <v>45597</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C69" s="27">
         <v>5</v>
@@ -3422,7 +3431,7 @@
         <v>45598</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C70" s="27">
         <v>5</v>
@@ -3440,7 +3449,7 @@
         <v>45612</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C71" s="27">
         <v>5</v>
@@ -3456,7 +3465,7 @@
         <v>45619</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C72" s="27">
         <v>15</v>
@@ -3521,7 +3530,7 @@
         <v>45654</v>
       </c>
       <c r="B76" s="33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C76" s="27">
         <v>30</v>
@@ -3539,7 +3548,7 @@
         <v>45686</v>
       </c>
       <c r="B77" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C77" s="27">
         <v>9</v>
@@ -3605,7 +3614,7 @@
         <v>45829</v>
       </c>
       <c r="B81" s="33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C81" s="27">
         <v>26.66</v>
@@ -3719,7 +3728,7 @@
         <v>45877</v>
       </c>
       <c r="B88" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C88" s="27">
         <v>5</v>
@@ -3753,7 +3762,7 @@
         <v>45879</v>
       </c>
       <c r="B90" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C90" s="27">
         <v>26</v>
@@ -3771,7 +3780,7 @@
         <v>45881</v>
       </c>
       <c r="B91" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C91" s="27">
         <v>5</v>
@@ -3827,7 +3836,7 @@
         <v>45886</v>
       </c>
       <c r="B95" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C95" s="27">
         <v>5</v>
@@ -4047,7 +4056,7 @@
         <v>45965</v>
       </c>
       <c r="B110" s="33" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C110" s="27">
         <v>60</v>
@@ -4097,7 +4106,7 @@
         <v>45972</v>
       </c>
       <c r="B113" s="33" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C113" s="27">
         <v>60</v>
@@ -4115,7 +4124,7 @@
         <v>45975</v>
       </c>
       <c r="B114" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C114" s="27">
         <v>37</v>
@@ -4149,7 +4158,7 @@
         <v>45980</v>
       </c>
       <c r="B116" s="33" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C116" s="27">
         <v>20</v>
@@ -4185,7 +4194,7 @@
         <v>46012</v>
       </c>
       <c r="B118" s="33" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C118" s="27">
         <v>10</v>
@@ -4301,7 +4310,7 @@
         <v>46054</v>
       </c>
       <c r="B125" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C125" s="27">
         <v>5</v>
@@ -4337,7 +4346,7 @@
         <v>46057</v>
       </c>
       <c r="B127" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C127" s="27">
         <v>5</v>
@@ -4371,7 +4380,7 @@
     <row r="129" spans="1:5">
       <c r="A129" s="36"/>
       <c r="B129" s="33" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C129" s="27">
         <v>30</v>
@@ -4449,7 +4458,7 @@
     <row r="134" spans="1:5">
       <c r="A134" s="31"/>
       <c r="B134" s="33" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C134" s="27">
         <v>10</v>
@@ -4481,7 +4490,7 @@
         <v>46079</v>
       </c>
       <c r="B136" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C136" s="27">
         <v>25</v>
@@ -4515,7 +4524,7 @@
         <v>46123</v>
       </c>
       <c r="B138" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C138" s="27">
         <v>70</v>
@@ -4565,7 +4574,7 @@
         <v>46136</v>
       </c>
       <c r="B141" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C141" s="27">
         <v>15</v>
@@ -4583,7 +4592,7 @@
         <v>46141</v>
       </c>
       <c r="B142" s="33" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C142" s="27">
         <v>10</v>
@@ -4677,7 +4686,7 @@
         <v>46158</v>
       </c>
       <c r="B148" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C148" s="27">
         <v>20</v>
@@ -4711,7 +4720,7 @@
         <v>46179</v>
       </c>
       <c r="B150" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C150" s="27">
         <v>30</v>
@@ -4729,7 +4738,7 @@
         <v>46184</v>
       </c>
       <c r="B151" s="33" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C151" s="27">
         <v>10</v>
@@ -4745,7 +4754,7 @@
         <v>46192</v>
       </c>
       <c r="B152" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C152" s="27">
         <v>20</v>
@@ -4762,39 +4771,62 @@
       <c r="A153" s="37">
         <v>46193</v>
       </c>
-      <c r="B153" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="C153" s="39">
+      <c r="B153" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="C153" s="27">
         <v>50</v>
       </c>
       <c r="D153" s="21">
         <f>SUM(C3:C153)</f>
         <v>-2944.11</v>
       </c>
-      <c r="E153" s="40"/>
-    </row>
-    <row r="154" ht="14.25" spans="1:5">
-      <c r="A154" s="41"/>
-      <c r="B154" s="42"/>
-      <c r="C154" s="43"/>
-      <c r="D154" s="43"/>
-      <c r="E154" s="44"/>
+      <c r="E153" s="34"/>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="38"/>
+      <c r="B154" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C154" s="40">
+        <v>10</v>
+      </c>
+      <c r="D154" s="21">
+        <f>SUM(C3:C154)</f>
+        <v>-2934.11</v>
+      </c>
+      <c r="E154" s="41" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="155" spans="1:5">
-      <c r="A155" s="45" t="s">
+      <c r="A155" s="42"/>
+      <c r="B155" s="39"/>
+      <c r="C155" s="40"/>
+      <c r="D155" s="43"/>
+      <c r="E155" s="41"/>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="44"/>
+      <c r="B156" s="45"/>
+      <c r="C156" s="46"/>
+      <c r="D156" s="46"/>
+      <c r="E156" s="47"/>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="B155" s="45"/>
-      <c r="C155" s="45"/>
-      <c r="D155" s="45"/>
-      <c r="E155" s="45"/>
+      <c r="B157" s="48"/>
+      <c r="C157" s="48"/>
+      <c r="D157" s="48"/>
+      <c r="E157" s="48"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="41">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A155:E155"/>
+    <mergeCell ref="A157:E157"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A23:A24"/>
@@ -4817,6 +4849,7 @@
     <mergeCell ref="A133:A134"/>
     <mergeCell ref="A142:A143"/>
     <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A153:A154"/>
     <mergeCell ref="D3:D7"/>
     <mergeCell ref="D18:D19"/>
     <mergeCell ref="D23:D24"/>
@@ -4842,7 +4875,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{98a94f9c-e0c3-4870-adac-f2367bfd30b1}</x14:id>
+          <x14:id>{c819861f-668f-4259-b4bb-d384cd5aff57}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4856,12 +4889,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ff01631d-39c9-4c9f-bfc5-bba5bec48ea1}</x14:id>
+          <x14:id>{90938403-bc59-4aa5-be85-7a6b49387e1f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D154 D156:D1048576">
+  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D156 D158:D1048576">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="min"/>
@@ -4882,7 +4915,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{86a41523-3f0d-4c7b-948f-419a27183af5}</x14:id>
+          <x14:id>{f1b0efb8-5c5d-4d32-b9ab-1af08cf87039}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4896,12 +4929,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bd849766-44d4-4525-b1e4-5a48fdccd65e}</x14:id>
+          <x14:id>{e2f33578-75a6-44dc-b1e1-9325d1cb347d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I12 I20:I24 I26:I1048576 I14:I18">
+  <conditionalFormatting sqref="I1:I12 I26:I1048576 I14:I18 I20:I24">
     <cfRule type="dataBar" priority="22">
       <dataBar>
         <cfvo type="min"/>
@@ -4910,12 +4943,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7f6ce5aa-7bdc-418d-a6a1-e7c6818c589c}</x14:id>
+          <x14:id>{3ee43b40-47e4-47a3-aeea-295a4d26d50d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I12 I20:I23 I26:I1048576 I14:I18">
+  <conditionalFormatting sqref="I1:I12 I26:I1048576 I14:I18 I20:I23">
     <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="min"/>
@@ -4924,7 +4957,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e898cec-500c-4080-9cbe-38899be16c06}</x14:id>
+          <x14:id>{afba1f70-d754-4277-ab3b-386407a9bd0d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4938,7 +4971,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0e2c7e0f-8bb5-42f0-a174-dbfbe7ae683b}</x14:id>
+          <x14:id>{c8c8a910-5cb9-4ec9-8ccd-e90e39fca01a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4952,12 +4985,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c93b6b46-28f5-4cd2-aa8d-b6c797d31cf1}</x14:id>
+          <x14:id>{6ba8c373-4340-4c3c-9e93-94534c36cf78}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5 I39:I1048576 I9:I12 I14:I18 I20:I23 I26:I37 I7">
+  <conditionalFormatting sqref="I2:I5 I26:I37 I9:I12 I39:I1048576 I20:I23 I14:I18 I7">
     <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
@@ -4966,12 +4999,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c715dd4e-a1a8-4450-84a1-294245efb383}</x14:id>
+          <x14:id>{89d366d6-92b1-48e8-8d55-1d82681fef7d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5 I39:I1048576 I9:I12 I14:I16 I18 I20:I23 I26:I37 I7">
+  <conditionalFormatting sqref="I2:I5 I9:I12 I14:I16 I39:I1048576 I20:I23 I18 I7 I26:I37">
     <cfRule type="dataBar" priority="30">
       <dataBar>
         <cfvo type="min"/>
@@ -4980,7 +5013,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{58db08af-b63e-44a7-a054-279b5ee1b5db}</x14:id>
+          <x14:id>{d69ac191-40e2-46e5-933e-5aa5d1ff3c18}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5017,7 +5050,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I5 I39:I40 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I7">
+  <conditionalFormatting sqref="I42:I47 I3:I5 I7 I39:I40 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33">
     <cfRule type="dataBar" priority="36">
       <dataBar>
         <cfvo type="min"/>
@@ -5026,12 +5059,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8d32aa55-f044-437d-b59b-54f9c7916967}</x14:id>
+          <x14:id>{c80afe5a-992e-49a2-9536-60242f5c65df}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I5 I39:I40 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I7">
+  <conditionalFormatting sqref="I42:I47 I3:I5 I7 I39:I40 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33">
     <cfRule type="dataBar" priority="37">
       <dataBar>
         <cfvo type="min"/>
@@ -5040,12 +5073,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f327f583-e5b7-4900-988b-c80741b2f08d}</x14:id>
+          <x14:id>{c660a138-f8d7-47d3-99e7-f6a54001241e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I5 I36:I37 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33 I39:I40 I7">
+  <conditionalFormatting sqref="I39:I40 I3:I5 I7 I36:I37 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33">
     <cfRule type="dataBar" priority="34">
       <dataBar>
         <cfvo type="min"/>
@@ -5054,12 +5087,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9b086bb2-6dd0-427d-b3d3-7fcb7bf1cfa5}</x14:id>
+          <x14:id>{f31a0447-ffca-4ac3-9bb0-bb658642ca58}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I5 I31:I34 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50 I36:I37 I7">
+  <conditionalFormatting sqref="I36:I37 I3:I5 I7 I31:I34 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50">
     <cfRule type="dataBar" priority="32">
       <dataBar>
         <cfvo type="min"/>
@@ -5068,12 +5101,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{60ec178e-31ef-4f64-ab1d-0eebd9a6bf6b}</x14:id>
+          <x14:id>{28bb1981-d57d-4a1a-8952-6f2efe47d18f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I5 I36:I37 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33 I39:I40 I7">
+  <conditionalFormatting sqref="I39:I40 I3:I5 I7 I36:I37 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33">
     <cfRule type="dataBar" priority="33">
       <dataBar>
         <cfvo type="min"/>
@@ -5082,12 +5115,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1291ca00-67bd-412a-89b5-54c1a6af1fb2}</x14:id>
+          <x14:id>{4ff42c0e-31bd-4704-8135-d893b82f56cc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I5 I31:I37 I9:I12 I20:I23 I18 I26:I29 I14:I16 I39:I50 I7">
+  <conditionalFormatting sqref="I39:I50 I3:I5 I7 I31:I37 I9:I12 I20:I23 I18 I26:I29 I14:I16">
     <cfRule type="dataBar" priority="28">
       <dataBar>
         <cfvo type="min"/>
@@ -5096,12 +5129,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{af1e29ee-bc5d-4681-a745-b361abd42c49}</x14:id>
+          <x14:id>{d73dbd87-a4ef-4a56-82b1-52adc1156ef1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I5 I31:I37 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29 I39:I50 I7">
+  <conditionalFormatting sqref="I39:I50 I3:I5 I7 I31:I37 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29">
     <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
@@ -5110,12 +5143,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cf4fe5e7-b1b8-44be-b8fc-6e3f21bd54da}</x14:id>
+          <x14:id>{298ba7be-3635-4279-8f3a-cbc8d5262c38}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I5 I39:I50 I9:I12 I20:I23 I14:I18 I26:I29 I31:I37 I7">
+  <conditionalFormatting sqref="I31:I37 I3:I5 I7 I39:I50 I9:I12 I20:I23 I14:I18 I26:I29">
     <cfRule type="dataBar" priority="27">
       <dataBar>
         <cfvo type="min"/>
@@ -5124,12 +5157,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2e577af9-f0b7-4600-a7fd-a88c0ecf8126}</x14:id>
+          <x14:id>{91c8aad1-a210-428d-a2f2-7a3b85a9543d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I7 I31:I50 I9:I12 I20:I23 I14:I18 I26:I29">
+  <conditionalFormatting sqref="I14:I18 I3:I7 I26:I29 I31:I50 I9:I12 I20:I23">
     <cfRule type="dataBar" priority="24">
       <dataBar>
         <cfvo type="min"/>
@@ -5138,12 +5171,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8525fa08-37b2-48c0-a29f-38a9fdf3ef8b}</x14:id>
+          <x14:id>{b64add38-6eed-4ee6-8198-3a8159f02cb5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I7 I31:I37 I9:I12 I20:I23 I14:I18 I26:I29 I39:I50">
+  <conditionalFormatting sqref="I26:I29 I3:I7 I39:I50 I31:I37 I9:I12 I20:I23 I14:I18">
     <cfRule type="dataBar" priority="25">
       <dataBar>
         <cfvo type="min"/>
@@ -5152,12 +5185,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a386a4b5-2781-420c-baa8-7a2d6f97403f}</x14:id>
+          <x14:id>{ac8396ae-2423-472a-9b22-d9688bafa5cd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I24 I26:I29 I31:I50">
+  <conditionalFormatting sqref="I26:I29 I3:I24 I31:I50">
     <cfRule type="dataBar" priority="20">
       <dataBar>
         <cfvo type="min"/>
@@ -5166,7 +5199,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{861a1f09-eddf-4662-b10c-6fa755587ec5}</x14:id>
+          <x14:id>{47b548a5-ccdc-4d43-9a8b-88e546b6236c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5174,13 +5207,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
+    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{98a94f9c-e0c3-4870-adac-f2367bfd30b1}">
+          <x14:cfRule type="dataBar" id="{c819861f-668f-4259-b4bb-d384cd5aff57}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5191,7 +5224,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ff01631d-39c9-4c9f-bfc5-bba5bec48ea1}">
+          <x14:cfRule type="dataBar" id="{90938403-bc59-4aa5-be85-7a6b49387e1f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5202,7 +5235,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{86a41523-3f0d-4c7b-948f-419a27183af5}">
+          <x14:cfRule type="dataBar" id="{f1b0efb8-5c5d-4d32-b9ab-1af08cf87039}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5215,7 +5248,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bd849766-44d4-4525-b1e4-5a48fdccd65e}">
+          <x14:cfRule type="dataBar" id="{e2f33578-75a6-44dc-b1e1-9325d1cb347d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5226,7 +5259,7 @@
           <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7f6ce5aa-7bdc-418d-a6a1-e7c6818c589c}">
+          <x14:cfRule type="dataBar" id="{3ee43b40-47e4-47a3-aeea-295a4d26d50d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5234,10 +5267,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I12 I20:I24 I26:I1048576 I14:I18</xm:sqref>
+          <xm:sqref>I1:I12 I26:I1048576 I14:I18 I20:I24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8e898cec-500c-4080-9cbe-38899be16c06}">
+          <x14:cfRule type="dataBar" id="{afba1f70-d754-4277-ab3b-386407a9bd0d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5245,10 +5278,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I12 I20:I23 I26:I1048576 I14:I18</xm:sqref>
+          <xm:sqref>I1:I12 I26:I1048576 I14:I18 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0e2c7e0f-8bb5-42f0-a174-dbfbe7ae683b}">
+          <x14:cfRule type="dataBar" id="{c8c8a910-5cb9-4ec9-8ccd-e90e39fca01a}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5259,7 +5292,7 @@
           <xm:sqref>I1:I18 I20:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c93b6b46-28f5-4cd2-aa8d-b6c797d31cf1}">
+          <x14:cfRule type="dataBar" id="{6ba8c373-4340-4c3c-9e93-94534c36cf78}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5270,7 +5303,7 @@
           <xm:sqref>I2 I30 I51:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c715dd4e-a1a8-4450-84a1-294245efb383}">
+          <x14:cfRule type="dataBar" id="{89d366d6-92b1-48e8-8d55-1d82681fef7d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5278,10 +5311,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I5 I39:I1048576 I9:I12 I14:I18 I20:I23 I26:I37 I7</xm:sqref>
+          <xm:sqref>I2:I5 I26:I37 I9:I12 I39:I1048576 I20:I23 I14:I18 I7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{58db08af-b63e-44a7-a054-279b5ee1b5db}">
+          <x14:cfRule type="dataBar" id="{d69ac191-40e2-46e5-933e-5aa5d1ff3c18}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5289,10 +5322,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I5 I39:I1048576 I9:I12 I14:I16 I18 I20:I23 I26:I37 I7</xm:sqref>
+          <xm:sqref>I2:I5 I9:I12 I14:I16 I39:I1048576 I20:I23 I18 I7 I26:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8d32aa55-f044-437d-b59b-54f9c7916967}">
+          <x14:cfRule type="dataBar" id="{c80afe5a-992e-49a2-9536-60242f5c65df}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5300,10 +5333,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I5 I39:I40 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I7</xm:sqref>
+          <xm:sqref>I42:I47 I3:I5 I7 I39:I40 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f327f583-e5b7-4900-988b-c80741b2f08d}">
+          <x14:cfRule type="dataBar" id="{c660a138-f8d7-47d3-99e7-f6a54001241e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5311,10 +5344,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I5 I39:I40 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33 I42:I47 I7</xm:sqref>
+          <xm:sqref>I42:I47 I3:I5 I7 I39:I40 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9b086bb2-6dd0-427d-b3d3-7fcb7bf1cfa5}">
+          <x14:cfRule type="dataBar" id="{f31a0447-ffca-4ac3-9bb0-bb658642ca58}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5322,10 +5355,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I5 I36:I37 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33 I39:I40 I7</xm:sqref>
+          <xm:sqref>I39:I40 I3:I5 I7 I36:I37 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{60ec178e-31ef-4f64-ab1d-0eebd9a6bf6b}">
+          <x14:cfRule type="dataBar" id="{28bb1981-d57d-4a1a-8952-6f2efe47d18f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5333,10 +5366,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I5 I31:I34 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50 I36:I37 I7</xm:sqref>
+          <xm:sqref>I36:I37 I3:I5 I7 I31:I34 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1291ca00-67bd-412a-89b5-54c1a6af1fb2}">
+          <x14:cfRule type="dataBar" id="{4ff42c0e-31bd-4704-8135-d893b82f56cc}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5344,10 +5377,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I5 I36:I37 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33 I39:I40 I7</xm:sqref>
+          <xm:sqref>I39:I40 I3:I5 I7 I36:I37 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{af1e29ee-bc5d-4681-a745-b361abd42c49}">
+          <x14:cfRule type="dataBar" id="{d73dbd87-a4ef-4a56-82b1-52adc1156ef1}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5355,10 +5388,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I5 I31:I37 I9:I12 I20:I23 I18 I26:I29 I14:I16 I39:I50 I7</xm:sqref>
+          <xm:sqref>I39:I50 I3:I5 I7 I31:I37 I9:I12 I20:I23 I18 I26:I29 I14:I16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cf4fe5e7-b1b8-44be-b8fc-6e3f21bd54da}">
+          <x14:cfRule type="dataBar" id="{298ba7be-3635-4279-8f3a-cbc8d5262c38}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5366,10 +5399,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I5 I31:I37 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29 I39:I50 I7</xm:sqref>
+          <xm:sqref>I39:I50 I3:I5 I7 I31:I37 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2e577af9-f0b7-4600-a7fd-a88c0ecf8126}">
+          <x14:cfRule type="dataBar" id="{91c8aad1-a210-428d-a2f2-7a3b85a9543d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5377,10 +5410,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I5 I39:I50 I9:I12 I20:I23 I14:I18 I26:I29 I31:I37 I7</xm:sqref>
+          <xm:sqref>I31:I37 I3:I5 I7 I39:I50 I9:I12 I20:I23 I14:I18 I26:I29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8525fa08-37b2-48c0-a29f-38a9fdf3ef8b}">
+          <x14:cfRule type="dataBar" id="{b64add38-6eed-4ee6-8198-3a8159f02cb5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5388,10 +5421,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I7 I31:I50 I9:I12 I20:I23 I14:I18 I26:I29</xm:sqref>
+          <xm:sqref>I14:I18 I3:I7 I26:I29 I31:I50 I9:I12 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a386a4b5-2781-420c-baa8-7a2d6f97403f}">
+          <x14:cfRule type="dataBar" id="{ac8396ae-2423-472a-9b22-d9688bafa5cd}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5399,10 +5432,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I7 I31:I37 I9:I12 I20:I23 I14:I18 I26:I29 I39:I50</xm:sqref>
+          <xm:sqref>I26:I29 I3:I7 I39:I50 I31:I37 I9:I12 I20:I23 I14:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{861a1f09-eddf-4662-b10c-6fa755587ec5}">
+          <x14:cfRule type="dataBar" id="{47b548a5-ccdc-4d43-9a8b-88e546b6236c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5410,7 +5443,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I3:I24 I26:I29 I31:I50</xm:sqref>
+          <xm:sqref>I26:I29 I3:I24 I31:I50</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="114">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -72,61 +72,61 @@
     <t>AL_1S_2</t>
   </si>
   <si>
-    <t>↑1</t>
-  </si>
-  <si>
     <t>MoFangYa_</t>
   </si>
   <si>
     <t>Celi2357</t>
   </si>
   <si>
+    <t>BYyihan</t>
+  </si>
+  <si>
+    <t>qmzp_</t>
+  </si>
+  <si>
+    <t>Mtve</t>
+  </si>
+  <si>
+    <t>KIRINIT</t>
+  </si>
+  <si>
+    <t>zkiftie</t>
+  </si>
+  <si>
+    <t>Disha_UUU2</t>
+  </si>
+  <si>
+    <t>_LoveSelf_</t>
+  </si>
+  <si>
+    <t>dog</t>
+  </si>
+  <si>
+    <t>NGZI</t>
+  </si>
+  <si>
+    <t>Guramchik</t>
+  </si>
+  <si>
+    <t>Press_on</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>用于购买内存条</t>
+  </si>
+  <si>
+    <t>partyking1145</t>
+  </si>
+  <si>
     <t>↓1</t>
   </si>
   <si>
-    <t>BYyihan</t>
-  </si>
-  <si>
-    <t>qmzp_</t>
-  </si>
-  <si>
-    <t>Mtve</t>
-  </si>
-  <si>
-    <t>KIRINIT</t>
-  </si>
-  <si>
-    <t>zkiftie</t>
-  </si>
-  <si>
-    <t>Disha_UUU2</t>
-  </si>
-  <si>
-    <t>_LoveSelf_</t>
-  </si>
-  <si>
-    <t>dog</t>
-  </si>
-  <si>
-    <t>NGZI</t>
-  </si>
-  <si>
-    <t>Guramchik</t>
-  </si>
-  <si>
-    <t>partyking1145</t>
-  </si>
-  <si>
-    <t>用于购买内存条</t>
-  </si>
-  <si>
     <t>购买内存条</t>
   </si>
   <si>
     <t>xiaoshenjin233</t>
-  </si>
-  <si>
-    <t>moqi</t>
   </si>
   <si>
     <t>主板、硬盘、机箱</t>
@@ -1216,7 +1216,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1327,27 +1327,6 @@
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1778,14 +1757,11 @@
       <c r="J3" s="3">
         <v>46193</v>
       </c>
-      <c r="K3" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="12"/>
       <c r="B4" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="13">
         <v>0.55</v>
@@ -1796,7 +1772,7 @@
         <v>2</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I4" s="16">
         <f>SUM(C10,C15,C18:C18,C21:C21,C24,C31:C31,C36,C43,C88,C90,C114)</f>
@@ -1805,14 +1781,11 @@
       <c r="J4" s="3">
         <v>45975</v>
       </c>
-      <c r="K4" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="12"/>
       <c r="B5" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="13">
         <v>2</v>
@@ -1823,7 +1796,7 @@
         <v>3</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I5" s="16">
         <f>SUM(C28:C28,C32:C32,C34:C34,C37,C39,C42:C42,C54,C57,C59,C61,C67,C69,C71,C76)</f>
@@ -1836,7 +1809,7 @@
     <row r="6" spans="1:11">
       <c r="A6" s="12"/>
       <c r="B6" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" s="13">
         <v>3</v>
@@ -1847,7 +1820,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I6" s="2">
         <f>SUM(C110:C110,C113,C116,C118,C129,C134,C142,C151,C153)</f>
@@ -1860,7 +1833,7 @@
     <row r="7" spans="1:11">
       <c r="A7" s="12"/>
       <c r="B7" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="13">
         <v>1.28</v>
@@ -1871,7 +1844,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I7" s="16">
         <f>SUM(C11,C16,C29,C25,C62,C81:C81)</f>
@@ -1886,7 +1859,7 @@
         <v>44164</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="13">
         <v>9</v>
@@ -1900,7 +1873,7 @@
         <v>6</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I8" s="2">
         <f>SUM(C121,C123,C126,C128,C131)</f>
@@ -1915,7 +1888,7 @@
         <v>44213</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="13">
         <v>0.1</v>
@@ -1929,7 +1902,7 @@
         <v>7</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I9" s="16">
         <f>SUM(C52,C65)</f>
@@ -1944,7 +1917,7 @@
         <v>44774</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="13">
         <v>39</v>
@@ -1957,15 +1930,18 @@
       <c r="G10" s="15">
         <v>8</v>
       </c>
-      <c r="H10" s="10" t="s">
-        <v>28</v>
+      <c r="H10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="I10" s="2">
-        <f>SUM(C86,C101,C105,C107,C112,C119,C124)</f>
-        <v>52.01</v>
+        <f>SUM(C133,C143,C147,C155)</f>
+        <v>63.32</v>
       </c>
       <c r="J10" s="3">
-        <v>46047</v>
+        <v>46196</v>
+      </c>
+      <c r="K10" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1973,7 +1949,7 @@
         <v>44781</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C11" s="13">
         <v>130</v>
@@ -1983,20 +1959,23 @@
         <v>193.93</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G11" s="15">
         <v>9</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="16">
-        <f>SUM(C8:C8,C47,C45,C50:C50)</f>
-        <v>49</v>
+        <v>29</v>
+      </c>
+      <c r="I11" s="2">
+        <f>SUM(C86,C101,C105,C107,C112,C119,C124)</f>
+        <v>52.01</v>
       </c>
       <c r="J11" s="3">
-        <v>45505</v>
+        <v>46047</v>
+      </c>
+      <c r="K11" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2012,20 +1991,23 @@
         <v>-5.06999999999999</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G12" s="15">
         <v>10</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I12" s="16">
-        <f>SUM(C3,C20:C20,C38,C104,C111)</f>
-        <v>39</v>
+        <f>SUM(C8:C8,C47,C45,C50:C50)</f>
+        <v>49</v>
       </c>
       <c r="J12" s="3">
-        <v>45968</v>
+        <v>45505</v>
+      </c>
+      <c r="K12" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2033,7 +2015,7 @@
         <v>44787</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="13">
         <v>5.02</v>
@@ -2046,15 +2028,18 @@
       <c r="G13" s="15">
         <v>11</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="2">
-        <f>SUM(C133,C143,C147)</f>
-        <v>38.32</v>
+      <c r="H13" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="16">
+        <f>SUM(C3,C20:C20,C38,C104,C111)</f>
+        <v>39</v>
       </c>
       <c r="J13" s="3">
-        <v>46146</v>
+        <v>45968</v>
+      </c>
+      <c r="K13" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2091,7 +2076,7 @@
         <v>44926</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="13">
         <v>120</v>
@@ -2122,7 +2107,7 @@
         <v>44946</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C16" s="13">
         <v>13</v>
@@ -2181,7 +2166,7 @@
         <v>44958</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" s="13">
         <f>11+45+29</f>
@@ -2265,7 +2250,7 @@
         <v>45138</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C21" s="13">
         <f>6+84+10+10</f>
@@ -2350,7 +2335,7 @@
     <row r="24" spans="1:10">
       <c r="A24" s="17"/>
       <c r="B24" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" s="13">
         <v>9</v>
@@ -2377,7 +2362,7 @@
         <v>45160</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C25" s="13">
         <v>3</v>
@@ -2458,7 +2443,7 @@
         <v>45249</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C28" s="13">
         <v>15.5</v>
@@ -2489,7 +2474,7 @@
         <v>45305</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C29" s="13">
         <v>50</v>
@@ -2547,7 +2532,7 @@
         <v>45341</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C31" s="13">
         <v>68</v>
@@ -2563,7 +2548,7 @@
         <v>29</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I31" s="16">
         <v>5.02</v>
@@ -2577,7 +2562,7 @@
         <v>45368</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C32" s="13">
         <v>33.01</v>
@@ -2637,7 +2622,7 @@
         <v>45394</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C34" s="13">
         <v>16</v>
@@ -2698,7 +2683,7 @@
         <v>45403</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C36" s="13">
         <v>3.2</v>
@@ -2712,7 +2697,7 @@
         <v>34</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I36" s="16">
         <v>3</v>
@@ -2726,7 +2711,7 @@
         <v>45403</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C37" s="13">
         <v>5</v>
@@ -2786,7 +2771,7 @@
         <v>45417</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C39" s="13">
         <v>11</v>
@@ -2833,7 +2818,7 @@
         <v>38</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I40" s="16">
         <v>2</v>
@@ -2876,7 +2861,7 @@
         <v>45494</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C42" s="13">
         <v>82.45</v>
@@ -2904,7 +2889,7 @@
     <row r="43" spans="1:10">
       <c r="A43" s="17"/>
       <c r="B43" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C43" s="13">
         <v>2</v>
@@ -2917,7 +2902,7 @@
         <v>41</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I43" s="16">
         <v>1.28</v>
@@ -2961,7 +2946,7 @@
         <v>45496</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C45" s="27">
         <v>5</v>
@@ -3000,7 +2985,7 @@
         <v>44</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I46" s="16">
         <v>0.55</v>
@@ -3014,7 +2999,7 @@
         <v>45497</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C47" s="27">
         <v>25</v>
@@ -3097,7 +3082,7 @@
         <v>45505</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C50" s="27">
         <v>10</v>
@@ -3113,7 +3098,7 @@
         <v>48</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I50" s="16">
         <v>0.1</v>
@@ -3143,7 +3128,7 @@
     <row r="52" spans="1:10">
       <c r="A52" s="31"/>
       <c r="B52" s="26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C52" s="27">
         <v>86</v>
@@ -3174,7 +3159,7 @@
     <row r="54" spans="1:10">
       <c r="A54" s="31"/>
       <c r="B54" s="26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C54" s="27">
         <v>10</v>
@@ -3214,7 +3199,7 @@
         <v>45510</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C57" s="27">
         <v>40</v>
@@ -3251,7 +3236,7 @@
         <v>45525</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C59" s="27">
         <v>6</v>
@@ -3285,7 +3270,7 @@
     <row r="61" spans="1:10">
       <c r="A61" s="29"/>
       <c r="B61" s="33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C61" s="27">
         <v>20</v>
@@ -3300,7 +3285,7 @@
         <v>45551</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C62" s="27">
         <v>17</v>
@@ -3346,7 +3331,7 @@
     <row r="65" spans="1:5">
       <c r="A65" s="31"/>
       <c r="B65" s="33" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C65" s="27">
         <v>20</v>
@@ -3379,7 +3364,7 @@
         <v>45584</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C67" s="27">
         <v>7</v>
@@ -3413,7 +3398,7 @@
         <v>45597</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C69" s="27">
         <v>5</v>
@@ -3449,7 +3434,7 @@
         <v>45612</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C71" s="27">
         <v>5</v>
@@ -3530,7 +3515,7 @@
         <v>45654</v>
       </c>
       <c r="B76" s="33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C76" s="27">
         <v>30</v>
@@ -3614,7 +3599,7 @@
         <v>45829</v>
       </c>
       <c r="B81" s="33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C81" s="27">
         <v>26.66</v>
@@ -3694,7 +3679,7 @@
         <v>45868</v>
       </c>
       <c r="B86" s="33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C86" s="27">
         <v>5.01</v>
@@ -3728,7 +3713,7 @@
         <v>45877</v>
       </c>
       <c r="B88" s="33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C88" s="27">
         <v>5</v>
@@ -3762,7 +3747,7 @@
         <v>45879</v>
       </c>
       <c r="B90" s="33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C90" s="27">
         <v>26</v>
@@ -3922,7 +3907,7 @@
     <row r="101" spans="1:5">
       <c r="A101" s="31"/>
       <c r="B101" s="33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C101" s="27">
         <v>2</v>
@@ -3980,7 +3965,7 @@
         <v>45925</v>
       </c>
       <c r="B105" s="33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C105" s="27">
         <v>10</v>
@@ -4012,7 +3997,7 @@
         <v>45934</v>
       </c>
       <c r="B107" s="33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C107" s="27">
         <v>2</v>
@@ -4056,7 +4041,7 @@
         <v>45965</v>
       </c>
       <c r="B110" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C110" s="27">
         <v>60</v>
@@ -4090,7 +4075,7 @@
         <v>45969</v>
       </c>
       <c r="B112" s="33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C112" s="27">
         <v>6</v>
@@ -4106,7 +4091,7 @@
         <v>45972</v>
       </c>
       <c r="B113" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C113" s="27">
         <v>60</v>
@@ -4124,7 +4109,7 @@
         <v>45975</v>
       </c>
       <c r="B114" s="33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C114" s="27">
         <v>37</v>
@@ -4158,7 +4143,7 @@
         <v>45980</v>
       </c>
       <c r="B116" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C116" s="27">
         <v>20</v>
@@ -4194,7 +4179,7 @@
         <v>46012</v>
       </c>
       <c r="B118" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C118" s="27">
         <v>10</v>
@@ -4210,7 +4195,7 @@
         <v>46029</v>
       </c>
       <c r="B119" s="33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C119" s="27">
         <v>16</v>
@@ -4244,7 +4229,7 @@
         <v>46038</v>
       </c>
       <c r="B121" s="33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C121" s="27">
         <v>66</v>
@@ -4278,7 +4263,7 @@
         <v>46047</v>
       </c>
       <c r="B123" s="33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C123" s="27">
         <v>7</v>
@@ -4294,7 +4279,7 @@
     <row r="124" spans="1:5">
       <c r="A124" s="31"/>
       <c r="B124" s="33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C124" s="27">
         <v>11</v>
@@ -4328,7 +4313,7 @@
         <v>46055</v>
       </c>
       <c r="B126" s="33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C126" s="27">
         <v>36</v>
@@ -4364,7 +4349,7 @@
         <v>46068</v>
       </c>
       <c r="B128" s="33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C128" s="27">
         <v>78</v>
@@ -4380,7 +4365,7 @@
     <row r="129" spans="1:5">
       <c r="A129" s="36"/>
       <c r="B129" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C129" s="27">
         <v>30</v>
@@ -4412,7 +4397,7 @@
     <row r="131" spans="1:5">
       <c r="A131" s="31"/>
       <c r="B131" s="33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C131" s="27">
         <v>8</v>
@@ -4444,7 +4429,7 @@
         <v>46070</v>
       </c>
       <c r="B133" s="33" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C133" s="27">
         <v>8.32</v>
@@ -4458,7 +4443,7 @@
     <row r="134" spans="1:5">
       <c r="A134" s="31"/>
       <c r="B134" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C134" s="27">
         <v>10</v>
@@ -4592,7 +4577,7 @@
         <v>46141</v>
       </c>
       <c r="B142" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C142" s="27">
         <v>10</v>
@@ -4606,7 +4591,7 @@
     <row r="143" spans="1:5">
       <c r="A143" s="31"/>
       <c r="B143" s="33" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C143" s="27">
         <v>10</v>
@@ -4670,7 +4655,7 @@
         <v>46146</v>
       </c>
       <c r="B147" s="33" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C147" s="27">
         <v>20</v>
@@ -4738,7 +4723,7 @@
         <v>46184</v>
       </c>
       <c r="B151" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C151" s="27">
         <v>10</v>
@@ -4768,11 +4753,11 @@
       </c>
     </row>
     <row r="153" spans="1:5">
-      <c r="A153" s="37">
+      <c r="A153" s="25">
         <v>46193</v>
       </c>
       <c r="B153" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C153" s="27">
         <v>50</v>
@@ -4784,43 +4769,54 @@
       <c r="E153" s="34"/>
     </row>
     <row r="154" spans="1:5">
-      <c r="A154" s="38"/>
-      <c r="B154" s="39" t="s">
+      <c r="A154" s="31"/>
+      <c r="B154" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C154" s="40">
+      <c r="C154" s="27">
         <v>10</v>
       </c>
       <c r="D154" s="21">
         <f>SUM(C3:C154)</f>
         <v>-2934.11</v>
       </c>
-      <c r="E154" s="41" t="s">
+      <c r="E154" s="34" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="155" spans="1:5">
-      <c r="A155" s="42"/>
-      <c r="B155" s="39"/>
-      <c r="C155" s="40"/>
-      <c r="D155" s="43"/>
-      <c r="E155" s="41"/>
-    </row>
-    <row r="156" spans="1:5">
-      <c r="A156" s="44"/>
-      <c r="B156" s="45"/>
-      <c r="C156" s="46"/>
-      <c r="D156" s="46"/>
-      <c r="E156" s="47"/>
+      <c r="A155" s="25">
+        <v>46196</v>
+      </c>
+      <c r="B155" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C155" s="27">
+        <v>25</v>
+      </c>
+      <c r="D155" s="21">
+        <f>SUM(C3:C155)</f>
+        <v>-2909.11</v>
+      </c>
+      <c r="E155" s="34" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="156" ht="14.25" spans="1:5">
+      <c r="A156" s="37"/>
+      <c r="B156" s="38"/>
+      <c r="C156" s="39"/>
+      <c r="D156" s="39"/>
+      <c r="E156" s="40"/>
     </row>
     <row r="157" spans="1:5">
-      <c r="A157" s="48" t="s">
+      <c r="A157" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="B157" s="48"/>
-      <c r="C157" s="48"/>
-      <c r="D157" s="48"/>
-      <c r="E157" s="48"/>
+      <c r="B157" s="41"/>
+      <c r="C157" s="41"/>
+      <c r="D157" s="41"/>
+      <c r="E157" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="41">
@@ -4875,7 +4871,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c819861f-668f-4259-b4bb-d384cd5aff57}</x14:id>
+          <x14:id>{da058e3d-9dcd-4d36-9dc3-f2603580b6cf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4889,7 +4885,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{90938403-bc59-4aa5-be85-7a6b49387e1f}</x14:id>
+          <x14:id>{343a36ed-df2a-44da-ac97-b5a8ddeb1a80}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4915,7 +4911,35 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f1b0efb8-5c5d-4d32-b9ab-1af08cf87039}</x14:id>
+          <x14:id>{8130e26c-ad89-41e8-b020-77ef462b9589}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I9 I20:I24 I26:I1048576 I11:I18">
+    <cfRule type="dataBar" priority="22">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2a202fd7-d66f-4214-9315-f3ded105ca2c}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I9 I20:I23 I26:I1048576 I11:I18">
+    <cfRule type="dataBar" priority="23">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{acc70ed1-e186-4af4-9771-253e446472bb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4929,35 +4953,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e2f33578-75a6-44dc-b1e1-9325d1cb347d}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I12 I26:I1048576 I14:I18 I20:I24">
-    <cfRule type="dataBar" priority="22">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3ee43b40-47e4-47a3-aeea-295a4d26d50d}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I12 I26:I1048576 I14:I18 I20:I23">
-    <cfRule type="dataBar" priority="23">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{afba1f70-d754-4277-ab3b-386407a9bd0d}</x14:id>
+          <x14:id>{9eb1a8ba-fc89-40bd-bde3-996978df0e7c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4971,7 +4967,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c8c8a910-5cb9-4ec9-8ccd-e90e39fca01a}</x14:id>
+          <x14:id>{18f73795-0eeb-4e3e-a8d2-6d45896c3cd5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4985,12 +4981,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ba8c373-4340-4c3c-9e93-94534c36cf78}</x14:id>
+          <x14:id>{4d4b3613-b502-4362-8360-97c65173fdd8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5 I26:I37 I9:I12 I39:I1048576 I20:I23 I14:I18 I7">
+  <conditionalFormatting sqref="I2:I5 I26:I37 I9 I7 I39:I1048576 I20:I23 I11:I18">
     <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
@@ -4999,12 +4995,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{89d366d6-92b1-48e8-8d55-1d82681fef7d}</x14:id>
+          <x14:id>{26b3ff75-3523-4c00-9aa0-530fd96110f7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5 I9:I12 I14:I16 I39:I1048576 I20:I23 I18 I7 I26:I37">
+  <conditionalFormatting sqref="I2:I5 I9 I26:I37 I11:I16 I39:I1048576 I20:I23 I18 I7">
     <cfRule type="dataBar" priority="30">
       <dataBar>
         <cfvo type="min"/>
@@ -5013,7 +5009,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d69ac191-40e2-46e5-933e-5aa5d1ff3c18}</x14:id>
+          <x14:id>{fe26b628-0753-4536-a930-61d231b8b00d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5050,7 +5046,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I42:I47 I3:I5 I7 I39:I40 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33">
+  <conditionalFormatting sqref="I42:I47 I3:I5 I7 I39:I40 I9 I31:I33 I28 I18 I12:I14 I26 I20:I23 I49:I50 I36:I37">
     <cfRule type="dataBar" priority="36">
       <dataBar>
         <cfvo type="min"/>
@@ -5059,12 +5055,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c80afe5a-992e-49a2-9536-60242f5c65df}</x14:id>
+          <x14:id>{66ebd06f-7781-4498-b1b8-7694f615d721}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I42:I47 I3:I5 I7 I39:I40 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33">
+  <conditionalFormatting sqref="I42:I47 I3:I5 I7 I39:I40 I9 I31:I33 I28 I18 I12:I14 I20:I23 I49:I50 I36:I37">
     <cfRule type="dataBar" priority="37">
       <dataBar>
         <cfvo type="min"/>
@@ -5073,12 +5069,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c660a138-f8d7-47d3-99e7-f6a54001241e}</x14:id>
+          <x14:id>{63c2fbaa-1fe8-4bcc-9e39-e5a094ac953b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I39:I40 I3:I5 I7 I36:I37 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33">
+  <conditionalFormatting sqref="I39:I40 I3:I5 I7 I36:I37 I9 I31:I33 I28 I18 I12:I14 I16 I26 I20:I23 I42:I47 I49:I50">
     <cfRule type="dataBar" priority="34">
       <dataBar>
         <cfvo type="min"/>
@@ -5087,12 +5083,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f31a0447-ffca-4ac3-9bb0-bb658642ca58}</x14:id>
+          <x14:id>{539cdf63-4d49-4975-bc58-1a19f30350ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I36:I37 I3:I5 I7 I31:I34 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50">
+  <conditionalFormatting sqref="I36:I37 I3:I5 I7 I31:I34 I9 I42:I50 I26 I18 I28:I29 I11:I14 I16 I20:I23 I39:I40">
     <cfRule type="dataBar" priority="32">
       <dataBar>
         <cfvo type="min"/>
@@ -5101,12 +5097,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{28bb1981-d57d-4a1a-8952-6f2efe47d18f}</x14:id>
+          <x14:id>{677cc7b2-bd9f-47d2-8df1-950ba4e05c92}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I39:I40 I3:I5 I7 I36:I37 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33">
+  <conditionalFormatting sqref="I39:I40 I3:I5 I7 I36:I37 I9 I31:I33 I26 I18 I11:I14 I16 I20:I23 I28:I29 I42:I47 I49:I50">
     <cfRule type="dataBar" priority="33">
       <dataBar>
         <cfvo type="min"/>
@@ -5115,12 +5111,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4ff42c0e-31bd-4704-8135-d893b82f56cc}</x14:id>
+          <x14:id>{3ac610e1-e0e9-4f1a-94aa-5a88363fbf03}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I39:I50 I3:I5 I7 I31:I37 I9:I12 I20:I23 I18 I26:I29 I14:I16">
+  <conditionalFormatting sqref="I39:I50 I3:I5 I7 I31:I37 I9 I11:I16 I20:I23 I18 I26:I29">
     <cfRule type="dataBar" priority="28">
       <dataBar>
         <cfvo type="min"/>
@@ -5129,12 +5125,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d73dbd87-a4ef-4a56-82b1-52adc1156ef1}</x14:id>
+          <x14:id>{003f7277-97d7-47d2-bce3-4882dae7986c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I39:I50 I3:I5 I7 I31:I37 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29">
+  <conditionalFormatting sqref="I39:I50 I3:I5 I7 I31:I37 I9 I28:I29 I26 I18 I20:I23 I11:I16">
     <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
@@ -5143,12 +5139,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{298ba7be-3635-4279-8f3a-cbc8d5262c38}</x14:id>
+          <x14:id>{1c7a5d01-645b-4373-861f-ba59db55032d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I31:I37 I3:I5 I7 I39:I50 I9:I12 I20:I23 I14:I18 I26:I29">
+  <conditionalFormatting sqref="I31:I37 I3:I5 I7 I39:I50 I9 I26:I29 I20:I23 I11:I18">
     <cfRule type="dataBar" priority="27">
       <dataBar>
         <cfvo type="min"/>
@@ -5157,12 +5153,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{91c8aad1-a210-428d-a2f2-7a3b85a9543d}</x14:id>
+          <x14:id>{cedcbad9-9f97-4a4f-8725-457fb7cbbe0d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:I18 I3:I7 I26:I29 I31:I50 I9:I12 I20:I23">
+  <conditionalFormatting sqref="I11:I18 I3:I7 I26:I29 I31:I50 I9 I20:I23">
     <cfRule type="dataBar" priority="24">
       <dataBar>
         <cfvo type="min"/>
@@ -5171,12 +5167,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b64add38-6eed-4ee6-8198-3a8159f02cb5}</x14:id>
+          <x14:id>{4ce24a99-4281-4a36-ba31-bec957e7cb57}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I26:I29 I3:I7 I39:I50 I31:I37 I9:I12 I20:I23 I14:I18">
+  <conditionalFormatting sqref="I26:I29 I3:I7 I39:I50 I31:I37 I9 I11:I18 I20:I23">
     <cfRule type="dataBar" priority="25">
       <dataBar>
         <cfvo type="min"/>
@@ -5185,7 +5181,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ac8396ae-2423-472a-9b22-d9688bafa5cd}</x14:id>
+          <x14:id>{4ddb43fa-af7c-4af0-a043-ad4f94475d9d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5199,7 +5195,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{47b548a5-ccdc-4d43-9a8b-88e546b6236c}</x14:id>
+          <x14:id>{ee482c8a-5e36-4846-9812-45102e72d250}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5207,13 +5203,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
+    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c819861f-668f-4259-b4bb-d384cd5aff57}">
+          <x14:cfRule type="dataBar" id="{da058e3d-9dcd-4d36-9dc3-f2603580b6cf}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5224,7 +5220,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{90938403-bc59-4aa5-be85-7a6b49387e1f}">
+          <x14:cfRule type="dataBar" id="{343a36ed-df2a-44da-ac97-b5a8ddeb1a80}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5235,7 +5231,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f1b0efb8-5c5d-4d32-b9ab-1af08cf87039}">
+          <x14:cfRule type="dataBar" id="{8130e26c-ad89-41e8-b020-77ef462b9589}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5248,7 +5244,29 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e2f33578-75a6-44dc-b1e1-9325d1cb347d}">
+          <x14:cfRule type="dataBar" id="{2a202fd7-d66f-4214-9315-f3ded105ca2c}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I1:I9 I20:I24 I26:I1048576 I11:I18</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{acc70ed1-e186-4af4-9771-253e446472bb}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I1:I9 I20:I23 I26:I1048576 I11:I18</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9eb1a8ba-fc89-40bd-bde3-996978df0e7c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5259,29 +5277,7 @@
           <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3ee43b40-47e4-47a3-aeea-295a4d26d50d}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>I1:I12 I26:I1048576 I14:I18 I20:I24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{afba1f70-d754-4277-ab3b-386407a9bd0d}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>I1:I12 I26:I1048576 I14:I18 I20:I23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c8c8a910-5cb9-4ec9-8ccd-e90e39fca01a}">
+          <x14:cfRule type="dataBar" id="{18f73795-0eeb-4e3e-a8d2-6d45896c3cd5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5292,7 +5288,7 @@
           <xm:sqref>I1:I18 I20:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6ba8c373-4340-4c3c-9e93-94534c36cf78}">
+          <x14:cfRule type="dataBar" id="{4d4b3613-b502-4362-8360-97c65173fdd8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5303,7 +5299,7 @@
           <xm:sqref>I2 I30 I51:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{89d366d6-92b1-48e8-8d55-1d82681fef7d}">
+          <x14:cfRule type="dataBar" id="{26b3ff75-3523-4c00-9aa0-530fd96110f7}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5311,10 +5307,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I5 I26:I37 I9:I12 I39:I1048576 I20:I23 I14:I18 I7</xm:sqref>
+          <xm:sqref>I2:I5 I26:I37 I9 I7 I39:I1048576 I20:I23 I11:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d69ac191-40e2-46e5-933e-5aa5d1ff3c18}">
+          <x14:cfRule type="dataBar" id="{fe26b628-0753-4536-a930-61d231b8b00d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5322,10 +5318,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I5 I9:I12 I14:I16 I39:I1048576 I20:I23 I18 I7 I26:I37</xm:sqref>
+          <xm:sqref>I2:I5 I9 I26:I37 I11:I16 I39:I1048576 I20:I23 I18 I7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c80afe5a-992e-49a2-9536-60242f5c65df}">
+          <x14:cfRule type="dataBar" id="{66ebd06f-7781-4498-b1b8-7694f615d721}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5333,10 +5329,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I42:I47 I3:I5 I7 I39:I40 I9 I11:I12 I28 I18 I14 I26 I20:I23 I49:I50 I36:I37 I31:I33</xm:sqref>
+          <xm:sqref>I42:I47 I3:I5 I7 I39:I40 I9 I31:I33 I28 I18 I12:I14 I26 I20:I23 I49:I50 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c660a138-f8d7-47d3-99e7-f6a54001241e}">
+          <x14:cfRule type="dataBar" id="{63c2fbaa-1fe8-4bcc-9e39-e5a094ac953b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5344,10 +5340,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I42:I47 I3:I5 I7 I39:I40 I9 I11:I12 I28 I18 I14 I20:I23 I49:I50 I36:I37 I31:I33</xm:sqref>
+          <xm:sqref>I42:I47 I3:I5 I7 I39:I40 I9 I31:I33 I28 I18 I12:I14 I20:I23 I49:I50 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f31a0447-ffca-4ac3-9bb0-bb658642ca58}">
+          <x14:cfRule type="dataBar" id="{539cdf63-4d49-4975-bc58-1a19f30350ee}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5355,10 +5351,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I39:I40 I3:I5 I7 I36:I37 I9 I11:I12 I28 I18 I14 I16 I26 I20:I23 I42:I47 I49:I50 I31:I33</xm:sqref>
+          <xm:sqref>I39:I40 I3:I5 I7 I36:I37 I9 I31:I33 I28 I18 I12:I14 I16 I26 I20:I23 I42:I47 I49:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{28bb1981-d57d-4a1a-8952-6f2efe47d18f}">
+          <x14:cfRule type="dataBar" id="{677cc7b2-bd9f-47d2-8df1-950ba4e05c92}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5366,10 +5362,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I36:I37 I3:I5 I7 I31:I34 I9:I12 I26 I18 I28:I29 I14 I16 I20:I23 I39:I40 I42:I50</xm:sqref>
+          <xm:sqref>I36:I37 I3:I5 I7 I31:I34 I9 I42:I50 I26 I18 I28:I29 I11:I14 I16 I20:I23 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4ff42c0e-31bd-4704-8135-d893b82f56cc}">
+          <x14:cfRule type="dataBar" id="{3ac610e1-e0e9-4f1a-94aa-5a88363fbf03}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5377,10 +5373,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I39:I40 I3:I5 I7 I36:I37 I9:I12 I26 I18 I14 I16 I20:I23 I28:I29 I42:I47 I49:I50 I31:I33</xm:sqref>
+          <xm:sqref>I39:I40 I3:I5 I7 I36:I37 I9 I31:I33 I26 I18 I11:I14 I16 I20:I23 I28:I29 I42:I47 I49:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d73dbd87-a4ef-4a56-82b1-52adc1156ef1}">
+          <x14:cfRule type="dataBar" id="{003f7277-97d7-47d2-bce3-4882dae7986c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5388,10 +5384,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I39:I50 I3:I5 I7 I31:I37 I9:I12 I20:I23 I18 I26:I29 I14:I16</xm:sqref>
+          <xm:sqref>I39:I50 I3:I5 I7 I31:I37 I9 I11:I16 I20:I23 I18 I26:I29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{298ba7be-3635-4279-8f3a-cbc8d5262c38}">
+          <x14:cfRule type="dataBar" id="{1c7a5d01-645b-4373-861f-ba59db55032d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5399,10 +5395,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I39:I50 I3:I5 I7 I31:I37 I9:I12 I26 I18 I20:I23 I14:I16 I28:I29</xm:sqref>
+          <xm:sqref>I39:I50 I3:I5 I7 I31:I37 I9 I28:I29 I26 I18 I20:I23 I11:I16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{91c8aad1-a210-428d-a2f2-7a3b85a9543d}">
+          <x14:cfRule type="dataBar" id="{cedcbad9-9f97-4a4f-8725-457fb7cbbe0d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5410,10 +5406,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I31:I37 I3:I5 I7 I39:I50 I9:I12 I20:I23 I14:I18 I26:I29</xm:sqref>
+          <xm:sqref>I31:I37 I3:I5 I7 I39:I50 I9 I26:I29 I20:I23 I11:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b64add38-6eed-4ee6-8198-3a8159f02cb5}">
+          <x14:cfRule type="dataBar" id="{4ce24a99-4281-4a36-ba31-bec957e7cb57}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5421,10 +5417,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I14:I18 I3:I7 I26:I29 I31:I50 I9:I12 I20:I23</xm:sqref>
+          <xm:sqref>I11:I18 I3:I7 I26:I29 I31:I50 I9 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ac8396ae-2423-472a-9b22-d9688bafa5cd}">
+          <x14:cfRule type="dataBar" id="{4ddb43fa-af7c-4af0-a043-ad4f94475d9d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5432,10 +5428,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I26:I29 I3:I7 I39:I50 I31:I37 I9:I12 I20:I23 I14:I18</xm:sqref>
+          <xm:sqref>I26:I29 I3:I7 I39:I50 I31:I37 I9 I11:I18 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{47b548a5-ccdc-4d43-9a8b-88e546b6236c}">
+          <x14:cfRule type="dataBar" id="{ee482c8a-5e36-4846-9812-45102e72d250}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="114">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -1216,7 +1216,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1326,6 +1326,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -1664,7 +1676,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K157"/>
+  <dimension ref="A1:K158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -1751,11 +1763,11 @@
         <v>13</v>
       </c>
       <c r="I3" s="16">
-        <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150,C152,C154)</f>
-        <v>507</v>
+        <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150,C152,C154,C156)</f>
+        <v>517</v>
       </c>
       <c r="J3" s="3">
-        <v>46193</v>
+        <v>46201</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -4802,27 +4814,45 @@
         <v>107</v>
       </c>
     </row>
-    <row r="156" ht="14.25" spans="1:5">
-      <c r="A156" s="37"/>
-      <c r="B156" s="38"/>
-      <c r="C156" s="39"/>
-      <c r="D156" s="39"/>
-      <c r="E156" s="40"/>
-    </row>
-    <row r="157" spans="1:5">
-      <c r="A157" s="41" t="s">
+    <row r="156" spans="1:5">
+      <c r="A156" s="37">
+        <v>46201</v>
+      </c>
+      <c r="B156" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C156" s="39">
+        <v>10</v>
+      </c>
+      <c r="D156" s="21">
+        <f>SUM(C3:C156)</f>
+        <v>-2899.11</v>
+      </c>
+      <c r="E156" s="40" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="157" ht="14.25" spans="1:5">
+      <c r="A157" s="41"/>
+      <c r="B157" s="42"/>
+      <c r="C157" s="43"/>
+      <c r="D157" s="43"/>
+      <c r="E157" s="44"/>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="B157" s="41"/>
-      <c r="C157" s="41"/>
-      <c r="D157" s="41"/>
-      <c r="E157" s="41"/>
+      <c r="B158" s="45"/>
+      <c r="C158" s="45"/>
+      <c r="D158" s="45"/>
+      <c r="E158" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="41">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A157:E157"/>
+    <mergeCell ref="A158:E158"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A23:A24"/>
@@ -4871,7 +4901,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{da058e3d-9dcd-4d36-9dc3-f2603580b6cf}</x14:id>
+          <x14:id>{33adc75a-1da8-4c89-8af6-be661affc362}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4885,12 +4915,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{343a36ed-df2a-44da-ac97-b5a8ddeb1a80}</x14:id>
+          <x14:id>{08747732-96ba-437d-b06e-ac4d0a43a89f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D156 D158:D1048576">
+  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D157 D159:D1048576">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="min"/>
@@ -4911,7 +4941,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8130e26c-ad89-41e8-b020-77ef462b9589}</x14:id>
+          <x14:id>{8e4be11a-2955-4b07-a67c-aa0f15ef676b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4925,7 +4955,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2a202fd7-d66f-4214-9315-f3ded105ca2c}</x14:id>
+          <x14:id>{5962f722-d975-4bad-9150-ee9898402e5d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4939,7 +4969,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{acc70ed1-e186-4af4-9771-253e446472bb}</x14:id>
+          <x14:id>{336e8abd-523f-46c9-b964-8d532a0987d1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4953,7 +4983,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9eb1a8ba-fc89-40bd-bde3-996978df0e7c}</x14:id>
+          <x14:id>{c6869f4e-0209-49c4-b055-60e0d3360ca8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4967,7 +4997,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{18f73795-0eeb-4e3e-a8d2-6d45896c3cd5}</x14:id>
+          <x14:id>{ab480e2a-3682-42e4-8362-f7dce5df0422}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4981,12 +5011,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4d4b3613-b502-4362-8360-97c65173fdd8}</x14:id>
+          <x14:id>{f7947776-ef49-4a82-833c-e3af790aa7c0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5 I26:I37 I9 I7 I39:I1048576 I20:I23 I11:I18">
+  <conditionalFormatting sqref="I2:I5 I26:I37 I9 I7 I39:I1048576 I11:I18 I20:I23">
     <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
@@ -4995,12 +5025,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{26b3ff75-3523-4c00-9aa0-530fd96110f7}</x14:id>
+          <x14:id>{c6edb7a5-6f88-4f3c-a328-d682bd1f1233}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5 I9 I26:I37 I11:I16 I39:I1048576 I20:I23 I18 I7">
+  <conditionalFormatting sqref="I2:I5 I9 I26:I37 I11:I16 I39:I1048576 I7 I18 I20:I23">
     <cfRule type="dataBar" priority="30">
       <dataBar>
         <cfvo type="min"/>
@@ -5009,7 +5039,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fe26b628-0753-4536-a930-61d231b8b00d}</x14:id>
+          <x14:id>{07255bb7-df68-4ba5-b4fa-ed506670b08c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5055,7 +5085,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{66ebd06f-7781-4498-b1b8-7694f615d721}</x14:id>
+          <x14:id>{9cd0042e-9a76-4489-9b6f-fa9308406915}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5069,7 +5099,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{63c2fbaa-1fe8-4bcc-9e39-e5a094ac953b}</x14:id>
+          <x14:id>{1cc9fd38-332e-476b-8755-b2bccd0a4c16}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5083,7 +5113,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{539cdf63-4d49-4975-bc58-1a19f30350ee}</x14:id>
+          <x14:id>{f918c27e-9787-4173-9a4b-ecb91226b81b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5097,7 +5127,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{677cc7b2-bd9f-47d2-8df1-950ba4e05c92}</x14:id>
+          <x14:id>{de961f03-d81d-4f0d-983e-f7014e42cee9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5111,7 +5141,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3ac610e1-e0e9-4f1a-94aa-5a88363fbf03}</x14:id>
+          <x14:id>{e502e735-a49d-461d-ba73-52d9f1da1119}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5125,7 +5155,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{003f7277-97d7-47d2-bce3-4882dae7986c}</x14:id>
+          <x14:id>{428af9ff-2b72-4c38-bf03-b09ed5caac37}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5139,7 +5169,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1c7a5d01-645b-4373-861f-ba59db55032d}</x14:id>
+          <x14:id>{7e48ffe1-d53c-4fbe-879a-d2ecbadeac9c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5153,7 +5183,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cedcbad9-9f97-4a4f-8725-457fb7cbbe0d}</x14:id>
+          <x14:id>{92f40775-060c-4e6b-a0e6-8044f636cd3d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5167,7 +5197,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4ce24a99-4281-4a36-ba31-bec957e7cb57}</x14:id>
+          <x14:id>{66ffbc46-b2a6-415a-a8a5-b25806b9abe6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5181,7 +5211,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4ddb43fa-af7c-4af0-a043-ad4f94475d9d}</x14:id>
+          <x14:id>{4ab18667-8c3d-427f-8900-2766c2064f78}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5195,7 +5225,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ee482c8a-5e36-4846-9812-45102e72d250}</x14:id>
+          <x14:id>{a37001fe-dc87-454a-87ee-11c29720151c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5203,13 +5233,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
+    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{da058e3d-9dcd-4d36-9dc3-f2603580b6cf}">
+          <x14:cfRule type="dataBar" id="{33adc75a-1da8-4c89-8af6-be661affc362}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5220,7 +5250,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{343a36ed-df2a-44da-ac97-b5a8ddeb1a80}">
+          <x14:cfRule type="dataBar" id="{08747732-96ba-437d-b06e-ac4d0a43a89f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5231,7 +5261,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8130e26c-ad89-41e8-b020-77ef462b9589}">
+          <x14:cfRule type="dataBar" id="{8e4be11a-2955-4b07-a67c-aa0f15ef676b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5244,7 +5274,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2a202fd7-d66f-4214-9315-f3ded105ca2c}">
+          <x14:cfRule type="dataBar" id="{5962f722-d975-4bad-9150-ee9898402e5d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5255,7 +5285,7 @@
           <xm:sqref>I1:I9 I20:I24 I26:I1048576 I11:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{acc70ed1-e186-4af4-9771-253e446472bb}">
+          <x14:cfRule type="dataBar" id="{336e8abd-523f-46c9-b964-8d532a0987d1}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5266,7 +5296,7 @@
           <xm:sqref>I1:I9 I20:I23 I26:I1048576 I11:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9eb1a8ba-fc89-40bd-bde3-996978df0e7c}">
+          <x14:cfRule type="dataBar" id="{c6869f4e-0209-49c4-b055-60e0d3360ca8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5277,7 +5307,7 @@
           <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{18f73795-0eeb-4e3e-a8d2-6d45896c3cd5}">
+          <x14:cfRule type="dataBar" id="{ab480e2a-3682-42e4-8362-f7dce5df0422}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5288,7 +5318,7 @@
           <xm:sqref>I1:I18 I20:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4d4b3613-b502-4362-8360-97c65173fdd8}">
+          <x14:cfRule type="dataBar" id="{f7947776-ef49-4a82-833c-e3af790aa7c0}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5299,7 +5329,7 @@
           <xm:sqref>I2 I30 I51:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{26b3ff75-3523-4c00-9aa0-530fd96110f7}">
+          <x14:cfRule type="dataBar" id="{c6edb7a5-6f88-4f3c-a328-d682bd1f1233}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5307,10 +5337,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I5 I26:I37 I9 I7 I39:I1048576 I20:I23 I11:I18</xm:sqref>
+          <xm:sqref>I2:I5 I26:I37 I9 I7 I39:I1048576 I11:I18 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fe26b628-0753-4536-a930-61d231b8b00d}">
+          <x14:cfRule type="dataBar" id="{07255bb7-df68-4ba5-b4fa-ed506670b08c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5318,10 +5348,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I5 I9 I26:I37 I11:I16 I39:I1048576 I20:I23 I18 I7</xm:sqref>
+          <xm:sqref>I2:I5 I9 I26:I37 I11:I16 I39:I1048576 I7 I18 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{66ebd06f-7781-4498-b1b8-7694f615d721}">
+          <x14:cfRule type="dataBar" id="{9cd0042e-9a76-4489-9b6f-fa9308406915}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5332,7 +5362,7 @@
           <xm:sqref>I42:I47 I3:I5 I7 I39:I40 I9 I31:I33 I28 I18 I12:I14 I26 I20:I23 I49:I50 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{63c2fbaa-1fe8-4bcc-9e39-e5a094ac953b}">
+          <x14:cfRule type="dataBar" id="{1cc9fd38-332e-476b-8755-b2bccd0a4c16}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5343,7 +5373,7 @@
           <xm:sqref>I42:I47 I3:I5 I7 I39:I40 I9 I31:I33 I28 I18 I12:I14 I20:I23 I49:I50 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{539cdf63-4d49-4975-bc58-1a19f30350ee}">
+          <x14:cfRule type="dataBar" id="{f918c27e-9787-4173-9a4b-ecb91226b81b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5354,7 +5384,7 @@
           <xm:sqref>I39:I40 I3:I5 I7 I36:I37 I9 I31:I33 I28 I18 I12:I14 I16 I26 I20:I23 I42:I47 I49:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{677cc7b2-bd9f-47d2-8df1-950ba4e05c92}">
+          <x14:cfRule type="dataBar" id="{de961f03-d81d-4f0d-983e-f7014e42cee9}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5365,7 +5395,7 @@
           <xm:sqref>I36:I37 I3:I5 I7 I31:I34 I9 I42:I50 I26 I18 I28:I29 I11:I14 I16 I20:I23 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3ac610e1-e0e9-4f1a-94aa-5a88363fbf03}">
+          <x14:cfRule type="dataBar" id="{e502e735-a49d-461d-ba73-52d9f1da1119}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5376,7 +5406,7 @@
           <xm:sqref>I39:I40 I3:I5 I7 I36:I37 I9 I31:I33 I26 I18 I11:I14 I16 I20:I23 I28:I29 I42:I47 I49:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{003f7277-97d7-47d2-bce3-4882dae7986c}">
+          <x14:cfRule type="dataBar" id="{428af9ff-2b72-4c38-bf03-b09ed5caac37}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5387,7 +5417,7 @@
           <xm:sqref>I39:I50 I3:I5 I7 I31:I37 I9 I11:I16 I20:I23 I18 I26:I29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1c7a5d01-645b-4373-861f-ba59db55032d}">
+          <x14:cfRule type="dataBar" id="{7e48ffe1-d53c-4fbe-879a-d2ecbadeac9c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5398,7 +5428,7 @@
           <xm:sqref>I39:I50 I3:I5 I7 I31:I37 I9 I28:I29 I26 I18 I20:I23 I11:I16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cedcbad9-9f97-4a4f-8725-457fb7cbbe0d}">
+          <x14:cfRule type="dataBar" id="{92f40775-060c-4e6b-a0e6-8044f636cd3d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5409,7 +5439,7 @@
           <xm:sqref>I31:I37 I3:I5 I7 I39:I50 I9 I26:I29 I20:I23 I11:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4ce24a99-4281-4a36-ba31-bec957e7cb57}">
+          <x14:cfRule type="dataBar" id="{66ffbc46-b2a6-415a-a8a5-b25806b9abe6}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5420,7 +5450,7 @@
           <xm:sqref>I11:I18 I3:I7 I26:I29 I31:I50 I9 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4ddb43fa-af7c-4af0-a043-ad4f94475d9d}">
+          <x14:cfRule type="dataBar" id="{4ab18667-8c3d-427f-8900-2766c2064f78}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5431,7 +5461,7 @@
           <xm:sqref>I26:I29 I3:I7 I39:I50 I31:I37 I9 I11:I18 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ee482c8a-5e36-4846-9812-45102e72d250}">
+          <x14:cfRule type="dataBar" id="{a37001fe-dc87-454a-87ee-11c29720151c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="25600" windowHeight="12200"/>
   </bookViews>
   <sheets>
     <sheet name="收支与赞助鸣谢" sheetId="1" r:id="rId1"/>
@@ -1216,7 +1216,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1326,18 +1326,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -1677,20 +1665,20 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:K158"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15.625" customWidth="1"/>
-    <col min="2" max="2" width="18.2583333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="9.375" customWidth="1"/>
-    <col min="5" max="5" width="33.125" customWidth="1"/>
-    <col min="7" max="7" width="5.125" customWidth="1"/>
-    <col min="8" max="8" width="18.2583333333333" customWidth="1"/>
-    <col min="9" max="9" width="12.875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="5.125" customWidth="1"/>
-    <col min="13" max="13" width="15.625"/>
-    <col min="14" max="14" width="13.375"/>
+    <col min="1" max="1" width="15.6272727272727" customWidth="1"/>
+    <col min="2" max="2" width="18.2545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
+    <col min="4" max="4" width="9.37272727272727" customWidth="1"/>
+    <col min="5" max="5" width="33.1272727272727" customWidth="1"/>
+    <col min="7" max="7" width="5.12727272727273" customWidth="1"/>
+    <col min="8" max="8" width="18.2545454545455" customWidth="1"/>
+    <col min="9" max="9" width="12.8727272727273" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.6272727272727" style="3" customWidth="1"/>
+    <col min="11" max="11" width="5.12727272727273" customWidth="1"/>
+    <col min="13" max="13" width="15.6272727272727"/>
+    <col min="14" max="14" width="13.3727272727273"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1764,10 +1752,10 @@
       </c>
       <c r="I3" s="16">
         <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150,C152,C154,C156)</f>
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="J3" s="3">
-        <v>46201</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -4815,38 +4803,38 @@
       </c>
     </row>
     <row r="156" spans="1:5">
-      <c r="A156" s="37">
-        <v>46201</v>
-      </c>
-      <c r="B156" s="38" t="s">
+      <c r="A156" s="25">
+        <v>46203</v>
+      </c>
+      <c r="B156" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C156" s="39">
-        <v>10</v>
+      <c r="C156" s="27">
+        <v>15</v>
       </c>
       <c r="D156" s="21">
         <f>SUM(C3:C156)</f>
-        <v>-2899.11</v>
-      </c>
-      <c r="E156" s="40" t="s">
+        <v>-2894.11</v>
+      </c>
+      <c r="E156" s="34" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="157" ht="14.25" spans="1:5">
-      <c r="A157" s="41"/>
-      <c r="B157" s="42"/>
-      <c r="C157" s="43"/>
-      <c r="D157" s="43"/>
-      <c r="E157" s="44"/>
+    <row r="157" spans="1:5">
+      <c r="A157" s="37"/>
+      <c r="B157" s="38"/>
+      <c r="C157" s="39"/>
+      <c r="D157" s="39"/>
+      <c r="E157" s="40"/>
     </row>
     <row r="158" spans="1:5">
-      <c r="A158" s="45" t="s">
+      <c r="A158" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="B158" s="45"/>
-      <c r="C158" s="45"/>
-      <c r="D158" s="45"/>
-      <c r="E158" s="45"/>
+      <c r="B158" s="41"/>
+      <c r="C158" s="41"/>
+      <c r="D158" s="41"/>
+      <c r="E158" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="41">
@@ -4901,7 +4889,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{33adc75a-1da8-4c89-8af6-be661affc362}</x14:id>
+          <x14:id>{e5c4ff38-cdbc-41f8-8111-33f11db47b07}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4915,7 +4903,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{08747732-96ba-437d-b06e-ac4d0a43a89f}</x14:id>
+          <x14:id>{ce6dd5b1-4f3b-44b3-845e-6501d65dbe3b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4941,7 +4929,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e4be11a-2955-4b07-a67c-aa0f15ef676b}</x14:id>
+          <x14:id>{7cd5f738-6c50-4ccb-b258-52bf47f3ed12}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4955,7 +4943,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5962f722-d975-4bad-9150-ee9898402e5d}</x14:id>
+          <x14:id>{95b38337-a990-4a02-8b6c-53d3265a49b8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4969,7 +4957,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{336e8abd-523f-46c9-b964-8d532a0987d1}</x14:id>
+          <x14:id>{53a33225-ebb9-4a41-abe2-2097e60ddc6e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4983,7 +4971,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c6869f4e-0209-49c4-b055-60e0d3360ca8}</x14:id>
+          <x14:id>{8aea5306-ef65-4627-8a66-58534deca117}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4997,7 +4985,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ab480e2a-3682-42e4-8362-f7dce5df0422}</x14:id>
+          <x14:id>{fb5b2f57-9451-49d9-b9a7-8d95f3248618}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5011,7 +4999,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f7947776-ef49-4a82-833c-e3af790aa7c0}</x14:id>
+          <x14:id>{a7f0002a-c702-415b-8169-4efa03b19759}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5025,7 +5013,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c6edb7a5-6f88-4f3c-a328-d682bd1f1233}</x14:id>
+          <x14:id>{ec983c11-db64-44bb-b541-b023879829a4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5039,7 +5027,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{07255bb7-df68-4ba5-b4fa-ed506670b08c}</x14:id>
+          <x14:id>{6f26c968-cebe-41cf-9944-480d0cdba0e5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5085,7 +5073,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9cd0042e-9a76-4489-9b6f-fa9308406915}</x14:id>
+          <x14:id>{7f0f6380-d4a2-4554-ac5a-7561718da915}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5099,7 +5087,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1cc9fd38-332e-476b-8755-b2bccd0a4c16}</x14:id>
+          <x14:id>{66bf1551-707f-44d6-8349-d1a8b8d45347}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5113,7 +5101,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f918c27e-9787-4173-9a4b-ecb91226b81b}</x14:id>
+          <x14:id>{35c887f0-183e-4c36-86fa-750de5b9b432}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5127,7 +5115,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{de961f03-d81d-4f0d-983e-f7014e42cee9}</x14:id>
+          <x14:id>{efe36e69-62a3-49c6-89aa-66ac6042bffd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5141,7 +5129,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e502e735-a49d-461d-ba73-52d9f1da1119}</x14:id>
+          <x14:id>{949e63e7-0ac7-49fd-83ca-769992c8a405}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5155,7 +5143,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{428af9ff-2b72-4c38-bf03-b09ed5caac37}</x14:id>
+          <x14:id>{2734b6f8-fa33-42fb-ae76-07e65bd29087}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5169,7 +5157,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7e48ffe1-d53c-4fbe-879a-d2ecbadeac9c}</x14:id>
+          <x14:id>{2d27626d-e539-4df3-aa87-7da12d7d1936}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5183,7 +5171,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{92f40775-060c-4e6b-a0e6-8044f636cd3d}</x14:id>
+          <x14:id>{bfcb78ce-6c53-47c0-b93a-0007575ce03b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5197,7 +5185,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{66ffbc46-b2a6-415a-a8a5-b25806b9abe6}</x14:id>
+          <x14:id>{59449685-1156-4c2f-99ed-6bf406b56117}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5211,7 +5199,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4ab18667-8c3d-427f-8900-2766c2064f78}</x14:id>
+          <x14:id>{80e88f1d-7691-46ce-8bde-4fe95a1daa20}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5225,7 +5213,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a37001fe-dc87-454a-87ee-11c29720151c}</x14:id>
+          <x14:id>{65951809-2866-4b2a-bf50-7c9f0209d743}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5233,13 +5221,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
+    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{33adc75a-1da8-4c89-8af6-be661affc362}">
+          <x14:cfRule type="dataBar" id="{e5c4ff38-cdbc-41f8-8111-33f11db47b07}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5250,7 +5238,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{08747732-96ba-437d-b06e-ac4d0a43a89f}">
+          <x14:cfRule type="dataBar" id="{ce6dd5b1-4f3b-44b3-845e-6501d65dbe3b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5261,7 +5249,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8e4be11a-2955-4b07-a67c-aa0f15ef676b}">
+          <x14:cfRule type="dataBar" id="{7cd5f738-6c50-4ccb-b258-52bf47f3ed12}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5274,7 +5262,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5962f722-d975-4bad-9150-ee9898402e5d}">
+          <x14:cfRule type="dataBar" id="{95b38337-a990-4a02-8b6c-53d3265a49b8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5285,7 +5273,7 @@
           <xm:sqref>I1:I9 I20:I24 I26:I1048576 I11:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{336e8abd-523f-46c9-b964-8d532a0987d1}">
+          <x14:cfRule type="dataBar" id="{53a33225-ebb9-4a41-abe2-2097e60ddc6e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5296,7 +5284,7 @@
           <xm:sqref>I1:I9 I20:I23 I26:I1048576 I11:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c6869f4e-0209-49c4-b055-60e0d3360ca8}">
+          <x14:cfRule type="dataBar" id="{8aea5306-ef65-4627-8a66-58534deca117}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5307,7 +5295,7 @@
           <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ab480e2a-3682-42e4-8362-f7dce5df0422}">
+          <x14:cfRule type="dataBar" id="{fb5b2f57-9451-49d9-b9a7-8d95f3248618}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5318,7 +5306,7 @@
           <xm:sqref>I1:I18 I20:I24 I26:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f7947776-ef49-4a82-833c-e3af790aa7c0}">
+          <x14:cfRule type="dataBar" id="{a7f0002a-c702-415b-8169-4efa03b19759}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5329,7 +5317,7 @@
           <xm:sqref>I2 I30 I51:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c6edb7a5-6f88-4f3c-a328-d682bd1f1233}">
+          <x14:cfRule type="dataBar" id="{ec983c11-db64-44bb-b541-b023879829a4}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5340,7 +5328,7 @@
           <xm:sqref>I2:I5 I26:I37 I9 I7 I39:I1048576 I11:I18 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{07255bb7-df68-4ba5-b4fa-ed506670b08c}">
+          <x14:cfRule type="dataBar" id="{6f26c968-cebe-41cf-9944-480d0cdba0e5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5351,7 +5339,7 @@
           <xm:sqref>I2:I5 I9 I26:I37 I11:I16 I39:I1048576 I7 I18 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9cd0042e-9a76-4489-9b6f-fa9308406915}">
+          <x14:cfRule type="dataBar" id="{7f0f6380-d4a2-4554-ac5a-7561718da915}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5362,7 +5350,7 @@
           <xm:sqref>I42:I47 I3:I5 I7 I39:I40 I9 I31:I33 I28 I18 I12:I14 I26 I20:I23 I49:I50 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1cc9fd38-332e-476b-8755-b2bccd0a4c16}">
+          <x14:cfRule type="dataBar" id="{66bf1551-707f-44d6-8349-d1a8b8d45347}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5373,7 +5361,7 @@
           <xm:sqref>I42:I47 I3:I5 I7 I39:I40 I9 I31:I33 I28 I18 I12:I14 I20:I23 I49:I50 I36:I37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f918c27e-9787-4173-9a4b-ecb91226b81b}">
+          <x14:cfRule type="dataBar" id="{35c887f0-183e-4c36-86fa-750de5b9b432}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5384,7 +5372,7 @@
           <xm:sqref>I39:I40 I3:I5 I7 I36:I37 I9 I31:I33 I28 I18 I12:I14 I16 I26 I20:I23 I42:I47 I49:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{de961f03-d81d-4f0d-983e-f7014e42cee9}">
+          <x14:cfRule type="dataBar" id="{efe36e69-62a3-49c6-89aa-66ac6042bffd}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5395,7 +5383,7 @@
           <xm:sqref>I36:I37 I3:I5 I7 I31:I34 I9 I42:I50 I26 I18 I28:I29 I11:I14 I16 I20:I23 I39:I40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e502e735-a49d-461d-ba73-52d9f1da1119}">
+          <x14:cfRule type="dataBar" id="{949e63e7-0ac7-49fd-83ca-769992c8a405}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5406,7 +5394,7 @@
           <xm:sqref>I39:I40 I3:I5 I7 I36:I37 I9 I31:I33 I26 I18 I11:I14 I16 I20:I23 I28:I29 I42:I47 I49:I50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{428af9ff-2b72-4c38-bf03-b09ed5caac37}">
+          <x14:cfRule type="dataBar" id="{2734b6f8-fa33-42fb-ae76-07e65bd29087}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5417,7 +5405,7 @@
           <xm:sqref>I39:I50 I3:I5 I7 I31:I37 I9 I11:I16 I20:I23 I18 I26:I29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7e48ffe1-d53c-4fbe-879a-d2ecbadeac9c}">
+          <x14:cfRule type="dataBar" id="{2d27626d-e539-4df3-aa87-7da12d7d1936}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5428,7 +5416,7 @@
           <xm:sqref>I39:I50 I3:I5 I7 I31:I37 I9 I28:I29 I26 I18 I20:I23 I11:I16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{92f40775-060c-4e6b-a0e6-8044f636cd3d}">
+          <x14:cfRule type="dataBar" id="{bfcb78ce-6c53-47c0-b93a-0007575ce03b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5439,7 +5427,7 @@
           <xm:sqref>I31:I37 I3:I5 I7 I39:I50 I9 I26:I29 I20:I23 I11:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{66ffbc46-b2a6-415a-a8a5-b25806b9abe6}">
+          <x14:cfRule type="dataBar" id="{59449685-1156-4c2f-99ed-6bf406b56117}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5450,7 +5438,7 @@
           <xm:sqref>I11:I18 I3:I7 I26:I29 I31:I50 I9 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4ab18667-8c3d-427f-8900-2766c2064f78}">
+          <x14:cfRule type="dataBar" id="{80e88f1d-7691-46ce-8bde-4fe95a1daa20}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5461,7 +5449,7 @@
           <xm:sqref>I26:I29 I3:I7 I39:I50 I31:I37 I9 I11:I18 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a37001fe-dc87-454a-87ee-11c29720151c}">
+          <x14:cfRule type="dataBar" id="{65951809-2866-4b2a-bf50-7c9f0209d743}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5481,11 +5469,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
-    <col min="2" max="2" width="8.125" customWidth="1"/>
-    <col min="3" max="3" width="8.875" customWidth="1"/>
+    <col min="2" max="2" width="8.12727272727273" customWidth="1"/>
+    <col min="3" max="3" width="8.87272727272727" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12200"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="收支与赞助鸣谢" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="116">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -111,177 +111,180 @@
     <t>Press_on</t>
   </si>
   <si>
-    <t>↑3</t>
-  </si>
-  <si>
     <t>用于购买内存条</t>
   </si>
   <si>
     <t>partyking1145</t>
   </si>
   <si>
+    <t>购买内存条</t>
+  </si>
+  <si>
+    <t>xiaoshenjin233</t>
+  </si>
+  <si>
+    <t>主板、硬盘、机箱</t>
+  </si>
+  <si>
+    <t>rocksuger</t>
+  </si>
+  <si>
+    <t>物品、电费</t>
+  </si>
+  <si>
+    <t>SNHGY</t>
+  </si>
+  <si>
+    <t>Sz05</t>
+  </si>
+  <si>
+    <t>woshixiaoliu_ovo</t>
+  </si>
+  <si>
+    <t>10天群管理员</t>
+  </si>
+  <si>
+    <t>Y37MzZ_TrusT</t>
+  </si>
+  <si>
+    <t>潜影盒、鞘翅、凋灵骷髅头颅</t>
+  </si>
+  <si>
+    <t>cgh</t>
+  </si>
+  <si>
+    <t>匿名玩家</t>
+  </si>
+  <si>
+    <t>srdownb</t>
+  </si>
+  <si>
+    <t>火药、遗物</t>
+  </si>
+  <si>
+    <t>Xs1st_</t>
+  </si>
+  <si>
+    <t>Alhion_WWW</t>
+  </si>
+  <si>
+    <t>chunfeng</t>
+  </si>
+  <si>
+    <t>darkmoon114514</t>
+  </si>
+  <si>
+    <t>KAMI</t>
+  </si>
+  <si>
+    <t>3组烟花</t>
+  </si>
+  <si>
+    <t>91kk</t>
+  </si>
+  <si>
+    <t>faxi</t>
+  </si>
+  <si>
+    <t>捐樱花映射VIP</t>
+  </si>
+  <si>
+    <t>wybhh51811</t>
+  </si>
+  <si>
+    <t>樱花映射VIP</t>
+  </si>
+  <si>
+    <t>red_chipi</t>
+  </si>
+  <si>
+    <t>↑24</t>
+  </si>
+  <si>
+    <t>5下界合金锭</t>
+  </si>
+  <si>
+    <t>Goocheu_fox</t>
+  </si>
+  <si>
     <t>↓1</t>
   </si>
   <si>
-    <t>购买内存条</t>
-  </si>
-  <si>
-    <t>xiaoshenjin233</t>
-  </si>
-  <si>
-    <t>主板、硬盘、机箱</t>
-  </si>
-  <si>
-    <t>rocksuger</t>
-  </si>
-  <si>
-    <t>物品、电费</t>
-  </si>
-  <si>
-    <t>SNHGY</t>
-  </si>
-  <si>
-    <t>Sz05</t>
-  </si>
-  <si>
-    <t>woshixiaoliu_ovo</t>
-  </si>
-  <si>
-    <t>10天群管理员</t>
-  </si>
-  <si>
-    <t>Y37MzZ_TrusT</t>
-  </si>
-  <si>
-    <t>潜影盒、鞘翅、凋灵骷髅头颅</t>
-  </si>
-  <si>
-    <t>cgh</t>
-  </si>
-  <si>
-    <t>匿名玩家</t>
-  </si>
-  <si>
-    <t>srdownb</t>
-  </si>
-  <si>
-    <t>火药、遗物</t>
-  </si>
-  <si>
-    <t>Xs1st_</t>
-  </si>
-  <si>
-    <t>Alhion_WWW</t>
-  </si>
-  <si>
-    <t>chunfeng</t>
-  </si>
-  <si>
-    <t>darkmoon114514</t>
-  </si>
-  <si>
-    <t>KAMI</t>
-  </si>
-  <si>
-    <t>3组烟花</t>
-  </si>
-  <si>
-    <t>91kk</t>
-  </si>
-  <si>
-    <t>faxi</t>
-  </si>
-  <si>
-    <t>捐樱花映射VIP</t>
-  </si>
-  <si>
-    <t>wybhh51811</t>
-  </si>
-  <si>
-    <t>樱花映射VIP</t>
-  </si>
-  <si>
-    <t>Goocheu_fox</t>
-  </si>
-  <si>
-    <t>5下界合金锭</t>
-  </si>
-  <si>
     <t>Cr_Dragon</t>
   </si>
   <si>
+    <t>拍卖账号</t>
+  </si>
+  <si>
     <t>XL12</t>
   </si>
   <si>
-    <t>拍卖账号</t>
+    <t>鞘翅、TP、电费、羊毛、村民、TNT</t>
   </si>
   <si>
     <t>Xiaoyingawa</t>
   </si>
   <si>
-    <t>鞘翅、TP、电费、羊毛、村民、TNT</t>
-  </si>
-  <si>
     <t>电费、经验</t>
   </si>
   <si>
+    <t>hanfengzunzhe</t>
+  </si>
+  <si>
+    <t>书架、紫珀块</t>
+  </si>
+  <si>
     <t>Onion520</t>
   </si>
   <si>
-    <t>hanfengzunzhe</t>
-  </si>
-  <si>
-    <t>书架、紫珀块</t>
+    <t>电费</t>
   </si>
   <si>
     <t>lhl</t>
   </si>
   <si>
-    <t>电费</t>
+    <t>10书架</t>
   </si>
   <si>
     <t>xhf</t>
   </si>
   <si>
-    <t>10书架</t>
-  </si>
-  <si>
     <t>YuSaMa1145</t>
   </si>
   <si>
+    <t>拍卖账号等</t>
+  </si>
+  <si>
     <t>Mo_Xuan_Yu</t>
   </si>
   <si>
-    <t>拍卖账号等</t>
+    <t>前哨战坐标等</t>
   </si>
   <si>
     <t>xiaomin</t>
   </si>
   <si>
-    <t>前哨战坐标等</t>
-  </si>
-  <si>
     <t>主板、CPU、电源、机械硬盘</t>
   </si>
   <si>
+    <t>海绵、电费、鞘翅、遗物</t>
+  </si>
+  <si>
     <t>A1TanJZ</t>
   </si>
   <si>
-    <t>海绵、电费、鞘翅、遗物</t>
-  </si>
-  <si>
     <t>村民</t>
   </si>
   <si>
     <t>4不详宝库</t>
   </si>
   <si>
+    <t>2村民蛋</t>
+  </si>
+  <si>
     <t>littlefish1688</t>
   </si>
   <si>
-    <t>2村民蛋</t>
-  </si>
-  <si>
     <t>鞘翅、神镐</t>
   </si>
   <si>
@@ -367,6 +370,9 @@
   </si>
   <si>
     <t>末地救援方案Pro</t>
+  </si>
+  <si>
+    <t>钻石胸甲</t>
   </si>
   <si>
     <t>电费的支出难以计算，故没有写入此表</t>
@@ -1216,7 +1222,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1326,6 +1332,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -1664,21 +1682,21 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K158"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:K159"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="15.6272727272727" customWidth="1"/>
-    <col min="2" max="2" width="18.2545454545455" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
-    <col min="4" max="4" width="9.37272727272727" customWidth="1"/>
-    <col min="5" max="5" width="33.1272727272727" customWidth="1"/>
-    <col min="7" max="7" width="5.12727272727273" customWidth="1"/>
-    <col min="8" max="8" width="18.2545454545455" customWidth="1"/>
-    <col min="9" max="9" width="12.8727272727273" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.6272727272727" style="3" customWidth="1"/>
-    <col min="11" max="11" width="5.12727272727273" customWidth="1"/>
-    <col min="13" max="13" width="15.6272727272727"/>
-    <col min="14" max="14" width="13.3727272727273"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="18.2583333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="9.375" customWidth="1"/>
+    <col min="5" max="5" width="33.125" customWidth="1"/>
+    <col min="7" max="7" width="5.125" customWidth="1"/>
+    <col min="8" max="8" width="18.2583333333333" customWidth="1"/>
+    <col min="9" max="9" width="12.875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="5.125" customWidth="1"/>
+    <col min="13" max="13" width="15.625"/>
+    <col min="14" max="14" width="13.375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1752,10 +1770,10 @@
       </c>
       <c r="I3" s="16">
         <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150,C152,C154,C156)</f>
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="J3" s="3">
-        <v>46203</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1940,9 +1958,6 @@
       <c r="J10" s="3">
         <v>46196</v>
       </c>
-      <c r="K10" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="17">
@@ -1959,13 +1974,13 @@
         <v>193.93</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" s="15">
         <v>9</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I11" s="2">
         <f>SUM(C86,C101,C105,C107,C112,C119,C124)</f>
@@ -1974,9 +1989,6 @@
       <c r="J11" s="3">
         <v>46047</v>
       </c>
-      <c r="K11" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="17">
@@ -1991,7 +2003,7 @@
         <v>-5.06999999999999</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G12" s="15">
         <v>10</v>
@@ -2006,16 +2018,13 @@
       <c r="J12" s="3">
         <v>45505</v>
       </c>
-      <c r="K12" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="17">
         <v>44787</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13" s="13">
         <v>5.02</v>
@@ -2038,9 +2047,6 @@
       <c r="J13" s="3">
         <v>45968</v>
       </c>
-      <c r="K13" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="17">
@@ -2055,13 +2061,13 @@
         <v>-780.05</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G14" s="15">
         <v>12</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I14" s="16">
         <f>SUM(C56,C46,C74)</f>
@@ -2086,13 +2092,13 @@
         <v>-660.05</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G15" s="15">
         <v>13</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I15" s="2">
         <f>SUM(C99,C109,C130,C137,C144)</f>
@@ -2121,7 +2127,7 @@
         <v>14</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I16" s="2">
         <f>SUM(C85:C85,C89,C96:C98,C117,C120,C122)</f>
@@ -2131,12 +2137,12 @@
         <v>46039</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:11">
       <c r="A17" s="17">
         <v>44953</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C17" s="13">
         <v>10</v>
@@ -2146,13 +2152,13 @@
         <v>-637.05</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G17" s="15">
         <v>15</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I17" s="2">
         <v>15</v>
@@ -2161,7 +2167,7 @@
         <v>45930</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:11">
       <c r="A18" s="17">
         <v>44958</v>
       </c>
@@ -2177,13 +2183,13 @@
         <v>-550.73</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G18" s="15">
         <v>16</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I18" s="16">
         <f>SUM(C40,C64)</f>
@@ -2193,10 +2199,10 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:11">
       <c r="A19" s="17"/>
       <c r="B19" s="22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C19" s="13">
         <v>1.32</v>
@@ -2207,7 +2213,7 @@
         <v>17</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I19" s="2">
         <f>SUM(C135,C139,C146)</f>
@@ -2217,7 +2223,7 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:11">
       <c r="A20" s="17">
         <v>44961</v>
       </c>
@@ -2236,7 +2242,7 @@
         <v>18</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I20" s="16">
         <v>10</v>
@@ -2245,7 +2251,7 @@
         <v>44953</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:11">
       <c r="A21" s="17">
         <v>45138</v>
       </c>
@@ -2261,13 +2267,13 @@
         <v>-428.73</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G21" s="15">
         <v>19</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I21" s="16">
         <v>10</v>
@@ -2276,12 +2282,12 @@
         <v>45234</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:11">
       <c r="A22" s="17">
         <v>45140</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C22" s="13">
         <v>0.11</v>
@@ -2295,7 +2301,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I22" s="16">
         <v>10</v>
@@ -2304,12 +2310,12 @@
         <v>45325</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:11">
       <c r="A23" s="17">
         <v>45141</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C23" s="13">
         <v>1.01</v>
@@ -2323,7 +2329,7 @@
         <v>21</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I23" s="16">
         <v>10</v>
@@ -2332,7 +2338,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:11">
       <c r="A24" s="17"/>
       <c r="B24" s="8" t="s">
         <v>15</v>
@@ -2342,13 +2348,13 @@
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G24" s="15">
         <v>22</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I24" s="2">
         <v>10</v>
@@ -2357,7 +2363,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:11">
       <c r="A25" s="17">
         <v>45160</v>
       </c>
@@ -2376,7 +2382,7 @@
         <v>23</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I25" s="16">
         <v>10</v>
@@ -2385,12 +2391,12 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:11">
       <c r="A26" s="17">
         <v>45234</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C26" s="13">
         <v>10</v>
@@ -2400,13 +2406,13 @@
         <v>-415.61</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G26">
         <v>24</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I26" s="2">
         <v>8</v>
@@ -2415,7 +2421,7 @@
         <v>45860</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:11">
       <c r="A27" s="17"/>
       <c r="B27" s="8"/>
       <c r="C27" s="18">
@@ -2423,22 +2429,25 @@
       </c>
       <c r="D27" s="23"/>
       <c r="E27" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G27">
         <v>25</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>57</v>
+      <c r="H27" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="I27" s="2">
-        <v>7.33</v>
+        <v>8</v>
       </c>
       <c r="J27" s="3">
-        <v>45907</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>46205</v>
+      </c>
+      <c r="K27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="17">
         <v>45249</v>
       </c>
@@ -2453,23 +2462,25 @@
         <v>-400.11</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G28">
         <v>26</v>
       </c>
       <c r="H28" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I28" s="2">
+        <v>7.33</v>
+      </c>
+      <c r="J28" s="3">
+        <v>45907</v>
+      </c>
+      <c r="K28" t="s">
         <v>59</v>
       </c>
-      <c r="I28" s="16">
-        <f>SUM(C82,C84,C94)</f>
-        <v>6.98</v>
-      </c>
-      <c r="J28" s="3">
-        <v>45861</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="17">
         <v>45305</v>
       </c>
@@ -2490,19 +2501,23 @@
       <c r="H29" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="I29" s="2">
-        <v>6</v>
+      <c r="I29" s="16">
+        <f>SUM(C82,C84,C94)</f>
+        <v>6.98</v>
       </c>
       <c r="J29" s="3">
-        <v>45868</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>45861</v>
+      </c>
+      <c r="K29" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="17">
         <v>45325</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C30" s="13">
         <v>10</v>
@@ -2521,13 +2536,16 @@
         <v>62</v>
       </c>
       <c r="I30" s="2">
-        <v>5.04</v>
+        <v>6</v>
       </c>
       <c r="J30" s="3">
-        <v>46160</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>45868</v>
+      </c>
+      <c r="K30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="17">
         <v>45341</v>
       </c>
@@ -2548,16 +2566,19 @@
         <v>29</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="16">
-        <v>5.02</v>
+        <v>64</v>
+      </c>
+      <c r="I31" s="2">
+        <v>5.04</v>
       </c>
       <c r="J31" s="3">
-        <v>44787</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>46160</v>
+      </c>
+      <c r="K31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="17">
         <v>45368</v>
       </c>
@@ -2572,22 +2593,25 @@
         <v>-239.1</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G32">
         <v>30</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="I32" s="16">
-        <v>5</v>
+        <v>5.02</v>
       </c>
       <c r="J32" s="3">
-        <v>45634</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>44787</v>
+      </c>
+      <c r="K32" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="17">
         <v>45387</v>
       </c>
@@ -2611,13 +2635,16 @@
         <v>68</v>
       </c>
       <c r="I33" s="16">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="J33" s="3">
-        <v>45707</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+        <v>45634</v>
+      </c>
+      <c r="K33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" s="17">
         <v>45394</v>
       </c>
@@ -2640,14 +2667,17 @@
       <c r="H34" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="I34" s="2">
-        <v>4</v>
+      <c r="I34" s="16">
+        <v>4.15</v>
       </c>
       <c r="J34" s="3">
-        <v>45885</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>45707</v>
+      </c>
+      <c r="K34" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" s="17">
         <v>45396</v>
       </c>
@@ -2667,18 +2697,20 @@
       <c r="G35">
         <v>33</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" s="10" t="s">
         <v>72</v>
       </c>
       <c r="I35" s="2">
-        <f>SUM(C100,C108)</f>
         <v>4</v>
       </c>
       <c r="J35" s="3">
-        <v>45934</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>45885</v>
+      </c>
+      <c r="K35" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="17">
         <v>45403</v>
       </c>
@@ -2696,17 +2728,21 @@
       <c r="G36">
         <v>34</v>
       </c>
-      <c r="H36" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I36" s="16">
-        <v>3</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+      <c r="H36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I36" s="2">
+        <f>SUM(C100,C108)</f>
+        <v>4</v>
+      </c>
+      <c r="J36" s="3">
+        <v>45934</v>
+      </c>
+      <c r="K36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" s="17">
         <v>45403</v>
       </c>
@@ -2727,16 +2763,19 @@
         <v>35</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="I37" s="16">
         <v>3</v>
       </c>
-      <c r="J37" s="3">
-        <v>45500</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+      <c r="J37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K37" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" s="17">
         <v>45412</v>
       </c>
@@ -2759,14 +2798,17 @@
       <c r="H38" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I38" s="2">
-        <v>2.5</v>
+      <c r="I38" s="16">
+        <v>3</v>
       </c>
       <c r="J38" s="3">
-        <v>45976</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>45500</v>
+      </c>
+      <c r="K38" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" s="17">
         <v>45417</v>
       </c>
@@ -2787,22 +2829,24 @@
         <v>37</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="I39" s="16">
-        <f>SUM(C35,C33:C33)</f>
-        <v>2.18</v>
+        <v>77</v>
+      </c>
+      <c r="I39" s="2">
+        <v>2.5</v>
       </c>
       <c r="J39" s="3">
-        <v>45396</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>45976</v>
+      </c>
+      <c r="K39" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" s="17">
         <v>45421</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C40" s="13">
         <v>5</v>
@@ -2818,16 +2862,20 @@
         <v>38</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="I40" s="16">
-        <v>2</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <f>SUM(C35,C33:C33)</f>
+        <v>2.18</v>
+      </c>
+      <c r="J40" s="3">
+        <v>45396</v>
+      </c>
+      <c r="K40" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" s="17">
         <v>45478</v>
       </c>
@@ -2841,22 +2889,25 @@
         <v>-1999.72</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G41">
         <v>39</v>
       </c>
-      <c r="H41" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I41" s="2">
+      <c r="H41" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="16">
         <v>2</v>
       </c>
-      <c r="J41" s="3">
-        <v>45907</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+      <c r="J41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K41" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" s="17">
         <v>45494</v>
       </c>
@@ -2876,17 +2927,20 @@
       <c r="G42" s="15">
         <v>40</v>
       </c>
-      <c r="H42" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="I42" s="16">
-        <v>1.32</v>
+      <c r="H42" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I42" s="2">
+        <v>2</v>
       </c>
       <c r="J42" s="3">
-        <v>44958</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>45907</v>
+      </c>
+      <c r="K42" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" s="17"/>
       <c r="B43" s="8" t="s">
         <v>15</v>
@@ -2896,22 +2950,25 @@
       </c>
       <c r="D43" s="23"/>
       <c r="E43" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G43">
         <v>41</v>
       </c>
-      <c r="H43" s="10" t="s">
-        <v>20</v>
+      <c r="H43" s="24" t="s">
+        <v>41</v>
       </c>
       <c r="I43" s="16">
-        <v>1.28</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
+        <v>1.32</v>
+      </c>
+      <c r="J43" s="3">
+        <v>44958</v>
+      </c>
+      <c r="K43" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" s="25">
         <v>45495</v>
       </c>
@@ -2926,22 +2983,25 @@
         <v>-1907.27</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G44">
         <v>42</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="I44" s="16">
-        <v>1.01</v>
-      </c>
-      <c r="J44" s="3">
-        <v>45141</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>1.28</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K44" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" s="25">
         <v>45496</v>
       </c>
@@ -2960,19 +3020,22 @@
         <v>43</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="I45" s="16">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="J45" s="3">
-        <v>45794</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
+        <v>45141</v>
+      </c>
+      <c r="K45" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" s="29"/>
       <c r="B46" s="26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C46" s="27">
         <v>3</v>
@@ -2985,16 +3048,19 @@
         <v>44</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="I46" s="16">
-        <v>0.55</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
+        <v>1</v>
+      </c>
+      <c r="J46" s="3">
+        <v>45794</v>
+      </c>
+      <c r="K46" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" s="17">
         <v>45497</v>
       </c>
@@ -3009,27 +3075,30 @@
         <v>-1874.27</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G47">
         <v>45</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="I47" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="J47" s="3">
-        <v>45697</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
+        <v>0.55</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K47" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" s="25">
         <v>45500</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C48" s="27">
         <v>3</v>
@@ -3045,14 +3114,17 @@
       <c r="H48" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="I48" s="2">
+      <c r="I48" s="16">
         <v>0.5</v>
       </c>
       <c r="J48" s="3">
-        <v>45885</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+        <v>45697</v>
+      </c>
+      <c r="K48" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" s="31"/>
       <c r="B49" s="26" t="s">
         <v>13</v>
@@ -3068,16 +3140,19 @@
         <v>47</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="I49" s="16">
-        <v>0.11</v>
+        <v>87</v>
+      </c>
+      <c r="I49" s="2">
+        <v>0.5</v>
       </c>
       <c r="J49" s="3">
-        <v>45140</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
+        <v>45885</v>
+      </c>
+      <c r="K49" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" s="25">
         <v>45505</v>
       </c>
@@ -3092,22 +3167,25 @@
         <v>-1856.27</v>
       </c>
       <c r="E50" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G50">
         <v>48</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="I50" s="16">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="J50" s="3">
-        <v>44213</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+        <v>45140</v>
+      </c>
+      <c r="K50" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" s="25">
         <v>45507</v>
       </c>
@@ -3124,8 +3202,23 @@
       <c r="E51" s="28" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="52" spans="1:10">
+      <c r="G51">
+        <v>49</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="J51" s="3">
+        <v>44213</v>
+      </c>
+      <c r="K51" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
       <c r="A52" s="31"/>
       <c r="B52" s="26" t="s">
         <v>25</v>
@@ -3135,10 +3228,10 @@
       </c>
       <c r="D52" s="30"/>
       <c r="E52" s="28" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53" s="25">
         <v>45508</v>
       </c>
@@ -3156,7 +3249,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:11">
       <c r="A54" s="31"/>
       <c r="B54" s="26" t="s">
         <v>17</v>
@@ -3167,7 +3260,7 @@
       <c r="D54" s="30"/>
       <c r="E54" s="28"/>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:11">
       <c r="A55" s="25">
         <v>45509</v>
       </c>
@@ -3180,13 +3273,13 @@
         <v>-1737.27</v>
       </c>
       <c r="E55" s="28" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
       <c r="A56" s="31"/>
       <c r="B56" s="26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C56" s="27">
         <v>10</v>
@@ -3194,7 +3287,7 @@
       <c r="D56" s="30"/>
       <c r="E56" s="28"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:11">
       <c r="A57" s="25">
         <v>45510</v>
       </c>
@@ -3209,10 +3302,10 @@
         <v>-1697.27</v>
       </c>
       <c r="E57" s="28" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" s="25">
         <v>45525</v>
       </c>
@@ -3228,10 +3321,10 @@
         <v>-1625.27</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
       <c r="A59" s="25">
         <v>45525</v>
       </c>
@@ -3246,10 +3339,10 @@
         <v>-1619.27</v>
       </c>
       <c r="E59" s="28" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60" s="25">
         <v>45549</v>
       </c>
@@ -3267,7 +3360,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:11">
       <c r="A61" s="29"/>
       <c r="B61" s="33" t="s">
         <v>17</v>
@@ -3277,10 +3370,10 @@
       </c>
       <c r="D61" s="30"/>
       <c r="E61" s="28" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62" s="31">
         <v>45551</v>
       </c>
@@ -3296,7 +3389,7 @@
       </c>
       <c r="E62" s="28"/>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:11">
       <c r="A63" s="25">
         <v>45552</v>
       </c>
@@ -3312,12 +3405,12 @@
       </c>
       <c r="E63" s="28"/>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:11">
       <c r="A64" s="25">
         <v>45555</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C64" s="27">
         <v>6</v>
@@ -3338,7 +3431,7 @@
       </c>
       <c r="D65" s="30"/>
       <c r="E65" s="28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3390,7 +3483,7 @@
         <v>-1389.27</v>
       </c>
       <c r="E68" s="28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3468,7 +3561,7 @@
         <v>45634</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C73" s="27">
         <v>5</v>
@@ -3484,14 +3577,14 @@
     <row r="74" spans="1:5">
       <c r="A74" s="17"/>
       <c r="B74" s="33" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C74" s="27">
         <v>10</v>
       </c>
       <c r="D74" s="30"/>
       <c r="E74" s="28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3499,7 +3592,7 @@
         <v>45649</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C75" s="27">
         <v>10</v>
@@ -3525,7 +3618,7 @@
         <v>-1304.27</v>
       </c>
       <c r="E76" s="28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3551,7 +3644,7 @@
         <v>45697</v>
       </c>
       <c r="B78" s="33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C78" s="27">
         <v>0.5</v>
@@ -3567,7 +3660,7 @@
         <v>45707</v>
       </c>
       <c r="B79" s="33" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C79" s="27">
         <v>4.15</v>
@@ -3583,7 +3676,7 @@
         <v>45794</v>
       </c>
       <c r="B80" s="33" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C80" s="27">
         <v>1</v>
@@ -3615,7 +3708,7 @@
         <v>45844</v>
       </c>
       <c r="B82" s="33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C82" s="27">
         <v>2.48</v>
@@ -3631,7 +3724,7 @@
         <v>45860</v>
       </c>
       <c r="B83" s="33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C83" s="27">
         <v>8</v>
@@ -3647,7 +3740,7 @@
         <v>45861</v>
       </c>
       <c r="B84" s="33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C84" s="27">
         <v>0.5</v>
@@ -3663,7 +3756,7 @@
         <v>45865</v>
       </c>
       <c r="B85" s="33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C85" s="27">
         <v>3</v>
@@ -3679,7 +3772,7 @@
         <v>45868</v>
       </c>
       <c r="B86" s="33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C86" s="27">
         <v>5.01</v>
@@ -3695,7 +3788,7 @@
         <v>45868</v>
       </c>
       <c r="B87" s="33" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C87" s="27">
         <v>6</v>
@@ -3705,7 +3798,7 @@
         <v>-1237.97</v>
       </c>
       <c r="E87" s="28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -3731,7 +3824,7 @@
         <v>45878</v>
       </c>
       <c r="B89" s="33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C89" s="27">
         <v>0.01</v>
@@ -3757,7 +3850,7 @@
         <v>-1206.96</v>
       </c>
       <c r="E90" s="34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -3783,7 +3876,7 @@
         <v>45885</v>
       </c>
       <c r="B92" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C92" s="27">
         <v>0.5</v>
@@ -3797,7 +3890,7 @@
     <row r="93" spans="1:5">
       <c r="A93" s="17"/>
       <c r="B93" s="33" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C93" s="27">
         <v>6</v>
@@ -3808,7 +3901,7 @@
     <row r="94" spans="1:5">
       <c r="A94" s="17"/>
       <c r="B94" s="33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C94" s="27">
         <v>4</v>
@@ -3839,7 +3932,7 @@
         <v>45894</v>
       </c>
       <c r="B96" s="33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C96" s="27">
         <v>1</v>
@@ -3855,7 +3948,7 @@
         <v>45905</v>
       </c>
       <c r="B97" s="33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C97" s="27">
         <v>7.33</v>
@@ -3871,7 +3964,7 @@
         <v>45907</v>
       </c>
       <c r="B98" s="33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C98" s="27">
         <v>2</v>
@@ -3885,7 +3978,7 @@
     <row r="99" spans="1:5">
       <c r="A99" s="31"/>
       <c r="B99" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C99" s="27">
         <v>2</v>
@@ -3896,7 +3989,7 @@
     <row r="100" spans="1:5">
       <c r="A100" s="31"/>
       <c r="B100" s="33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C100" s="27">
         <v>2</v>
@@ -3907,7 +4000,7 @@
     <row r="101" spans="1:5">
       <c r="A101" s="31"/>
       <c r="B101" s="33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C101" s="27">
         <v>2</v>
@@ -3918,7 +4011,7 @@
     <row r="102" spans="1:5">
       <c r="A102" s="31"/>
       <c r="B102" s="33" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C102" s="27">
         <v>2</v>
@@ -3939,7 +4032,7 @@
         <v>-1298.13</v>
       </c>
       <c r="E103" s="34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -3965,7 +4058,7 @@
         <v>45925</v>
       </c>
       <c r="B105" s="33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C105" s="27">
         <v>10</v>
@@ -3981,7 +4074,7 @@
         <v>45930</v>
       </c>
       <c r="B106" s="33" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C106" s="27">
         <v>15</v>
@@ -3997,7 +4090,7 @@
         <v>45934</v>
       </c>
       <c r="B107" s="33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C107" s="27">
         <v>2</v>
@@ -4011,7 +4104,7 @@
     <row r="108" spans="1:5">
       <c r="A108" s="31"/>
       <c r="B108" s="33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C108" s="27">
         <v>2</v>
@@ -4025,7 +4118,7 @@
     <row r="109" spans="1:5">
       <c r="A109" s="31"/>
       <c r="B109" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C109" s="27">
         <v>0.45</v>
@@ -4051,7 +4144,7 @@
         <v>-1202.68</v>
       </c>
       <c r="E110" s="34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -4075,7 +4168,7 @@
         <v>45969</v>
       </c>
       <c r="B112" s="33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C112" s="27">
         <v>6</v>
@@ -4101,7 +4194,7 @@
         <v>-1131.68</v>
       </c>
       <c r="E113" s="34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -4119,7 +4212,7 @@
         <v>-1094.68</v>
       </c>
       <c r="E114" s="34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -4127,7 +4220,7 @@
         <v>45976</v>
       </c>
       <c r="B115" s="33" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C115" s="27">
         <v>2.5</v>
@@ -4153,7 +4246,7 @@
         <v>-1072.18</v>
       </c>
       <c r="E116" s="34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -4161,7 +4254,7 @@
         <v>45990</v>
       </c>
       <c r="B117" s="33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C117" s="27">
         <v>1</v>
@@ -4171,7 +4264,7 @@
         <v>-1071.18</v>
       </c>
       <c r="E117" s="34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -4195,7 +4288,7 @@
         <v>46029</v>
       </c>
       <c r="B119" s="33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C119" s="27">
         <v>16</v>
@@ -4205,7 +4298,7 @@
         <v>-1045.18</v>
       </c>
       <c r="E119" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -4213,7 +4306,7 @@
         <v>46031</v>
       </c>
       <c r="B120" s="33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C120" s="27">
         <v>2</v>
@@ -4239,7 +4332,7 @@
         <v>-977.18</v>
       </c>
       <c r="E121" s="34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -4247,7 +4340,7 @@
         <v>46039</v>
       </c>
       <c r="B122" s="33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C122" s="27">
         <v>1</v>
@@ -4273,13 +4366,13 @@
         <v>-969.18</v>
       </c>
       <c r="E123" s="34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="31"/>
       <c r="B124" s="33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C124" s="27">
         <v>11</v>
@@ -4323,7 +4416,7 @@
         <v>-917.18</v>
       </c>
       <c r="E126" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -4359,7 +4452,7 @@
         <v>-834.18</v>
       </c>
       <c r="E128" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -4375,7 +4468,7 @@
         <v>-804.18</v>
       </c>
       <c r="E129" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -4383,7 +4476,7 @@
         <v>46069</v>
       </c>
       <c r="B130" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C130" s="27">
         <v>5</v>
@@ -4407,13 +4500,13 @@
         <v>-791.18</v>
       </c>
       <c r="E131" s="34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="31"/>
       <c r="B132" s="33" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C132" s="27">
         <v>10</v>
@@ -4459,7 +4552,7 @@
         <v>46074</v>
       </c>
       <c r="B135" s="33" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C135" s="27">
         <v>1.5</v>
@@ -4493,7 +4586,7 @@
         <v>46085</v>
       </c>
       <c r="B137" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C137" s="27">
         <v>10</v>
@@ -4519,7 +4612,7 @@
         <v>-656.36</v>
       </c>
       <c r="E138" s="34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -4527,7 +4620,7 @@
         <v>46130</v>
       </c>
       <c r="B139" s="33" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C139" s="27">
         <v>3</v>
@@ -4551,7 +4644,7 @@
         <v>-3151.15</v>
       </c>
       <c r="E140" s="34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -4607,7 +4700,7 @@
         <v>46144</v>
       </c>
       <c r="B144" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C144" s="27">
         <v>1</v>
@@ -4623,7 +4716,7 @@
         <v>46145</v>
       </c>
       <c r="B145" s="33" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C145" s="27">
         <v>10</v>
@@ -4633,13 +4726,13 @@
         <v>-3105.15</v>
       </c>
       <c r="E145" s="34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="31"/>
       <c r="B146" s="33" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C146" s="27">
         <v>6</v>
@@ -4689,7 +4782,7 @@
         <v>46160</v>
       </c>
       <c r="B149" s="33" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C149" s="27">
         <v>5.04</v>
@@ -4799,48 +4892,66 @@
         <v>-2909.11</v>
       </c>
       <c r="E155" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="25">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B156" s="33" t="s">
         <v>13</v>
       </c>
       <c r="C156" s="27">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D156" s="21">
         <f>SUM(C3:C156)</f>
-        <v>-2894.11</v>
+        <v>-2889.11</v>
       </c>
       <c r="E156" s="34" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="157" spans="1:5">
-      <c r="A157" s="37"/>
-      <c r="B157" s="38"/>
-      <c r="C157" s="39"/>
-      <c r="D157" s="39"/>
-      <c r="E157" s="40"/>
-    </row>
-    <row r="158" spans="1:5">
-      <c r="A158" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="B158" s="41"/>
-      <c r="C158" s="41"/>
-      <c r="D158" s="41"/>
-      <c r="E158" s="41"/>
+      <c r="A157" s="37">
+        <v>46205</v>
+      </c>
+      <c r="B157" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C157" s="39">
+        <v>8</v>
+      </c>
+      <c r="D157" s="21">
+        <f>SUM(C3:C157)</f>
+        <v>-2881.11</v>
+      </c>
+      <c r="E157" s="40" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="158" ht="14.25" spans="1:5">
+      <c r="A158" s="41"/>
+      <c r="B158" s="42"/>
+      <c r="C158" s="43"/>
+      <c r="D158" s="43"/>
+      <c r="E158" s="44"/>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="B159" s="45"/>
+      <c r="C159" s="45"/>
+      <c r="D159" s="45"/>
+      <c r="E159" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="41">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A158:E158"/>
+    <mergeCell ref="A159:E159"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A23:A24"/>
@@ -4881,7 +4992,7 @@
     <mergeCell ref="D98:D102"/>
   </mergeCells>
   <conditionalFormatting sqref="I25">
-    <cfRule type="dataBar" priority="18">
+    <cfRule type="dataBar" priority="19">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4889,7 +5000,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e5c4ff38-cdbc-41f8-8111-33f11db47b07}</x14:id>
+          <x14:id>{aff9f52c-85a9-499b-ae27-3ebe825d11aa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4903,13 +5014,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ce6dd5b1-4f3b-44b3-845e-6501d65dbe3b}</x14:id>
+          <x14:id>{b036c6b4-b3b1-447e-9995-6217e4e4fef8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D157 D159:D1048576">
-    <cfRule type="colorScale" priority="80">
+  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D158 D160:D1048576">
+    <cfRule type="colorScale" priority="81">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4921,7 +5032,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1 G2:I2">
-    <cfRule type="dataBar" priority="91">
+    <cfRule type="dataBar" priority="92">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4929,12 +5040,68 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7cd5f738-6c50-4ccb-b258-52bf47f3ed12}</x14:id>
+          <x14:id>{20fa9b1b-7838-4ea5-b137-a512bdd60548}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I9 I20:I24 I26:I1048576 I11:I18">
+  <conditionalFormatting sqref="I1:I26 I28:I1048576">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{c3fe1633-2d15-4c57-b396-2ebba2782a46}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I9 I20:I24 I26 I28:I1048576 I11:I18">
+    <cfRule type="dataBar" priority="23">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{c2454dbf-2bba-497e-bb46-cf5ae34c8309}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I9 I20:I23 I26 I28:I1048576 I11:I18">
+    <cfRule type="dataBar" priority="24">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{47aaa231-4aaf-4fd8-bdd3-2ae040de8f51}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I24 I26 I28:I1048576">
+    <cfRule type="dataBar" priority="20">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{b838d886-995e-4ce0-817f-9f82e986b46d}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I18 I20:I24 I26 I28:I1048576">
     <cfRule type="dataBar" priority="22">
       <dataBar>
         <cfvo type="min"/>
@@ -4943,13 +5110,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{95b38337-a990-4a02-8b6c-53d3265a49b8}</x14:id>
+          <x14:id>{86dcc80c-759d-4a5a-acd3-643f9ca3fceb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I9 I20:I23 I26:I1048576 I11:I18">
-    <cfRule type="dataBar" priority="23">
+  <conditionalFormatting sqref="I2 I52:I1048576 I31">
+    <cfRule type="dataBar" priority="50">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4957,13 +5124,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{53a33225-ebb9-4a41-abe2-2097e60ddc6e}</x14:id>
+          <x14:id>{f23da25e-49e7-4674-b7d1-52a3df7f4321}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I24 I26:I1048576">
-    <cfRule type="dataBar" priority="19">
+  <conditionalFormatting sqref="I2:I5 I26 I11:I18 I9 I7 I40:I1048576 I20:I23 I28:I38">
+    <cfRule type="dataBar" priority="27">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4971,13 +5138,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8aea5306-ef65-4627-8a66-58534deca117}</x14:id>
+          <x14:id>{3eac9ceb-21d2-4efc-920e-08e287498c57}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I18 I20:I24 I26:I1048576">
-    <cfRule type="dataBar" priority="21">
+  <conditionalFormatting sqref="I2:I5 I9 I26 I7 I11:I16 I40:I1048576 I20:I23 I18 I28:I38">
+    <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4985,55 +5152,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fb5b2f57-9451-49d9-b9a7-8d95f3248618}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2 I30 I51:I1048576">
-    <cfRule type="dataBar" priority="49">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a7f0002a-c702-415b-8169-4efa03b19759}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5 I26:I37 I9 I7 I39:I1048576 I11:I18 I20:I23">
-    <cfRule type="dataBar" priority="26">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ec983c11-db64-44bb-b541-b023879829a4}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5 I9 I26:I37 I11:I16 I39:I1048576 I7 I18 I20:I23">
-    <cfRule type="dataBar" priority="30">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6f26c968-cebe-41cf-9944-480d0cdba0e5}</x14:id>
+          <x14:id>{6646db04-ae3d-46e5-bbff-2d8592bdc898}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3 D10:D18 D20:D23 D25:D26 D28:D33">
-    <cfRule type="colorScale" priority="103">
+    <cfRule type="colorScale" priority="104">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5043,7 +5168,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="115">
+    <cfRule type="colorScale" priority="116">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5053,7 +5178,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D18 D20:D23 D25:D26 D28:D34">
-    <cfRule type="colorScale" priority="81">
+    <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5064,21 +5189,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I42:I47 I3:I5 I7 I39:I40 I9 I31:I33 I28 I18 I12:I14 I26 I20:I23 I49:I50 I36:I37">
-    <cfRule type="dataBar" priority="36">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7f0f6380-d4a2-4554-ac5a-7561718da915}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I42:I47 I3:I5 I7 I39:I40 I9 I31:I33 I28 I18 I12:I14 I20:I23 I49:I50 I36:I37">
+  <conditionalFormatting sqref="I12:I14 I3:I5 I7 I18 I9 I20:I23 I26 I37:I38 I29 I32:I34 I40:I41 I43:I48 I50:I51">
     <cfRule type="dataBar" priority="37">
       <dataBar>
         <cfvo type="min"/>
@@ -5087,12 +5198,54 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{66bf1551-707f-44d6-8349-d1a8b8d45347}</x14:id>
+          <x14:id>{3d9ec24e-a1da-440a-bfaa-cbf724d2cdac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I39:I40 I3:I5 I7 I36:I37 I9 I31:I33 I28 I18 I12:I14 I16 I26 I20:I23 I42:I47 I49:I50">
+  <conditionalFormatting sqref="I18 I3:I5 I7 I12:I14 I9 I20:I23 I37:I38 I29 I32:I34 I40:I41 I43:I48 I50:I51">
+    <cfRule type="dataBar" priority="38">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{213a9139-65c9-4b34-a9e0-585d2d02d42e}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I16 I3:I5 I7 I12:I14 I9 I20:I23 I26 I18 I50:I51 I29 I32:I34 I37:I38 I40:I41 I43:I48">
+    <cfRule type="dataBar" priority="35">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{ab67dc00-3d99-4bc8-8c0f-a963b304cff5}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:I14 I3:I5 I7 I20:I23 I9 I16 I26 I18 I40:I41 I29:I30 I43:I51 I32:I35 I37:I38">
+    <cfRule type="dataBar" priority="33">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{f2ad4f43-4518-41c6-8a22-0234dd053784}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I20:I23 I3:I5 I7 I16 I9 I11:I14 I26 I18 I50:I51 I32:I34 I37:I38 I40:I41 I43:I48 I29:I30">
     <cfRule type="dataBar" priority="34">
       <dataBar>
         <cfvo type="min"/>
@@ -5101,12 +5254,26 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{35c887f0-183e-4c36-86fa-750de5b9b432}</x14:id>
+          <x14:id>{fcc7d6c5-9727-4ec5-bfc8-cb96708af8cc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I36:I37 I3:I5 I7 I31:I34 I9 I42:I50 I26 I18 I28:I29 I11:I14 I16 I20:I23 I39:I40">
+  <conditionalFormatting sqref="I18 I20:I23 I3:I5 I7 I26 I9 I11:I16 I28:I30 I32:I38 I40:I51">
+    <cfRule type="dataBar" priority="29">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2e9e720d-2fc5-47e8-986e-7a35ff4cafdc}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:I16 I3:I5 I7 I20:I23 I9 I18 I26 I40:I51 I29:I30 I32:I38">
     <cfRule type="dataBar" priority="32">
       <dataBar>
         <cfvo type="min"/>
@@ -5115,26 +5282,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{efe36e69-62a3-49c6-89aa-66ac6042bffd}</x14:id>
+          <x14:id>{d8123ca4-e3e4-41ac-9faf-b882f660c764}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I39:I40 I3:I5 I7 I36:I37 I9 I31:I33 I26 I18 I11:I14 I16 I20:I23 I28:I29 I42:I47 I49:I50">
-    <cfRule type="dataBar" priority="33">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{949e63e7-0ac7-49fd-83ca-769992c8a405}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I39:I50 I3:I5 I7 I31:I37 I9 I11:I16 I20:I23 I18 I26:I29">
+  <conditionalFormatting sqref="I11:I18 I3:I5 I7 I20:I23 I9 I26 I32:I38 I28:I30 I40:I51">
     <cfRule type="dataBar" priority="28">
       <dataBar>
         <cfvo type="min"/>
@@ -5143,54 +5296,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2734b6f8-fa33-42fb-ae76-07e65bd29087}</x14:id>
+          <x14:id>{57788638-193d-4e69-be69-87ed19204da0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I39:I50 I3:I5 I7 I31:I37 I9 I28:I29 I26 I18 I20:I23 I11:I16">
-    <cfRule type="dataBar" priority="31">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2d27626d-e539-4df3-aa87-7da12d7d1936}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I31:I37 I3:I5 I7 I39:I50 I9 I26:I29 I20:I23 I11:I18">
-    <cfRule type="dataBar" priority="27">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bfcb78ce-6c53-47c0-b93a-0007575ce03b}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I18 I3:I7 I26:I29 I31:I50 I9 I20:I23">
-    <cfRule type="dataBar" priority="24">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{59449685-1156-4c2f-99ed-6bf406b56117}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I26:I29 I3:I7 I39:I50 I31:I37 I9 I11:I18 I20:I23">
+  <conditionalFormatting sqref="I11:I18 I3:I7 I26 I20:I23 I9 I28:I30 I32:I51">
     <cfRule type="dataBar" priority="25">
       <dataBar>
         <cfvo type="min"/>
@@ -5199,13 +5310,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{80e88f1d-7691-46ce-8bde-4fe95a1daa20}</x14:id>
+          <x14:id>{2bc491ac-0919-4df1-b05b-c2556d76ce29}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I26:I29 I3:I24 I31:I50">
-    <cfRule type="dataBar" priority="20">
+  <conditionalFormatting sqref="I26 I20:I23 I3:I7 I11:I18 I9 I28:I30 I32:I38 I40:I51">
+    <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5213,7 +5324,21 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{65951809-2866-4b2a-bf50-7c9f0209d743}</x14:id>
+          <x14:id>{750e69f7-5f96-4d4c-aa99-1d48c2b8295a}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I26 I3:I24 I32:I51 I28:I30">
+    <cfRule type="dataBar" priority="21">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{39a9d97c-1701-4008-b243-abcc23b82f6b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5221,13 +5346,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
+    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e5c4ff38-cdbc-41f8-8111-33f11db47b07}">
+          <x14:cfRule type="dataBar" id="{aff9f52c-85a9-499b-ae27-3ebe825d11aa}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5238,7 +5363,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ce6dd5b1-4f3b-44b3-845e-6501d65dbe3b}">
+          <x14:cfRule type="dataBar" id="{b036c6b4-b3b1-447e-9995-6217e4e4fef8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5249,7 +5374,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7cd5f738-6c50-4ccb-b258-52bf47f3ed12}">
+          <x14:cfRule type="dataBar" id="{20fa9b1b-7838-4ea5-b137-a512bdd60548}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5262,7 +5387,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{95b38337-a990-4a02-8b6c-53d3265a49b8}">
+          <x14:cfRule type="dataBar" id="{c3fe1633-2d15-4c57-b396-2ebba2782a46}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5270,10 +5395,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I9 I20:I24 I26:I1048576 I11:I18</xm:sqref>
+          <xm:sqref>I1:I26 I28:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{53a33225-ebb9-4a41-abe2-2097e60ddc6e}">
+          <x14:cfRule type="dataBar" id="{c2454dbf-2bba-497e-bb46-cf5ae34c8309}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5281,10 +5406,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I9 I20:I23 I26:I1048576 I11:I18</xm:sqref>
+          <xm:sqref>I1:I9 I20:I24 I26 I28:I1048576 I11:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8aea5306-ef65-4627-8a66-58534deca117}">
+          <x14:cfRule type="dataBar" id="{47aaa231-4aaf-4fd8-bdd3-2ae040de8f51}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5292,10 +5417,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I24 I26:I1048576</xm:sqref>
+          <xm:sqref>I1:I9 I20:I23 I26 I28:I1048576 I11:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fb5b2f57-9451-49d9-b9a7-8d95f3248618}">
+          <x14:cfRule type="dataBar" id="{b838d886-995e-4ce0-817f-9f82e986b46d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5303,10 +5428,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I18 I20:I24 I26:I1048576</xm:sqref>
+          <xm:sqref>I1:I24 I26 I28:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a7f0002a-c702-415b-8169-4efa03b19759}">
+          <x14:cfRule type="dataBar" id="{86dcc80c-759d-4a5a-acd3-643f9ca3fceb}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5314,10 +5439,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2 I30 I51:I1048576</xm:sqref>
+          <xm:sqref>I1:I18 I20:I24 I26 I28:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ec983c11-db64-44bb-b541-b023879829a4}">
+          <x14:cfRule type="dataBar" id="{f23da25e-49e7-4674-b7d1-52a3df7f4321}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5325,10 +5450,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I5 I26:I37 I9 I7 I39:I1048576 I11:I18 I20:I23</xm:sqref>
+          <xm:sqref>I2 I52:I1048576 I31</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6f26c968-cebe-41cf-9944-480d0cdba0e5}">
+          <x14:cfRule type="dataBar" id="{3eac9ceb-21d2-4efc-920e-08e287498c57}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5336,10 +5461,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I5 I9 I26:I37 I11:I16 I39:I1048576 I7 I18 I20:I23</xm:sqref>
+          <xm:sqref>I2:I5 I26 I11:I18 I9 I7 I40:I1048576 I20:I23 I28:I38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7f0f6380-d4a2-4554-ac5a-7561718da915}">
+          <x14:cfRule type="dataBar" id="{6646db04-ae3d-46e5-bbff-2d8592bdc898}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5347,10 +5472,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I42:I47 I3:I5 I7 I39:I40 I9 I31:I33 I28 I18 I12:I14 I26 I20:I23 I49:I50 I36:I37</xm:sqref>
+          <xm:sqref>I2:I5 I9 I26 I7 I11:I16 I40:I1048576 I20:I23 I18 I28:I38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{66bf1551-707f-44d6-8349-d1a8b8d45347}">
+          <x14:cfRule type="dataBar" id="{3d9ec24e-a1da-440a-bfaa-cbf724d2cdac}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5358,10 +5483,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I42:I47 I3:I5 I7 I39:I40 I9 I31:I33 I28 I18 I12:I14 I20:I23 I49:I50 I36:I37</xm:sqref>
+          <xm:sqref>I12:I14 I3:I5 I7 I18 I9 I20:I23 I26 I37:I38 I29 I32:I34 I40:I41 I43:I48 I50:I51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{35c887f0-183e-4c36-86fa-750de5b9b432}">
+          <x14:cfRule type="dataBar" id="{213a9139-65c9-4b34-a9e0-585d2d02d42e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5369,10 +5494,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I39:I40 I3:I5 I7 I36:I37 I9 I31:I33 I28 I18 I12:I14 I16 I26 I20:I23 I42:I47 I49:I50</xm:sqref>
+          <xm:sqref>I18 I3:I5 I7 I12:I14 I9 I20:I23 I37:I38 I29 I32:I34 I40:I41 I43:I48 I50:I51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{efe36e69-62a3-49c6-89aa-66ac6042bffd}">
+          <x14:cfRule type="dataBar" id="{ab67dc00-3d99-4bc8-8c0f-a963b304cff5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5380,10 +5505,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I36:I37 I3:I5 I7 I31:I34 I9 I42:I50 I26 I18 I28:I29 I11:I14 I16 I20:I23 I39:I40</xm:sqref>
+          <xm:sqref>I16 I3:I5 I7 I12:I14 I9 I20:I23 I26 I18 I50:I51 I29 I32:I34 I37:I38 I40:I41 I43:I48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{949e63e7-0ac7-49fd-83ca-769992c8a405}">
+          <x14:cfRule type="dataBar" id="{f2ad4f43-4518-41c6-8a22-0234dd053784}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5391,10 +5516,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I39:I40 I3:I5 I7 I36:I37 I9 I31:I33 I26 I18 I11:I14 I16 I20:I23 I28:I29 I42:I47 I49:I50</xm:sqref>
+          <xm:sqref>I11:I14 I3:I5 I7 I20:I23 I9 I16 I26 I18 I40:I41 I29:I30 I43:I51 I32:I35 I37:I38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2734b6f8-fa33-42fb-ae76-07e65bd29087}">
+          <x14:cfRule type="dataBar" id="{fcc7d6c5-9727-4ec5-bfc8-cb96708af8cc}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5402,10 +5527,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I39:I50 I3:I5 I7 I31:I37 I9 I11:I16 I20:I23 I18 I26:I29</xm:sqref>
+          <xm:sqref>I20:I23 I3:I5 I7 I16 I9 I11:I14 I26 I18 I50:I51 I32:I34 I37:I38 I40:I41 I43:I48 I29:I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2d27626d-e539-4df3-aa87-7da12d7d1936}">
+          <x14:cfRule type="dataBar" id="{2e9e720d-2fc5-47e8-986e-7a35ff4cafdc}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5413,10 +5538,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I39:I50 I3:I5 I7 I31:I37 I9 I28:I29 I26 I18 I20:I23 I11:I16</xm:sqref>
+          <xm:sqref>I18 I20:I23 I3:I5 I7 I26 I9 I11:I16 I28:I30 I32:I38 I40:I51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bfcb78ce-6c53-47c0-b93a-0007575ce03b}">
+          <x14:cfRule type="dataBar" id="{d8123ca4-e3e4-41ac-9faf-b882f660c764}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5424,10 +5549,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I31:I37 I3:I5 I7 I39:I50 I9 I26:I29 I20:I23 I11:I18</xm:sqref>
+          <xm:sqref>I11:I16 I3:I5 I7 I20:I23 I9 I18 I26 I40:I51 I29:I30 I32:I38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{59449685-1156-4c2f-99ed-6bf406b56117}">
+          <x14:cfRule type="dataBar" id="{57788638-193d-4e69-be69-87ed19204da0}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5435,10 +5560,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I18 I3:I7 I26:I29 I31:I50 I9 I20:I23</xm:sqref>
+          <xm:sqref>I11:I18 I3:I5 I7 I20:I23 I9 I26 I32:I38 I28:I30 I40:I51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{80e88f1d-7691-46ce-8bde-4fe95a1daa20}">
+          <x14:cfRule type="dataBar" id="{2bc491ac-0919-4df1-b05b-c2556d76ce29}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5446,10 +5571,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I26:I29 I3:I7 I39:I50 I31:I37 I9 I11:I18 I20:I23</xm:sqref>
+          <xm:sqref>I11:I18 I3:I7 I26 I20:I23 I9 I28:I30 I32:I51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{65951809-2866-4b2a-bf50-7c9f0209d743}">
+          <x14:cfRule type="dataBar" id="{750e69f7-5f96-4d4c-aa99-1d48c2b8295a}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5457,7 +5582,18 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I26:I29 I3:I24 I31:I50</xm:sqref>
+          <xm:sqref>I26 I20:I23 I3:I7 I11:I18 I9 I28:I30 I32:I38 I40:I51</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{39a9d97c-1701-4008-b243-abcc23b82f6b}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I26 I3:I24 I32:I51 I28:I30</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -5469,11 +5605,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
-    <col min="2" max="2" width="8.12727272727273" customWidth="1"/>
-    <col min="3" max="3" width="8.87272727272727" customWidth="1"/>
+    <col min="2" max="2" width="8.125" customWidth="1"/>
+    <col min="3" max="3" width="8.875" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="117">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -81,13 +81,19 @@
     <t>BYyihan</t>
   </si>
   <si>
+    <t>KIRINIT</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>Mtve</t>
+  </si>
+  <si>
     <t>qmzp_</t>
   </si>
   <si>
-    <t>Mtve</t>
-  </si>
-  <si>
-    <t>KIRINIT</t>
+    <t>↓1</t>
   </si>
   <si>
     <t>zkiftie</t>
@@ -205,9 +211,6 @@
   </si>
   <si>
     <t>Goocheu_fox</t>
-  </si>
-  <si>
-    <t>↓1</t>
   </si>
   <si>
     <t>Cr_Dragon</t>
@@ -1222,7 +1225,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1337,6 +1340,9 @@
     <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1345,6 +1351,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1682,7 +1694,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K159"/>
+  <dimension ref="A1:K161"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -1813,21 +1825,24 @@
       <c r="G5" s="15">
         <v>3</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="16">
-        <f>SUM(C28:C28,C32:C32,C34:C34,C37,C39,C42:C42,C54,C57,C59,C61,C67,C69,C71,C76)</f>
-        <v>285.96</v>
+      <c r="I5" s="2">
+        <f>SUM(C110:C110,C113,C116,C118,C129,C134,C142,C151,C153,C158)</f>
+        <v>500</v>
       </c>
       <c r="J5" s="3">
-        <v>45654</v>
+        <v>46205</v>
+      </c>
+      <c r="K5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="12"/>
       <c r="B6" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="13">
         <v>3</v>
@@ -1837,21 +1852,24 @@
       <c r="G6" s="15">
         <v>4</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="2">
-        <f>SUM(C110:C110,C113,C116,C118,C129,C134,C142,C151,C153)</f>
-        <v>260</v>
+      <c r="H6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="16">
+        <f>SUM(C28:C28,C32:C32,C34:C34,C37,C39,C42:C42,C54,C57,C59,C61,C67,C69,C71,C76)</f>
+        <v>285.96</v>
       </c>
       <c r="J6" s="3">
-        <v>46193</v>
+        <v>45654</v>
+      </c>
+      <c r="K6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="12"/>
       <c r="B7" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="13">
         <v>1.28</v>
@@ -1862,7 +1880,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I7" s="16">
         <f>SUM(C11,C16,C29,C25,C62,C81:C81)</f>
@@ -1877,7 +1895,7 @@
         <v>44164</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="13">
         <v>9</v>
@@ -1891,7 +1909,7 @@
         <v>6</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I8" s="2">
         <f>SUM(C121,C123,C126,C128,C131)</f>
@@ -1906,7 +1924,7 @@
         <v>44213</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="13">
         <v>0.1</v>
@@ -1920,7 +1938,7 @@
         <v>7</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I9" s="16">
         <f>SUM(C52,C65)</f>
@@ -1949,7 +1967,7 @@
         <v>8</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I10" s="2">
         <f>SUM(C133,C143,C147,C155)</f>
@@ -1964,7 +1982,7 @@
         <v>44781</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C11" s="13">
         <v>130</v>
@@ -1974,13 +1992,13 @@
         <v>193.93</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G11" s="15">
         <v>9</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I11" s="2">
         <f>SUM(C86,C101,C105,C107,C112,C119,C124)</f>
@@ -2003,13 +2021,13 @@
         <v>-5.06999999999999</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G12" s="15">
         <v>10</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I12" s="16">
         <f>SUM(C8:C8,C47,C45,C50:C50)</f>
@@ -2024,7 +2042,7 @@
         <v>44787</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C13" s="13">
         <v>5.02</v>
@@ -2061,13 +2079,13 @@
         <v>-780.05</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G14" s="15">
         <v>12</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I14" s="16">
         <f>SUM(C56,C46,C74)</f>
@@ -2092,13 +2110,13 @@
         <v>-660.05</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G15" s="15">
         <v>13</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I15" s="2">
         <f>SUM(C99,C109,C130,C137,C144)</f>
@@ -2113,7 +2131,7 @@
         <v>44946</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16" s="13">
         <v>13</v>
@@ -2127,7 +2145,7 @@
         <v>14</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I16" s="2">
         <f>SUM(C85:C85,C89,C96:C98,C117,C120,C122)</f>
@@ -2142,7 +2160,7 @@
         <v>44953</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C17" s="13">
         <v>10</v>
@@ -2152,13 +2170,13 @@
         <v>-637.05</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G17" s="15">
         <v>15</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I17" s="2">
         <v>15</v>
@@ -2183,13 +2201,13 @@
         <v>-550.73</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G18" s="15">
         <v>16</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I18" s="16">
         <f>SUM(C40,C64)</f>
@@ -2202,7 +2220,7 @@
     <row r="19" spans="1:11">
       <c r="A19" s="17"/>
       <c r="B19" s="22" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C19" s="13">
         <v>1.32</v>
@@ -2213,7 +2231,7 @@
         <v>17</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I19" s="2">
         <f>SUM(C135,C139,C146)</f>
@@ -2242,7 +2260,7 @@
         <v>18</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I20" s="16">
         <v>10</v>
@@ -2267,13 +2285,13 @@
         <v>-428.73</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G21" s="15">
         <v>19</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I21" s="16">
         <v>10</v>
@@ -2287,7 +2305,7 @@
         <v>45140</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C22" s="13">
         <v>0.11</v>
@@ -2301,7 +2319,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I22" s="16">
         <v>10</v>
@@ -2315,7 +2333,7 @@
         <v>45141</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C23" s="13">
         <v>1.01</v>
@@ -2329,7 +2347,7 @@
         <v>21</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I23" s="16">
         <v>10</v>
@@ -2348,13 +2366,13 @@
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G24" s="15">
         <v>22</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I24" s="2">
         <v>10</v>
@@ -2368,7 +2386,7 @@
         <v>45160</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C25" s="13">
         <v>3</v>
@@ -2382,7 +2400,7 @@
         <v>23</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I25" s="16">
         <v>10</v>
@@ -2396,7 +2414,7 @@
         <v>45234</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C26" s="13">
         <v>10</v>
@@ -2406,13 +2424,13 @@
         <v>-415.61</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G26">
         <v>24</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I26" s="2">
         <v>8</v>
@@ -2429,13 +2447,13 @@
       </c>
       <c r="D27" s="23"/>
       <c r="E27" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G27">
         <v>25</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I27" s="2">
         <v>8</v>
@@ -2444,7 +2462,7 @@
         <v>46205</v>
       </c>
       <c r="K27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2452,7 +2470,7 @@
         <v>45249</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C28" s="13">
         <v>15.5</v>
@@ -2462,13 +2480,13 @@
         <v>-400.11</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G28">
         <v>26</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I28" s="2">
         <v>7.33</v>
@@ -2477,7 +2495,7 @@
         <v>45907</v>
       </c>
       <c r="K28" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2485,7 +2503,7 @@
         <v>45305</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C29" s="13">
         <v>50</v>
@@ -2499,7 +2517,7 @@
         <v>27</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I29" s="16">
         <f>SUM(C82,C84,C94)</f>
@@ -2509,7 +2527,7 @@
         <v>45861</v>
       </c>
       <c r="K29" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2517,7 +2535,7 @@
         <v>45325</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C30" s="13">
         <v>10</v>
@@ -2527,13 +2545,13 @@
         <v>-340.11</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G30">
         <v>28</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I30" s="2">
         <v>6</v>
@@ -2542,7 +2560,7 @@
         <v>45868</v>
       </c>
       <c r="K30" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2560,13 +2578,13 @@
         <v>-272.11</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G31">
         <v>29</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I31" s="2">
         <v>5.04</v>
@@ -2575,7 +2593,7 @@
         <v>46160</v>
       </c>
       <c r="K31" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2583,7 +2601,7 @@
         <v>45368</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C32" s="13">
         <v>33.01</v>
@@ -2593,13 +2611,13 @@
         <v>-239.1</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G32">
         <v>30</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I32" s="16">
         <v>5.02</v>
@@ -2608,7 +2626,7 @@
         <v>44787</v>
       </c>
       <c r="K32" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2616,7 +2634,7 @@
         <v>45387</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C33" s="13">
         <v>1.38</v>
@@ -2626,13 +2644,13 @@
         <v>-237.72</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G33">
         <v>31</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I33" s="16">
         <v>5</v>
@@ -2641,7 +2659,7 @@
         <v>45634</v>
       </c>
       <c r="K33" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2649,7 +2667,7 @@
         <v>45394</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C34" s="13">
         <v>16</v>
@@ -2659,13 +2677,13 @@
         <v>-221.72</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G34">
         <v>32</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I34" s="16">
         <v>4.15</v>
@@ -2674,7 +2692,7 @@
         <v>45707</v>
       </c>
       <c r="K34" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2682,7 +2700,7 @@
         <v>45396</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C35" s="13">
         <v>0.8</v>
@@ -2692,13 +2710,13 @@
         <v>-220.92</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G35">
         <v>33</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I35" s="2">
         <v>4</v>
@@ -2707,7 +2725,7 @@
         <v>45885</v>
       </c>
       <c r="K35" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2729,7 +2747,7 @@
         <v>34</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I36" s="2">
         <f>SUM(C100,C108)</f>
@@ -2739,7 +2757,7 @@
         <v>45934</v>
       </c>
       <c r="K36" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2747,7 +2765,7 @@
         <v>45403</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C37" s="13">
         <v>5</v>
@@ -2757,13 +2775,13 @@
         <v>-212.72</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G37">
         <v>35</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I37" s="16">
         <v>3</v>
@@ -2772,7 +2790,7 @@
         <v>11</v>
       </c>
       <c r="K37" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2790,13 +2808,13 @@
         <v>-205.72</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G38" s="15">
         <v>36</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I38" s="16">
         <v>3</v>
@@ -2805,7 +2823,7 @@
         <v>45500</v>
       </c>
       <c r="K38" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2813,7 +2831,7 @@
         <v>45417</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C39" s="13">
         <v>11</v>
@@ -2823,13 +2841,13 @@
         <v>-194.72</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G39" s="15">
         <v>37</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I39" s="2">
         <v>2.5</v>
@@ -2838,7 +2856,7 @@
         <v>45976</v>
       </c>
       <c r="K39" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2846,7 +2864,7 @@
         <v>45421</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C40" s="13">
         <v>5</v>
@@ -2856,13 +2874,13 @@
         <v>-189.72</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G40" s="15">
         <v>38</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I40" s="16">
         <f>SUM(C35,C33:C33)</f>
@@ -2872,7 +2890,7 @@
         <v>45396</v>
       </c>
       <c r="K40" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -2889,7 +2907,7 @@
         <v>-1999.72</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G41">
         <v>39</v>
@@ -2904,7 +2922,7 @@
         <v>11</v>
       </c>
       <c r="K41" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2912,7 +2930,7 @@
         <v>45494</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C42" s="13">
         <v>82.45</v>
@@ -2922,13 +2940,13 @@
         <v>-1915.27</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G42" s="15">
         <v>40</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I42" s="2">
         <v>2</v>
@@ -2937,7 +2955,7 @@
         <v>45907</v>
       </c>
       <c r="K42" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2950,13 +2968,13 @@
       </c>
       <c r="D43" s="23"/>
       <c r="E43" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G43">
         <v>41</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I43" s="16">
         <v>1.32</v>
@@ -2965,7 +2983,7 @@
         <v>44958</v>
       </c>
       <c r="K43" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -2983,13 +3001,13 @@
         <v>-1907.27</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G44">
         <v>42</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I44" s="16">
         <v>1.28</v>
@@ -2998,7 +3016,7 @@
         <v>11</v>
       </c>
       <c r="K44" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -3006,7 +3024,7 @@
         <v>45496</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C45" s="27">
         <v>5</v>
@@ -3020,7 +3038,7 @@
         <v>43</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I45" s="16">
         <v>1.01</v>
@@ -3029,26 +3047,26 @@
         <v>45141</v>
       </c>
       <c r="K45" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="29"/>
       <c r="B46" s="26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C46" s="27">
         <v>3</v>
       </c>
       <c r="D46" s="30"/>
       <c r="E46" s="28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G46">
         <v>44</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I46" s="16">
         <v>1</v>
@@ -3057,7 +3075,7 @@
         <v>45794</v>
       </c>
       <c r="K46" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -3065,7 +3083,7 @@
         <v>45497</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C47" s="27">
         <v>25</v>
@@ -3075,7 +3093,7 @@
         <v>-1874.27</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G47">
         <v>45</v>
@@ -3090,7 +3108,7 @@
         <v>11</v>
       </c>
       <c r="K47" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -3098,7 +3116,7 @@
         <v>45500</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C48" s="27">
         <v>3</v>
@@ -3112,7 +3130,7 @@
         <v>46</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I48" s="16">
         <v>0.5</v>
@@ -3121,7 +3139,7 @@
         <v>45697</v>
       </c>
       <c r="K48" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -3134,13 +3152,13 @@
       </c>
       <c r="D49" s="30"/>
       <c r="E49" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G49">
         <v>47</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I49" s="2">
         <v>0.5</v>
@@ -3149,7 +3167,7 @@
         <v>45885</v>
       </c>
       <c r="K49" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -3157,7 +3175,7 @@
         <v>45505</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C50" s="27">
         <v>10</v>
@@ -3167,13 +3185,13 @@
         <v>-1856.27</v>
       </c>
       <c r="E50" s="28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G50">
         <v>48</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I50" s="16">
         <v>0.11</v>
@@ -3182,7 +3200,7 @@
         <v>45140</v>
       </c>
       <c r="K50" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -3200,13 +3218,13 @@
         <v>-1756.27</v>
       </c>
       <c r="E51" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G51">
         <v>49</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I51" s="16">
         <v>0.1</v>
@@ -3215,20 +3233,20 @@
         <v>44213</v>
       </c>
       <c r="K51" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="31"/>
       <c r="B52" s="26" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C52" s="27">
         <v>86</v>
       </c>
       <c r="D52" s="30"/>
       <c r="E52" s="28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -3246,13 +3264,13 @@
         <v>-1737.27</v>
       </c>
       <c r="E53" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="31"/>
       <c r="B54" s="26" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C54" s="27">
         <v>10</v>
@@ -3273,13 +3291,13 @@
         <v>-1737.27</v>
       </c>
       <c r="E55" s="28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="31"/>
       <c r="B56" s="26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C56" s="27">
         <v>10</v>
@@ -3292,7 +3310,7 @@
         <v>45510</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C57" s="27">
         <v>40</v>
@@ -3302,7 +3320,7 @@
         <v>-1697.27</v>
       </c>
       <c r="E57" s="28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -3321,7 +3339,7 @@
         <v>-1625.27</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -3329,7 +3347,7 @@
         <v>45525</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C59" s="27">
         <v>6</v>
@@ -3339,7 +3357,7 @@
         <v>-1619.27</v>
       </c>
       <c r="E59" s="28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -3357,20 +3375,20 @@
         <v>-1569.27</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="29"/>
       <c r="B61" s="33" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C61" s="27">
         <v>20</v>
       </c>
       <c r="D61" s="30"/>
       <c r="E61" s="28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -3378,7 +3396,7 @@
         <v>45551</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C62" s="27">
         <v>17</v>
@@ -3410,7 +3428,7 @@
         <v>45555</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C64" s="27">
         <v>6</v>
@@ -3424,14 +3442,14 @@
     <row r="65" spans="1:5">
       <c r="A65" s="31"/>
       <c r="B65" s="33" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C65" s="27">
         <v>20</v>
       </c>
       <c r="D65" s="30"/>
       <c r="E65" s="28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3449,7 +3467,7 @@
         <v>-1456.27</v>
       </c>
       <c r="E66" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3457,7 +3475,7 @@
         <v>45584</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C67" s="27">
         <v>7</v>
@@ -3483,7 +3501,7 @@
         <v>-1389.27</v>
       </c>
       <c r="E68" s="28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3491,7 +3509,7 @@
         <v>45597</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C69" s="27">
         <v>5</v>
@@ -3501,7 +3519,7 @@
         <v>-1384.27</v>
       </c>
       <c r="E69" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3519,7 +3537,7 @@
         <v>-1379.27</v>
       </c>
       <c r="E70" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3527,7 +3545,7 @@
         <v>45612</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C71" s="27">
         <v>5</v>
@@ -3553,7 +3571,7 @@
         <v>-1359.27</v>
       </c>
       <c r="E72" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -3561,7 +3579,7 @@
         <v>45634</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C73" s="27">
         <v>5</v>
@@ -3571,20 +3589,20 @@
         <v>-1344.27</v>
       </c>
       <c r="E73" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="17"/>
       <c r="B74" s="33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C74" s="27">
         <v>10</v>
       </c>
       <c r="D74" s="30"/>
       <c r="E74" s="28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3592,7 +3610,7 @@
         <v>45649</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C75" s="27">
         <v>10</v>
@@ -3608,7 +3626,7 @@
         <v>45654</v>
       </c>
       <c r="B76" s="33" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C76" s="27">
         <v>30</v>
@@ -3618,7 +3636,7 @@
         <v>-1304.27</v>
       </c>
       <c r="E76" s="28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3636,7 +3654,7 @@
         <v>-1295.27</v>
       </c>
       <c r="E77" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3644,7 +3662,7 @@
         <v>45697</v>
       </c>
       <c r="B78" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C78" s="27">
         <v>0.5</v>
@@ -3660,7 +3678,7 @@
         <v>45707</v>
       </c>
       <c r="B79" s="33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C79" s="27">
         <v>4.15</v>
@@ -3676,7 +3694,7 @@
         <v>45794</v>
       </c>
       <c r="B80" s="33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C80" s="27">
         <v>1</v>
@@ -3692,7 +3710,7 @@
         <v>45829</v>
       </c>
       <c r="B81" s="33" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C81" s="27">
         <v>26.66</v>
@@ -3708,7 +3726,7 @@
         <v>45844</v>
       </c>
       <c r="B82" s="33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C82" s="27">
         <v>2.48</v>
@@ -3724,7 +3742,7 @@
         <v>45860</v>
       </c>
       <c r="B83" s="33" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C83" s="27">
         <v>8</v>
@@ -3740,7 +3758,7 @@
         <v>45861</v>
       </c>
       <c r="B84" s="33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C84" s="27">
         <v>0.5</v>
@@ -3756,7 +3774,7 @@
         <v>45865</v>
       </c>
       <c r="B85" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C85" s="27">
         <v>3</v>
@@ -3772,7 +3790,7 @@
         <v>45868</v>
       </c>
       <c r="B86" s="33" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C86" s="27">
         <v>5.01</v>
@@ -3788,7 +3806,7 @@
         <v>45868</v>
       </c>
       <c r="B87" s="33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C87" s="27">
         <v>6</v>
@@ -3798,7 +3816,7 @@
         <v>-1237.97</v>
       </c>
       <c r="E87" s="28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -3816,7 +3834,7 @@
         <v>-1232.97</v>
       </c>
       <c r="E88" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -3824,7 +3842,7 @@
         <v>45878</v>
       </c>
       <c r="B89" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C89" s="27">
         <v>0.01</v>
@@ -3850,7 +3868,7 @@
         <v>-1206.96</v>
       </c>
       <c r="E90" s="34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -3868,7 +3886,7 @@
         <v>-1201.96</v>
       </c>
       <c r="E91" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -3876,7 +3894,7 @@
         <v>45885</v>
       </c>
       <c r="B92" s="33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C92" s="27">
         <v>0.5</v>
@@ -3890,7 +3908,7 @@
     <row r="93" spans="1:5">
       <c r="A93" s="17"/>
       <c r="B93" s="33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C93" s="27">
         <v>6</v>
@@ -3901,7 +3919,7 @@
     <row r="94" spans="1:5">
       <c r="A94" s="17"/>
       <c r="B94" s="33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C94" s="27">
         <v>4</v>
@@ -3924,7 +3942,7 @@
         <v>-1186.46</v>
       </c>
       <c r="E95" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -3932,7 +3950,7 @@
         <v>45894</v>
       </c>
       <c r="B96" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C96" s="27">
         <v>1</v>
@@ -3948,7 +3966,7 @@
         <v>45905</v>
       </c>
       <c r="B97" s="33" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C97" s="27">
         <v>7.33</v>
@@ -3964,7 +3982,7 @@
         <v>45907</v>
       </c>
       <c r="B98" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C98" s="27">
         <v>2</v>
@@ -3978,7 +3996,7 @@
     <row r="99" spans="1:5">
       <c r="A99" s="31"/>
       <c r="B99" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C99" s="27">
         <v>2</v>
@@ -3989,7 +4007,7 @@
     <row r="100" spans="1:5">
       <c r="A100" s="31"/>
       <c r="B100" s="33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C100" s="27">
         <v>2</v>
@@ -4000,7 +4018,7 @@
     <row r="101" spans="1:5">
       <c r="A101" s="31"/>
       <c r="B101" s="33" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C101" s="27">
         <v>2</v>
@@ -4011,7 +4029,7 @@
     <row r="102" spans="1:5">
       <c r="A102" s="31"/>
       <c r="B102" s="33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C102" s="27">
         <v>2</v>
@@ -4032,7 +4050,7 @@
         <v>-1298.13</v>
       </c>
       <c r="E103" s="34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -4050,7 +4068,7 @@
         <v>-1292.13</v>
       </c>
       <c r="E104" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -4058,7 +4076,7 @@
         <v>45925</v>
       </c>
       <c r="B105" s="33" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C105" s="27">
         <v>10</v>
@@ -4074,7 +4092,7 @@
         <v>45930</v>
       </c>
       <c r="B106" s="33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C106" s="27">
         <v>15</v>
@@ -4090,7 +4108,7 @@
         <v>45934</v>
       </c>
       <c r="B107" s="33" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C107" s="27">
         <v>2</v>
@@ -4104,7 +4122,7 @@
     <row r="108" spans="1:5">
       <c r="A108" s="31"/>
       <c r="B108" s="33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C108" s="27">
         <v>2</v>
@@ -4118,7 +4136,7 @@
     <row r="109" spans="1:5">
       <c r="A109" s="31"/>
       <c r="B109" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C109" s="27">
         <v>0.45</v>
@@ -4134,7 +4152,7 @@
         <v>45965</v>
       </c>
       <c r="B110" s="33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C110" s="27">
         <v>60</v>
@@ -4144,7 +4162,7 @@
         <v>-1202.68</v>
       </c>
       <c r="E110" s="34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -4168,7 +4186,7 @@
         <v>45969</v>
       </c>
       <c r="B112" s="33" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C112" s="27">
         <v>6</v>
@@ -4184,7 +4202,7 @@
         <v>45972</v>
       </c>
       <c r="B113" s="33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C113" s="27">
         <v>60</v>
@@ -4194,7 +4212,7 @@
         <v>-1131.68</v>
       </c>
       <c r="E113" s="34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -4212,7 +4230,7 @@
         <v>-1094.68</v>
       </c>
       <c r="E114" s="34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -4220,7 +4238,7 @@
         <v>45976</v>
       </c>
       <c r="B115" s="33" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C115" s="27">
         <v>2.5</v>
@@ -4236,7 +4254,7 @@
         <v>45980</v>
       </c>
       <c r="B116" s="33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C116" s="27">
         <v>20</v>
@@ -4246,7 +4264,7 @@
         <v>-1072.18</v>
       </c>
       <c r="E116" s="34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -4254,7 +4272,7 @@
         <v>45990</v>
       </c>
       <c r="B117" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C117" s="27">
         <v>1</v>
@@ -4264,7 +4282,7 @@
         <v>-1071.18</v>
       </c>
       <c r="E117" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -4272,7 +4290,7 @@
         <v>46012</v>
       </c>
       <c r="B118" s="33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C118" s="27">
         <v>10</v>
@@ -4288,7 +4306,7 @@
         <v>46029</v>
       </c>
       <c r="B119" s="33" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C119" s="27">
         <v>16</v>
@@ -4298,7 +4316,7 @@
         <v>-1045.18</v>
       </c>
       <c r="E119" s="34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -4306,7 +4324,7 @@
         <v>46031</v>
       </c>
       <c r="B120" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C120" s="27">
         <v>2</v>
@@ -4322,7 +4340,7 @@
         <v>46038</v>
       </c>
       <c r="B121" s="33" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C121" s="27">
         <v>66</v>
@@ -4332,7 +4350,7 @@
         <v>-977.18</v>
       </c>
       <c r="E121" s="34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -4340,7 +4358,7 @@
         <v>46039</v>
       </c>
       <c r="B122" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C122" s="27">
         <v>1</v>
@@ -4356,7 +4374,7 @@
         <v>46047</v>
       </c>
       <c r="B123" s="33" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C123" s="27">
         <v>7</v>
@@ -4366,13 +4384,13 @@
         <v>-969.18</v>
       </c>
       <c r="E123" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="31"/>
       <c r="B124" s="33" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C124" s="27">
         <v>11</v>
@@ -4398,7 +4416,7 @@
         <v>-953.18</v>
       </c>
       <c r="E125" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -4406,7 +4424,7 @@
         <v>46055</v>
       </c>
       <c r="B126" s="33" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C126" s="27">
         <v>36</v>
@@ -4416,7 +4434,7 @@
         <v>-917.18</v>
       </c>
       <c r="E126" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -4434,7 +4452,7 @@
         <v>-912.18</v>
       </c>
       <c r="E127" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -4442,7 +4460,7 @@
         <v>46068</v>
       </c>
       <c r="B128" s="33" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C128" s="27">
         <v>78</v>
@@ -4452,13 +4470,13 @@
         <v>-834.18</v>
       </c>
       <c r="E128" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="36"/>
       <c r="B129" s="33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C129" s="27">
         <v>30</v>
@@ -4468,7 +4486,7 @@
         <v>-804.18</v>
       </c>
       <c r="E129" s="34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -4476,7 +4494,7 @@
         <v>46069</v>
       </c>
       <c r="B130" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C130" s="27">
         <v>5</v>
@@ -4490,7 +4508,7 @@
     <row r="131" spans="1:5">
       <c r="A131" s="31"/>
       <c r="B131" s="33" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C131" s="27">
         <v>8</v>
@@ -4500,13 +4518,13 @@
         <v>-791.18</v>
       </c>
       <c r="E131" s="34" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="31"/>
       <c r="B132" s="33" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C132" s="27">
         <v>10</v>
@@ -4522,7 +4540,7 @@
         <v>46070</v>
       </c>
       <c r="B133" s="33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C133" s="27">
         <v>8.32</v>
@@ -4536,7 +4554,7 @@
     <row r="134" spans="1:5">
       <c r="A134" s="31"/>
       <c r="B134" s="33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C134" s="27">
         <v>10</v>
@@ -4552,7 +4570,7 @@
         <v>46074</v>
       </c>
       <c r="B135" s="33" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C135" s="27">
         <v>1.5</v>
@@ -4578,7 +4596,7 @@
         <v>-736.36</v>
       </c>
       <c r="E136" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -4586,7 +4604,7 @@
         <v>46085</v>
       </c>
       <c r="B137" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C137" s="27">
         <v>10</v>
@@ -4612,7 +4630,7 @@
         <v>-656.36</v>
       </c>
       <c r="E138" s="34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -4620,7 +4638,7 @@
         <v>46130</v>
       </c>
       <c r="B139" s="33" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C139" s="27">
         <v>3</v>
@@ -4644,7 +4662,7 @@
         <v>-3151.15</v>
       </c>
       <c r="E140" s="34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -4662,7 +4680,7 @@
         <v>-3136.15</v>
       </c>
       <c r="E141" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -4670,7 +4688,7 @@
         <v>46141</v>
       </c>
       <c r="B142" s="33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C142" s="27">
         <v>10</v>
@@ -4684,7 +4702,7 @@
     <row r="143" spans="1:5">
       <c r="A143" s="31"/>
       <c r="B143" s="33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C143" s="27">
         <v>10</v>
@@ -4700,7 +4718,7 @@
         <v>46144</v>
       </c>
       <c r="B144" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C144" s="27">
         <v>1</v>
@@ -4716,7 +4734,7 @@
         <v>46145</v>
       </c>
       <c r="B145" s="33" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C145" s="27">
         <v>10</v>
@@ -4726,13 +4744,13 @@
         <v>-3105.15</v>
       </c>
       <c r="E145" s="34" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="31"/>
       <c r="B146" s="33" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C146" s="27">
         <v>6</v>
@@ -4748,7 +4766,7 @@
         <v>46146</v>
       </c>
       <c r="B147" s="33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C147" s="27">
         <v>20</v>
@@ -4774,7 +4792,7 @@
         <v>-3059.15</v>
       </c>
       <c r="E148" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -4782,7 +4800,7 @@
         <v>46160</v>
       </c>
       <c r="B149" s="33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C149" s="27">
         <v>5.04</v>
@@ -4808,7 +4826,7 @@
         <v>-3024.11</v>
       </c>
       <c r="E150" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -4816,7 +4834,7 @@
         <v>46184</v>
       </c>
       <c r="B151" s="33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C151" s="27">
         <v>10</v>
@@ -4842,7 +4860,7 @@
         <v>-2994.11</v>
       </c>
       <c r="E152" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -4850,7 +4868,7 @@
         <v>46193</v>
       </c>
       <c r="B153" s="33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C153" s="27">
         <v>50</v>
@@ -4874,7 +4892,7 @@
         <v>-2934.11</v>
       </c>
       <c r="E154" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -4882,7 +4900,7 @@
         <v>46196</v>
       </c>
       <c r="B155" s="33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C155" s="27">
         <v>25</v>
@@ -4892,7 +4910,7 @@
         <v>-2909.11</v>
       </c>
       <c r="E155" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -4910,48 +4928,69 @@
         <v>-2889.11</v>
       </c>
       <c r="E156" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="37">
         <v>46205</v>
       </c>
-      <c r="B157" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="C157" s="39">
+      <c r="B157" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C157" s="27">
         <v>8</v>
       </c>
       <c r="D157" s="21">
         <f>SUM(C3:C157)</f>
         <v>-2881.11</v>
       </c>
-      <c r="E157" s="40" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="158" ht="14.25" spans="1:5">
-      <c r="A158" s="41"/>
-      <c r="B158" s="42"/>
-      <c r="C158" s="43"/>
-      <c r="D158" s="43"/>
-      <c r="E158" s="44"/>
+      <c r="E157" s="34" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="38"/>
+      <c r="B158" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C158" s="40">
+        <v>240</v>
+      </c>
+      <c r="D158" s="21">
+        <f>SUM(C3:C158)</f>
+        <v>-2641.11</v>
+      </c>
+      <c r="E158" s="41"/>
     </row>
     <row r="159" spans="1:5">
-      <c r="A159" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="B159" s="45"/>
-      <c r="C159" s="45"/>
-      <c r="D159" s="45"/>
-      <c r="E159" s="45"/>
+      <c r="A159" s="42"/>
+      <c r="B159" s="39"/>
+      <c r="C159" s="40"/>
+      <c r="D159" s="43"/>
+      <c r="E159" s="41"/>
+    </row>
+    <row r="160" ht="14.25" spans="1:5">
+      <c r="A160" s="44"/>
+      <c r="B160" s="45"/>
+      <c r="C160" s="46"/>
+      <c r="D160" s="46"/>
+      <c r="E160" s="47"/>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="B161" s="48"/>
+      <c r="C161" s="48"/>
+      <c r="D161" s="48"/>
+      <c r="E161" s="48"/>
     </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="42">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A159:E159"/>
+    <mergeCell ref="A161:E161"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A23:A24"/>
@@ -4975,6 +5014,7 @@
     <mergeCell ref="A142:A143"/>
     <mergeCell ref="A145:A146"/>
     <mergeCell ref="A153:A154"/>
+    <mergeCell ref="A157:A158"/>
     <mergeCell ref="D3:D7"/>
     <mergeCell ref="D18:D19"/>
     <mergeCell ref="D23:D24"/>
@@ -5000,7 +5040,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aff9f52c-85a9-499b-ae27-3ebe825d11aa}</x14:id>
+          <x14:id>{191398e4-7383-4f9f-bf42-8a41e529687a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5014,12 +5054,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b036c6b4-b3b1-447e-9995-6217e4e4fef8}</x14:id>
+          <x14:id>{4048862c-1979-4697-960b-bc7e2f05316f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D158 D160:D1048576">
+  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D160 D162:D1048576">
     <cfRule type="colorScale" priority="81">
       <colorScale>
         <cfvo type="min"/>
@@ -5040,7 +5080,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{20fa9b1b-7838-4ea5-b137-a512bdd60548}</x14:id>
+          <x14:id>{2f9c3b63-fbdd-40ac-8a10-2bc6ca07880d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5054,12 +5094,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c3fe1633-2d15-4c57-b396-2ebba2782a46}</x14:id>
+          <x14:id>{1ab22eb6-ea8d-480b-b9e3-ae4305d6d1b7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I9 I20:I24 I26 I28:I1048576 I11:I18">
+  <conditionalFormatting sqref="I1:I9 I28:I1048576 I11:I18 I20:I24 I26">
     <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="min"/>
@@ -5068,12 +5108,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c2454dbf-2bba-497e-bb46-cf5ae34c8309}</x14:id>
+          <x14:id>{5b8deb84-b20f-4361-ae3c-71c211e8a335}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I9 I20:I23 I26 I28:I1048576 I11:I18">
+  <conditionalFormatting sqref="I1:I9 I28:I1048576 I11:I18 I20:I23 I26">
     <cfRule type="dataBar" priority="24">
       <dataBar>
         <cfvo type="min"/>
@@ -5082,7 +5122,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{47aaa231-4aaf-4fd8-bdd3-2ae040de8f51}</x14:id>
+          <x14:id>{c4a1018c-2230-41a2-94ef-bb1243319065}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5096,12 +5136,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b838d886-995e-4ce0-817f-9f82e986b46d}</x14:id>
+          <x14:id>{423bf82b-a1a3-4506-ad04-424a90f609d0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I18 I20:I24 I26 I28:I1048576">
+  <conditionalFormatting sqref="I1:I18 I26 I28:I1048576 I20:I24">
     <cfRule type="dataBar" priority="22">
       <dataBar>
         <cfvo type="min"/>
@@ -5110,7 +5150,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{86dcc80c-759d-4a5a-acd3-643f9ca3fceb}</x14:id>
+          <x14:id>{ad5707fa-bd6a-4700-8f00-0636840721de}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5124,12 +5164,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f23da25e-49e7-4674-b7d1-52a3df7f4321}</x14:id>
+          <x14:id>{19b03e17-2eec-4dd3-8919-83dd38f2ef20}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5 I26 I11:I18 I9 I7 I40:I1048576 I20:I23 I28:I38">
+  <conditionalFormatting sqref="I2:I4 I28:I38 I26 I11:I18 I9 I6:I7 I40:I1048576 I20:I23">
     <cfRule type="dataBar" priority="27">
       <dataBar>
         <cfvo type="min"/>
@@ -5138,12 +5178,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3eac9ceb-21d2-4efc-920e-08e287498c57}</x14:id>
+          <x14:id>{1e97c95b-eb46-459e-818d-0ad9bdc0da87}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5 I9 I26 I7 I11:I16 I40:I1048576 I20:I23 I18 I28:I38">
+  <conditionalFormatting sqref="I2:I4 I28:I38 I9 I26 I6:I7 I11:I16 I40:I1048576 I20:I23 I18">
     <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
@@ -5152,7 +5192,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6646db04-ae3d-46e5-bbff-2d8592bdc898}</x14:id>
+          <x14:id>{e6795abe-41ad-4669-9a58-ffa762e0a49c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5189,7 +5229,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I12:I14 I3:I5 I7 I18 I9 I20:I23 I26 I37:I38 I29 I32:I34 I40:I41 I43:I48 I50:I51">
+  <conditionalFormatting sqref="I12:I14 I3:I4 I50:I51 I6:I7 I18 I9 I20:I23 I26 I37:I38 I29 I32:I34 I40:I41 I43:I48">
     <cfRule type="dataBar" priority="37">
       <dataBar>
         <cfvo type="min"/>
@@ -5198,12 +5238,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3d9ec24e-a1da-440a-bfaa-cbf724d2cdac}</x14:id>
+          <x14:id>{cebb4688-f38f-4dd5-a5b2-34d89dfb24db}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I18 I3:I5 I7 I12:I14 I9 I20:I23 I37:I38 I29 I32:I34 I40:I41 I43:I48 I50:I51">
+  <conditionalFormatting sqref="I18 I3:I4 I50:I51 I6:I7 I12:I14 I9 I20:I23 I37:I38 I29 I32:I34 I40:I41 I43:I48">
     <cfRule type="dataBar" priority="38">
       <dataBar>
         <cfvo type="min"/>
@@ -5212,12 +5252,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{213a9139-65c9-4b34-a9e0-585d2d02d42e}</x14:id>
+          <x14:id>{fca5342d-b635-4402-95eb-b1c6c70e1602}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I16 I3:I5 I7 I12:I14 I9 I20:I23 I26 I18 I50:I51 I29 I32:I34 I37:I38 I40:I41 I43:I48">
+  <conditionalFormatting sqref="I16 I3:I4 I43:I48 I6:I7 I12:I14 I9 I20:I23 I26 I18 I50:I51 I29 I32:I34 I37:I38 I40:I41">
     <cfRule type="dataBar" priority="35">
       <dataBar>
         <cfvo type="min"/>
@@ -5226,12 +5266,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ab67dc00-3d99-4bc8-8c0f-a963b304cff5}</x14:id>
+          <x14:id>{005ac478-b54e-40b6-86e1-8cf36abd3db4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I14 I3:I5 I7 I20:I23 I9 I16 I26 I18 I40:I41 I29:I30 I43:I51 I32:I35 I37:I38">
+  <conditionalFormatting sqref="I11:I14 I3:I4 I37:I38 I6:I7 I20:I23 I9 I16 I26 I18 I40:I41 I29:I30 I43:I51 I32:I35">
     <cfRule type="dataBar" priority="33">
       <dataBar>
         <cfvo type="min"/>
@@ -5240,12 +5280,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f2ad4f43-4518-41c6-8a22-0234dd053784}</x14:id>
+          <x14:id>{9e0b4405-4d85-4a99-8e74-9b3fcf8c332f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I20:I23 I3:I5 I7 I16 I9 I11:I14 I26 I18 I50:I51 I32:I34 I37:I38 I40:I41 I43:I48 I29:I30">
+  <conditionalFormatting sqref="I20:I23 I3:I4 I29:I30 I6:I7 I16 I9 I11:I14 I26 I18 I50:I51 I32:I34 I37:I38 I40:I41 I43:I48">
     <cfRule type="dataBar" priority="34">
       <dataBar>
         <cfvo type="min"/>
@@ -5254,12 +5294,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fcc7d6c5-9727-4ec5-bfc8-cb96708af8cc}</x14:id>
+          <x14:id>{1b26c7ed-6040-423e-b843-1e1125a1e5af}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I18 I20:I23 I3:I5 I7 I26 I9 I11:I16 I28:I30 I32:I38 I40:I51">
+  <conditionalFormatting sqref="I18 I20:I23 I3:I4 I40:I51 I6:I7 I26 I9 I11:I16 I28:I30 I32:I38">
     <cfRule type="dataBar" priority="29">
       <dataBar>
         <cfvo type="min"/>
@@ -5268,12 +5308,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2e9e720d-2fc5-47e8-986e-7a35ff4cafdc}</x14:id>
+          <x14:id>{61ee1db0-d5bd-41a5-8f68-6ef6244386f1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I16 I3:I5 I7 I20:I23 I9 I18 I26 I40:I51 I29:I30 I32:I38">
+  <conditionalFormatting sqref="I11:I16 I3:I4 I32:I38 I6:I7 I20:I23 I9 I18 I26 I40:I51 I29:I30">
     <cfRule type="dataBar" priority="32">
       <dataBar>
         <cfvo type="min"/>
@@ -5282,12 +5322,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d8123ca4-e3e4-41ac-9faf-b882f660c764}</x14:id>
+          <x14:id>{7f835b2a-72a9-4953-9523-b8d4fee6978c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I18 I3:I5 I7 I20:I23 I9 I26 I32:I38 I28:I30 I40:I51">
+  <conditionalFormatting sqref="I11:I18 I3:I4 I40:I51 I6:I7 I20:I23 I9 I26 I32:I38 I28:I30">
     <cfRule type="dataBar" priority="28">
       <dataBar>
         <cfvo type="min"/>
@@ -5296,12 +5336,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{57788638-193d-4e69-be69-87ed19204da0}</x14:id>
+          <x14:id>{90708e7a-6782-40dc-af53-6f2f8e04c202}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I18 I3:I7 I26 I20:I23 I9 I28:I30 I32:I51">
+  <conditionalFormatting sqref="I11:I18 I3:I7 I28:I30 I32:I51 I26 I20:I23 I9">
     <cfRule type="dataBar" priority="25">
       <dataBar>
         <cfvo type="min"/>
@@ -5310,12 +5350,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2bc491ac-0919-4df1-b05b-c2556d76ce29}</x14:id>
+          <x14:id>{c8a0abfd-999b-41dc-8adb-4e1c276343eb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I26 I20:I23 I3:I7 I11:I18 I9 I28:I30 I32:I38 I40:I51">
+  <conditionalFormatting sqref="I26 I20:I23 I3:I7 I32:I38 I40:I51 I11:I18 I9 I28:I30">
     <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
@@ -5324,7 +5364,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{750e69f7-5f96-4d4c-aa99-1d48c2b8295a}</x14:id>
+          <x14:id>{ad6ddf03-3bf3-43e8-90b0-7ad8718bac5b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5338,7 +5378,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{39a9d97c-1701-4008-b243-abcc23b82f6b}</x14:id>
+          <x14:id>{9dc82c74-1d90-4b35-ba55-0c2d3503c2d3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5346,13 +5386,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
+    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{aff9f52c-85a9-499b-ae27-3ebe825d11aa}">
+          <x14:cfRule type="dataBar" id="{191398e4-7383-4f9f-bf42-8a41e529687a}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5363,7 +5403,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b036c6b4-b3b1-447e-9995-6217e4e4fef8}">
+          <x14:cfRule type="dataBar" id="{4048862c-1979-4697-960b-bc7e2f05316f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5374,7 +5414,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{20fa9b1b-7838-4ea5-b137-a512bdd60548}">
+          <x14:cfRule type="dataBar" id="{2f9c3b63-fbdd-40ac-8a10-2bc6ca07880d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5387,7 +5427,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c3fe1633-2d15-4c57-b396-2ebba2782a46}">
+          <x14:cfRule type="dataBar" id="{1ab22eb6-ea8d-480b-b9e3-ae4305d6d1b7}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5398,7 +5438,7 @@
           <xm:sqref>I1:I26 I28:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c2454dbf-2bba-497e-bb46-cf5ae34c8309}">
+          <x14:cfRule type="dataBar" id="{5b8deb84-b20f-4361-ae3c-71c211e8a335}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5406,10 +5446,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I9 I20:I24 I26 I28:I1048576 I11:I18</xm:sqref>
+          <xm:sqref>I1:I9 I28:I1048576 I11:I18 I20:I24 I26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{47aaa231-4aaf-4fd8-bdd3-2ae040de8f51}">
+          <x14:cfRule type="dataBar" id="{c4a1018c-2230-41a2-94ef-bb1243319065}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5417,10 +5457,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I9 I20:I23 I26 I28:I1048576 I11:I18</xm:sqref>
+          <xm:sqref>I1:I9 I28:I1048576 I11:I18 I20:I23 I26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b838d886-995e-4ce0-817f-9f82e986b46d}">
+          <x14:cfRule type="dataBar" id="{423bf82b-a1a3-4506-ad04-424a90f609d0}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5431,7 +5471,7 @@
           <xm:sqref>I1:I24 I26 I28:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{86dcc80c-759d-4a5a-acd3-643f9ca3fceb}">
+          <x14:cfRule type="dataBar" id="{ad5707fa-bd6a-4700-8f00-0636840721de}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5439,10 +5479,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I18 I20:I24 I26 I28:I1048576</xm:sqref>
+          <xm:sqref>I1:I18 I26 I28:I1048576 I20:I24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f23da25e-49e7-4674-b7d1-52a3df7f4321}">
+          <x14:cfRule type="dataBar" id="{19b03e17-2eec-4dd3-8919-83dd38f2ef20}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5453,7 +5493,7 @@
           <xm:sqref>I2 I52:I1048576 I31</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3eac9ceb-21d2-4efc-920e-08e287498c57}">
+          <x14:cfRule type="dataBar" id="{1e97c95b-eb46-459e-818d-0ad9bdc0da87}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5461,10 +5501,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I5 I26 I11:I18 I9 I7 I40:I1048576 I20:I23 I28:I38</xm:sqref>
+          <xm:sqref>I2:I4 I28:I38 I26 I11:I18 I9 I6:I7 I40:I1048576 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6646db04-ae3d-46e5-bbff-2d8592bdc898}">
+          <x14:cfRule type="dataBar" id="{e6795abe-41ad-4669-9a58-ffa762e0a49c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5472,10 +5512,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I5 I9 I26 I7 I11:I16 I40:I1048576 I20:I23 I18 I28:I38</xm:sqref>
+          <xm:sqref>I2:I4 I28:I38 I9 I26 I6:I7 I11:I16 I40:I1048576 I20:I23 I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3d9ec24e-a1da-440a-bfaa-cbf724d2cdac}">
+          <x14:cfRule type="dataBar" id="{cebb4688-f38f-4dd5-a5b2-34d89dfb24db}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5483,10 +5523,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I12:I14 I3:I5 I7 I18 I9 I20:I23 I26 I37:I38 I29 I32:I34 I40:I41 I43:I48 I50:I51</xm:sqref>
+          <xm:sqref>I12:I14 I3:I4 I50:I51 I6:I7 I18 I9 I20:I23 I26 I37:I38 I29 I32:I34 I40:I41 I43:I48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{213a9139-65c9-4b34-a9e0-585d2d02d42e}">
+          <x14:cfRule type="dataBar" id="{fca5342d-b635-4402-95eb-b1c6c70e1602}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5494,10 +5534,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I18 I3:I5 I7 I12:I14 I9 I20:I23 I37:I38 I29 I32:I34 I40:I41 I43:I48 I50:I51</xm:sqref>
+          <xm:sqref>I18 I3:I4 I50:I51 I6:I7 I12:I14 I9 I20:I23 I37:I38 I29 I32:I34 I40:I41 I43:I48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ab67dc00-3d99-4bc8-8c0f-a963b304cff5}">
+          <x14:cfRule type="dataBar" id="{005ac478-b54e-40b6-86e1-8cf36abd3db4}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5505,10 +5545,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I16 I3:I5 I7 I12:I14 I9 I20:I23 I26 I18 I50:I51 I29 I32:I34 I37:I38 I40:I41 I43:I48</xm:sqref>
+          <xm:sqref>I16 I3:I4 I43:I48 I6:I7 I12:I14 I9 I20:I23 I26 I18 I50:I51 I29 I32:I34 I37:I38 I40:I41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f2ad4f43-4518-41c6-8a22-0234dd053784}">
+          <x14:cfRule type="dataBar" id="{9e0b4405-4d85-4a99-8e74-9b3fcf8c332f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5516,10 +5556,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I14 I3:I5 I7 I20:I23 I9 I16 I26 I18 I40:I41 I29:I30 I43:I51 I32:I35 I37:I38</xm:sqref>
+          <xm:sqref>I11:I14 I3:I4 I37:I38 I6:I7 I20:I23 I9 I16 I26 I18 I40:I41 I29:I30 I43:I51 I32:I35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fcc7d6c5-9727-4ec5-bfc8-cb96708af8cc}">
+          <x14:cfRule type="dataBar" id="{1b26c7ed-6040-423e-b843-1e1125a1e5af}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5527,10 +5567,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I20:I23 I3:I5 I7 I16 I9 I11:I14 I26 I18 I50:I51 I32:I34 I37:I38 I40:I41 I43:I48 I29:I30</xm:sqref>
+          <xm:sqref>I20:I23 I3:I4 I29:I30 I6:I7 I16 I9 I11:I14 I26 I18 I50:I51 I32:I34 I37:I38 I40:I41 I43:I48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2e9e720d-2fc5-47e8-986e-7a35ff4cafdc}">
+          <x14:cfRule type="dataBar" id="{61ee1db0-d5bd-41a5-8f68-6ef6244386f1}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5538,10 +5578,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I18 I20:I23 I3:I5 I7 I26 I9 I11:I16 I28:I30 I32:I38 I40:I51</xm:sqref>
+          <xm:sqref>I18 I20:I23 I3:I4 I40:I51 I6:I7 I26 I9 I11:I16 I28:I30 I32:I38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d8123ca4-e3e4-41ac-9faf-b882f660c764}">
+          <x14:cfRule type="dataBar" id="{7f835b2a-72a9-4953-9523-b8d4fee6978c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5549,10 +5589,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I16 I3:I5 I7 I20:I23 I9 I18 I26 I40:I51 I29:I30 I32:I38</xm:sqref>
+          <xm:sqref>I11:I16 I3:I4 I32:I38 I6:I7 I20:I23 I9 I18 I26 I40:I51 I29:I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{57788638-193d-4e69-be69-87ed19204da0}">
+          <x14:cfRule type="dataBar" id="{90708e7a-6782-40dc-af53-6f2f8e04c202}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5560,10 +5600,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I18 I3:I5 I7 I20:I23 I9 I26 I32:I38 I28:I30 I40:I51</xm:sqref>
+          <xm:sqref>I11:I18 I3:I4 I40:I51 I6:I7 I20:I23 I9 I26 I32:I38 I28:I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2bc491ac-0919-4df1-b05b-c2556d76ce29}">
+          <x14:cfRule type="dataBar" id="{c8a0abfd-999b-41dc-8adb-4e1c276343eb}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5571,10 +5611,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I18 I3:I7 I26 I20:I23 I9 I28:I30 I32:I51</xm:sqref>
+          <xm:sqref>I11:I18 I3:I7 I28:I30 I32:I51 I26 I20:I23 I9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{750e69f7-5f96-4d4c-aa99-1d48c2b8295a}">
+          <x14:cfRule type="dataBar" id="{ad6ddf03-3bf3-43e8-90b0-7ad8718bac5b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5582,10 +5622,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I26 I20:I23 I3:I7 I11:I18 I9 I28:I30 I32:I38 I40:I51</xm:sqref>
+          <xm:sqref>I26 I20:I23 I3:I7 I32:I38 I40:I51 I11:I18 I9 I28:I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{39a9d97c-1701-4008-b243-abcc23b82f6b}">
+          <x14:cfRule type="dataBar" id="{9dc82c74-1d90-4b35-ba55-0c2d3503c2d3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="117">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -1343,20 +1343,20 @@
     <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1694,7 +1694,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K161"/>
+  <dimension ref="A1:K162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -1781,8 +1781,8 @@
         <v>13</v>
       </c>
       <c r="I3" s="16">
-        <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150,C152,C154,C156)</f>
-        <v>527</v>
+        <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150,C152,C154,C156,C159)</f>
+        <v>537</v>
       </c>
       <c r="J3" s="3">
         <v>46204</v>
@@ -4951,46 +4951,62 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="38"/>
-      <c r="B158" s="39" t="s">
+      <c r="B158" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="C158" s="40">
+      <c r="C158" s="27">
         <v>240</v>
       </c>
       <c r="D158" s="21">
         <f>SUM(C3:C158)</f>
         <v>-2641.11</v>
       </c>
-      <c r="E158" s="41"/>
+      <c r="E158" s="34"/>
     </row>
     <row r="159" spans="1:5">
-      <c r="A159" s="42"/>
-      <c r="B159" s="39"/>
-      <c r="C159" s="40"/>
-      <c r="D159" s="43"/>
-      <c r="E159" s="41"/>
-    </row>
-    <row r="160" ht="14.25" spans="1:5">
-      <c r="A160" s="44"/>
-      <c r="B160" s="45"/>
-      <c r="C160" s="46"/>
-      <c r="D160" s="46"/>
-      <c r="E160" s="47"/>
-    </row>
-    <row r="161" spans="1:5">
-      <c r="A161" s="48" t="s">
+      <c r="A159" s="38"/>
+      <c r="B159" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C159" s="27">
+        <v>10</v>
+      </c>
+      <c r="D159" s="21">
+        <f>SUM(C3:C159)</f>
+        <v>-2631.11</v>
+      </c>
+      <c r="E159" s="34" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" s="39"/>
+      <c r="B160" s="40"/>
+      <c r="C160" s="41"/>
+      <c r="D160" s="42"/>
+      <c r="E160" s="43"/>
+    </row>
+    <row r="161" ht="14.25" spans="1:5">
+      <c r="A161" s="44"/>
+      <c r="B161" s="45"/>
+      <c r="C161" s="46"/>
+      <c r="D161" s="46"/>
+      <c r="E161" s="47"/>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="B161" s="48"/>
-      <c r="C161" s="48"/>
-      <c r="D161" s="48"/>
-      <c r="E161" s="48"/>
+      <c r="B162" s="48"/>
+      <c r="C162" s="48"/>
+      <c r="D162" s="48"/>
+      <c r="E162" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A161:E161"/>
+    <mergeCell ref="A162:E162"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A23:A24"/>
@@ -5014,7 +5030,7 @@
     <mergeCell ref="A142:A143"/>
     <mergeCell ref="A145:A146"/>
     <mergeCell ref="A153:A154"/>
-    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="A157:A159"/>
     <mergeCell ref="D3:D7"/>
     <mergeCell ref="D18:D19"/>
     <mergeCell ref="D23:D24"/>
@@ -5040,7 +5056,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{191398e4-7383-4f9f-bf42-8a41e529687a}</x14:id>
+          <x14:id>{fdb89135-96d0-4f2f-9a6c-3e2ec41f4a60}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5054,12 +5070,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4048862c-1979-4697-960b-bc7e2f05316f}</x14:id>
+          <x14:id>{bcd5dc8c-26ec-48a2-b776-00b967d598b3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D160 D162:D1048576">
+  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D161 D163:D1048576">
     <cfRule type="colorScale" priority="81">
       <colorScale>
         <cfvo type="min"/>
@@ -5080,7 +5096,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2f9c3b63-fbdd-40ac-8a10-2bc6ca07880d}</x14:id>
+          <x14:id>{9b4235c6-7175-4c6c-b217-9ca1a9e6fe14}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5094,35 +5110,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1ab22eb6-ea8d-480b-b9e3-ae4305d6d1b7}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I9 I28:I1048576 I11:I18 I20:I24 I26">
-    <cfRule type="dataBar" priority="23">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5b8deb84-b20f-4361-ae3c-71c211e8a335}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I9 I28:I1048576 I11:I18 I20:I23 I26">
-    <cfRule type="dataBar" priority="24">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c4a1018c-2230-41a2-94ef-bb1243319065}</x14:id>
+          <x14:id>{c1f121e4-54fa-4a57-9007-c0138f1d5bde}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5136,7 +5124,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{423bf82b-a1a3-4506-ad04-424a90f609d0}</x14:id>
+          <x14:id>{55df90ec-b513-4b8c-a9f3-27fdd63d9921}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5150,7 +5138,35 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ad5707fa-bd6a-4700-8f00-0636840721de}</x14:id>
+          <x14:id>{2dc85a85-b96a-4a8f-8388-9ae38d0773e9}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I9 I28:I1048576 I26 I20:I24 I11:I18">
+    <cfRule type="dataBar" priority="23">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{f3c03a1d-6bbe-4f2b-a135-c5cc367df31f}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I9 I28:I1048576 I26 I20:I23 I11:I18">
+    <cfRule type="dataBar" priority="24">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6205d76f-1026-4c38-910f-8d022127e333}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5164,7 +5180,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{19b03e17-2eec-4dd3-8919-83dd38f2ef20}</x14:id>
+          <x14:id>{e3aa1032-bf69-45ce-b0dd-5aee01468238}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5178,12 +5194,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1e97c95b-eb46-459e-818d-0ad9bdc0da87}</x14:id>
+          <x14:id>{eee5d117-610d-4a45-bf13-8a21e9f7c383}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4 I28:I38 I9 I26 I6:I7 I11:I16 I40:I1048576 I20:I23 I18">
+  <conditionalFormatting sqref="I2:I4 I28:I38 I9 I26 I6:I7 I11:I16 I40:I1048576 I18 I20:I23">
     <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
@@ -5192,7 +5208,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e6795abe-41ad-4669-9a58-ffa762e0a49c}</x14:id>
+          <x14:id>{6a4af19f-0423-4a62-b0f7-6763a34f461e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5238,7 +5254,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cebb4688-f38f-4dd5-a5b2-34d89dfb24db}</x14:id>
+          <x14:id>{13ada5db-e343-44d5-b878-59ed8a8079d0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5252,7 +5268,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fca5342d-b635-4402-95eb-b1c6c70e1602}</x14:id>
+          <x14:id>{211f3150-2e75-4d46-9ef6-67fd18d661f2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5266,7 +5282,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{005ac478-b54e-40b6-86e1-8cf36abd3db4}</x14:id>
+          <x14:id>{c64c8938-0d27-4fa9-8ab6-3f3b466e47b3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5280,7 +5296,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9e0b4405-4d85-4a99-8e74-9b3fcf8c332f}</x14:id>
+          <x14:id>{a3126a1f-66d0-49fe-ba1a-8e75bcbd8a30}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5294,7 +5310,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1b26c7ed-6040-423e-b843-1e1125a1e5af}</x14:id>
+          <x14:id>{60aa269e-0902-4405-ba1c-84e3a985323d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5308,7 +5324,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{61ee1db0-d5bd-41a5-8f68-6ef6244386f1}</x14:id>
+          <x14:id>{fb7ba5d0-3108-4a3c-bf13-de30a93af1ae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5322,7 +5338,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7f835b2a-72a9-4953-9523-b8d4fee6978c}</x14:id>
+          <x14:id>{6671f810-8b2c-4f90-8291-325c15a4c283}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5336,7 +5352,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{90708e7a-6782-40dc-af53-6f2f8e04c202}</x14:id>
+          <x14:id>{4f0f8d9c-2a05-47db-a5ea-ff2608562442}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5350,7 +5366,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c8a0abfd-999b-41dc-8adb-4e1c276343eb}</x14:id>
+          <x14:id>{67d8acd6-0ad0-4d41-8e96-04ec4cbc4a00}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5364,7 +5380,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ad6ddf03-3bf3-43e8-90b0-7ad8718bac5b}</x14:id>
+          <x14:id>{a51aba8d-4551-4e72-925a-7df83b76002e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5378,7 +5394,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9dc82c74-1d90-4b35-ba55-0c2d3503c2d3}</x14:id>
+          <x14:id>{3320de92-7744-4bc7-9957-d48f81e24f6d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5386,13 +5402,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
+    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{191398e4-7383-4f9f-bf42-8a41e529687a}">
+          <x14:cfRule type="dataBar" id="{fdb89135-96d0-4f2f-9a6c-3e2ec41f4a60}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5403,7 +5419,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4048862c-1979-4697-960b-bc7e2f05316f}">
+          <x14:cfRule type="dataBar" id="{bcd5dc8c-26ec-48a2-b776-00b967d598b3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5414,7 +5430,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2f9c3b63-fbdd-40ac-8a10-2bc6ca07880d}">
+          <x14:cfRule type="dataBar" id="{9b4235c6-7175-4c6c-b217-9ca1a9e6fe14}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5427,7 +5443,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1ab22eb6-ea8d-480b-b9e3-ae4305d6d1b7}">
+          <x14:cfRule type="dataBar" id="{c1f121e4-54fa-4a57-9007-c0138f1d5bde}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5438,29 +5454,7 @@
           <xm:sqref>I1:I26 I28:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5b8deb84-b20f-4361-ae3c-71c211e8a335}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>I1:I9 I28:I1048576 I11:I18 I20:I24 I26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c4a1018c-2230-41a2-94ef-bb1243319065}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>I1:I9 I28:I1048576 I11:I18 I20:I23 I26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{423bf82b-a1a3-4506-ad04-424a90f609d0}">
+          <x14:cfRule type="dataBar" id="{55df90ec-b513-4b8c-a9f3-27fdd63d9921}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5471,7 +5465,7 @@
           <xm:sqref>I1:I24 I26 I28:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ad5707fa-bd6a-4700-8f00-0636840721de}">
+          <x14:cfRule type="dataBar" id="{2dc85a85-b96a-4a8f-8388-9ae38d0773e9}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5482,7 +5476,29 @@
           <xm:sqref>I1:I18 I26 I28:I1048576 I20:I24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{19b03e17-2eec-4dd3-8919-83dd38f2ef20}">
+          <x14:cfRule type="dataBar" id="{f3c03a1d-6bbe-4f2b-a135-c5cc367df31f}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I1:I9 I28:I1048576 I26 I20:I24 I11:I18</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{6205d76f-1026-4c38-910f-8d022127e333}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I1:I9 I28:I1048576 I26 I20:I23 I11:I18</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{e3aa1032-bf69-45ce-b0dd-5aee01468238}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5493,7 +5509,7 @@
           <xm:sqref>I2 I52:I1048576 I31</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1e97c95b-eb46-459e-818d-0ad9bdc0da87}">
+          <x14:cfRule type="dataBar" id="{eee5d117-610d-4a45-bf13-8a21e9f7c383}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5504,7 +5520,7 @@
           <xm:sqref>I2:I4 I28:I38 I26 I11:I18 I9 I6:I7 I40:I1048576 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e6795abe-41ad-4669-9a58-ffa762e0a49c}">
+          <x14:cfRule type="dataBar" id="{6a4af19f-0423-4a62-b0f7-6763a34f461e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5512,10 +5528,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I4 I28:I38 I9 I26 I6:I7 I11:I16 I40:I1048576 I20:I23 I18</xm:sqref>
+          <xm:sqref>I2:I4 I28:I38 I9 I26 I6:I7 I11:I16 I40:I1048576 I18 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cebb4688-f38f-4dd5-a5b2-34d89dfb24db}">
+          <x14:cfRule type="dataBar" id="{13ada5db-e343-44d5-b878-59ed8a8079d0}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5526,7 +5542,7 @@
           <xm:sqref>I12:I14 I3:I4 I50:I51 I6:I7 I18 I9 I20:I23 I26 I37:I38 I29 I32:I34 I40:I41 I43:I48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fca5342d-b635-4402-95eb-b1c6c70e1602}">
+          <x14:cfRule type="dataBar" id="{211f3150-2e75-4d46-9ef6-67fd18d661f2}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5537,7 +5553,7 @@
           <xm:sqref>I18 I3:I4 I50:I51 I6:I7 I12:I14 I9 I20:I23 I37:I38 I29 I32:I34 I40:I41 I43:I48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{005ac478-b54e-40b6-86e1-8cf36abd3db4}">
+          <x14:cfRule type="dataBar" id="{c64c8938-0d27-4fa9-8ab6-3f3b466e47b3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5548,7 +5564,7 @@
           <xm:sqref>I16 I3:I4 I43:I48 I6:I7 I12:I14 I9 I20:I23 I26 I18 I50:I51 I29 I32:I34 I37:I38 I40:I41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9e0b4405-4d85-4a99-8e74-9b3fcf8c332f}">
+          <x14:cfRule type="dataBar" id="{a3126a1f-66d0-49fe-ba1a-8e75bcbd8a30}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5559,7 +5575,7 @@
           <xm:sqref>I11:I14 I3:I4 I37:I38 I6:I7 I20:I23 I9 I16 I26 I18 I40:I41 I29:I30 I43:I51 I32:I35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1b26c7ed-6040-423e-b843-1e1125a1e5af}">
+          <x14:cfRule type="dataBar" id="{60aa269e-0902-4405-ba1c-84e3a985323d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5570,7 +5586,7 @@
           <xm:sqref>I20:I23 I3:I4 I29:I30 I6:I7 I16 I9 I11:I14 I26 I18 I50:I51 I32:I34 I37:I38 I40:I41 I43:I48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{61ee1db0-d5bd-41a5-8f68-6ef6244386f1}">
+          <x14:cfRule type="dataBar" id="{fb7ba5d0-3108-4a3c-bf13-de30a93af1ae}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5581,7 +5597,7 @@
           <xm:sqref>I18 I20:I23 I3:I4 I40:I51 I6:I7 I26 I9 I11:I16 I28:I30 I32:I38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7f835b2a-72a9-4953-9523-b8d4fee6978c}">
+          <x14:cfRule type="dataBar" id="{6671f810-8b2c-4f90-8291-325c15a4c283}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5592,7 +5608,7 @@
           <xm:sqref>I11:I16 I3:I4 I32:I38 I6:I7 I20:I23 I9 I18 I26 I40:I51 I29:I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{90708e7a-6782-40dc-af53-6f2f8e04c202}">
+          <x14:cfRule type="dataBar" id="{4f0f8d9c-2a05-47db-a5ea-ff2608562442}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5603,7 +5619,7 @@
           <xm:sqref>I11:I18 I3:I4 I40:I51 I6:I7 I20:I23 I9 I26 I32:I38 I28:I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c8a0abfd-999b-41dc-8adb-4e1c276343eb}">
+          <x14:cfRule type="dataBar" id="{67d8acd6-0ad0-4d41-8e96-04ec4cbc4a00}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5614,7 +5630,7 @@
           <xm:sqref>I11:I18 I3:I7 I28:I30 I32:I51 I26 I20:I23 I9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ad6ddf03-3bf3-43e8-90b0-7ad8718bac5b}">
+          <x14:cfRule type="dataBar" id="{a51aba8d-4551-4e72-925a-7df83b76002e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5625,7 +5641,7 @@
           <xm:sqref>I26 I20:I23 I3:I7 I32:I38 I40:I51 I11:I18 I9 I28:I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9dc82c74-1d90-4b35-ba55-0c2d3503c2d3}">
+          <x14:cfRule type="dataBar" id="{3320de92-7744-4bc7-9957-d48f81e24f6d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="117">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -1225,7 +1225,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1335,27 +1335,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -1970,11 +1949,11 @@
         <v>28</v>
       </c>
       <c r="I10" s="2">
-        <f>SUM(C133,C143,C147,C155)</f>
-        <v>63.32</v>
+        <f>SUM(C133,C143,C147,C155,C160)</f>
+        <v>68.32</v>
       </c>
       <c r="J10" s="3">
-        <v>46196</v>
+        <v>46206</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -4932,7 +4911,7 @@
       </c>
     </row>
     <row r="157" spans="1:5">
-      <c r="A157" s="37">
+      <c r="A157" s="25">
         <v>46205</v>
       </c>
       <c r="B157" s="33" t="s">
@@ -4950,7 +4929,7 @@
       </c>
     </row>
     <row r="158" spans="1:5">
-      <c r="A158" s="38"/>
+      <c r="A158" s="31"/>
       <c r="B158" s="33" t="s">
         <v>17</v>
       </c>
@@ -4964,7 +4943,7 @@
       <c r="E158" s="34"/>
     </row>
     <row r="159" spans="1:5">
-      <c r="A159" s="38"/>
+      <c r="A159" s="31"/>
       <c r="B159" s="33" t="s">
         <v>13</v>
       </c>
@@ -4980,27 +4959,38 @@
       </c>
     </row>
     <row r="160" spans="1:5">
-      <c r="A160" s="39"/>
-      <c r="B160" s="40"/>
-      <c r="C160" s="41"/>
-      <c r="D160" s="42"/>
-      <c r="E160" s="43"/>
+      <c r="A160" s="25">
+        <v>46206</v>
+      </c>
+      <c r="B160" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C160" s="27">
+        <v>5</v>
+      </c>
+      <c r="D160" s="21">
+        <f>SUM(C3:C160)</f>
+        <v>-2626.11</v>
+      </c>
+      <c r="E160" s="34" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="161" ht="14.25" spans="1:5">
-      <c r="A161" s="44"/>
-      <c r="B161" s="45"/>
-      <c r="C161" s="46"/>
-      <c r="D161" s="46"/>
-      <c r="E161" s="47"/>
+      <c r="A161" s="37"/>
+      <c r="B161" s="38"/>
+      <c r="C161" s="39"/>
+      <c r="D161" s="39"/>
+      <c r="E161" s="40"/>
     </row>
     <row r="162" spans="1:5">
-      <c r="A162" s="48" t="s">
+      <c r="A162" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="B162" s="48"/>
-      <c r="C162" s="48"/>
-      <c r="D162" s="48"/>
-      <c r="E162" s="48"/>
+      <c r="B162" s="41"/>
+      <c r="C162" s="41"/>
+      <c r="D162" s="41"/>
+      <c r="E162" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="42">
@@ -5056,7 +5046,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fdb89135-96d0-4f2f-9a6c-3e2ec41f4a60}</x14:id>
+          <x14:id>{0d4c8d68-faf2-4041-af46-365e584f8499}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5070,7 +5060,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bcd5dc8c-26ec-48a2-b776-00b967d598b3}</x14:id>
+          <x14:id>{025aae90-7e20-4b89-a1ac-2f6a67c26524}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5096,7 +5086,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9b4235c6-7175-4c6c-b217-9ca1a9e6fe14}</x14:id>
+          <x14:id>{d27d09e6-277d-4adc-a7a5-d748768367ff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5110,7 +5100,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c1f121e4-54fa-4a57-9007-c0138f1d5bde}</x14:id>
+          <x14:id>{0e8a266e-af67-43fb-97ce-0323bbb26cfe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5124,7 +5114,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{55df90ec-b513-4b8c-a9f3-27fdd63d9921}</x14:id>
+          <x14:id>{e7dcaf4d-4269-4870-b888-6c621f80559f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5138,7 +5128,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2dc85a85-b96a-4a8f-8388-9ae38d0773e9}</x14:id>
+          <x14:id>{f7ace123-fc75-4fe6-b752-cb9e4447b375}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5152,7 +5142,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f3c03a1d-6bbe-4f2b-a135-c5cc367df31f}</x14:id>
+          <x14:id>{cec5b922-c7e5-464a-a6dc-01aba1ba78c0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5166,7 +5156,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6205d76f-1026-4c38-910f-8d022127e333}</x14:id>
+          <x14:id>{de7bce7f-7e1b-4ced-ae61-906e218fbbe4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5180,7 +5170,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e3aa1032-bf69-45ce-b0dd-5aee01468238}</x14:id>
+          <x14:id>{b33d155f-0aa1-4aeb-8f0a-f37a20bace06}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5194,7 +5184,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eee5d117-610d-4a45-bf13-8a21e9f7c383}</x14:id>
+          <x14:id>{afa3f27f-221f-4360-b2e7-39e4fedb0e99}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5208,7 +5198,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6a4af19f-0423-4a62-b0f7-6763a34f461e}</x14:id>
+          <x14:id>{93e67e42-5e6b-4f4e-84a2-af56e8b47763}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5254,7 +5244,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{13ada5db-e343-44d5-b878-59ed8a8079d0}</x14:id>
+          <x14:id>{6905f099-6eb3-489d-b0d1-175283691f17}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5268,7 +5258,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{211f3150-2e75-4d46-9ef6-67fd18d661f2}</x14:id>
+          <x14:id>{a521ca54-40d5-456f-b5db-152e77310afc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5282,7 +5272,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c64c8938-0d27-4fa9-8ab6-3f3b466e47b3}</x14:id>
+          <x14:id>{b05d5905-c9c2-4db6-894f-b5b967be6dca}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5296,7 +5286,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a3126a1f-66d0-49fe-ba1a-8e75bcbd8a30}</x14:id>
+          <x14:id>{a315770e-cfa1-4edb-923d-eca1f2edaeba}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5310,7 +5300,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{60aa269e-0902-4405-ba1c-84e3a985323d}</x14:id>
+          <x14:id>{ddbd8b7a-8878-437d-8154-09e6afb4b8ec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5324,7 +5314,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fb7ba5d0-3108-4a3c-bf13-de30a93af1ae}</x14:id>
+          <x14:id>{00fee901-0269-4625-9d6a-7738e4dec67a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5338,7 +5328,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6671f810-8b2c-4f90-8291-325c15a4c283}</x14:id>
+          <x14:id>{f1e39b4e-e540-4cd4-846a-6b12d1762b7b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5352,7 +5342,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4f0f8d9c-2a05-47db-a5ea-ff2608562442}</x14:id>
+          <x14:id>{a147da21-7c8b-4825-8051-dbc86a4bbbca}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5366,7 +5356,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{67d8acd6-0ad0-4d41-8e96-04ec4cbc4a00}</x14:id>
+          <x14:id>{03a945b7-3341-41eb-8969-f3daa63c3c3c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5380,7 +5370,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a51aba8d-4551-4e72-925a-7df83b76002e}</x14:id>
+          <x14:id>{264d65c3-553f-4cec-9fde-2fea3f5889e6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5394,7 +5384,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3320de92-7744-4bc7-9957-d48f81e24f6d}</x14:id>
+          <x14:id>{072bcdbd-01d9-42b2-9cd5-bb64483348a0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5402,13 +5392,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="D3 D8:D108 E32:E49 E8:E30" formulaRange="1"/>
+    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fdb89135-96d0-4f2f-9a6c-3e2ec41f4a60}">
+          <x14:cfRule type="dataBar" id="{0d4c8d68-faf2-4041-af46-365e584f8499}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5419,7 +5409,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bcd5dc8c-26ec-48a2-b776-00b967d598b3}">
+          <x14:cfRule type="dataBar" id="{025aae90-7e20-4b89-a1ac-2f6a67c26524}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5430,7 +5420,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9b4235c6-7175-4c6c-b217-9ca1a9e6fe14}">
+          <x14:cfRule type="dataBar" id="{d27d09e6-277d-4adc-a7a5-d748768367ff}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5443,7 +5433,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c1f121e4-54fa-4a57-9007-c0138f1d5bde}">
+          <x14:cfRule type="dataBar" id="{0e8a266e-af67-43fb-97ce-0323bbb26cfe}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5454,7 +5444,7 @@
           <xm:sqref>I1:I26 I28:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{55df90ec-b513-4b8c-a9f3-27fdd63d9921}">
+          <x14:cfRule type="dataBar" id="{e7dcaf4d-4269-4870-b888-6c621f80559f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5465,7 +5455,7 @@
           <xm:sqref>I1:I24 I26 I28:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2dc85a85-b96a-4a8f-8388-9ae38d0773e9}">
+          <x14:cfRule type="dataBar" id="{f7ace123-fc75-4fe6-b752-cb9e4447b375}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5476,7 +5466,7 @@
           <xm:sqref>I1:I18 I26 I28:I1048576 I20:I24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f3c03a1d-6bbe-4f2b-a135-c5cc367df31f}">
+          <x14:cfRule type="dataBar" id="{cec5b922-c7e5-464a-a6dc-01aba1ba78c0}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5487,7 +5477,7 @@
           <xm:sqref>I1:I9 I28:I1048576 I26 I20:I24 I11:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6205d76f-1026-4c38-910f-8d022127e333}">
+          <x14:cfRule type="dataBar" id="{de7bce7f-7e1b-4ced-ae61-906e218fbbe4}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5498,7 +5488,7 @@
           <xm:sqref>I1:I9 I28:I1048576 I26 I20:I23 I11:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e3aa1032-bf69-45ce-b0dd-5aee01468238}">
+          <x14:cfRule type="dataBar" id="{b33d155f-0aa1-4aeb-8f0a-f37a20bace06}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5509,7 +5499,7 @@
           <xm:sqref>I2 I52:I1048576 I31</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eee5d117-610d-4a45-bf13-8a21e9f7c383}">
+          <x14:cfRule type="dataBar" id="{afa3f27f-221f-4360-b2e7-39e4fedb0e99}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5520,7 +5510,7 @@
           <xm:sqref>I2:I4 I28:I38 I26 I11:I18 I9 I6:I7 I40:I1048576 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6a4af19f-0423-4a62-b0f7-6763a34f461e}">
+          <x14:cfRule type="dataBar" id="{93e67e42-5e6b-4f4e-84a2-af56e8b47763}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5531,7 +5521,7 @@
           <xm:sqref>I2:I4 I28:I38 I9 I26 I6:I7 I11:I16 I40:I1048576 I18 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{13ada5db-e343-44d5-b878-59ed8a8079d0}">
+          <x14:cfRule type="dataBar" id="{6905f099-6eb3-489d-b0d1-175283691f17}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5542,7 +5532,7 @@
           <xm:sqref>I12:I14 I3:I4 I50:I51 I6:I7 I18 I9 I20:I23 I26 I37:I38 I29 I32:I34 I40:I41 I43:I48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{211f3150-2e75-4d46-9ef6-67fd18d661f2}">
+          <x14:cfRule type="dataBar" id="{a521ca54-40d5-456f-b5db-152e77310afc}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5553,7 +5543,7 @@
           <xm:sqref>I18 I3:I4 I50:I51 I6:I7 I12:I14 I9 I20:I23 I37:I38 I29 I32:I34 I40:I41 I43:I48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c64c8938-0d27-4fa9-8ab6-3f3b466e47b3}">
+          <x14:cfRule type="dataBar" id="{b05d5905-c9c2-4db6-894f-b5b967be6dca}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5564,7 +5554,7 @@
           <xm:sqref>I16 I3:I4 I43:I48 I6:I7 I12:I14 I9 I20:I23 I26 I18 I50:I51 I29 I32:I34 I37:I38 I40:I41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a3126a1f-66d0-49fe-ba1a-8e75bcbd8a30}">
+          <x14:cfRule type="dataBar" id="{a315770e-cfa1-4edb-923d-eca1f2edaeba}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5575,7 +5565,7 @@
           <xm:sqref>I11:I14 I3:I4 I37:I38 I6:I7 I20:I23 I9 I16 I26 I18 I40:I41 I29:I30 I43:I51 I32:I35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{60aa269e-0902-4405-ba1c-84e3a985323d}">
+          <x14:cfRule type="dataBar" id="{ddbd8b7a-8878-437d-8154-09e6afb4b8ec}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5586,7 +5576,7 @@
           <xm:sqref>I20:I23 I3:I4 I29:I30 I6:I7 I16 I9 I11:I14 I26 I18 I50:I51 I32:I34 I37:I38 I40:I41 I43:I48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fb7ba5d0-3108-4a3c-bf13-de30a93af1ae}">
+          <x14:cfRule type="dataBar" id="{00fee901-0269-4625-9d6a-7738e4dec67a}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5597,7 +5587,7 @@
           <xm:sqref>I18 I20:I23 I3:I4 I40:I51 I6:I7 I26 I9 I11:I16 I28:I30 I32:I38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6671f810-8b2c-4f90-8291-325c15a4c283}">
+          <x14:cfRule type="dataBar" id="{f1e39b4e-e540-4cd4-846a-6b12d1762b7b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5608,7 +5598,7 @@
           <xm:sqref>I11:I16 I3:I4 I32:I38 I6:I7 I20:I23 I9 I18 I26 I40:I51 I29:I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4f0f8d9c-2a05-47db-a5ea-ff2608562442}">
+          <x14:cfRule type="dataBar" id="{a147da21-7c8b-4825-8051-dbc86a4bbbca}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5619,7 +5609,7 @@
           <xm:sqref>I11:I18 I3:I4 I40:I51 I6:I7 I20:I23 I9 I26 I32:I38 I28:I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{67d8acd6-0ad0-4d41-8e96-04ec4cbc4a00}">
+          <x14:cfRule type="dataBar" id="{03a945b7-3341-41eb-8969-f3daa63c3c3c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5630,7 +5620,7 @@
           <xm:sqref>I11:I18 I3:I7 I28:I30 I32:I51 I26 I20:I23 I9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a51aba8d-4551-4e72-925a-7df83b76002e}">
+          <x14:cfRule type="dataBar" id="{264d65c3-553f-4cec-9fde-2fea3f5889e6}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5641,7 +5631,7 @@
           <xm:sqref>I26 I20:I23 I3:I7 I32:I38 I40:I51 I11:I18 I9 I28:I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3320de92-7744-4bc7-9957-d48f81e24f6d}">
+          <x14:cfRule type="dataBar" id="{072bcdbd-01d9-42b2-9cd5-bb64483348a0}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="117">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -1673,7 +1673,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K162"/>
+  <dimension ref="A1:K163"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -1891,11 +1891,11 @@
         <v>25</v>
       </c>
       <c r="I8" s="2">
-        <f>SUM(C121,C123,C126,C128,C131)</f>
-        <v>195</v>
+        <f>SUM(C121,C123,C126,C128,C131,C161)</f>
+        <v>228</v>
       </c>
       <c r="J8" s="3">
-        <v>46069</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -4976,27 +4976,43 @@
         <v>70</v>
       </c>
     </row>
-    <row r="161" ht="14.25" spans="1:5">
-      <c r="A161" s="37"/>
-      <c r="B161" s="38"/>
-      <c r="C161" s="39"/>
-      <c r="D161" s="39"/>
-      <c r="E161" s="40"/>
-    </row>
-    <row r="162" spans="1:5">
-      <c r="A162" s="41" t="s">
+    <row r="161" spans="1:5">
+      <c r="A161" s="25">
+        <v>46210</v>
+      </c>
+      <c r="B161" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C161" s="27">
+        <v>33</v>
+      </c>
+      <c r="D161" s="21">
+        <f>SUM(C3:C161)</f>
+        <v>-2593.11</v>
+      </c>
+      <c r="E161" s="34"/>
+    </row>
+    <row r="162" ht="14.25" spans="1:5">
+      <c r="A162" s="37"/>
+      <c r="B162" s="38"/>
+      <c r="C162" s="39"/>
+      <c r="D162" s="39"/>
+      <c r="E162" s="40"/>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="B162" s="41"/>
-      <c r="C162" s="41"/>
-      <c r="D162" s="41"/>
-      <c r="E162" s="41"/>
+      <c r="B163" s="41"/>
+      <c r="C163" s="41"/>
+      <c r="D163" s="41"/>
+      <c r="E163" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A162:E162"/>
+    <mergeCell ref="A163:E163"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A23:A24"/>
@@ -5046,7 +5062,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0d4c8d68-faf2-4041-af46-365e584f8499}</x14:id>
+          <x14:id>{dda28aed-6bab-4d98-b172-9310ed1317e6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5060,12 +5076,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{025aae90-7e20-4b89-a1ac-2f6a67c26524}</x14:id>
+          <x14:id>{41a5e2b1-2edc-4d68-a131-5d85c7b12d5b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D161 D163:D1048576">
+  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D162 D164:D1048576">
     <cfRule type="colorScale" priority="81">
       <colorScale>
         <cfvo type="min"/>
@@ -5086,7 +5102,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d27d09e6-277d-4adc-a7a5-d748768367ff}</x14:id>
+          <x14:id>{379cd7c2-ea14-4e26-92d4-43b8b1501090}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5100,7 +5116,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0e8a266e-af67-43fb-97ce-0323bbb26cfe}</x14:id>
+          <x14:id>{6f2b8e67-1bee-4d6f-8afa-aa05396ac993}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5114,7 +5130,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e7dcaf4d-4269-4870-b888-6c621f80559f}</x14:id>
+          <x14:id>{d1d4e2aa-e34d-4c30-a599-78e4ec12c99b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5128,12 +5144,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f7ace123-fc75-4fe6-b752-cb9e4447b375}</x14:id>
+          <x14:id>{2eebbc89-811f-4b74-b357-9ce3b4b5a7f6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I9 I28:I1048576 I26 I20:I24 I11:I18">
+  <conditionalFormatting sqref="I1:I9 I28:I1048576 I11:I18 I20:I24 I26">
     <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="min"/>
@@ -5142,12 +5158,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cec5b922-c7e5-464a-a6dc-01aba1ba78c0}</x14:id>
+          <x14:id>{e5fe87ac-32ec-4bc5-b64a-300233a562fd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I9 I28:I1048576 I26 I20:I23 I11:I18">
+  <conditionalFormatting sqref="I1:I9 I28:I1048576 I11:I18 I20:I23 I26">
     <cfRule type="dataBar" priority="24">
       <dataBar>
         <cfvo type="min"/>
@@ -5156,7 +5172,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{de7bce7f-7e1b-4ced-ae61-906e218fbbe4}</x14:id>
+          <x14:id>{23c28805-668f-4e18-9773-e879fdb4fb3a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5170,7 +5186,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b33d155f-0aa1-4aeb-8f0a-f37a20bace06}</x14:id>
+          <x14:id>{a1f4dccc-d946-4b9a-9b68-6190d4797408}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5184,12 +5200,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{afa3f27f-221f-4360-b2e7-39e4fedb0e99}</x14:id>
+          <x14:id>{1b61aaca-83ea-44ad-8ea7-0574f315436b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4 I28:I38 I9 I26 I6:I7 I11:I16 I40:I1048576 I18 I20:I23">
+  <conditionalFormatting sqref="I2:I4 I28:I38 I9 I26 I6:I7 I11:I16 I40:I1048576 I20:I23 I18">
     <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
@@ -5198,7 +5214,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{93e67e42-5e6b-4f4e-84a2-af56e8b47763}</x14:id>
+          <x14:id>{f8b8b31c-f96d-42d1-8e93-c62e7be8891b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5244,7 +5260,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6905f099-6eb3-489d-b0d1-175283691f17}</x14:id>
+          <x14:id>{e8ad24d4-8614-4351-a124-6d7c863227e8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5258,7 +5274,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a521ca54-40d5-456f-b5db-152e77310afc}</x14:id>
+          <x14:id>{085014cf-1b84-4c22-838a-e5cd85a403f5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5272,7 +5288,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b05d5905-c9c2-4db6-894f-b5b967be6dca}</x14:id>
+          <x14:id>{d62c5a28-755d-48b4-bfcb-4acbc45cc0e8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5286,7 +5302,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a315770e-cfa1-4edb-923d-eca1f2edaeba}</x14:id>
+          <x14:id>{521a02ac-3d11-4d91-a132-60da00920526}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5300,7 +5316,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ddbd8b7a-8878-437d-8154-09e6afb4b8ec}</x14:id>
+          <x14:id>{6ae66a5b-4736-4a18-87bc-85ad8631268b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5314,7 +5330,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{00fee901-0269-4625-9d6a-7738e4dec67a}</x14:id>
+          <x14:id>{fc969919-126a-4c45-af96-85eefa8791da}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5328,7 +5344,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f1e39b4e-e540-4cd4-846a-6b12d1762b7b}</x14:id>
+          <x14:id>{55c90aec-be42-48c9-9a1d-34d7ae269098}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5342,7 +5358,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a147da21-7c8b-4825-8051-dbc86a4bbbca}</x14:id>
+          <x14:id>{17d50051-15f7-4451-8f66-f9dab37b6e79}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5356,7 +5372,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{03a945b7-3341-41eb-8969-f3daa63c3c3c}</x14:id>
+          <x14:id>{8002b3ac-a8b8-43e8-9020-25131c57a717}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5370,7 +5386,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{264d65c3-553f-4cec-9fde-2fea3f5889e6}</x14:id>
+          <x14:id>{1dc8d6e4-2b04-4017-878d-17a32f711389}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5384,7 +5400,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{072bcdbd-01d9-42b2-9cd5-bb64483348a0}</x14:id>
+          <x14:id>{6530289b-41df-4775-9c46-630bce9f8921}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5398,7 +5414,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0d4c8d68-faf2-4041-af46-365e584f8499}">
+          <x14:cfRule type="dataBar" id="{dda28aed-6bab-4d98-b172-9310ed1317e6}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5409,7 +5425,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{025aae90-7e20-4b89-a1ac-2f6a67c26524}">
+          <x14:cfRule type="dataBar" id="{41a5e2b1-2edc-4d68-a131-5d85c7b12d5b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5420,7 +5436,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d27d09e6-277d-4adc-a7a5-d748768367ff}">
+          <x14:cfRule type="dataBar" id="{379cd7c2-ea14-4e26-92d4-43b8b1501090}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5433,7 +5449,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0e8a266e-af67-43fb-97ce-0323bbb26cfe}">
+          <x14:cfRule type="dataBar" id="{6f2b8e67-1bee-4d6f-8afa-aa05396ac993}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5444,7 +5460,7 @@
           <xm:sqref>I1:I26 I28:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e7dcaf4d-4269-4870-b888-6c621f80559f}">
+          <x14:cfRule type="dataBar" id="{d1d4e2aa-e34d-4c30-a599-78e4ec12c99b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5455,7 +5471,7 @@
           <xm:sqref>I1:I24 I26 I28:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f7ace123-fc75-4fe6-b752-cb9e4447b375}">
+          <x14:cfRule type="dataBar" id="{2eebbc89-811f-4b74-b357-9ce3b4b5a7f6}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5466,7 +5482,7 @@
           <xm:sqref>I1:I18 I26 I28:I1048576 I20:I24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cec5b922-c7e5-464a-a6dc-01aba1ba78c0}">
+          <x14:cfRule type="dataBar" id="{e5fe87ac-32ec-4bc5-b64a-300233a562fd}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5474,10 +5490,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I9 I28:I1048576 I26 I20:I24 I11:I18</xm:sqref>
+          <xm:sqref>I1:I9 I28:I1048576 I11:I18 I20:I24 I26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{de7bce7f-7e1b-4ced-ae61-906e218fbbe4}">
+          <x14:cfRule type="dataBar" id="{23c28805-668f-4e18-9773-e879fdb4fb3a}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5485,10 +5501,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I9 I28:I1048576 I26 I20:I23 I11:I18</xm:sqref>
+          <xm:sqref>I1:I9 I28:I1048576 I11:I18 I20:I23 I26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b33d155f-0aa1-4aeb-8f0a-f37a20bace06}">
+          <x14:cfRule type="dataBar" id="{a1f4dccc-d946-4b9a-9b68-6190d4797408}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5499,7 +5515,7 @@
           <xm:sqref>I2 I52:I1048576 I31</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{afa3f27f-221f-4360-b2e7-39e4fedb0e99}">
+          <x14:cfRule type="dataBar" id="{1b61aaca-83ea-44ad-8ea7-0574f315436b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5510,7 +5526,7 @@
           <xm:sqref>I2:I4 I28:I38 I26 I11:I18 I9 I6:I7 I40:I1048576 I20:I23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{93e67e42-5e6b-4f4e-84a2-af56e8b47763}">
+          <x14:cfRule type="dataBar" id="{f8b8b31c-f96d-42d1-8e93-c62e7be8891b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5518,10 +5534,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I4 I28:I38 I9 I26 I6:I7 I11:I16 I40:I1048576 I18 I20:I23</xm:sqref>
+          <xm:sqref>I2:I4 I28:I38 I9 I26 I6:I7 I11:I16 I40:I1048576 I20:I23 I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6905f099-6eb3-489d-b0d1-175283691f17}">
+          <x14:cfRule type="dataBar" id="{e8ad24d4-8614-4351-a124-6d7c863227e8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5532,7 +5548,7 @@
           <xm:sqref>I12:I14 I3:I4 I50:I51 I6:I7 I18 I9 I20:I23 I26 I37:I38 I29 I32:I34 I40:I41 I43:I48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a521ca54-40d5-456f-b5db-152e77310afc}">
+          <x14:cfRule type="dataBar" id="{085014cf-1b84-4c22-838a-e5cd85a403f5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5543,7 +5559,7 @@
           <xm:sqref>I18 I3:I4 I50:I51 I6:I7 I12:I14 I9 I20:I23 I37:I38 I29 I32:I34 I40:I41 I43:I48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b05d5905-c9c2-4db6-894f-b5b967be6dca}">
+          <x14:cfRule type="dataBar" id="{d62c5a28-755d-48b4-bfcb-4acbc45cc0e8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5554,7 +5570,7 @@
           <xm:sqref>I16 I3:I4 I43:I48 I6:I7 I12:I14 I9 I20:I23 I26 I18 I50:I51 I29 I32:I34 I37:I38 I40:I41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a315770e-cfa1-4edb-923d-eca1f2edaeba}">
+          <x14:cfRule type="dataBar" id="{521a02ac-3d11-4d91-a132-60da00920526}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5565,7 +5581,7 @@
           <xm:sqref>I11:I14 I3:I4 I37:I38 I6:I7 I20:I23 I9 I16 I26 I18 I40:I41 I29:I30 I43:I51 I32:I35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ddbd8b7a-8878-437d-8154-09e6afb4b8ec}">
+          <x14:cfRule type="dataBar" id="{6ae66a5b-4736-4a18-87bc-85ad8631268b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5576,7 +5592,7 @@
           <xm:sqref>I20:I23 I3:I4 I29:I30 I6:I7 I16 I9 I11:I14 I26 I18 I50:I51 I32:I34 I37:I38 I40:I41 I43:I48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{00fee901-0269-4625-9d6a-7738e4dec67a}">
+          <x14:cfRule type="dataBar" id="{fc969919-126a-4c45-af96-85eefa8791da}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5587,7 +5603,7 @@
           <xm:sqref>I18 I20:I23 I3:I4 I40:I51 I6:I7 I26 I9 I11:I16 I28:I30 I32:I38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f1e39b4e-e540-4cd4-846a-6b12d1762b7b}">
+          <x14:cfRule type="dataBar" id="{55c90aec-be42-48c9-9a1d-34d7ae269098}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5598,7 +5614,7 @@
           <xm:sqref>I11:I16 I3:I4 I32:I38 I6:I7 I20:I23 I9 I18 I26 I40:I51 I29:I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a147da21-7c8b-4825-8051-dbc86a4bbbca}">
+          <x14:cfRule type="dataBar" id="{17d50051-15f7-4451-8f66-f9dab37b6e79}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5609,7 +5625,7 @@
           <xm:sqref>I11:I18 I3:I4 I40:I51 I6:I7 I20:I23 I9 I26 I32:I38 I28:I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{03a945b7-3341-41eb-8969-f3daa63c3c3c}">
+          <x14:cfRule type="dataBar" id="{8002b3ac-a8b8-43e8-9020-25131c57a717}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5620,7 +5636,7 @@
           <xm:sqref>I11:I18 I3:I7 I28:I30 I32:I51 I26 I20:I23 I9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{264d65c3-553f-4cec-9fde-2fea3f5889e6}">
+          <x14:cfRule type="dataBar" id="{1dc8d6e4-2b04-4017-878d-17a32f711389}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5631,7 +5647,7 @@
           <xm:sqref>I26 I20:I23 I3:I7 I32:I38 I40:I51 I11:I18 I9 I28:I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{072bcdbd-01d9-42b2-9cd5-bb64483348a0}">
+          <x14:cfRule type="dataBar" id="{6530289b-41df-4775-9c46-630bce9f8921}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/CrCraft收支与赞助鸣谢单.xlsx
+++ b/CrCraft收支与赞助鸣谢单.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="77">
   <si>
     <t>服务器收入与支出</t>
   </si>
@@ -69,13 +69,19 @@
     <t>Moquan0_0</t>
   </si>
   <si>
+    <t>Celi2357</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>MoFangYa_</t>
+  </si>
+  <si>
     <t>AL_1S_2</t>
   </si>
   <si>
-    <t>MoFangYa_</t>
-  </si>
-  <si>
-    <t>Celi2357</t>
+    <t>↓1</t>
   </si>
   <si>
     <t>BYyihan</t>
@@ -84,18 +90,12 @@
     <t>KIRINIT</t>
   </si>
   <si>
-    <t>↑1</t>
-  </si>
-  <si>
     <t>Mtve</t>
   </si>
   <si>
     <t>qmzp_</t>
   </si>
   <si>
-    <t>↓1</t>
-  </si>
-  <si>
     <t>zkiftie</t>
   </si>
   <si>
@@ -135,247 +135,127 @@
     <t>rocksuger</t>
   </si>
   <si>
+    <t>电费</t>
+  </si>
+  <si>
+    <t>SNHGY</t>
+  </si>
+  <si>
+    <t>Sz05</t>
+  </si>
+  <si>
+    <t>woshixiaoliu_ovo</t>
+  </si>
+  <si>
+    <t>10天群管理员</t>
+  </si>
+  <si>
+    <t>Y37MzZ_TrusT</t>
+  </si>
+  <si>
+    <t>cgh</t>
+  </si>
+  <si>
+    <t>匿名玩家</t>
+  </si>
+  <si>
+    <t>srdownb</t>
+  </si>
+  <si>
+    <t>Xs1st_</t>
+  </si>
+  <si>
+    <t>Alhion_WWW</t>
+  </si>
+  <si>
+    <t>chunfeng</t>
+  </si>
+  <si>
+    <t>darkmoon114514</t>
+  </si>
+  <si>
+    <t>KAMI</t>
+  </si>
+  <si>
+    <t>91kk</t>
+  </si>
+  <si>
+    <t>faxi</t>
+  </si>
+  <si>
+    <t>捐樱花映射VIP</t>
+  </si>
+  <si>
+    <t>wybhh51811</t>
+  </si>
+  <si>
+    <t>樱花映射VIP</t>
+  </si>
+  <si>
+    <t>red_chipi</t>
+  </si>
+  <si>
+    <t>Goocheu_fox</t>
+  </si>
+  <si>
+    <t>Cr_Dragon</t>
+  </si>
+  <si>
+    <t>XL12</t>
+  </si>
+  <si>
+    <t>Xiaoyingawa</t>
+  </si>
+  <si>
+    <t>hanfengzunzhe</t>
+  </si>
+  <si>
+    <t>Onion520</t>
+  </si>
+  <si>
+    <t>lhl</t>
+  </si>
+  <si>
+    <t>xhf</t>
+  </si>
+  <si>
+    <t>YuSaMa1145</t>
+  </si>
+  <si>
+    <t>Mo_Xuan_Yu</t>
+  </si>
+  <si>
+    <t>xiaomin</t>
+  </si>
+  <si>
+    <t>主板、CPU、电源、机械硬盘</t>
+  </si>
+  <si>
+    <t>A1TanJZ</t>
+  </si>
+  <si>
+    <t>littlefish1688</t>
+  </si>
+  <si>
+    <t>QSWY_MC</t>
+  </si>
+  <si>
+    <t>CHYunyou</t>
+  </si>
+  <si>
+    <t>遗物</t>
+  </si>
+  <si>
+    <t>映射VIP</t>
+  </si>
+  <si>
     <t>物品、电费</t>
   </si>
   <si>
-    <t>SNHGY</t>
-  </si>
-  <si>
-    <t>Sz05</t>
-  </si>
-  <si>
-    <t>woshixiaoliu_ovo</t>
-  </si>
-  <si>
-    <t>10天群管理员</t>
-  </si>
-  <si>
-    <t>Y37MzZ_TrusT</t>
-  </si>
-  <si>
-    <t>潜影盒、鞘翅、凋灵骷髅头颅</t>
-  </si>
-  <si>
-    <t>cgh</t>
-  </si>
-  <si>
-    <t>匿名玩家</t>
-  </si>
-  <si>
-    <t>srdownb</t>
-  </si>
-  <si>
-    <t>火药、遗物</t>
-  </si>
-  <si>
-    <t>Xs1st_</t>
-  </si>
-  <si>
-    <t>Alhion_WWW</t>
-  </si>
-  <si>
-    <t>chunfeng</t>
-  </si>
-  <si>
-    <t>darkmoon114514</t>
-  </si>
-  <si>
-    <t>KAMI</t>
-  </si>
-  <si>
-    <t>3组烟花</t>
-  </si>
-  <si>
-    <t>91kk</t>
-  </si>
-  <si>
-    <t>faxi</t>
-  </si>
-  <si>
-    <t>捐樱花映射VIP</t>
-  </si>
-  <si>
-    <t>wybhh51811</t>
-  </si>
-  <si>
-    <t>樱花映射VIP</t>
-  </si>
-  <si>
-    <t>red_chipi</t>
-  </si>
-  <si>
-    <t>↑24</t>
-  </si>
-  <si>
-    <t>5下界合金锭</t>
-  </si>
-  <si>
-    <t>Goocheu_fox</t>
-  </si>
-  <si>
-    <t>Cr_Dragon</t>
-  </si>
-  <si>
-    <t>拍卖账号</t>
-  </si>
-  <si>
-    <t>XL12</t>
-  </si>
-  <si>
-    <t>鞘翅、TP、电费、羊毛、村民、TNT</t>
-  </si>
-  <si>
-    <t>Xiaoyingawa</t>
-  </si>
-  <si>
-    <t>电费、经验</t>
-  </si>
-  <si>
-    <t>hanfengzunzhe</t>
-  </si>
-  <si>
-    <t>书架、紫珀块</t>
-  </si>
-  <si>
-    <t>Onion520</t>
-  </si>
-  <si>
-    <t>电费</t>
-  </si>
-  <si>
-    <t>lhl</t>
-  </si>
-  <si>
-    <t>10书架</t>
-  </si>
-  <si>
-    <t>xhf</t>
-  </si>
-  <si>
-    <t>YuSaMa1145</t>
-  </si>
-  <si>
-    <t>拍卖账号等</t>
-  </si>
-  <si>
-    <t>Mo_Xuan_Yu</t>
-  </si>
-  <si>
-    <t>前哨战坐标等</t>
-  </si>
-  <si>
-    <t>xiaomin</t>
-  </si>
-  <si>
-    <t>主板、CPU、电源、机械硬盘</t>
-  </si>
-  <si>
-    <t>海绵、电费、鞘翅、遗物</t>
-  </si>
-  <si>
-    <t>A1TanJZ</t>
-  </si>
-  <si>
-    <t>村民</t>
-  </si>
-  <si>
-    <t>4不详宝库</t>
-  </si>
-  <si>
-    <t>2村民蛋</t>
-  </si>
-  <si>
-    <t>littlefish1688</t>
-  </si>
-  <si>
-    <t>鞘翅、神镐</t>
-  </si>
-  <si>
-    <t>QSWY_MC</t>
-  </si>
-  <si>
-    <t>CHYunyou</t>
-  </si>
-  <si>
-    <t>电费、染料</t>
-  </si>
-  <si>
-    <t>遗物</t>
-  </si>
-  <si>
-    <t>映射VIP</t>
-  </si>
-  <si>
-    <t>村民、霰弹枪、电费、遗物</t>
-  </si>
-  <si>
-    <t>村民蛋</t>
-  </si>
-  <si>
-    <t>龙蛋</t>
-  </si>
-  <si>
-    <t>弩、电费</t>
-  </si>
-  <si>
-    <t>6村民 3僵尸</t>
-  </si>
-  <si>
-    <t>装备</t>
-  </si>
-  <si>
-    <t>拍卖</t>
-  </si>
-  <si>
-    <t>1盒沙砾、13组染料、4盒石英块</t>
-  </si>
-  <si>
     <t>750W影驰白牌80plus电源</t>
   </si>
   <si>
-    <t>重锤</t>
-  </si>
-  <si>
-    <t>4*风爆I</t>
-  </si>
-  <si>
-    <t>7盒海晶灯1盒海晶石砖台阶</t>
-  </si>
-  <si>
-    <t>3盒图腾+1鞘翅</t>
-  </si>
-  <si>
-    <t>4组烟花</t>
-  </si>
-  <si>
-    <t>幽静</t>
-  </si>
-  <si>
-    <t>鞘翅+风爆+烟花</t>
-  </si>
-  <si>
-    <t>钻石、青金石</t>
-  </si>
-  <si>
-    <t>鞘翅</t>
-  </si>
-  <si>
-    <t>经验修补、三叉戟、鞘翅、风爆</t>
-  </si>
-  <si>
-    <t>图腾、风爆、破甲</t>
-  </si>
-  <si>
-    <t>电费、遗物</t>
-  </si>
-  <si>
     <t>主板、CPU、机箱、散热</t>
-  </si>
-  <si>
-    <t>末地救援方案Pro</t>
-  </si>
-  <si>
-    <t>钻石胸甲</t>
   </si>
   <si>
     <t>电费的支出难以计算，故没有写入此表</t>
@@ -1225,7 +1105,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1335,6 +1215,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -1673,7 +1565,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K163"/>
+  <dimension ref="A1:K164"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -1760,17 +1652,20 @@
         <v>13</v>
       </c>
       <c r="I3" s="16">
-        <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150,C152,C154,C156,C159)</f>
-        <v>537</v>
+        <f>SUM(C10,C15,C18:C18,C21:C21,C24,C31:C31,C36,C43,C88,C90,C114,C162)</f>
+        <v>625.24</v>
       </c>
       <c r="J3" s="3">
-        <v>46204</v>
+        <v>46219</v>
+      </c>
+      <c r="K3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="12"/>
       <c r="B4" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="13">
         <v>0.55</v>
@@ -1781,20 +1676,23 @@
         <v>2</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="16">
-        <f>SUM(C10,C15,C18:C18,C21:C21,C24,C31:C31,C36,C43,C88,C90,C114)</f>
-        <v>504.2</v>
+        <f>SUM(C44,C49,C51:C51,C53,C58:C58,C60:C60,C63,C66:C66,C68:C68,C70,C72:C72,C77,C91,C95,C125,C127,C136,C138,C141,C148,C150,C152,C154,C156,C159)</f>
+        <v>537</v>
       </c>
       <c r="J4" s="3">
-        <v>45975</v>
+        <v>46204</v>
+      </c>
+      <c r="K4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="12"/>
       <c r="B5" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" s="13">
         <v>2</v>
@@ -1805,7 +1703,7 @@
         <v>3</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I5" s="2">
         <f>SUM(C110:C110,C113,C116,C118,C129,C134,C142,C151,C153,C158)</f>
@@ -1814,14 +1712,11 @@
       <c r="J5" s="3">
         <v>46205</v>
       </c>
-      <c r="K5" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="12"/>
       <c r="B6" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="13">
         <v>3</v>
@@ -1832,7 +1727,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I6" s="16">
         <f>SUM(C28:C28,C32:C32,C34:C34,C37,C39,C42:C42,C54,C57,C59,C61,C67,C69,C71,C76)</f>
@@ -1840,9 +1735,6 @@
       </c>
       <c r="J6" s="3">
         <v>45654</v>
-      </c>
-      <c r="K6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1932,7 +1824,7 @@
         <v>44774</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" s="13">
         <v>39</v>
@@ -2079,7 +1971,7 @@
         <v>44926</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C15" s="13">
         <v>120</v>
@@ -2134,7 +2026,7 @@
         <v>46039</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:10">
       <c r="A17" s="17">
         <v>44953</v>
       </c>
@@ -2164,12 +2056,12 @@
         <v>45930</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:10">
       <c r="A18" s="17">
         <v>44958</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18" s="13">
         <f>11+45+29</f>
@@ -2179,14 +2071,12 @@
         <f>SUM(C3:C19)</f>
         <v>-550.73</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>41</v>
-      </c>
+      <c r="E18" s="9"/>
       <c r="G18" s="15">
         <v>16</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I18" s="16">
         <f>SUM(C40,C64)</f>
@@ -2196,10 +2086,10 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:10">
       <c r="A19" s="17"/>
       <c r="B19" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C19" s="13">
         <v>1.32</v>
@@ -2210,7 +2100,7 @@
         <v>17</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I19" s="2">
         <f>SUM(C135,C139,C146)</f>
@@ -2220,7 +2110,7 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:10">
       <c r="A20" s="17">
         <v>44961</v>
       </c>
@@ -2248,12 +2138,12 @@
         <v>44953</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:10">
       <c r="A21" s="17">
         <v>45138</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C21" s="13">
         <f>6+84+10+10</f>
@@ -2263,14 +2153,12 @@
         <f>SUM(C3:C21)</f>
         <v>-428.73</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>45</v>
-      </c>
+      <c r="E21" s="9"/>
       <c r="G21" s="15">
         <v>19</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I21" s="16">
         <v>10</v>
@@ -2279,12 +2167,12 @@
         <v>45234</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:10">
       <c r="A22" s="17">
         <v>45140</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C22" s="13">
         <v>0.11</v>
@@ -2298,7 +2186,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I22" s="16">
         <v>10</v>
@@ -2307,12 +2195,12 @@
         <v>45325</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:10">
       <c r="A23" s="17">
         <v>45141</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C23" s="13">
         <v>1.01</v>
@@ -2326,7 +2214,7 @@
         <v>21</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I23" s="16">
         <v>10</v>
@@ -2335,23 +2223,21 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:10">
       <c r="A24" s="17"/>
       <c r="B24" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C24" s="13">
         <v>9</v>
       </c>
       <c r="D24" s="23"/>
-      <c r="E24" s="9" t="s">
-        <v>51</v>
-      </c>
+      <c r="E24" s="9"/>
       <c r="G24" s="15">
         <v>22</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I24" s="2">
         <v>10</v>
@@ -2360,7 +2246,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:10">
       <c r="A25" s="17">
         <v>45160</v>
       </c>
@@ -2379,7 +2265,7 @@
         <v>23</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I25" s="16">
         <v>10</v>
@@ -2388,12 +2274,12 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:10">
       <c r="A26" s="17">
         <v>45234</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C26" s="13">
         <v>10</v>
@@ -2403,13 +2289,13 @@
         <v>-415.61</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G26">
         <v>24</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I26" s="2">
         <v>8</v>
@@ -2418,7 +2304,7 @@
         <v>45860</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:10">
       <c r="A27" s="17"/>
       <c r="B27" s="8"/>
       <c r="C27" s="18">
@@ -2426,13 +2312,13 @@
       </c>
       <c r="D27" s="23"/>
       <c r="E27" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G27">
         <v>25</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I27" s="2">
         <v>8</v>
@@ -2440,16 +2326,13 @@
       <c r="J27" s="3">
         <v>46205</v>
       </c>
-      <c r="K27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="17">
         <v>45249</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C28" s="13">
         <v>15.5</v>
@@ -2458,14 +2341,12 @@
         <f>SUM(C3:C28)</f>
         <v>-400.11</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>59</v>
-      </c>
+      <c r="E28" s="9"/>
       <c r="G28">
         <v>26</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I28" s="2">
         <v>7.33</v>
@@ -2473,11 +2354,8 @@
       <c r="J28" s="3">
         <v>45907</v>
       </c>
-      <c r="K28" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="17">
         <v>45305</v>
       </c>
@@ -2496,7 +2374,7 @@
         <v>27</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I29" s="16">
         <f>SUM(C82,C84,C94)</f>
@@ -2505,16 +2383,13 @@
       <c r="J29" s="3">
         <v>45861</v>
       </c>
-      <c r="K29" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="17">
         <v>45325</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C30" s="13">
         <v>10</v>
@@ -2523,14 +2398,12 @@
         <f>SUM(C3:C30)</f>
         <v>-340.11</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>62</v>
-      </c>
+      <c r="E30" s="9"/>
       <c r="G30">
         <v>28</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="I30" s="2">
         <v>6</v>
@@ -2538,16 +2411,13 @@
       <c r="J30" s="3">
         <v>45868</v>
       </c>
-      <c r="K30" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="17">
         <v>45341</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C31" s="13">
         <v>68</v>
@@ -2556,14 +2426,12 @@
         <f>SUM(C3:C31)</f>
         <v>-272.11</v>
       </c>
-      <c r="E31" s="9" t="s">
-        <v>64</v>
-      </c>
+      <c r="E31" s="9"/>
       <c r="G31">
         <v>29</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="I31" s="2">
         <v>5.04</v>
@@ -2571,16 +2439,13 @@
       <c r="J31" s="3">
         <v>46160</v>
       </c>
-      <c r="K31" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="17">
         <v>45368</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C32" s="13">
         <v>33.01</v>
@@ -2590,7 +2455,7 @@
         <v>-239.1</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="G32">
         <v>30</v>
@@ -2604,16 +2469,13 @@
       <c r="J32" s="3">
         <v>44787</v>
       </c>
-      <c r="K32" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="17">
         <v>45387</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C33" s="13">
         <v>1.38</v>
@@ -2622,14 +2484,12 @@
         <f>SUM(C3:C33)</f>
         <v>-237.72</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>68</v>
-      </c>
+      <c r="E33" s="9"/>
       <c r="G33">
         <v>31</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="I33" s="16">
         <v>5</v>
@@ -2637,16 +2497,13 @@
       <c r="J33" s="3">
         <v>45634</v>
       </c>
-      <c r="K33" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="17">
         <v>45394</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C34" s="13">
         <v>16</v>
@@ -2656,13 +2513,13 @@
         <v>-221.72</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G34">
         <v>32</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="I34" s="16">
         <v>4.15</v>
@@ -2670,16 +2527,13 @@
       <c r="J34" s="3">
         <v>45707</v>
       </c>
-      <c r="K34" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="17">
         <v>45396</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C35" s="13">
         <v>0.8</v>
@@ -2688,14 +2542,12 @@
         <f>SUM(C3:C35)</f>
         <v>-220.92</v>
       </c>
-      <c r="E35" s="9" t="s">
-        <v>72</v>
-      </c>
+      <c r="E35" s="9"/>
       <c r="G35">
         <v>33</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="I35" s="2">
         <v>4</v>
@@ -2703,16 +2555,13 @@
       <c r="J35" s="3">
         <v>45885</v>
       </c>
-      <c r="K35" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="17">
         <v>45403</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C36" s="13">
         <v>3.2</v>
@@ -2726,7 +2575,7 @@
         <v>34</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="I36" s="2">
         <f>SUM(C100,C108)</f>
@@ -2735,16 +2584,13 @@
       <c r="J36" s="3">
         <v>45934</v>
       </c>
-      <c r="K36" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="17">
         <v>45403</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C37" s="13">
         <v>5</v>
@@ -2754,13 +2600,13 @@
         <v>-212.72</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G37">
         <v>35</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I37" s="16">
         <v>3</v>
@@ -2768,11 +2614,8 @@
       <c r="J37" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K37" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="17">
         <v>45412</v>
       </c>
@@ -2786,14 +2629,12 @@
         <f>SUM(C3:C38)</f>
         <v>-205.72</v>
       </c>
-      <c r="E38" s="9" t="s">
-        <v>75</v>
-      </c>
+      <c r="E38" s="9"/>
       <c r="G38" s="15">
         <v>36</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="I38" s="16">
         <v>3</v>
@@ -2801,16 +2642,13 @@
       <c r="J38" s="3">
         <v>45500</v>
       </c>
-      <c r="K38" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="17">
         <v>45417</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C39" s="13">
         <v>11</v>
@@ -2819,14 +2657,12 @@
         <f>SUM(C3:C39)</f>
         <v>-194.72</v>
       </c>
-      <c r="E39" s="9" t="s">
-        <v>77</v>
-      </c>
+      <c r="E39" s="9"/>
       <c r="G39" s="15">
         <v>37</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="I39" s="2">
         <v>2.5</v>
@@ -2834,16 +2670,13 @@
       <c r="J39" s="3">
         <v>45976</v>
       </c>
-      <c r="K39" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="17">
         <v>45421</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40" s="13">
         <v>5</v>
@@ -2853,13 +2686,13 @@
         <v>-189.72</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G40" s="15">
         <v>38</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="I40" s="16">
         <f>SUM(C35,C33:C33)</f>
@@ -2868,11 +2701,8 @@
       <c r="J40" s="3">
         <v>45396</v>
       </c>
-      <c r="K40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="17">
         <v>45478</v>
       </c>
@@ -2886,13 +2716,13 @@
         <v>-1999.72</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="G41">
         <v>39</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I41" s="16">
         <v>2</v>
@@ -2900,16 +2730,13 @@
       <c r="J41" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K41" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="17">
         <v>45494</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C42" s="13">
         <v>82.45</v>
@@ -2919,13 +2746,13 @@
         <v>-1915.27</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="G42" s="15">
         <v>40</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="I42" s="2">
         <v>2</v>
@@ -2933,27 +2760,22 @@
       <c r="J42" s="3">
         <v>45907</v>
       </c>
-      <c r="K42" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="17"/>
       <c r="B43" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C43" s="13">
         <v>2</v>
       </c>
       <c r="D43" s="23"/>
-      <c r="E43" s="9" t="s">
-        <v>82</v>
-      </c>
+      <c r="E43" s="9"/>
       <c r="G43">
         <v>41</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I43" s="16">
         <v>1.32</v>
@@ -2961,16 +2783,13 @@
       <c r="J43" s="3">
         <v>44958</v>
       </c>
-      <c r="K43" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="25">
         <v>45495</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C44" s="27">
         <v>8</v>
@@ -2979,9 +2798,7 @@
         <f>SUM(C3:C44)</f>
         <v>-1907.27</v>
       </c>
-      <c r="E44" s="28" t="s">
-        <v>83</v>
-      </c>
+      <c r="E44" s="28"/>
       <c r="G44">
         <v>42</v>
       </c>
@@ -2994,11 +2811,8 @@
       <c r="J44" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K44" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="25">
         <v>45496</v>
       </c>
@@ -3017,7 +2831,7 @@
         <v>43</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I45" s="16">
         <v>1.01</v>
@@ -3025,11 +2839,8 @@
       <c r="J45" s="3">
         <v>45141</v>
       </c>
-      <c r="K45" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" s="29"/>
       <c r="B46" s="26" t="s">
         <v>34</v>
@@ -3038,14 +2849,12 @@
         <v>3</v>
       </c>
       <c r="D46" s="30"/>
-      <c r="E46" s="28" t="s">
-        <v>84</v>
-      </c>
+      <c r="E46" s="28"/>
       <c r="G46">
         <v>44</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="I46" s="16">
         <v>1</v>
@@ -3053,11 +2862,8 @@
       <c r="J46" s="3">
         <v>45794</v>
       </c>
-      <c r="K46" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" s="17">
         <v>45497</v>
       </c>
@@ -3071,14 +2877,12 @@
         <f>SUM(C3:C47)</f>
         <v>-1874.27</v>
       </c>
-      <c r="E47" s="28" t="s">
-        <v>86</v>
-      </c>
+      <c r="E47" s="28"/>
       <c r="G47">
         <v>45</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I47" s="16">
         <v>0.55</v>
@@ -3086,16 +2890,13 @@
       <c r="J47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K47" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" s="25">
         <v>45500</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C48" s="27">
         <v>3</v>
@@ -3109,7 +2910,7 @@
         <v>46</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="I48" s="16">
         <v>0.5</v>
@@ -3117,27 +2918,24 @@
       <c r="J48" s="3">
         <v>45697</v>
       </c>
-      <c r="K48" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="31"/>
       <c r="B49" s="26" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C49" s="27">
         <v>5</v>
       </c>
       <c r="D49" s="30"/>
       <c r="E49" s="28" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G49">
         <v>47</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="I49" s="2">
         <v>0.5</v>
@@ -3145,11 +2943,8 @@
       <c r="J49" s="3">
         <v>45885</v>
       </c>
-      <c r="K49" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="25">
         <v>45505</v>
       </c>
@@ -3164,13 +2959,13 @@
         <v>-1856.27</v>
       </c>
       <c r="E50" s="28" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="G50">
         <v>48</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I50" s="16">
         <v>0.11</v>
@@ -3178,16 +2973,13 @@
       <c r="J50" s="3">
         <v>45140</v>
       </c>
-      <c r="K50" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" s="25">
         <v>45507</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C51" s="27">
         <v>14</v>
@@ -3197,7 +2989,7 @@
         <v>-1756.27</v>
       </c>
       <c r="E51" s="28" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G51">
         <v>49</v>
@@ -3211,11 +3003,8 @@
       <c r="J51" s="3">
         <v>44213</v>
       </c>
-      <c r="K51" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" s="31"/>
       <c r="B52" s="26" t="s">
         <v>27</v>
@@ -3225,15 +3014,15 @@
       </c>
       <c r="D52" s="30"/>
       <c r="E52" s="28" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="25">
         <v>45508</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C53" s="27">
         <v>9</v>
@@ -3243,13 +3032,13 @@
         <v>-1737.27</v>
       </c>
       <c r="E53" s="28" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" s="31"/>
       <c r="B54" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C54" s="27">
         <v>10</v>
@@ -3257,7 +3046,7 @@
       <c r="D54" s="30"/>
       <c r="E54" s="28"/>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:10">
       <c r="A55" s="25">
         <v>45509</v>
       </c>
@@ -3270,10 +3059,10 @@
         <v>-1737.27</v>
       </c>
       <c r="E55" s="28" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" s="31"/>
       <c r="B56" s="26" t="s">
         <v>34</v>
@@ -3284,12 +3073,12 @@
       <c r="D56" s="30"/>
       <c r="E56" s="28"/>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:10">
       <c r="A57" s="25">
         <v>45510</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C57" s="27">
         <v>40</v>
@@ -3298,16 +3087,14 @@
         <f>SUM(C3:C57)</f>
         <v>-1697.27</v>
       </c>
-      <c r="E57" s="28" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
+      <c r="E57" s="28"/>
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58" s="25">
         <v>45525</v>
       </c>
       <c r="B58" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C58" s="27">
         <f>6+5+5+5+6+5+5+5+30</f>
@@ -3318,15 +3105,15 @@
         <v>-1625.27</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" s="25">
         <v>45525</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C59" s="27">
         <v>6</v>
@@ -3335,16 +3122,14 @@
         <f>SUM(C3:C59)</f>
         <v>-1619.27</v>
       </c>
-      <c r="E59" s="28" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+      <c r="E59" s="28"/>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60" s="25">
         <v>45549</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C60" s="27">
         <v>30</v>
@@ -3354,23 +3139,21 @@
         <v>-1569.27</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" s="29"/>
       <c r="B61" s="33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C61" s="27">
         <v>20</v>
       </c>
       <c r="D61" s="30"/>
-      <c r="E61" s="28" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+      <c r="E61" s="28"/>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" s="31">
         <v>45551</v>
       </c>
@@ -3386,12 +3169,12 @@
       </c>
       <c r="E62" s="28"/>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:10">
       <c r="A63" s="25">
         <v>45552</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C63" s="27">
         <v>40</v>
@@ -3402,12 +3185,12 @@
       </c>
       <c r="E63" s="28"/>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:10">
       <c r="A64" s="25">
         <v>45555</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C64" s="27">
         <v>6</v>
@@ -3427,16 +3210,14 @@
         <v>20</v>
       </c>
       <c r="D65" s="30"/>
-      <c r="E65" s="28" t="s">
-        <v>94</v>
-      </c>
+      <c r="E65" s="28"/>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="25">
         <v>45584</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C66" s="27">
         <v>30</v>
@@ -3446,7 +3227,7 @@
         <v>-1456.27</v>
       </c>
       <c r="E66" s="28" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3454,7 +3235,7 @@
         <v>45584</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C67" s="27">
         <v>7</v>
@@ -3470,7 +3251,7 @@
         <v>45592</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C68" s="27">
         <v>60</v>
@@ -3480,7 +3261,7 @@
         <v>-1389.27</v>
       </c>
       <c r="E68" s="28" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3488,7 +3269,7 @@
         <v>45597</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C69" s="27">
         <v>5</v>
@@ -3498,7 +3279,7 @@
         <v>-1384.27</v>
       </c>
       <c r="E69" s="28" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3506,7 +3287,7 @@
         <v>45598</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C70" s="27">
         <v>5</v>
@@ -3516,7 +3297,7 @@
         <v>-1379.27</v>
       </c>
       <c r="E70" s="28" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3524,7 +3305,7 @@
         <v>45612</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C71" s="27">
         <v>5</v>
@@ -3540,7 +3321,7 @@
         <v>45619</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C72" s="27">
         <v>15</v>
@@ -3550,7 +3331,7 @@
         <v>-1359.27</v>
       </c>
       <c r="E72" s="28" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -3558,7 +3339,7 @@
         <v>45634</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C73" s="27">
         <v>5</v>
@@ -3568,7 +3349,7 @@
         <v>-1344.27</v>
       </c>
       <c r="E73" s="28" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -3580,16 +3361,14 @@
         <v>10</v>
       </c>
       <c r="D74" s="30"/>
-      <c r="E74" s="28" t="s">
-        <v>96</v>
-      </c>
+      <c r="E74" s="28"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="17">
         <v>45649</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C75" s="27">
         <v>10</v>
@@ -3605,7 +3384,7 @@
         <v>45654</v>
       </c>
       <c r="B76" s="33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C76" s="27">
         <v>30</v>
@@ -3614,16 +3393,14 @@
         <f>SUM(C3:C76)</f>
         <v>-1304.27</v>
       </c>
-      <c r="E76" s="28" t="s">
-        <v>97</v>
-      </c>
+      <c r="E76" s="28"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="25">
         <v>45686</v>
       </c>
       <c r="B77" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C77" s="27">
         <v>9</v>
@@ -3633,7 +3410,7 @@
         <v>-1295.27</v>
       </c>
       <c r="E77" s="28" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3641,7 +3418,7 @@
         <v>45697</v>
       </c>
       <c r="B78" s="33" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="C78" s="27">
         <v>0.5</v>
@@ -3657,7 +3434,7 @@
         <v>45707</v>
       </c>
       <c r="B79" s="33" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C79" s="27">
         <v>4.15</v>
@@ -3673,7 +3450,7 @@
         <v>45794</v>
       </c>
       <c r="B80" s="33" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C80" s="27">
         <v>1</v>
@@ -3705,7 +3482,7 @@
         <v>45844</v>
       </c>
       <c r="B82" s="33" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C82" s="27">
         <v>2.48</v>
@@ -3721,7 +3498,7 @@
         <v>45860</v>
       </c>
       <c r="B83" s="33" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C83" s="27">
         <v>8</v>
@@ -3737,7 +3514,7 @@
         <v>45861</v>
       </c>
       <c r="B84" s="33" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C84" s="27">
         <v>0.5</v>
@@ -3785,7 +3562,7 @@
         <v>45868</v>
       </c>
       <c r="B87" s="33" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C87" s="27">
         <v>6</v>
@@ -3794,16 +3571,14 @@
         <f>SUM(C3:C87)</f>
         <v>-1237.97</v>
       </c>
-      <c r="E87" s="28" t="s">
-        <v>98</v>
-      </c>
+      <c r="E87" s="28"/>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="25">
         <v>45877</v>
       </c>
       <c r="B88" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C88" s="27">
         <v>5</v>
@@ -3813,7 +3588,7 @@
         <v>-1232.97</v>
       </c>
       <c r="E88" s="28" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -3837,7 +3612,7 @@
         <v>45879</v>
       </c>
       <c r="B90" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C90" s="27">
         <v>26</v>
@@ -3846,16 +3621,14 @@
         <f>SUM(C3:C90)</f>
         <v>-1206.96</v>
       </c>
-      <c r="E90" s="34" t="s">
-        <v>99</v>
-      </c>
+      <c r="E90" s="34"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="25">
         <v>45881</v>
       </c>
       <c r="B91" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C91" s="27">
         <v>5</v>
@@ -3865,7 +3638,7 @@
         <v>-1201.96</v>
       </c>
       <c r="E91" s="34" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -3873,7 +3646,7 @@
         <v>45885</v>
       </c>
       <c r="B92" s="33" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C92" s="27">
         <v>0.5</v>
@@ -3887,7 +3660,7 @@
     <row r="93" spans="1:5">
       <c r="A93" s="17"/>
       <c r="B93" s="33" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C93" s="27">
         <v>6</v>
@@ -3898,7 +3671,7 @@
     <row r="94" spans="1:5">
       <c r="A94" s="17"/>
       <c r="B94" s="33" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C94" s="27">
         <v>4</v>
@@ -3911,7 +3684,7 @@
         <v>45886</v>
       </c>
       <c r="B95" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C95" s="27">
         <v>5</v>
@@ -3921,7 +3694,7 @@
         <v>-1186.46</v>
       </c>
       <c r="E95" s="34" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -3945,7 +3718,7 @@
         <v>45905</v>
       </c>
       <c r="B97" s="33" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C97" s="27">
         <v>7.33</v>
@@ -3986,7 +3759,7 @@
     <row r="100" spans="1:5">
       <c r="A100" s="31"/>
       <c r="B100" s="33" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C100" s="27">
         <v>2</v>
@@ -4008,7 +3781,7 @@
     <row r="102" spans="1:5">
       <c r="A102" s="31"/>
       <c r="B102" s="33" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C102" s="27">
         <v>2</v>
@@ -4029,7 +3802,7 @@
         <v>-1298.13</v>
       </c>
       <c r="E103" s="34" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -4047,7 +3820,7 @@
         <v>-1292.13</v>
       </c>
       <c r="E104" s="34" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -4101,7 +3874,7 @@
     <row r="108" spans="1:5">
       <c r="A108" s="31"/>
       <c r="B108" s="33" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C108" s="27">
         <v>2</v>
@@ -4131,7 +3904,7 @@
         <v>45965</v>
       </c>
       <c r="B110" s="33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C110" s="27">
         <v>60</v>
@@ -4140,9 +3913,7 @@
         <f>SUM(C3:C110)</f>
         <v>-1202.68</v>
       </c>
-      <c r="E110" s="34" t="s">
-        <v>101</v>
-      </c>
+      <c r="E110" s="34"/>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="25">
@@ -4181,7 +3952,7 @@
         <v>45972</v>
       </c>
       <c r="B113" s="33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C113" s="27">
         <v>60</v>
@@ -4190,16 +3961,14 @@
         <f>SUM(C3:C113)</f>
         <v>-1131.68</v>
       </c>
-      <c r="E113" s="34" t="s">
-        <v>102</v>
-      </c>
+      <c r="E113" s="34"/>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="25">
         <v>45975</v>
       </c>
       <c r="B114" s="33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C114" s="27">
         <v>37</v>
@@ -4208,16 +3977,14 @@
         <f>SUM(C3:C114)</f>
         <v>-1094.68</v>
       </c>
-      <c r="E114" s="34" t="s">
-        <v>103</v>
-      </c>
+      <c r="E114" s="34"/>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="25">
         <v>45976</v>
       </c>
       <c r="B115" s="33" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C115" s="27">
         <v>2.5</v>
@@ -4233,7 +4000,7 @@
         <v>45980</v>
       </c>
       <c r="B116" s="33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C116" s="27">
         <v>20</v>
@@ -4242,9 +4009,7 @@
         <f>SUM(C3:C116)</f>
         <v>-1072.18</v>
       </c>
-      <c r="E116" s="34" t="s">
-        <v>104</v>
-      </c>
+      <c r="E116" s="34"/>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="25">
@@ -4260,16 +4025,14 @@
         <f>SUM(C3:C117)</f>
         <v>-1071.18</v>
       </c>
-      <c r="E117" s="34" t="s">
-        <v>105</v>
-      </c>
+      <c r="E117" s="34"/>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="25">
         <v>46012</v>
       </c>
       <c r="B118" s="33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C118" s="27">
         <v>10</v>
@@ -4294,9 +4057,7 @@
         <f>SUM(C3:C119)</f>
         <v>-1045.18</v>
       </c>
-      <c r="E119" s="34" t="s">
-        <v>106</v>
-      </c>
+      <c r="E119" s="34"/>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="25">
@@ -4328,9 +4089,7 @@
         <f>SUM(C3:C121)</f>
         <v>-977.18</v>
       </c>
-      <c r="E121" s="34" t="s">
-        <v>107</v>
-      </c>
+      <c r="E121" s="34"/>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="25">
@@ -4362,9 +4121,7 @@
         <f>SUM(C3:C123)</f>
         <v>-969.18</v>
       </c>
-      <c r="E123" s="34" t="s">
-        <v>108</v>
-      </c>
+      <c r="E123" s="34"/>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="31"/>
@@ -4385,7 +4142,7 @@
         <v>46054</v>
       </c>
       <c r="B125" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C125" s="27">
         <v>5</v>
@@ -4395,7 +4152,7 @@
         <v>-953.18</v>
       </c>
       <c r="E125" s="34" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -4412,16 +4169,14 @@
         <f>SUM(C3:C126)</f>
         <v>-917.18</v>
       </c>
-      <c r="E126" s="34" t="s">
-        <v>109</v>
-      </c>
+      <c r="E126" s="34"/>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="25">
         <v>46057</v>
       </c>
       <c r="B127" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C127" s="27">
         <v>5</v>
@@ -4431,7 +4186,7 @@
         <v>-912.18</v>
       </c>
       <c r="E127" s="34" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -4448,14 +4203,12 @@
         <f>SUM(C3:C128)</f>
         <v>-834.18</v>
       </c>
-      <c r="E128" s="34" t="s">
-        <v>110</v>
-      </c>
+      <c r="E128" s="34"/>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="36"/>
       <c r="B129" s="33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C129" s="27">
         <v>30</v>
@@ -4464,9 +4217,7 @@
         <f>SUM(C3:C129)</f>
         <v>-804.18</v>
       </c>
-      <c r="E129" s="34" t="s">
-        <v>111</v>
-      </c>
+      <c r="E129" s="34"/>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="25">
@@ -4496,14 +4247,12 @@
         <f>SUM(C3:C131)</f>
         <v>-791.18</v>
       </c>
-      <c r="E131" s="34" t="s">
-        <v>82</v>
-      </c>
+      <c r="E131" s="34"/>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="31"/>
       <c r="B132" s="33" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C132" s="27">
         <v>10</v>
@@ -4533,7 +4282,7 @@
     <row r="134" spans="1:5">
       <c r="A134" s="31"/>
       <c r="B134" s="33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C134" s="27">
         <v>10</v>
@@ -4549,7 +4298,7 @@
         <v>46074</v>
       </c>
       <c r="B135" s="33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C135" s="27">
         <v>1.5</v>
@@ -4565,7 +4314,7 @@
         <v>46079</v>
       </c>
       <c r="B136" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C136" s="27">
         <v>25</v>
@@ -4575,7 +4324,7 @@
         <v>-736.36</v>
       </c>
       <c r="E136" s="34" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -4599,7 +4348,7 @@
         <v>46123</v>
       </c>
       <c r="B138" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C138" s="27">
         <v>70</v>
@@ -4609,7 +4358,7 @@
         <v>-656.36</v>
       </c>
       <c r="E138" s="34" t="s">
-        <v>112</v>
+        <v>35</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -4617,7 +4366,7 @@
         <v>46130</v>
       </c>
       <c r="B139" s="33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C139" s="27">
         <v>3</v>
@@ -4641,7 +4390,7 @@
         <v>-3151.15</v>
       </c>
       <c r="E140" s="34" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -4649,7 +4398,7 @@
         <v>46136</v>
       </c>
       <c r="B141" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C141" s="27">
         <v>15</v>
@@ -4659,7 +4408,7 @@
         <v>-3136.15</v>
       </c>
       <c r="E141" s="34" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -4667,7 +4416,7 @@
         <v>46141</v>
       </c>
       <c r="B142" s="33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C142" s="27">
         <v>10</v>
@@ -4713,7 +4462,7 @@
         <v>46145</v>
       </c>
       <c r="B145" s="33" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C145" s="27">
         <v>10</v>
@@ -4722,14 +4471,12 @@
         <f>SUM(C3:C145)</f>
         <v>-3105.15</v>
       </c>
-      <c r="E145" s="34" t="s">
-        <v>114</v>
-      </c>
+      <c r="E145" s="34"/>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="31"/>
       <c r="B146" s="33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C146" s="27">
         <v>6</v>
@@ -4761,7 +4508,7 @@
         <v>46158</v>
       </c>
       <c r="B148" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C148" s="27">
         <v>20</v>
@@ -4771,7 +4518,7 @@
         <v>-3059.15</v>
       </c>
       <c r="E148" s="34" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -4779,7 +4526,7 @@
         <v>46160</v>
       </c>
       <c r="B149" s="33" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C149" s="27">
         <v>5.04</v>
@@ -4795,7 +4542,7 @@
         <v>46179</v>
       </c>
       <c r="B150" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C150" s="27">
         <v>30</v>
@@ -4805,7 +4552,7 @@
         <v>-3024.11</v>
       </c>
       <c r="E150" s="34" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -4813,7 +4560,7 @@
         <v>46184</v>
       </c>
       <c r="B151" s="33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C151" s="27">
         <v>10</v>
@@ -4829,7 +4576,7 @@
         <v>46192</v>
       </c>
       <c r="B152" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C152" s="27">
         <v>20</v>
@@ -4839,7 +4586,7 @@
         <v>-2994.11</v>
       </c>
       <c r="E152" s="34" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -4847,7 +4594,7 @@
         <v>46193</v>
       </c>
       <c r="B153" s="33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C153" s="27">
         <v>50</v>
@@ -4861,7 +4608,7 @@
     <row r="154" spans="1:5">
       <c r="A154" s="31"/>
       <c r="B154" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C154" s="27">
         <v>10</v>
@@ -4871,7 +4618,7 @@
         <v>-2934.11</v>
       </c>
       <c r="E154" s="34" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -4888,16 +4635,14 @@
         <f>SUM(C3:C155)</f>
         <v>-2909.11</v>
       </c>
-      <c r="E155" s="34" t="s">
-        <v>109</v>
-      </c>
+      <c r="E155" s="34"/>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="25">
         <v>46204</v>
       </c>
       <c r="B156" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C156" s="27">
         <v>20</v>
@@ -4907,7 +4652,7 @@
         <v>-2889.11</v>
       </c>
       <c r="E156" s="34" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -4915,7 +4660,7 @@
         <v>46205</v>
       </c>
       <c r="B157" s="33" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C157" s="27">
         <v>8</v>
@@ -4924,14 +4669,12 @@
         <f>SUM(C3:C157)</f>
         <v>-2881.11</v>
       </c>
-      <c r="E157" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="E157" s="34"/>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="31"/>
       <c r="B158" s="33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C158" s="27">
         <v>240</v>
@@ -4945,7 +4688,7 @@
     <row r="159" spans="1:5">
       <c r="A159" s="31"/>
       <c r="B159" s="33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C159" s="27">
         <v>10</v>
@@ -4955,7 +4698,7 @@
         <v>-2631.11</v>
       </c>
       <c r="E159" s="34" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -4973,7 +4716,7 @@
         <v>-2626.11</v>
       </c>
       <c r="E160" s="34" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -4992,27 +4735,43 @@
       </c>
       <c r="E161" s="34"/>
     </row>
-    <row r="162" ht="14.25" spans="1:5">
-      <c r="A162" s="37"/>
-      <c r="B162" s="38"/>
-      <c r="C162" s="39"/>
-      <c r="D162" s="39"/>
+    <row r="162" spans="1:5">
+      <c r="A162" s="37">
+        <v>46219</v>
+      </c>
+      <c r="B162" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C162" s="39">
+        <v>121.04</v>
+      </c>
+      <c r="D162" s="21">
+        <f>SUM(C3:C162)</f>
+        <v>-2472.07</v>
+      </c>
       <c r="E162" s="40"/>
     </row>
-    <row r="163" spans="1:5">
-      <c r="A163" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="B163" s="41"/>
-      <c r="C163" s="41"/>
-      <c r="D163" s="41"/>
-      <c r="E163" s="41"/>
+    <row r="163" ht="14.25" spans="1:5">
+      <c r="A163" s="41"/>
+      <c r="B163" s="42"/>
+      <c r="C163" s="43"/>
+      <c r="D163" s="43"/>
+      <c r="E163" s="44"/>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="45" t="s">
+        <v>76</v>
+      </c>
+      <c r="B164" s="45"/>
+      <c r="C164" s="45"/>
+      <c r="D164" s="45"/>
+      <c r="E164" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A163:E163"/>
+    <mergeCell ref="A164:E164"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A23:A24"/>
@@ -5062,7 +4821,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dda28aed-6bab-4d98-b172-9310ed1317e6}</x14:id>
+          <x14:id>{0516d668-bde6-4820-9c21-bd9bfe863a0b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5076,12 +4835,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{41a5e2b1-2edc-4d68-a131-5d85c7b12d5b}</x14:id>
+          <x14:id>{f9af9851-3b3f-4134-b8de-49494a92d3d3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D162 D164:D1048576">
+  <conditionalFormatting sqref="D1:D18 D20:D23 D25:D26 D28:D42 D44:D45 D47:D48 D50:D51 D53 D55 D57:D60 D62:D64 D66:D73 D75:D92 D95:D98 D103:D163 D165:D1048576">
     <cfRule type="colorScale" priority="81">
       <colorScale>
         <cfvo type="min"/>
@@ -5102,7 +4861,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{379cd7c2-ea14-4e26-92d4-43b8b1501090}</x14:id>
+          <x14:id>{d8c93784-4d59-402c-bd64-0ae50c373c64}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5116,7 +4875,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6f2b8e67-1bee-4d6f-8afa-aa05396ac993}</x14:id>
+          <x14:id>{c6782148-85aa-4485-ac94-2bb6567ca129}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5130,12 +4889,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d1d4e2aa-e34d-4c30-a599-78e4ec12c99b}</x14:id>
+          <x14:id>{1f04ca4b-f0e5-4ce8-82e6-d45a7293206e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I18 I26 I28:I1048576 I20:I24">
+  <conditionalFormatting sqref="I1:I18 I28:I1048576 I20:I24 I26">
     <cfRule type="dataBar" priority="22">
       <dataBar>
         <cfvo type="min"/>
@@ -5144,12 +4903,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2eebbc89-811f-4b74-b357-9ce3b4b5a7f6}</x14:id>
+          <x14:id>{580211c7-d112-48e0-b9ff-a7e120b3cd1e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I9 I28:I1048576 I11:I18 I20:I24 I26">
+  <conditionalFormatting sqref="I1:I9 I20:I24 I11:I18 I28:I1048576 I26">
     <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="min"/>
@@ -5158,12 +4917,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e5fe87ac-32ec-4bc5-b64a-300233a562fd}</x14:id>
+          <x14:id>{5a4de853-09f0-4ccd-ab01-c5117ab4fa1e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I9 I28:I1048576 I11:I18 I20:I23 I26">
+  <conditionalFormatting sqref="I1:I9 I20:I23 I11:I18 I28:I1048576 I26">
     <cfRule type="dataBar" priority="24">
       <dataBar>
         <cfvo type="min"/>
@@ -5172,7 +4931,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{23c28805-668f-4e18-9773-e879fdb4fb3a}</x14:id>
+          <x14:id>{a7117f6a-d99b-4cb0-9716-f960ad6ce4cc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5186,12 +4945,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a1f4dccc-d946-4b9a-9b68-6190d4797408}</x14:id>
+          <x14:id>{47aea96c-dd5e-4001-99bd-35c4d627f457}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4 I28:I38 I26 I11:I18 I9 I6:I7 I40:I1048576 I20:I23">
+  <conditionalFormatting sqref="I2:I4 I20:I23 I28:I38 I26 I11:I18 I9 I6:I7 I40:I1048576">
     <cfRule type="dataBar" priority="27">
       <dataBar>
         <cfvo type="min"/>
@@ -5200,12 +4959,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1b61aaca-83ea-44ad-8ea7-0574f315436b}</x14:id>
+          <x14:id>{cf5ce95e-bb0a-4cbd-9e21-64ebd53e1e9c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4 I28:I38 I9 I26 I6:I7 I11:I16 I40:I1048576 I20:I23 I18">
+  <conditionalFormatting sqref="I2:I4 I20:I23 I28:I38 I9 I26 I6:I7 I11:I16 I40:I1048576 I18">
     <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
@@ -5214,7 +4973,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f8b8b31c-f96d-42d1-8e93-c62e7be8891b}</x14:id>
+          <x14:id>{379edc11-7862-47d4-9e53-f459d953d005}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5251,7 +5010,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I12:I14 I3:I4 I50:I51 I6:I7 I18 I9 I20:I23 I26 I37:I38 I29 I32:I34 I40:I41 I43:I48">
+  <conditionalFormatting sqref="I12:I14 I3:I4 I43:I48 I50:I51 I6:I7 I18 I9 I20:I23 I26 I37:I38 I29 I32:I34 I40:I41">
     <cfRule type="dataBar" priority="37">
       <dataBar>
         <cfvo type="min"/>
@@ -5260,12 +5019,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e8ad24d4-8614-4351-a124-6d7c863227e8}</x14:id>
+          <x14:id>{b940c2a0-92a9-4e3b-a50c-1071151a728e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I18 I3:I4 I50:I51 I6:I7 I12:I14 I9 I20:I23 I37:I38 I29 I32:I34 I40:I41 I43:I48">
+  <conditionalFormatting sqref="I18 I3:I4 I43:I48 I50:I51 I6:I7 I12:I14 I9 I20:I23 I37:I38 I29 I32:I34 I40:I41">
     <cfRule type="dataBar" priority="38">
       <dataBar>
         <cfvo type="min"/>
@@ -5274,12 +5033,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{085014cf-1b84-4c22-838a-e5cd85a403f5}</x14:id>
+          <x14:id>{401edcdf-43ae-4b44-99c5-0e95810b949c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I16 I3:I4 I43:I48 I6:I7 I12:I14 I9 I20:I23 I26 I18 I50:I51 I29 I32:I34 I37:I38 I40:I41">
+  <conditionalFormatting sqref="I16 I3:I4 I40:I41 I43:I48 I6:I7 I12:I14 I9 I20:I23 I26 I18 I50:I51 I29 I32:I34 I37:I38">
     <cfRule type="dataBar" priority="35">
       <dataBar>
         <cfvo type="min"/>
@@ -5288,12 +5047,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d62c5a28-755d-48b4-bfcb-4acbc45cc0e8}</x14:id>
+          <x14:id>{523fecbb-3adb-4d79-a75b-8b4a50bc759a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I14 I3:I4 I37:I38 I6:I7 I20:I23 I9 I16 I26 I18 I40:I41 I29:I30 I43:I51 I32:I35">
+  <conditionalFormatting sqref="I11:I14 I3:I4 I32:I35 I37:I38 I6:I7 I20:I23 I9 I16 I26 I18 I40:I41 I29:I30 I43:I51">
     <cfRule type="dataBar" priority="33">
       <dataBar>
         <cfvo type="min"/>
@@ -5302,12 +5061,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{521a02ac-3d11-4d91-a132-60da00920526}</x14:id>
+          <x14:id>{32087ca6-3254-40a7-8cc5-b988d1d7a0c2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I20:I23 I3:I4 I29:I30 I6:I7 I16 I9 I11:I14 I26 I18 I50:I51 I32:I34 I37:I38 I40:I41 I43:I48">
+  <conditionalFormatting sqref="I20:I23 I3:I4 I43:I48 I29:I30 I6:I7 I16 I9 I11:I14 I26 I18 I50:I51 I32:I34 I37:I38 I40:I41">
     <cfRule type="dataBar" priority="34">
       <dataBar>
         <cfvo type="min"/>
@@ -5316,12 +5075,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ae66a5b-4736-4a18-87bc-85ad8631268b}</x14:id>
+          <x14:id>{dc69e5a5-d61c-4a5e-82bd-46b575a4d8cb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I18 I20:I23 I3:I4 I40:I51 I6:I7 I26 I9 I11:I16 I28:I30 I32:I38">
+  <conditionalFormatting sqref="I18 I20:I23 I3:I4 I32:I38 I40:I51 I6:I7 I26 I9 I11:I16 I28:I30">
     <cfRule type="dataBar" priority="29">
       <dataBar>
         <cfvo type="min"/>
@@ -5330,12 +5089,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fc969919-126a-4c45-af96-85eefa8791da}</x14:id>
+          <x14:id>{42579923-6e79-4eea-92bf-7b4dfaf2fb1c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I16 I3:I4 I32:I38 I6:I7 I20:I23 I9 I18 I26 I40:I51 I29:I30">
+  <conditionalFormatting sqref="I11:I16 I3:I4 I29:I30 I32:I38 I6:I7 I20:I23 I9 I18 I26 I40:I51">
     <cfRule type="dataBar" priority="32">
       <dataBar>
         <cfvo type="min"/>
@@ -5344,12 +5103,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{55c90aec-be42-48c9-9a1d-34d7ae269098}</x14:id>
+          <x14:id>{7052e990-7149-4d2c-bc26-fe0346d51423}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I18 I3:I4 I40:I51 I6:I7 I20:I23 I9 I26 I32:I38 I28:I30">
+  <conditionalFormatting sqref="I11:I18 I3:I4 I28:I30 I40:I51 I6:I7 I20:I23 I9 I26 I32:I38">
     <cfRule type="dataBar" priority="28">
       <dataBar>
         <cfvo type="min"/>
@@ -5358,12 +5117,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{17d50051-15f7-4451-8f66-f9dab37b6e79}</x14:id>
+          <x14:id>{6b05bec6-0fe7-4451-8778-669f759a2cba}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I18 I3:I7 I28:I30 I32:I51 I26 I20:I23 I9">
+  <conditionalFormatting sqref="I11:I18 I20:I23 I3:I7 I9 I28:I30 I32:I51 I26">
     <cfRule type="dataBar" priority="25">
       <dataBar>
         <cfvo type="min"/>
@@ -5372,12 +5131,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8002b3ac-a8b8-43e8-9020-25131c57a717}</x14:id>
+          <x14:id>{a3ec90ee-0edb-4044-a3ca-e7b0fbb2eb3f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I26 I20:I23 I3:I7 I32:I38 I40:I51 I11:I18 I9 I28:I30">
+  <conditionalFormatting sqref="I26 I20:I23 I9 I3:I7 I28:I30 I32:I38 I40:I51 I11:I18">
     <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
@@ -5386,12 +5145,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1dc8d6e4-2b04-4017-878d-17a32f711389}</x14:id>
+          <x14:id>{8e0cbaf6-6166-4117-96ff-bf728ed8445d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I26 I3:I24 I32:I51 I28:I30">
+  <conditionalFormatting sqref="I26 I32:I51 I3:I24 I28:I30">
     <cfRule type="dataBar" priority="21">
       <dataBar>
         <cfvo type="min"/>
@@ -5400,7 +5159,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6530289b-41df-4775-9c46-630bce9f8921}</x14:id>
+          <x14:id>{2b82bf50-89c6-4846-b5dd-7ef49ea29902}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5408,13 +5167,13 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="E8:E30 E32:E49 D8:D108 D3" formulaRange="1"/>
+    <ignoredError sqref="E40:E41 E45 E48:E49 E34 E36:E37 D3 D8:D108 E8:E14 E16:E17 E19:E20 E22:E23 E25:E27 E29" formulaRange="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dda28aed-6bab-4d98-b172-9310ed1317e6}">
+          <x14:cfRule type="dataBar" id="{0516d668-bde6-4820-9c21-bd9bfe863a0b}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5425,7 +5184,7 @@
           <xm:sqref>I25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{41a5e2b1-2edc-4d68-a131-5d85c7b12d5b}">
+          <x14:cfRule type="dataBar" id="{f9af9851-3b3f-4134-b8de-49494a92d3d3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5436,7 +5195,7 @@
           <xm:sqref>I$1:I$1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{379cd7c2-ea14-4e26-92d4-43b8b1501090}">
+          <x14:cfRule type="dataBar" id="{d8c93784-4d59-402c-bd64-0ae50c373c64}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5449,7 +5208,7 @@
           <xm:sqref>G1 G2:I2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6f2b8e67-1bee-4d6f-8afa-aa05396ac993}">
+          <x14:cfRule type="dataBar" id="{c6782148-85aa-4485-ac94-2bb6567ca129}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5460,7 +5219,7 @@
           <xm:sqref>I1:I26 I28:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d1d4e2aa-e34d-4c30-a599-78e4ec12c99b}">
+          <x14:cfRule type="dataBar" id="{1f04ca4b-f0e5-4ce8-82e6-d45a7293206e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5471,7 +5230,7 @@
           <xm:sqref>I1:I24 I26 I28:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2eebbc89-811f-4b74-b357-9ce3b4b5a7f6}">
+          <x14:cfRule type="dataBar" id="{580211c7-d112-48e0-b9ff-a7e120b3cd1e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5479,10 +5238,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I18 I26 I28:I1048576 I20:I24</xm:sqref>
+          <xm:sqref>I1:I18 I28:I1048576 I20:I24 I26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e5fe87ac-32ec-4bc5-b64a-300233a562fd}">
+          <x14:cfRule type="dataBar" id="{5a4de853-09f0-4ccd-ab01-c5117ab4fa1e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5490,10 +5249,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I9 I28:I1048576 I11:I18 I20:I24 I26</xm:sqref>
+          <xm:sqref>I1:I9 I20:I24 I11:I18 I28:I1048576 I26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{23c28805-668f-4e18-9773-e879fdb4fb3a}">
+          <x14:cfRule type="dataBar" id="{a7117f6a-d99b-4cb0-9716-f960ad6ce4cc}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5501,10 +5260,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I1:I9 I28:I1048576 I11:I18 I20:I23 I26</xm:sqref>
+          <xm:sqref>I1:I9 I20:I23 I11:I18 I28:I1048576 I26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a1f4dccc-d946-4b9a-9b68-6190d4797408}">
+          <x14:cfRule type="dataBar" id="{47aea96c-dd5e-4001-99bd-35c4d627f457}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5515,7 +5274,7 @@
           <xm:sqref>I2 I52:I1048576 I31</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1b61aaca-83ea-44ad-8ea7-0574f315436b}">
+          <x14:cfRule type="dataBar" id="{cf5ce95e-bb0a-4cbd-9e21-64ebd53e1e9c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5523,10 +5282,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I4 I28:I38 I26 I11:I18 I9 I6:I7 I40:I1048576 I20:I23</xm:sqref>
+          <xm:sqref>I2:I4 I20:I23 I28:I38 I26 I11:I18 I9 I6:I7 I40:I1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f8b8b31c-f96d-42d1-8e93-c62e7be8891b}">
+          <x14:cfRule type="dataBar" id="{379edc11-7862-47d4-9e53-f459d953d005}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5534,10 +5293,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I2:I4 I28:I38 I9 I26 I6:I7 I11:I16 I40:I1048576 I20:I23 I18</xm:sqref>
+          <xm:sqref>I2:I4 I20:I23 I28:I38 I9 I26 I6:I7 I11:I16 I40:I1048576 I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e8ad24d4-8614-4351-a124-6d7c863227e8}">
+          <x14:cfRule type="dataBar" id="{b940c2a0-92a9-4e3b-a50c-1071151a728e}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5545,10 +5304,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I12:I14 I3:I4 I50:I51 I6:I7 I18 I9 I20:I23 I26 I37:I38 I29 I32:I34 I40:I41 I43:I48</xm:sqref>
+          <xm:sqref>I12:I14 I3:I4 I43:I48 I50:I51 I6:I7 I18 I9 I20:I23 I26 I37:I38 I29 I32:I34 I40:I41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{085014cf-1b84-4c22-838a-e5cd85a403f5}">
+          <x14:cfRule type="dataBar" id="{401edcdf-43ae-4b44-99c5-0e95810b949c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5556,10 +5315,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I18 I3:I4 I50:I51 I6:I7 I12:I14 I9 I20:I23 I37:I38 I29 I32:I34 I40:I41 I43:I48</xm:sqref>
+          <xm:sqref>I18 I3:I4 I43:I48 I50:I51 I6:I7 I12:I14 I9 I20:I23 I37:I38 I29 I32:I34 I40:I41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d62c5a28-755d-48b4-bfcb-4acbc45cc0e8}">
+          <x14:cfRule type="dataBar" id="{523fecbb-3adb-4d79-a75b-8b4a50bc759a}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5567,10 +5326,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I16 I3:I4 I43:I48 I6:I7 I12:I14 I9 I20:I23 I26 I18 I50:I51 I29 I32:I34 I37:I38 I40:I41</xm:sqref>
+          <xm:sqref>I16 I3:I4 I40:I41 I43:I48 I6:I7 I12:I14 I9 I20:I23 I26 I18 I50:I51 I29 I32:I34 I37:I38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{521a02ac-3d11-4d91-a132-60da00920526}">
+          <x14:cfRule type="dataBar" id="{32087ca6-3254-40a7-8cc5-b988d1d7a0c2}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5578,10 +5337,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I14 I3:I4 I37:I38 I6:I7 I20:I23 I9 I16 I26 I18 I40:I41 I29:I30 I43:I51 I32:I35</xm:sqref>
+          <xm:sqref>I11:I14 I3:I4 I32:I35 I37:I38 I6:I7 I20:I23 I9 I16 I26 I18 I40:I41 I29:I30 I43:I51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6ae66a5b-4736-4a18-87bc-85ad8631268b}">
+          <x14:cfRule type="dataBar" id="{dc69e5a5-d61c-4a5e-82bd-46b575a4d8cb}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5589,10 +5348,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I20:I23 I3:I4 I29:I30 I6:I7 I16 I9 I11:I14 I26 I18 I50:I51 I32:I34 I37:I38 I40:I41 I43:I48</xm:sqref>
+          <xm:sqref>I20:I23 I3:I4 I43:I48 I29:I30 I6:I7 I16 I9 I11:I14 I26 I18 I50:I51 I32:I34 I37:I38 I40:I41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fc969919-126a-4c45-af96-85eefa8791da}">
+          <x14:cfRule type="dataBar" id="{42579923-6e79-4eea-92bf-7b4dfaf2fb1c}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5600,10 +5359,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I18 I20:I23 I3:I4 I40:I51 I6:I7 I26 I9 I11:I16 I28:I30 I32:I38</xm:sqref>
+          <xm:sqref>I18 I20:I23 I3:I4 I32:I38 I40:I51 I6:I7 I26 I9 I11:I16 I28:I30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{55c90aec-be42-48c9-9a1d-34d7ae269098}">
+          <x14:cfRule type="dataBar" id="{7052e990-7149-4d2c-bc26-fe0346d51423}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5611,10 +5370,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I16 I3:I4 I32:I38 I6:I7 I20:I23 I9 I18 I26 I40:I51 I29:I30</xm:sqref>
+          <xm:sqref>I11:I16 I3:I4 I29:I30 I32:I38 I6:I7 I20:I23 I9 I18 I26 I40:I51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{17d50051-15f7-4451-8f66-f9dab37b6e79}">
+          <x14:cfRule type="dataBar" id="{6b05bec6-0fe7-4451-8778-669f759a2cba}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5622,10 +5381,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I18 I3:I4 I40:I51 I6:I7 I20:I23 I9 I26 I32:I38 I28:I30</xm:sqref>
+          <xm:sqref>I11:I18 I3:I4 I28:I30 I40:I51 I6:I7 I20:I23 I9 I26 I32:I38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8002b3ac-a8b8-43e8-9020-25131c57a717}">
+          <x14:cfRule type="dataBar" id="{a3ec90ee-0edb-4044-a3ca-e7b0fbb2eb3f}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5633,10 +5392,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I11:I18 I3:I7 I28:I30 I32:I51 I26 I20:I23 I9</xm:sqref>
+          <xm:sqref>I11:I18 I20:I23 I3:I7 I9 I28:I30 I32:I51 I26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1dc8d6e4-2b04-4017-878d-17a32f711389}">
+          <x14:cfRule type="dataBar" id="{8e0cbaf6-6166-4117-96ff-bf728ed8445d}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5644,10 +5403,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I26 I20:I23 I3:I7 I32:I38 I40:I51 I11:I18 I9 I28:I30</xm:sqref>
+          <xm:sqref>I26 I20:I23 I9 I3:I7 I28:I30 I32:I38 I40:I51 I11:I18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6530289b-41df-4775-9c46-630bce9f8921}">
+          <x14:cfRule type="dataBar" id="{2b82bf50-89c6-4846-b5dd-7ef49ea29902}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5655,7 +5414,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I26 I3:I24 I32:I51 I28:I30</xm:sqref>
+          <xm:sqref>I26 I32:I51 I3:I24 I28:I30</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
